--- a/doc/spec/Y8960_Specifications.xlsx
+++ b/doc/spec/Y8960_Specifications.xlsx
@@ -1,18 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\HRA_product\Y8960_Cartridge\doc\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1F87E7-1B68-4ECF-81AB-D1A38A6C3819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="modules" sheetId="1" r:id="rId1"/>
+    <sheet name="MemoryMappedIO" sheetId="6" r:id="rId2"/>
+    <sheet name="ssg" sheetId="2" r:id="rId3"/>
+    <sheet name="dcsg" sheetId="7" r:id="rId4"/>
+    <sheet name="OPLL-EX" sheetId="3" r:id="rId5"/>
+    <sheet name="OPL2+ADPCM" sheetId="4" r:id="rId6"/>
+    <sheet name="SCC" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -24,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="379">
   <si>
     <t>Y8960 Cartridge は、MSX用のオーディオ系チップのコンボカートリッジです。</t>
     <rPh sb="21" eb="22">
@@ -182,14 +189,1685 @@
   </si>
   <si>
     <t>BSD 3-Clause</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG (YM2149) [PSG(AY-3-8910) Compatible]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I/O</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Address</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Description</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A0h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RW</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Register Address</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A1h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A2h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>WO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Write専用。Readすると 255。</t>
+    <rPh sb="5" eb="7">
+      <t>センヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Read専用。</t>
+    <rPh sb="4" eb="6">
+      <t>センヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Register</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG1: Ch.A 分周比下位8bit</t>
+    <rPh sb="11" eb="14">
+      <t>ブンシュウヒ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG1: Ch.A 分周比上位4bit</t>
+    <rPh sb="11" eb="14">
+      <t>ブンシュウヒ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジョウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG1: Ch.B 分周比下位8bit</t>
+    <rPh sb="11" eb="14">
+      <t>ブンシュウヒ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG1: Ch.B 分周比上位4bit</t>
+    <rPh sb="11" eb="14">
+      <t>ブンシュウヒ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジョウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG1: Ch.C 分周比下位8bit</t>
+    <rPh sb="11" eb="14">
+      <t>ブンシュウヒ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG1: Ch.C 分周比上位4bit</t>
+    <rPh sb="11" eb="14">
+      <t>ブンシュウヒ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジョウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG1: ノイズ分周比</t>
+    <rPh sb="9" eb="12">
+      <t>ブンシュウヒ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG1: /ENABLE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG1: Ch.A音量</t>
+    <rPh sb="10" eb="12">
+      <t>オンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>SSG1: Ch.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>B音量</t>
+    </r>
+    <rPh sb="10" eb="12">
+      <t>オンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG1: Ch.C音量</t>
+    <rPh sb="10" eb="12">
+      <t>オンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG1: エンベロープ周期 下位8bit</t>
+    <rPh sb="12" eb="14">
+      <t>シュウキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG1: エンベロープ周期 上位8bit</t>
+    <rPh sb="12" eb="14">
+      <t>シュウキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジョウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG1: エンベロープ波形</t>
+    <rPh sb="12" eb="14">
+      <t>ハケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG2: Ch.A 分周比下位8bit</t>
+    <rPh sb="11" eb="14">
+      <t>ブンシュウヒ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG2: Ch.A 分周比上位4bit</t>
+    <rPh sb="11" eb="14">
+      <t>ブンシュウヒ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジョウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG2: Ch.B 分周比下位8bit</t>
+    <rPh sb="11" eb="14">
+      <t>ブンシュウヒ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG2: Ch.B 分周比上位4bit</t>
+    <rPh sb="11" eb="14">
+      <t>ブンシュウヒ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジョウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG2: Ch.C 分周比下位8bit</t>
+    <rPh sb="11" eb="14">
+      <t>ブンシュウヒ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG2: Ch.C 分周比上位4bit</t>
+    <rPh sb="11" eb="14">
+      <t>ブンシュウヒ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジョウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG2: ノイズ分周比</t>
+    <rPh sb="9" eb="12">
+      <t>ブンシュウヒ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG2: /ENABLE</t>
+  </si>
+  <si>
+    <t>SSG2: Ch.A音量</t>
+    <rPh sb="10" eb="12">
+      <t>オンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG2: Ch.B音量</t>
+    <rPh sb="10" eb="12">
+      <t>オンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG2: Ch.C音量</t>
+    <rPh sb="10" eb="12">
+      <t>オンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG2: エンベロープ周期 下位8bit</t>
+    <rPh sb="12" eb="14">
+      <t>シュウキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG2: エンベロープ周期 上位8bit</t>
+    <rPh sb="12" eb="14">
+      <t>シュウキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジョウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG2: エンベロープ波形</t>
+    <rPh sb="12" eb="14">
+      <t>ハケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG2: GPIO A</t>
+  </si>
+  <si>
+    <t>SSG2: GPIO B 下位4bit は LED に接続</t>
+    <rPh sb="13" eb="15">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>セツゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG1: GPIO B 未接続</t>
+    <rPh sb="13" eb="16">
+      <t>ミセツゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG1: GPIO A 未接続</t>
+    <rPh sb="13" eb="16">
+      <t>ミセツゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>b7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>b6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>b5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>b4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>b3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>b2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>b1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>b0</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IOB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IOA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>M</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未接続</t>
+    <rPh sb="0" eb="3">
+      <t>ミセツゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7Ch</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7Dh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7Bh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7Ah</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPLL1 Register Address</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPLL1 Register Value</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPLL2 Register Address</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPLL2 Register Value</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Memory Mapped I/O</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FF4h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FF5h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FF3h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FF2h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FF6h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TESTレジスタ (常に 0)</t>
+    <rPh sb="10" eb="11">
+      <t>ツネ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BD</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SD</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HH</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>KSR</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MULTI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>KS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AR</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DR</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RR</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TEST</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LED</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>08-0D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0E</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>12</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>13</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>16</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>18</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>19-1F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SUS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>KEY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BLOCK</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F#</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>21</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>24</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>26</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>27</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>28</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>29-2F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>32</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>33</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>35</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>36</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>38</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39-3F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>INST</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>41</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>43</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>45</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>46</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>47</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>48</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>49-FF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPLL-EX (YM2413)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>YM2413 に、OPLL/OPLL-X/OPLL-P/VRC7 のプリセット音色バンクを追加したもの。</t>
+    <rPh sb="39" eb="41">
+      <t>ネイロ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新設。ROM音色選択レジスタ。</t>
+    <rPh sb="0" eb="2">
+      <t>シンセツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ネイロ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPLL2 Register Data</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPLL1 Register Data</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPLL1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPLL2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分周比下位</t>
+    <rPh sb="0" eb="3">
+      <t>ブンシュウヒ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分周比上位</t>
+    <rPh sb="0" eb="3">
+      <t>ブンシュウヒ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジョウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ノイズ分周比</t>
+    <rPh sb="3" eb="6">
+      <t>ブンシュウヒ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音量</t>
+    <rPh sb="0" eb="2">
+      <t>オンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エンベロープ周期下位</t>
+    <rPh sb="6" eb="8">
+      <t>シュウキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エンベロープ周期下位周期上位</t>
+    <rPh sb="6" eb="8">
+      <t>シュウキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>シュウキジョウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エンベロープ波形</t>
+    <rPh sb="6" eb="8">
+      <t>ハケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPL2 (YM3812) + ADPCM  [MSX-AUDIO(Y8950) Compatible]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C0h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C1h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C2h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C3h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPL2-1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPL2-2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>08</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>19</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1E</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>20～EF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F0</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F8</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F9</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FD</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>N/A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TIMER1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TIMER2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IRQRST</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>T1MSK</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>T2MSK</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EOSMSK</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BRMSK</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ST2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ST1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Key Board IN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Key Board OUT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>START</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>REC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MEMD</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>REPT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SPOFF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RST</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CSM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NSEL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SMPL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DAAD</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>64K</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ROM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>START ADD (L)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>START ADD (H)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>STOP ADD (L)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>STOP ADD (H)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PRESCALE (L)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PRESCALE (H)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ADPCM-DATA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DELTA-N (L)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DELTA-N (H)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EG-CTRL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DAC DATA(H)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DAC DATA(L)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SHIFT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I/O-CTRL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I/ DATA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PCM-DATA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>20～35</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>40～55</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>60～75</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>80～95</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A0～A8</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B0～B8</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C0～C8</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その他</t>
+    <rPh sb="2" eb="3">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ETY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>KSL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>KON</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AMD</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIBD</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TOM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPL2-1 Register Address</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPL2-1 Register Value</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPL2-2 Register Address</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPL2-2 Register Value</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>WS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>E0～F5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPL2から追加</t>
+    <rPh sb="6" eb="8">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FEEh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FEFh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FF0h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FF1h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPL2-2 Regisger Address</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPL2-2 Register Data</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPL2-1 Register Data</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FEDh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FECh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DCSG2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DCSG1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DCSG2 Write</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DCSG1 Write</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DCSG2 Access</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DCSG1 Access</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FEBh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FEAh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG Register Address</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG Register Write</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FF7h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FF8h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FF9h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FFAh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FFBh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FFCh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FFDh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FFEh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FFFh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I/O Enabler1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I/O Enabler2(Mirror 3FFFh)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bank selecter(Mirror 3FFEh)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5000-57FFh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7000-77FFh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK0(4000-5FFFh) Bank Register</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK1(6000-7FFFh) Bank Register</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK2(8000-9FFFh) Bank Register</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK3(A000-BFFFh) Bank Register</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK Mode Register</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4XFCh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4XFDh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4XFEh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4XFFh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4XFBh (X=8～F)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bank Register (RAM Mode = 1)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bank Register (RAM Mode = 0)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Note</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=1 の時のみ利用可能</t>
+    <rPh sb="12" eb="13">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>リヨウカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常に出現している。1 にすると、BANK1～3 への /WR が SRAM まで到達。</t>
+    <rPh sb="0" eb="1">
+      <t>ツネ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>トウタツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 の時のみ利用可能</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#15) のときのみ利用可能</t>
+    <rPh sb="47" eb="51">
+      <t>リヨウカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#16) のときのみ利用可能</t>
+    <rPh sb="47" eb="51">
+      <t>リヨウカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#17) のときのみ利用可能</t>
+    <rPh sb="47" eb="51">
+      <t>リヨウカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#18) のときのみ利用可能</t>
+    <rPh sb="47" eb="51">
+      <t>リヨウカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#19) のときのみ利用可能</t>
+    <rPh sb="47" eb="51">
+      <t>リヨウカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#20) のときのみ利用可能</t>
+    <rPh sb="47" eb="51">
+      <t>リヨウカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#21) のときのみ利用可能</t>
+    <rPh sb="47" eb="51">
+      <t>リヨウカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#22) のときのみ利用可能</t>
+    <rPh sb="47" eb="51">
+      <t>リヨウカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#23) のときのみ利用可能</t>
+    <rPh sb="47" eb="51">
+      <t>リヨウカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#24) のときのみ利用可能</t>
+    <rPh sb="47" eb="51">
+      <t>リヨウカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#25) のときのみ利用可能</t>
+    <rPh sb="47" eb="51">
+      <t>リヨウカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#26) のときのみ利用可能</t>
+    <rPh sb="47" eb="51">
+      <t>リヨウカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#27) のときのみ利用可能</t>
+    <rPh sb="47" eb="51">
+      <t>リヨウカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#28) のときのみ利用可能</t>
+    <rPh sb="47" eb="51">
+      <t>リヨウカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#29) のときのみ利用可能</t>
+    <rPh sb="47" eb="51">
+      <t>リヨウカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#30) のときのみ利用可能</t>
+    <rPh sb="47" eb="51">
+      <t>リヨウカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#31) のときのみ利用可能</t>
+    <rPh sb="47" eb="51">
+      <t>リヨウカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#32) のときのみ利用可能</t>
+    <rPh sb="47" eb="51">
+      <t>リヨウカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#33) のときのみ利用可能</t>
+    <rPh sb="47" eb="51">
+      <t>リヨウカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#34) のときのみ利用可能</t>
+    <rPh sb="47" eb="51">
+      <t>リヨウカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#35) のときのみ利用可能</t>
+    <rPh sb="47" eb="51">
+      <t>リヨウカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#36) のときのみ利用可能</t>
+    <rPh sb="47" eb="51">
+      <t>リヨウカノウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,8 +1892,39 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -228,8 +1937,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -252,6 +1979,308 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -261,7 +2290,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -274,10 +2303,253 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -560,7 +2832,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -771,33 +3043,4374 @@
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B16" s="4">
+      <c r="B16" s="1">
         <v>12</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="4" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
-    <hyperlink ref="F6" r:id="rId1"/>
-    <hyperlink ref="F10" r:id="rId2"/>
-    <hyperlink ref="F7" r:id="rId3"/>
-    <hyperlink ref="F15" r:id="rId4"/>
-    <hyperlink ref="F16" r:id="rId5"/>
-    <hyperlink ref="F9" r:id="rId6"/>
+    <hyperlink ref="F6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="F10" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="F7" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="F15" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="F16" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="F9" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="67" fitToHeight="0" orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId7"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F17AAC-1091-414B-9A6F-EA5ABE92574A}">
+  <dimension ref="B2:N34"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="2" max="2" width="3.25" customWidth="1"/>
+    <col min="3" max="3" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="14" max="14" width="65.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C3" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C4" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="53" t="s">
+        <v>344</v>
+      </c>
+      <c r="F4" s="54"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="26" t="s">
+        <v>350</v>
+      </c>
+      <c r="N4" s="84" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C5" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="51" t="s">
+        <v>340</v>
+      </c>
+      <c r="F5" s="62" t="s">
+        <v>351</v>
+      </c>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+      <c r="L5" s="63"/>
+      <c r="M5" s="64"/>
+      <c r="N5" s="85" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C6" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="51" t="s">
+        <v>341</v>
+      </c>
+      <c r="F6" s="62" t="s">
+        <v>351</v>
+      </c>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="63"/>
+      <c r="L6" s="63"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="85" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="51" t="s">
+        <v>342</v>
+      </c>
+      <c r="F7" s="62" t="s">
+        <v>351</v>
+      </c>
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="63"/>
+      <c r="L7" s="63"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="85" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C8" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>343</v>
+      </c>
+      <c r="F8" s="62" t="s">
+        <v>351</v>
+      </c>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="63"/>
+      <c r="J8" s="63"/>
+      <c r="K8" s="63"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="85" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C9" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="F9" s="59" t="s">
+        <v>352</v>
+      </c>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="60"/>
+      <c r="K9" s="60"/>
+      <c r="L9" s="60"/>
+      <c r="M9" s="61"/>
+      <c r="N9" s="85" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C10" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="F10" s="59" t="s">
+        <v>352</v>
+      </c>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="60"/>
+      <c r="K10" s="60"/>
+      <c r="L10" s="60"/>
+      <c r="M10" s="61"/>
+      <c r="N10" s="85" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C11" s="51" t="s">
+        <v>323</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>324</v>
+      </c>
+      <c r="F11" s="62" t="s">
+        <v>324</v>
+      </c>
+      <c r="G11" s="63"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="63"/>
+      <c r="J11" s="63"/>
+      <c r="K11" s="63"/>
+      <c r="L11" s="63"/>
+      <c r="M11" s="64"/>
+      <c r="N11" s="86" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C12" s="51" t="s">
+        <v>322</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="51" t="s">
+        <v>325</v>
+      </c>
+      <c r="F12" s="62" t="s">
+        <v>325</v>
+      </c>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="63"/>
+      <c r="J12" s="63"/>
+      <c r="K12" s="63"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="86" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C13" s="50" t="s">
+        <v>313</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="50" t="s">
+        <v>316</v>
+      </c>
+      <c r="F13" s="68" t="s">
+        <v>318</v>
+      </c>
+      <c r="G13" s="63"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="63"/>
+      <c r="K13" s="63"/>
+      <c r="L13" s="63"/>
+      <c r="M13" s="64"/>
+      <c r="N13" s="86" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C14" s="51" t="s">
+        <v>312</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="51" t="s">
+        <v>317</v>
+      </c>
+      <c r="F14" s="68" t="s">
+        <v>319</v>
+      </c>
+      <c r="G14" s="63"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="63"/>
+      <c r="J14" s="63"/>
+      <c r="K14" s="63"/>
+      <c r="L14" s="63"/>
+      <c r="M14" s="64"/>
+      <c r="N14" s="86" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C15" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>309</v>
+      </c>
+      <c r="F15" s="68" t="s">
+        <v>300</v>
+      </c>
+      <c r="G15" s="63"/>
+      <c r="H15" s="63"/>
+      <c r="I15" s="63"/>
+      <c r="J15" s="63"/>
+      <c r="K15" s="63"/>
+      <c r="L15" s="63"/>
+      <c r="M15" s="64"/>
+      <c r="N15" s="86" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C16" s="25" t="s">
+        <v>306</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>301</v>
+      </c>
+      <c r="F16" s="68" t="s">
+        <v>310</v>
+      </c>
+      <c r="G16" s="63"/>
+      <c r="H16" s="63"/>
+      <c r="I16" s="63"/>
+      <c r="J16" s="63"/>
+      <c r="K16" s="63"/>
+      <c r="L16" s="63"/>
+      <c r="M16" s="64"/>
+      <c r="N16" s="86" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="17" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C17" s="25" t="s">
+        <v>307</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="F17" s="68" t="s">
+        <v>298</v>
+      </c>
+      <c r="G17" s="63"/>
+      <c r="H17" s="63"/>
+      <c r="I17" s="63"/>
+      <c r="J17" s="63"/>
+      <c r="K17" s="63"/>
+      <c r="L17" s="63"/>
+      <c r="M17" s="64"/>
+      <c r="N17" s="86" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C18" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>299</v>
+      </c>
+      <c r="F18" s="68" t="s">
+        <v>311</v>
+      </c>
+      <c r="G18" s="63"/>
+      <c r="H18" s="63"/>
+      <c r="I18" s="63"/>
+      <c r="J18" s="63"/>
+      <c r="K18" s="63"/>
+      <c r="L18" s="63"/>
+      <c r="M18" s="64"/>
+      <c r="N18" s="86" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C19" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="D19" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="F19" s="68" t="s">
+        <v>107</v>
+      </c>
+      <c r="G19" s="63"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="63"/>
+      <c r="J19" s="63"/>
+      <c r="K19" s="63"/>
+      <c r="L19" s="63"/>
+      <c r="M19" s="64"/>
+      <c r="N19" s="86" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="20" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C20" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="F20" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="G20" s="63"/>
+      <c r="H20" s="63"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="63"/>
+      <c r="K20" s="63"/>
+      <c r="L20" s="63"/>
+      <c r="M20" s="64"/>
+      <c r="N20" s="86" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C21" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="G21" s="69"/>
+      <c r="H21" s="69"/>
+      <c r="I21" s="69"/>
+      <c r="J21" s="69"/>
+      <c r="K21" s="69"/>
+      <c r="L21" s="69"/>
+      <c r="M21" s="58"/>
+      <c r="N21" s="86" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C22" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F22" s="57" t="s">
+        <v>198</v>
+      </c>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="69"/>
+      <c r="J22" s="69"/>
+      <c r="K22" s="69"/>
+      <c r="L22" s="69"/>
+      <c r="M22" s="58"/>
+      <c r="N22" s="86" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C23" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" s="52" t="s">
+        <v>335</v>
+      </c>
+      <c r="F23" s="65"/>
+      <c r="G23" s="66"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="66"/>
+      <c r="J23" s="66"/>
+      <c r="K23" s="67"/>
+      <c r="L23" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="M23" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="N23" s="86" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C24" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E24" s="6"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="55"/>
+      <c r="H24" s="55"/>
+      <c r="I24" s="55"/>
+      <c r="J24" s="55"/>
+      <c r="K24" s="55"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="56"/>
+      <c r="N24" s="86" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C25" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="55"/>
+      <c r="H25" s="55"/>
+      <c r="I25" s="55"/>
+      <c r="J25" s="55"/>
+      <c r="K25" s="55"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="56"/>
+      <c r="N25" s="86" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C26" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E26" s="1"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="55"/>
+      <c r="H26" s="55"/>
+      <c r="I26" s="55"/>
+      <c r="J26" s="55"/>
+      <c r="K26" s="55"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="56"/>
+      <c r="N26" s="86" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C27" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="55"/>
+      <c r="H27" s="55"/>
+      <c r="I27" s="55"/>
+      <c r="J27" s="55"/>
+      <c r="K27" s="55"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="56"/>
+      <c r="N27" s="86" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C28" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E28" s="1"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="55"/>
+      <c r="K28" s="55"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="56"/>
+      <c r="N28" s="86" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C29" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" s="1"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="55"/>
+      <c r="H29" s="55"/>
+      <c r="I29" s="55"/>
+      <c r="J29" s="55"/>
+      <c r="K29" s="55"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="56"/>
+      <c r="N29" s="86" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C30" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" s="1"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="55"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="55"/>
+      <c r="J30" s="55"/>
+      <c r="K30" s="55"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="56"/>
+      <c r="N30" s="86" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C31" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="F31" s="54"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="55"/>
+      <c r="J31" s="55"/>
+      <c r="K31" s="56"/>
+      <c r="L31" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="M31" s="58"/>
+      <c r="N31" s="86" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C32" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="F32" s="54"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="26" t="s">
+        <v>321</v>
+      </c>
+      <c r="I32" s="34" t="s">
+        <v>320</v>
+      </c>
+      <c r="J32" s="34" t="s">
+        <v>314</v>
+      </c>
+      <c r="K32" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="L32" s="47" t="s">
+        <v>214</v>
+      </c>
+      <c r="M32" s="47" t="s">
+        <v>213</v>
+      </c>
+      <c r="N32" s="86" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="33" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C33" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="F33" s="59" t="s">
+        <v>352</v>
+      </c>
+      <c r="G33" s="60"/>
+      <c r="H33" s="60"/>
+      <c r="I33" s="60"/>
+      <c r="J33" s="60"/>
+      <c r="K33" s="60"/>
+      <c r="L33" s="60"/>
+      <c r="M33" s="61"/>
+      <c r="N33" s="85" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="34" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C34" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="F34" s="59" t="s">
+        <v>352</v>
+      </c>
+      <c r="G34" s="60"/>
+      <c r="H34" s="60"/>
+      <c r="I34" s="60"/>
+      <c r="J34" s="60"/>
+      <c r="K34" s="60"/>
+      <c r="L34" s="60"/>
+      <c r="M34" s="61"/>
+      <c r="N34" s="85" t="s">
+        <v>356</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="32">
+    <mergeCell ref="F34:M34"/>
+    <mergeCell ref="F5:M5"/>
+    <mergeCell ref="F6:M6"/>
+    <mergeCell ref="F7:M7"/>
+    <mergeCell ref="F8:M8"/>
+    <mergeCell ref="F23:K23"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F24:M24"/>
+    <mergeCell ref="F25:M25"/>
+    <mergeCell ref="F26:M26"/>
+    <mergeCell ref="F27:M27"/>
+    <mergeCell ref="F28:M28"/>
+    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="F30:M30"/>
+    <mergeCell ref="F31:K31"/>
+    <mergeCell ref="F14:M14"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="F9:M9"/>
+    <mergeCell ref="F10:M10"/>
+    <mergeCell ref="F33:M33"/>
+    <mergeCell ref="F13:M13"/>
+    <mergeCell ref="F11:M11"/>
+    <mergeCell ref="F12:M12"/>
+    <mergeCell ref="F19:M19"/>
+    <mergeCell ref="F20:M20"/>
+    <mergeCell ref="F21:M21"/>
+    <mergeCell ref="F22:M22"/>
+    <mergeCell ref="F15:M15"/>
+    <mergeCell ref="F16:M16"/>
+    <mergeCell ref="F17:M17"/>
+    <mergeCell ref="F18:M18"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FDBFF0C-F6C5-44DC-82FE-2CD49F464A20}">
+  <dimension ref="B2:M60"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="5" max="5" width="39.75" customWidth="1"/>
+    <col min="6" max="13" width="4.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="C5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="C6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="C7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="C8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C12" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="72" t="s">
+        <v>201</v>
+      </c>
+      <c r="G12" s="73"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73"/>
+      <c r="J12" s="73"/>
+      <c r="K12" s="73"/>
+      <c r="L12" s="73"/>
+      <c r="M12" s="74"/>
+    </row>
+    <row r="13" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C13" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="36"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="72" t="s">
+        <v>202</v>
+      </c>
+      <c r="K13" s="73"/>
+      <c r="L13" s="73"/>
+      <c r="M13" s="74"/>
+    </row>
+    <row r="14" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C14" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="72" t="s">
+        <v>201</v>
+      </c>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="73"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="73"/>
+      <c r="M14" s="74"/>
+    </row>
+    <row r="15" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C15" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="36"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="72" t="s">
+        <v>202</v>
+      </c>
+      <c r="K15" s="73"/>
+      <c r="L15" s="73"/>
+      <c r="M15" s="74"/>
+    </row>
+    <row r="16" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C16" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="72" t="s">
+        <v>201</v>
+      </c>
+      <c r="G16" s="73"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73"/>
+      <c r="J16" s="73"/>
+      <c r="K16" s="73"/>
+      <c r="L16" s="73"/>
+      <c r="M16" s="74"/>
+    </row>
+    <row r="17" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C17" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" s="36"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="72" t="s">
+        <v>202</v>
+      </c>
+      <c r="K17" s="73"/>
+      <c r="L17" s="73"/>
+      <c r="M17" s="74"/>
+    </row>
+    <row r="18" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C18" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="36"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="72" t="s">
+        <v>203</v>
+      </c>
+      <c r="J18" s="73"/>
+      <c r="K18" s="73"/>
+      <c r="L18" s="73"/>
+      <c r="M18" s="74"/>
+    </row>
+    <row r="19" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C19" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="G19" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="I19" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="J19" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="K19" s="42" t="s">
+        <v>94</v>
+      </c>
+      <c r="L19" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="M19" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C20" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="36"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="J20" s="72" t="s">
+        <v>204</v>
+      </c>
+      <c r="K20" s="73"/>
+      <c r="L20" s="73"/>
+      <c r="M20" s="74"/>
+    </row>
+    <row r="21" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C21" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" s="36"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="J21" s="72" t="s">
+        <v>204</v>
+      </c>
+      <c r="K21" s="73"/>
+      <c r="L21" s="73"/>
+      <c r="M21" s="74"/>
+    </row>
+    <row r="22" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C22" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" s="36"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="J22" s="72" t="s">
+        <v>204</v>
+      </c>
+      <c r="K22" s="73"/>
+      <c r="L22" s="73"/>
+      <c r="M22" s="74"/>
+    </row>
+    <row r="23" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C23" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F23" s="72" t="s">
+        <v>205</v>
+      </c>
+      <c r="G23" s="73"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="73"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="73"/>
+      <c r="M23" s="74"/>
+    </row>
+    <row r="24" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C24" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="72" t="s">
+        <v>206</v>
+      </c>
+      <c r="G24" s="73"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73"/>
+      <c r="J24" s="73"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="73"/>
+      <c r="M24" s="74"/>
+    </row>
+    <row r="25" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C25" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F25" s="36"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="72" t="s">
+        <v>207</v>
+      </c>
+      <c r="K25" s="73"/>
+      <c r="L25" s="73"/>
+      <c r="M25" s="74"/>
+    </row>
+    <row r="26" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C26" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" s="9"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="11"/>
+    </row>
+    <row r="27" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C27" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F27" s="9"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="11"/>
+    </row>
+    <row r="28" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C28" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="F28" s="68" t="s">
+        <v>201</v>
+      </c>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="70"/>
+      <c r="K28" s="70"/>
+      <c r="L28" s="70"/>
+      <c r="M28" s="71"/>
+    </row>
+    <row r="29" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C29" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="F29" s="27"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="K29" s="70"/>
+      <c r="L29" s="70"/>
+      <c r="M29" s="71"/>
+    </row>
+    <row r="30" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C30" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E30" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="F30" s="68" t="s">
+        <v>201</v>
+      </c>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="70"/>
+      <c r="K30" s="70"/>
+      <c r="L30" s="70"/>
+      <c r="M30" s="71"/>
+    </row>
+    <row r="31" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C31" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="F31" s="27"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="K31" s="70"/>
+      <c r="L31" s="70"/>
+      <c r="M31" s="71"/>
+    </row>
+    <row r="32" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C32" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="F32" s="68" t="s">
+        <v>201</v>
+      </c>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="70"/>
+      <c r="K32" s="70"/>
+      <c r="L32" s="70"/>
+      <c r="M32" s="71"/>
+    </row>
+    <row r="33" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C33" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="F33" s="27"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="K33" s="70"/>
+      <c r="L33" s="70"/>
+      <c r="M33" s="71"/>
+    </row>
+    <row r="34" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C34" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="F34" s="27"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="68" t="s">
+        <v>203</v>
+      </c>
+      <c r="J34" s="70"/>
+      <c r="K34" s="70"/>
+      <c r="L34" s="70"/>
+      <c r="M34" s="71"/>
+    </row>
+    <row r="35" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C35" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="F35" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="G35" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="H35" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="I35" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="J35" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="K35" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="L35" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="M35" s="31" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C36" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E36" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="F36" s="27"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="J36" s="68" t="s">
+        <v>204</v>
+      </c>
+      <c r="K36" s="70"/>
+      <c r="L36" s="70"/>
+      <c r="M36" s="71"/>
+    </row>
+    <row r="37" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C37" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E37" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="F37" s="27"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="J37" s="68" t="s">
+        <v>204</v>
+      </c>
+      <c r="K37" s="70"/>
+      <c r="L37" s="70"/>
+      <c r="M37" s="71"/>
+    </row>
+    <row r="38" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C38" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E38" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="F38" s="27"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="J38" s="68" t="s">
+        <v>204</v>
+      </c>
+      <c r="K38" s="70"/>
+      <c r="L38" s="70"/>
+      <c r="M38" s="71"/>
+    </row>
+    <row r="39" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C39" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E39" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="F39" s="68" t="s">
+        <v>205</v>
+      </c>
+      <c r="G39" s="70"/>
+      <c r="H39" s="70"/>
+      <c r="I39" s="70"/>
+      <c r="J39" s="70"/>
+      <c r="K39" s="70"/>
+      <c r="L39" s="70"/>
+      <c r="M39" s="71"/>
+    </row>
+    <row r="40" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C40" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E40" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" s="68" t="s">
+        <v>206</v>
+      </c>
+      <c r="G40" s="70"/>
+      <c r="H40" s="70"/>
+      <c r="I40" s="70"/>
+      <c r="J40" s="70"/>
+      <c r="K40" s="70"/>
+      <c r="L40" s="70"/>
+      <c r="M40" s="71"/>
+    </row>
+    <row r="41" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C41" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E41" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="F41" s="27"/>
+      <c r="G41" s="28"/>
+      <c r="H41" s="28"/>
+      <c r="I41" s="29"/>
+      <c r="J41" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="K41" s="70"/>
+      <c r="L41" s="70"/>
+      <c r="M41" s="71"/>
+    </row>
+    <row r="42" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C42" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E42" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="F42" s="27"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="28"/>
+      <c r="J42" s="28"/>
+      <c r="K42" s="28"/>
+      <c r="L42" s="28"/>
+      <c r="M42" s="29"/>
+    </row>
+    <row r="43" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C43" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E43" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="F43" s="27"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="35"/>
+      <c r="J43" s="68" t="s">
+        <v>135</v>
+      </c>
+      <c r="K43" s="70"/>
+      <c r="L43" s="70"/>
+      <c r="M43" s="71"/>
+    </row>
+    <row r="44" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C44" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="F44" s="9"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="11"/>
+    </row>
+    <row r="45" spans="3:13" x14ac:dyDescent="0.15">
+      <c r="C45" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E45" s="1"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="8"/>
+    </row>
+    <row r="46" spans="3:13" x14ac:dyDescent="0.15">
+      <c r="C46" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+    </row>
+    <row r="47" spans="3:13" x14ac:dyDescent="0.15">
+      <c r="C47" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+    </row>
+    <row r="48" spans="3:13" x14ac:dyDescent="0.15">
+      <c r="C48" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.15">
+      <c r="C49" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.15">
+      <c r="C50" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.15">
+      <c r="C51" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.15">
+      <c r="C52" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.15">
+      <c r="C53" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.15">
+      <c r="C54" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.15">
+      <c r="C55" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.15">
+      <c r="C56" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.15">
+      <c r="C57" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.15">
+      <c r="C58" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.15">
+      <c r="C59" s="20" t="s">
+        <v>242</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+      <c r="M59" s="1"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.15">
+      <c r="C60" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+      <c r="M60" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="F12:M12"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="F14:M14"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="F16:M16"/>
+    <mergeCell ref="F32:M32"/>
+    <mergeCell ref="I18:M18"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="F23:M23"/>
+    <mergeCell ref="F24:M24"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="F28:M28"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="F30:M30"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="J41:M41"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="I34:M34"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="F39:M39"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4BDE2C0-5DC7-478D-B843-6E7F3F1D9EC9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E2DED5E-7C95-4688-9B07-1F9D6B740CA6}">
+  <dimension ref="B2:M71"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="5" max="5" width="29.125" customWidth="1"/>
+    <col min="6" max="13" width="4.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C6" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="F6" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="58"/>
+    </row>
+    <row r="7" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="F7" s="57" t="s">
+        <v>197</v>
+      </c>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="69"/>
+      <c r="K7" s="69"/>
+      <c r="L7" s="69"/>
+      <c r="M7" s="58"/>
+    </row>
+    <row r="8" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C8" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F8" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="69"/>
+      <c r="M8" s="58"/>
+    </row>
+    <row r="9" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C9" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F9" s="57" t="s">
+        <v>198</v>
+      </c>
+      <c r="G9" s="69"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="69"/>
+      <c r="J9" s="69"/>
+      <c r="K9" s="69"/>
+      <c r="L9" s="69"/>
+      <c r="M9" s="58"/>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C21" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="6"/>
+      <c r="F21" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="J21" s="57" t="s">
+        <v>124</v>
+      </c>
+      <c r="K21" s="69"/>
+      <c r="L21" s="69"/>
+      <c r="M21" s="58"/>
+    </row>
+    <row r="22" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C22" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="6"/>
+      <c r="F22" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="I22" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="J22" s="57" t="s">
+        <v>124</v>
+      </c>
+      <c r="K22" s="69"/>
+      <c r="L22" s="69"/>
+      <c r="M22" s="58"/>
+    </row>
+    <row r="23" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C23" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" s="6"/>
+      <c r="F23" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="G23" s="58"/>
+      <c r="H23" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="I23" s="69"/>
+      <c r="J23" s="69"/>
+      <c r="K23" s="69"/>
+      <c r="L23" s="69"/>
+      <c r="M23" s="58"/>
+    </row>
+    <row r="24" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C24" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" s="6"/>
+      <c r="F24" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="G24" s="58"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="K24" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="L24" s="69"/>
+      <c r="M24" s="58"/>
+    </row>
+    <row r="25" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C25" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" s="6"/>
+      <c r="F25" s="57" t="s">
+        <v>130</v>
+      </c>
+      <c r="G25" s="69"/>
+      <c r="H25" s="69"/>
+      <c r="I25" s="58"/>
+      <c r="J25" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="K25" s="69"/>
+      <c r="L25" s="69"/>
+      <c r="M25" s="58"/>
+    </row>
+    <row r="26" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C26" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="6"/>
+      <c r="F26" s="57" t="s">
+        <v>130</v>
+      </c>
+      <c r="G26" s="69"/>
+      <c r="H26" s="69"/>
+      <c r="I26" s="58"/>
+      <c r="J26" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="K26" s="69"/>
+      <c r="L26" s="69"/>
+      <c r="M26" s="58"/>
+    </row>
+    <row r="27" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C27" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="F27" s="57" t="s">
+        <v>132</v>
+      </c>
+      <c r="G27" s="69"/>
+      <c r="H27" s="69"/>
+      <c r="I27" s="58"/>
+      <c r="J27" s="57" t="s">
+        <v>133</v>
+      </c>
+      <c r="K27" s="69"/>
+      <c r="L27" s="69"/>
+      <c r="M27" s="58"/>
+    </row>
+    <row r="28" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C28" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" s="6"/>
+      <c r="F28" s="57" t="s">
+        <v>132</v>
+      </c>
+      <c r="G28" s="69"/>
+      <c r="H28" s="69"/>
+      <c r="I28" s="58"/>
+      <c r="J28" s="57" t="s">
+        <v>133</v>
+      </c>
+      <c r="K28" s="69"/>
+      <c r="L28" s="69"/>
+      <c r="M28" s="58"/>
+    </row>
+    <row r="29" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C29" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" s="6"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="11"/>
+    </row>
+    <row r="30" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C30" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" s="6"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="I30" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="J30" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="K30" s="15"/>
+      <c r="L30" s="16"/>
+      <c r="M30" s="18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C31" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F31" s="57" t="s">
+        <v>160</v>
+      </c>
+      <c r="G31" s="69"/>
+      <c r="H31" s="69"/>
+      <c r="I31" s="69"/>
+      <c r="J31" s="69"/>
+      <c r="K31" s="69"/>
+      <c r="L31" s="69"/>
+      <c r="M31" s="58"/>
+    </row>
+    <row r="32" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C32" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" s="6"/>
+      <c r="F32" s="57" t="s">
+        <v>160</v>
+      </c>
+      <c r="G32" s="69"/>
+      <c r="H32" s="69"/>
+      <c r="I32" s="69"/>
+      <c r="J32" s="69"/>
+      <c r="K32" s="69"/>
+      <c r="L32" s="69"/>
+      <c r="M32" s="58"/>
+    </row>
+    <row r="33" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C33" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" s="6"/>
+      <c r="F33" s="57" t="s">
+        <v>160</v>
+      </c>
+      <c r="G33" s="69"/>
+      <c r="H33" s="69"/>
+      <c r="I33" s="69"/>
+      <c r="J33" s="69"/>
+      <c r="K33" s="69"/>
+      <c r="L33" s="69"/>
+      <c r="M33" s="58"/>
+    </row>
+    <row r="34" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C34" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" s="6"/>
+      <c r="F34" s="57" t="s">
+        <v>160</v>
+      </c>
+      <c r="G34" s="69"/>
+      <c r="H34" s="69"/>
+      <c r="I34" s="69"/>
+      <c r="J34" s="69"/>
+      <c r="K34" s="69"/>
+      <c r="L34" s="69"/>
+      <c r="M34" s="58"/>
+    </row>
+    <row r="35" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C35" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E35" s="6"/>
+      <c r="F35" s="57" t="s">
+        <v>160</v>
+      </c>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
+      <c r="I35" s="69"/>
+      <c r="J35" s="69"/>
+      <c r="K35" s="69"/>
+      <c r="L35" s="69"/>
+      <c r="M35" s="58"/>
+    </row>
+    <row r="36" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C36" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" s="6"/>
+      <c r="F36" s="57" t="s">
+        <v>160</v>
+      </c>
+      <c r="G36" s="69"/>
+      <c r="H36" s="69"/>
+      <c r="I36" s="69"/>
+      <c r="J36" s="69"/>
+      <c r="K36" s="69"/>
+      <c r="L36" s="69"/>
+      <c r="M36" s="58"/>
+    </row>
+    <row r="37" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C37" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E37" s="1"/>
+      <c r="F37" s="57" t="s">
+        <v>160</v>
+      </c>
+      <c r="G37" s="69"/>
+      <c r="H37" s="69"/>
+      <c r="I37" s="69"/>
+      <c r="J37" s="69"/>
+      <c r="K37" s="69"/>
+      <c r="L37" s="69"/>
+      <c r="M37" s="58"/>
+    </row>
+    <row r="38" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C38" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E38" s="1"/>
+      <c r="F38" s="57" t="s">
+        <v>160</v>
+      </c>
+      <c r="G38" s="69"/>
+      <c r="H38" s="69"/>
+      <c r="I38" s="69"/>
+      <c r="J38" s="69"/>
+      <c r="K38" s="69"/>
+      <c r="L38" s="69"/>
+      <c r="M38" s="58"/>
+    </row>
+    <row r="39" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C39" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E39" s="1"/>
+      <c r="F39" s="57" t="s">
+        <v>160</v>
+      </c>
+      <c r="G39" s="69"/>
+      <c r="H39" s="69"/>
+      <c r="I39" s="69"/>
+      <c r="J39" s="69"/>
+      <c r="K39" s="69"/>
+      <c r="L39" s="69"/>
+      <c r="M39" s="58"/>
+    </row>
+    <row r="40" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C40" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="57" t="s">
+        <v>160</v>
+      </c>
+      <c r="G40" s="69"/>
+      <c r="H40" s="69"/>
+      <c r="I40" s="69"/>
+      <c r="J40" s="69"/>
+      <c r="K40" s="69"/>
+      <c r="L40" s="69"/>
+      <c r="M40" s="58"/>
+    </row>
+    <row r="41" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C41" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E41" s="1"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="11"/>
+    </row>
+    <row r="42" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C42" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E42" s="1"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="J42" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="K42" s="69"/>
+      <c r="L42" s="58"/>
+      <c r="M42" s="14" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="43" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C43" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E43" s="1"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="I43" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="J43" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="K43" s="69"/>
+      <c r="L43" s="58"/>
+      <c r="M43" s="14" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="44" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C44" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E44" s="1"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="I44" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="J44" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="K44" s="69"/>
+      <c r="L44" s="58"/>
+      <c r="M44" s="14" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="45" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C45" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E45" s="1"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="I45" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="J45" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="K45" s="69"/>
+      <c r="L45" s="58"/>
+      <c r="M45" s="14" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="46" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C46" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E46" s="1"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="I46" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="J46" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="K46" s="69"/>
+      <c r="L46" s="58"/>
+      <c r="M46" s="14" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="47" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C47" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E47" s="1"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="I47" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="J47" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="K47" s="69"/>
+      <c r="L47" s="58"/>
+      <c r="M47" s="14" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="48" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C48" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E48" s="1"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="I48" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="J48" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="K48" s="69"/>
+      <c r="L48" s="58"/>
+      <c r="M48" s="14" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C49" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E49" s="1"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="I49" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="J49" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="K49" s="69"/>
+      <c r="L49" s="58"/>
+      <c r="M49" s="14" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C50" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E50" s="1"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="I50" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="J50" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="K50" s="69"/>
+      <c r="L50" s="58"/>
+      <c r="M50" s="14" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C51" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E51" s="1"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="11"/>
+    </row>
+    <row r="52" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C52" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E52" s="1"/>
+      <c r="F52" s="57" t="s">
+        <v>181</v>
+      </c>
+      <c r="G52" s="69"/>
+      <c r="H52" s="69"/>
+      <c r="I52" s="58"/>
+      <c r="J52" s="57" t="s">
+        <v>182</v>
+      </c>
+      <c r="K52" s="69"/>
+      <c r="L52" s="69"/>
+      <c r="M52" s="58"/>
+    </row>
+    <row r="53" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C53" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="E53" s="13"/>
+      <c r="F53" s="57" t="s">
+        <v>181</v>
+      </c>
+      <c r="G53" s="69"/>
+      <c r="H53" s="69"/>
+      <c r="I53" s="58"/>
+      <c r="J53" s="57" t="s">
+        <v>182</v>
+      </c>
+      <c r="K53" s="69"/>
+      <c r="L53" s="69"/>
+      <c r="M53" s="58"/>
+    </row>
+    <row r="54" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C54" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E54" s="1"/>
+      <c r="F54" s="57" t="s">
+        <v>181</v>
+      </c>
+      <c r="G54" s="69"/>
+      <c r="H54" s="69"/>
+      <c r="I54" s="58"/>
+      <c r="J54" s="57" t="s">
+        <v>182</v>
+      </c>
+      <c r="K54" s="69"/>
+      <c r="L54" s="69"/>
+      <c r="M54" s="58"/>
+    </row>
+    <row r="55" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C55" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E55" s="1"/>
+      <c r="F55" s="57" t="s">
+        <v>181</v>
+      </c>
+      <c r="G55" s="69"/>
+      <c r="H55" s="69"/>
+      <c r="I55" s="58"/>
+      <c r="J55" s="57" t="s">
+        <v>182</v>
+      </c>
+      <c r="K55" s="69"/>
+      <c r="L55" s="69"/>
+      <c r="M55" s="58"/>
+    </row>
+    <row r="56" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C56" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E56" s="1"/>
+      <c r="F56" s="57" t="s">
+        <v>181</v>
+      </c>
+      <c r="G56" s="69"/>
+      <c r="H56" s="69"/>
+      <c r="I56" s="58"/>
+      <c r="J56" s="57" t="s">
+        <v>182</v>
+      </c>
+      <c r="K56" s="69"/>
+      <c r="L56" s="69"/>
+      <c r="M56" s="58"/>
+    </row>
+    <row r="57" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C57" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E57" s="1"/>
+      <c r="F57" s="57" t="s">
+        <v>181</v>
+      </c>
+      <c r="G57" s="69"/>
+      <c r="H57" s="69"/>
+      <c r="I57" s="58"/>
+      <c r="J57" s="57" t="s">
+        <v>182</v>
+      </c>
+      <c r="K57" s="69"/>
+      <c r="L57" s="69"/>
+      <c r="M57" s="58"/>
+    </row>
+    <row r="58" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C58" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E58" s="1"/>
+      <c r="F58" s="57" t="s">
+        <v>181</v>
+      </c>
+      <c r="G58" s="69"/>
+      <c r="H58" s="69"/>
+      <c r="I58" s="58"/>
+      <c r="J58" s="57" t="s">
+        <v>182</v>
+      </c>
+      <c r="K58" s="69"/>
+      <c r="L58" s="69"/>
+      <c r="M58" s="58"/>
+    </row>
+    <row r="59" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C59" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E59" s="1"/>
+      <c r="F59" s="57" t="s">
+        <v>181</v>
+      </c>
+      <c r="G59" s="69"/>
+      <c r="H59" s="69"/>
+      <c r="I59" s="58"/>
+      <c r="J59" s="57" t="s">
+        <v>182</v>
+      </c>
+      <c r="K59" s="69"/>
+      <c r="L59" s="69"/>
+      <c r="M59" s="58"/>
+    </row>
+    <row r="60" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C60" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E60" s="1"/>
+      <c r="F60" s="57" t="s">
+        <v>181</v>
+      </c>
+      <c r="G60" s="69"/>
+      <c r="H60" s="69"/>
+      <c r="I60" s="58"/>
+      <c r="J60" s="57" t="s">
+        <v>182</v>
+      </c>
+      <c r="K60" s="69"/>
+      <c r="L60" s="69"/>
+      <c r="M60" s="58"/>
+    </row>
+    <row r="61" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C61" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E61" s="1"/>
+      <c r="F61" s="9"/>
+      <c r="G61" s="10"/>
+      <c r="H61" s="10"/>
+      <c r="I61" s="10"/>
+      <c r="J61" s="10"/>
+      <c r="K61" s="10"/>
+      <c r="L61" s="10"/>
+      <c r="M61" s="11"/>
+    </row>
+    <row r="62" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C62" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E62" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="F62" s="9"/>
+      <c r="G62" s="10"/>
+      <c r="H62" s="10"/>
+      <c r="I62" s="10"/>
+      <c r="J62" s="10"/>
+      <c r="K62" s="11"/>
+      <c r="L62" s="68" t="s">
+        <v>193</v>
+      </c>
+      <c r="M62" s="64"/>
+    </row>
+    <row r="63" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C63" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E63" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="F63" s="9"/>
+      <c r="G63" s="10"/>
+      <c r="H63" s="10"/>
+      <c r="I63" s="10"/>
+      <c r="J63" s="10"/>
+      <c r="K63" s="11"/>
+      <c r="L63" s="62" t="s">
+        <v>193</v>
+      </c>
+      <c r="M63" s="64"/>
+    </row>
+    <row r="64" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C64" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E64" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="F64" s="9"/>
+      <c r="G64" s="10"/>
+      <c r="H64" s="10"/>
+      <c r="I64" s="10"/>
+      <c r="J64" s="10"/>
+      <c r="K64" s="11"/>
+      <c r="L64" s="62" t="s">
+        <v>193</v>
+      </c>
+      <c r="M64" s="64"/>
+    </row>
+    <row r="65" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C65" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E65" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="F65" s="9"/>
+      <c r="G65" s="10"/>
+      <c r="H65" s="10"/>
+      <c r="I65" s="10"/>
+      <c r="J65" s="10"/>
+      <c r="K65" s="11"/>
+      <c r="L65" s="62" t="s">
+        <v>193</v>
+      </c>
+      <c r="M65" s="64"/>
+    </row>
+    <row r="66" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C66" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E66" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="F66" s="9"/>
+      <c r="G66" s="10"/>
+      <c r="H66" s="10"/>
+      <c r="I66" s="10"/>
+      <c r="J66" s="10"/>
+      <c r="K66" s="11"/>
+      <c r="L66" s="62" t="s">
+        <v>193</v>
+      </c>
+      <c r="M66" s="64"/>
+    </row>
+    <row r="67" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C67" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E67" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="F67" s="9"/>
+      <c r="G67" s="10"/>
+      <c r="H67" s="10"/>
+      <c r="I67" s="10"/>
+      <c r="J67" s="10"/>
+      <c r="K67" s="11"/>
+      <c r="L67" s="62" t="s">
+        <v>193</v>
+      </c>
+      <c r="M67" s="64"/>
+    </row>
+    <row r="68" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C68" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E68" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="F68" s="9"/>
+      <c r="G68" s="10"/>
+      <c r="H68" s="10"/>
+      <c r="I68" s="10"/>
+      <c r="J68" s="10"/>
+      <c r="K68" s="11"/>
+      <c r="L68" s="62" t="s">
+        <v>193</v>
+      </c>
+      <c r="M68" s="64"/>
+    </row>
+    <row r="69" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C69" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E69" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="F69" s="9"/>
+      <c r="G69" s="10"/>
+      <c r="H69" s="10"/>
+      <c r="I69" s="10"/>
+      <c r="J69" s="10"/>
+      <c r="K69" s="11"/>
+      <c r="L69" s="62" t="s">
+        <v>193</v>
+      </c>
+      <c r="M69" s="64"/>
+    </row>
+    <row r="70" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C70" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E70" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="F70" s="9"/>
+      <c r="G70" s="10"/>
+      <c r="H70" s="10"/>
+      <c r="I70" s="10"/>
+      <c r="J70" s="10"/>
+      <c r="K70" s="11"/>
+      <c r="L70" s="62" t="s">
+        <v>193</v>
+      </c>
+      <c r="M70" s="64"/>
+    </row>
+    <row r="71" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C71" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E71" s="1"/>
+      <c r="F71" s="9"/>
+      <c r="G71" s="10"/>
+      <c r="H71" s="10"/>
+      <c r="I71" s="10"/>
+      <c r="J71" s="10"/>
+      <c r="K71" s="10"/>
+      <c r="L71" s="10"/>
+      <c r="M71" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="64">
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F34:M34"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="F28:I28"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="F31:M31"/>
+    <mergeCell ref="F32:M32"/>
+    <mergeCell ref="F33:M33"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="F35:M35"/>
+    <mergeCell ref="F36:M36"/>
+    <mergeCell ref="F37:M37"/>
+    <mergeCell ref="F38:M38"/>
+    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="J56:M56"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="J52:M52"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="J53:M53"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="L69:M69"/>
+    <mergeCell ref="L70:M70"/>
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="J60:M60"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="L64:M64"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="F6:M6"/>
+    <mergeCell ref="F7:M7"/>
+    <mergeCell ref="F8:M8"/>
+    <mergeCell ref="F9:M9"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="F57:I57"/>
+    <mergeCell ref="J57:M57"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="J58:M58"/>
+    <mergeCell ref="F59:I59"/>
+    <mergeCell ref="J59:M59"/>
+    <mergeCell ref="F54:I54"/>
+    <mergeCell ref="J54:M54"/>
+    <mergeCell ref="F55:I55"/>
+    <mergeCell ref="J55:M55"/>
+    <mergeCell ref="F56:I56"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC57A460-A3F1-420B-B8CC-FFCC94C867CA}">
+  <dimension ref="B2:M54"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="5" max="5" width="39.75" customWidth="1"/>
+    <col min="6" max="13" width="4.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="C5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="C6" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="C7" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="C8" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="C9" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C13" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="45" t="s">
+        <v>244</v>
+      </c>
+      <c r="F13" s="81"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="82"/>
+      <c r="K13" s="82"/>
+      <c r="L13" s="82"/>
+      <c r="M13" s="83"/>
+    </row>
+    <row r="14" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C14" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14" s="59" t="s">
+        <v>134</v>
+      </c>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="60"/>
+      <c r="K14" s="60"/>
+      <c r="L14" s="60"/>
+      <c r="M14" s="61"/>
+    </row>
+    <row r="15" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C15" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="45" t="s">
+        <v>245</v>
+      </c>
+      <c r="F15" s="59" t="s">
+        <v>245</v>
+      </c>
+      <c r="G15" s="60"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="60"/>
+      <c r="L15" s="60"/>
+      <c r="M15" s="61"/>
+    </row>
+    <row r="16" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C16" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="44" t="s">
+        <v>246</v>
+      </c>
+      <c r="F16" s="59" t="s">
+        <v>246</v>
+      </c>
+      <c r="G16" s="60"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="60"/>
+      <c r="L16" s="60"/>
+      <c r="M16" s="61"/>
+    </row>
+    <row r="17" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C17" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="45"/>
+      <c r="F17" s="47" t="s">
+        <v>247</v>
+      </c>
+      <c r="G17" s="47" t="s">
+        <v>248</v>
+      </c>
+      <c r="H17" s="47" t="s">
+        <v>249</v>
+      </c>
+      <c r="I17" s="47" t="s">
+        <v>250</v>
+      </c>
+      <c r="J17" s="47" t="s">
+        <v>251</v>
+      </c>
+      <c r="K17" s="46"/>
+      <c r="L17" s="47" t="s">
+        <v>252</v>
+      </c>
+      <c r="M17" s="47" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C18" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="45"/>
+      <c r="F18" s="81" t="s">
+        <v>254</v>
+      </c>
+      <c r="G18" s="82"/>
+      <c r="H18" s="82"/>
+      <c r="I18" s="82"/>
+      <c r="J18" s="82"/>
+      <c r="K18" s="82"/>
+      <c r="L18" s="82"/>
+      <c r="M18" s="83"/>
+    </row>
+    <row r="19" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C19" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="45"/>
+      <c r="F19" s="81" t="s">
+        <v>255</v>
+      </c>
+      <c r="G19" s="82"/>
+      <c r="H19" s="82"/>
+      <c r="I19" s="82"/>
+      <c r="J19" s="82"/>
+      <c r="K19" s="82"/>
+      <c r="L19" s="82"/>
+      <c r="M19" s="83"/>
+    </row>
+    <row r="20" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C20" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="45"/>
+      <c r="F20" s="47" t="s">
+        <v>256</v>
+      </c>
+      <c r="G20" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="H20" s="47" t="s">
+        <v>258</v>
+      </c>
+      <c r="I20" s="47" t="s">
+        <v>259</v>
+      </c>
+      <c r="J20" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="K20" s="81"/>
+      <c r="L20" s="83"/>
+      <c r="M20" s="47" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C21" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="45"/>
+      <c r="F21" s="47" t="s">
+        <v>262</v>
+      </c>
+      <c r="G21" s="47" t="s">
+        <v>263</v>
+      </c>
+      <c r="H21" s="81"/>
+      <c r="I21" s="83"/>
+      <c r="J21" s="47" t="s">
+        <v>264</v>
+      </c>
+      <c r="K21" s="47" t="s">
+        <v>265</v>
+      </c>
+      <c r="L21" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="M21" s="47" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C22" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="45"/>
+      <c r="F22" s="59" t="s">
+        <v>268</v>
+      </c>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="60"/>
+      <c r="K22" s="60"/>
+      <c r="L22" s="60"/>
+      <c r="M22" s="61"/>
+    </row>
+    <row r="23" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C23" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" s="44"/>
+      <c r="F23" s="59" t="s">
+        <v>269</v>
+      </c>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="60"/>
+      <c r="J23" s="60"/>
+      <c r="K23" s="60"/>
+      <c r="L23" s="60"/>
+      <c r="M23" s="61"/>
+    </row>
+    <row r="24" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C24" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" s="44"/>
+      <c r="F24" s="59" t="s">
+        <v>270</v>
+      </c>
+      <c r="G24" s="60"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="60"/>
+      <c r="J24" s="60"/>
+      <c r="K24" s="60"/>
+      <c r="L24" s="60"/>
+      <c r="M24" s="61"/>
+    </row>
+    <row r="25" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C25" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" s="44"/>
+      <c r="F25" s="59" t="s">
+        <v>271</v>
+      </c>
+      <c r="G25" s="60"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="60"/>
+      <c r="J25" s="60"/>
+      <c r="K25" s="60"/>
+      <c r="L25" s="60"/>
+      <c r="M25" s="61"/>
+    </row>
+    <row r="26" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C26" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="44"/>
+      <c r="F26" s="59" t="s">
+        <v>272</v>
+      </c>
+      <c r="G26" s="60"/>
+      <c r="H26" s="60"/>
+      <c r="I26" s="60"/>
+      <c r="J26" s="60"/>
+      <c r="K26" s="60"/>
+      <c r="L26" s="60"/>
+      <c r="M26" s="61"/>
+    </row>
+    <row r="27" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C27" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" s="44"/>
+      <c r="F27" s="59" t="s">
+        <v>273</v>
+      </c>
+      <c r="G27" s="60"/>
+      <c r="H27" s="60"/>
+      <c r="I27" s="60"/>
+      <c r="J27" s="60"/>
+      <c r="K27" s="60"/>
+      <c r="L27" s="60"/>
+      <c r="M27" s="61"/>
+    </row>
+    <row r="28" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C28" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" s="44"/>
+      <c r="F28" s="59" t="s">
+        <v>274</v>
+      </c>
+      <c r="G28" s="60"/>
+      <c r="H28" s="60"/>
+      <c r="I28" s="60"/>
+      <c r="J28" s="60"/>
+      <c r="K28" s="60"/>
+      <c r="L28" s="60"/>
+      <c r="M28" s="61"/>
+    </row>
+    <row r="29" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C29" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" s="44"/>
+      <c r="F29" s="59" t="s">
+        <v>275</v>
+      </c>
+      <c r="G29" s="60"/>
+      <c r="H29" s="60"/>
+      <c r="I29" s="60"/>
+      <c r="J29" s="60"/>
+      <c r="K29" s="60"/>
+      <c r="L29" s="60"/>
+      <c r="M29" s="61"/>
+    </row>
+    <row r="30" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C30" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" s="44"/>
+      <c r="F30" s="59" t="s">
+        <v>276</v>
+      </c>
+      <c r="G30" s="60"/>
+      <c r="H30" s="60"/>
+      <c r="I30" s="60"/>
+      <c r="J30" s="60"/>
+      <c r="K30" s="60"/>
+      <c r="L30" s="60"/>
+      <c r="M30" s="61"/>
+    </row>
+    <row r="31" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C31" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" s="44"/>
+      <c r="F31" s="59" t="s">
+        <v>277</v>
+      </c>
+      <c r="G31" s="60"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="60"/>
+      <c r="J31" s="60"/>
+      <c r="K31" s="60"/>
+      <c r="L31" s="60"/>
+      <c r="M31" s="61"/>
+    </row>
+    <row r="32" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C32" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" s="44"/>
+      <c r="F32" s="81"/>
+      <c r="G32" s="82"/>
+      <c r="H32" s="82"/>
+      <c r="I32" s="82"/>
+      <c r="J32" s="82"/>
+      <c r="K32" s="82"/>
+      <c r="L32" s="82"/>
+      <c r="M32" s="83"/>
+    </row>
+    <row r="33" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C33" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" s="44"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="82"/>
+      <c r="H33" s="82"/>
+      <c r="I33" s="82"/>
+      <c r="J33" s="82"/>
+      <c r="K33" s="82"/>
+      <c r="L33" s="82"/>
+      <c r="M33" s="83"/>
+    </row>
+    <row r="34" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C34" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" s="44"/>
+      <c r="F34" s="59" t="s">
+        <v>278</v>
+      </c>
+      <c r="G34" s="60"/>
+      <c r="H34" s="60"/>
+      <c r="I34" s="60"/>
+      <c r="J34" s="60"/>
+      <c r="K34" s="60"/>
+      <c r="L34" s="60"/>
+      <c r="M34" s="61"/>
+    </row>
+    <row r="35" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C35" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E35" s="45"/>
+      <c r="F35" s="59" t="s">
+        <v>279</v>
+      </c>
+      <c r="G35" s="61"/>
+      <c r="H35" s="81"/>
+      <c r="I35" s="82"/>
+      <c r="J35" s="82"/>
+      <c r="K35" s="82"/>
+      <c r="L35" s="82"/>
+      <c r="M35" s="83"/>
+    </row>
+    <row r="36" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C36" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" s="45"/>
+      <c r="F36" s="81"/>
+      <c r="G36" s="82"/>
+      <c r="H36" s="82"/>
+      <c r="I36" s="82"/>
+      <c r="J36" s="83"/>
+      <c r="K36" s="59" t="s">
+        <v>280</v>
+      </c>
+      <c r="L36" s="60"/>
+      <c r="M36" s="61"/>
+    </row>
+    <row r="37" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C37" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E37" s="44"/>
+      <c r="F37" s="81"/>
+      <c r="G37" s="82"/>
+      <c r="H37" s="82"/>
+      <c r="I37" s="83"/>
+      <c r="J37" s="59" t="s">
+        <v>281</v>
+      </c>
+      <c r="K37" s="60"/>
+      <c r="L37" s="60"/>
+      <c r="M37" s="61"/>
+    </row>
+    <row r="38" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C38" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E38" s="44"/>
+      <c r="F38" s="81"/>
+      <c r="G38" s="82"/>
+      <c r="H38" s="82"/>
+      <c r="I38" s="83"/>
+      <c r="J38" s="59" t="s">
+        <v>282</v>
+      </c>
+      <c r="K38" s="60"/>
+      <c r="L38" s="60"/>
+      <c r="M38" s="61"/>
+    </row>
+    <row r="39" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C39" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E39" s="44"/>
+      <c r="F39" s="59" t="s">
+        <v>283</v>
+      </c>
+      <c r="G39" s="60"/>
+      <c r="H39" s="60"/>
+      <c r="I39" s="60"/>
+      <c r="J39" s="60"/>
+      <c r="K39" s="60"/>
+      <c r="L39" s="60"/>
+      <c r="M39" s="61"/>
+    </row>
+    <row r="40" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C40" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E40" s="44"/>
+      <c r="F40" s="81"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="82"/>
+      <c r="I40" s="82"/>
+      <c r="J40" s="82"/>
+      <c r="K40" s="82"/>
+      <c r="L40" s="82"/>
+      <c r="M40" s="83"/>
+    </row>
+    <row r="41" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C41" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E41" s="44"/>
+      <c r="F41" s="81"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="82"/>
+      <c r="K41" s="82"/>
+      <c r="L41" s="82"/>
+      <c r="M41" s="83"/>
+    </row>
+    <row r="42" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C42" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E42" s="44"/>
+      <c r="F42" s="81"/>
+      <c r="G42" s="82"/>
+      <c r="H42" s="82"/>
+      <c r="I42" s="82"/>
+      <c r="J42" s="82"/>
+      <c r="K42" s="82"/>
+      <c r="L42" s="82"/>
+      <c r="M42" s="83"/>
+    </row>
+    <row r="43" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C43" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E43" s="44"/>
+      <c r="F43" s="81"/>
+      <c r="G43" s="82"/>
+      <c r="H43" s="82"/>
+      <c r="I43" s="82"/>
+      <c r="J43" s="82"/>
+      <c r="K43" s="82"/>
+      <c r="L43" s="82"/>
+      <c r="M43" s="83"/>
+    </row>
+    <row r="44" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C44" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E44" s="44"/>
+      <c r="F44" s="81"/>
+      <c r="G44" s="82"/>
+      <c r="H44" s="82"/>
+      <c r="I44" s="82"/>
+      <c r="J44" s="82"/>
+      <c r="K44" s="82"/>
+      <c r="L44" s="82"/>
+      <c r="M44" s="83"/>
+    </row>
+    <row r="45" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C45" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E45" s="45"/>
+      <c r="F45" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="G45" s="47" t="s">
+        <v>121</v>
+      </c>
+      <c r="H45" s="47" t="s">
+        <v>292</v>
+      </c>
+      <c r="I45" s="47" t="s">
+        <v>123</v>
+      </c>
+      <c r="J45" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="K45" s="60"/>
+      <c r="L45" s="60"/>
+      <c r="M45" s="61"/>
+    </row>
+    <row r="46" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C46" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E46" s="45"/>
+      <c r="F46" s="59" t="s">
+        <v>293</v>
+      </c>
+      <c r="G46" s="61"/>
+      <c r="H46" s="59" t="s">
+        <v>126</v>
+      </c>
+      <c r="I46" s="60"/>
+      <c r="J46" s="60"/>
+      <c r="K46" s="60"/>
+      <c r="L46" s="60"/>
+      <c r="M46" s="61"/>
+    </row>
+    <row r="47" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C47" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E47" s="45"/>
+      <c r="F47" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="G47" s="76"/>
+      <c r="H47" s="76"/>
+      <c r="I47" s="77"/>
+      <c r="J47" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="K47" s="60"/>
+      <c r="L47" s="60"/>
+      <c r="M47" s="61"/>
+    </row>
+    <row r="48" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C48" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E48" s="6"/>
+      <c r="F48" s="59" t="s">
+        <v>132</v>
+      </c>
+      <c r="G48" s="60"/>
+      <c r="H48" s="60"/>
+      <c r="I48" s="61"/>
+      <c r="J48" s="78" t="s">
+        <v>133</v>
+      </c>
+      <c r="K48" s="79"/>
+      <c r="L48" s="79"/>
+      <c r="M48" s="80"/>
+    </row>
+    <row r="49" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C49" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E49" s="6"/>
+      <c r="F49" s="57" t="s">
+        <v>160</v>
+      </c>
+      <c r="G49" s="69"/>
+      <c r="H49" s="69"/>
+      <c r="I49" s="69"/>
+      <c r="J49" s="69"/>
+      <c r="K49" s="69"/>
+      <c r="L49" s="69"/>
+      <c r="M49" s="58"/>
+    </row>
+    <row r="50" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C50" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E50" s="6"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="56"/>
+      <c r="H50" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="I50" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="J50" s="69"/>
+      <c r="K50" s="58"/>
+      <c r="L50" s="57" t="s">
+        <v>160</v>
+      </c>
+      <c r="M50" s="58"/>
+    </row>
+    <row r="51" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C51" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E51" s="6"/>
+      <c r="F51" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="H51" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="I51" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K51" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="L51" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="M51" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C52" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E52" s="6"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="55"/>
+      <c r="H52" s="55"/>
+      <c r="I52" s="56"/>
+      <c r="J52" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="K52" s="69"/>
+      <c r="L52" s="58"/>
+      <c r="M52" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C53" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E53" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="F53" s="81"/>
+      <c r="G53" s="82"/>
+      <c r="H53" s="82"/>
+      <c r="I53" s="82"/>
+      <c r="J53" s="82"/>
+      <c r="K53" s="83"/>
+      <c r="L53" s="62" t="s">
+        <v>302</v>
+      </c>
+      <c r="M53" s="64"/>
+    </row>
+    <row r="54" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C54" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E54" s="6"/>
+      <c r="F54" s="81"/>
+      <c r="G54" s="82"/>
+      <c r="H54" s="82"/>
+      <c r="I54" s="82"/>
+      <c r="J54" s="82"/>
+      <c r="K54" s="82"/>
+      <c r="L54" s="82"/>
+      <c r="M54" s="83"/>
+    </row>
+  </sheetData>
+  <mergeCells count="51">
+    <mergeCell ref="F13:M13"/>
+    <mergeCell ref="F15:M15"/>
+    <mergeCell ref="F54:M54"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="F53:K53"/>
+    <mergeCell ref="J52:L52"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="F41:M41"/>
+    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="F31:M31"/>
+    <mergeCell ref="F33:M33"/>
+    <mergeCell ref="F14:M14"/>
+    <mergeCell ref="F16:M16"/>
+    <mergeCell ref="F18:M18"/>
+    <mergeCell ref="F19:M19"/>
+    <mergeCell ref="F22:M22"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="F28:M28"/>
+    <mergeCell ref="F30:M30"/>
+    <mergeCell ref="F32:M32"/>
+    <mergeCell ref="F34:M34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="F36:J36"/>
+    <mergeCell ref="F23:M23"/>
+    <mergeCell ref="F26:M26"/>
+    <mergeCell ref="F27:M27"/>
+    <mergeCell ref="F24:M24"/>
+    <mergeCell ref="F25:M25"/>
+    <mergeCell ref="F42:M42"/>
+    <mergeCell ref="F43:M43"/>
+    <mergeCell ref="F44:M44"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="F47:I47"/>
+    <mergeCell ref="J47:M47"/>
+    <mergeCell ref="F48:I48"/>
+    <mergeCell ref="J48:M48"/>
+    <mergeCell ref="F49:M49"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="F50:G50"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D191A0C-02CD-4BD6-9BF3-D97117CF844C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/doc/spec/Y8960_Specifications.xlsx
+++ b/doc/spec/Y8960_Specifications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\HRA_product\Y8960_Cartridge\doc\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1F87E7-1B68-4ECF-81AB-D1A38A6C3819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F968610-A728-40F1-ADF7-5A48FC638A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1260" yWindow="1020" windowWidth="17280" windowHeight="14130" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="modules" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="386">
   <si>
     <t>Y8960 Cartridge は、MSX用のオーディオ系チップのコンボカートリッジです。</t>
     <rPh sb="21" eb="22">
@@ -1692,19 +1692,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>常に出現している。1 にすると、BANK1～3 への /WR が SRAM まで到達。</t>
-    <rPh sb="0" eb="1">
-      <t>ツネ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>シュツゲン</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>トウタツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>RAM Mode=0 の時のみ利用可能</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1860,6 +1847,99 @@
     <rPh sb="47" eb="51">
       <t>リヨウカノウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>常に出現している。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1 にすると、BANK1～3 への /WR が SRAM まで到達</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>。
+かつ、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BANK1 に SCCレジスタバンクを出現させられるようになる</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <rPh sb="0" eb="1">
+      <t>ツネ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>トウタツ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>シュツゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>INT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>T1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>T2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EOS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PCM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BUF</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1867,7 +1947,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1923,8 +2003,17 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1952,6 +2041,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2290,7 +2385,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2453,13 +2548,61 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2468,52 +2611,40 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2533,24 +2664,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3129,7 +3242,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="4" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:14" ht="27.75" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C4" s="13" t="s">
         <v>349</v>
       </c>
@@ -3139,18 +3252,18 @@
       <c r="E4" s="53" t="s">
         <v>344</v>
       </c>
-      <c r="F4" s="54"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="56"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="70"/>
       <c r="M4" s="26" t="s">
         <v>350</v>
       </c>
-      <c r="N4" s="84" t="s">
-        <v>355</v>
+      <c r="N4" s="56" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="5" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3163,17 +3276,17 @@
       <c r="E5" s="51" t="s">
         <v>340</v>
       </c>
-      <c r="F5" s="62" t="s">
+      <c r="F5" s="63" t="s">
         <v>351</v>
       </c>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="63"/>
-      <c r="L5" s="63"/>
-      <c r="M5" s="64"/>
-      <c r="N5" s="85" t="s">
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+      <c r="K5" s="64"/>
+      <c r="L5" s="64"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="54" t="s">
         <v>354</v>
       </c>
     </row>
@@ -3187,17 +3300,17 @@
       <c r="E6" s="51" t="s">
         <v>341</v>
       </c>
-      <c r="F6" s="62" t="s">
+      <c r="F6" s="63" t="s">
         <v>351</v>
       </c>
-      <c r="G6" s="63"/>
-      <c r="H6" s="63"/>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="63"/>
-      <c r="L6" s="63"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="85" t="s">
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="54" t="s">
         <v>354</v>
       </c>
     </row>
@@ -3211,17 +3324,17 @@
       <c r="E7" s="51" t="s">
         <v>342</v>
       </c>
-      <c r="F7" s="62" t="s">
+      <c r="F7" s="63" t="s">
         <v>351</v>
       </c>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="63"/>
-      <c r="J7" s="63"/>
-      <c r="K7" s="63"/>
-      <c r="L7" s="63"/>
-      <c r="M7" s="64"/>
-      <c r="N7" s="85" t="s">
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="65"/>
+      <c r="N7" s="54" t="s">
         <v>354</v>
       </c>
     </row>
@@ -3235,17 +3348,17 @@
       <c r="E8" s="25" t="s">
         <v>343</v>
       </c>
-      <c r="F8" s="62" t="s">
+      <c r="F8" s="63" t="s">
         <v>351</v>
       </c>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="63"/>
-      <c r="K8" s="63"/>
-      <c r="L8" s="63"/>
-      <c r="M8" s="64"/>
-      <c r="N8" s="85" t="s">
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="64"/>
+      <c r="K8" s="64"/>
+      <c r="L8" s="64"/>
+      <c r="M8" s="65"/>
+      <c r="N8" s="54" t="s">
         <v>354</v>
       </c>
     </row>
@@ -3259,18 +3372,18 @@
       <c r="E9" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="F9" s="59" t="s">
+      <c r="F9" s="60" t="s">
         <v>352</v>
       </c>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="60"/>
-      <c r="K9" s="60"/>
-      <c r="L9" s="60"/>
-      <c r="M9" s="61"/>
-      <c r="N9" s="85" t="s">
-        <v>356</v>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="61"/>
+      <c r="K9" s="61"/>
+      <c r="L9" s="61"/>
+      <c r="M9" s="62"/>
+      <c r="N9" s="54" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="10" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3283,18 +3396,18 @@
       <c r="E10" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="F10" s="59" t="s">
+      <c r="F10" s="60" t="s">
         <v>352</v>
       </c>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="60"/>
-      <c r="K10" s="60"/>
-      <c r="L10" s="60"/>
-      <c r="M10" s="61"/>
-      <c r="N10" s="85" t="s">
-        <v>356</v>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
+      <c r="L10" s="61"/>
+      <c r="M10" s="62"/>
+      <c r="N10" s="54" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="11" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3307,18 +3420,18 @@
       <c r="E11" s="51" t="s">
         <v>324</v>
       </c>
-      <c r="F11" s="62" t="s">
+      <c r="F11" s="63" t="s">
         <v>324</v>
       </c>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
-      <c r="I11" s="63"/>
-      <c r="J11" s="63"/>
-      <c r="K11" s="63"/>
-      <c r="L11" s="63"/>
-      <c r="M11" s="64"/>
-      <c r="N11" s="86" t="s">
-        <v>357</v>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="64"/>
+      <c r="K11" s="64"/>
+      <c r="L11" s="64"/>
+      <c r="M11" s="65"/>
+      <c r="N11" s="55" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="12" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3331,18 +3444,18 @@
       <c r="E12" s="51" t="s">
         <v>325</v>
       </c>
-      <c r="F12" s="62" t="s">
+      <c r="F12" s="63" t="s">
         <v>325</v>
       </c>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-      <c r="I12" s="63"/>
-      <c r="J12" s="63"/>
-      <c r="K12" s="63"/>
-      <c r="L12" s="63"/>
-      <c r="M12" s="64"/>
-      <c r="N12" s="86" t="s">
-        <v>358</v>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="64"/>
+      <c r="K12" s="64"/>
+      <c r="L12" s="64"/>
+      <c r="M12" s="65"/>
+      <c r="N12" s="55" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="13" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3355,18 +3468,18 @@
       <c r="E13" s="50" t="s">
         <v>316</v>
       </c>
-      <c r="F13" s="68" t="s">
+      <c r="F13" s="72" t="s">
         <v>318</v>
       </c>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
-      <c r="I13" s="63"/>
-      <c r="J13" s="63"/>
-      <c r="K13" s="63"/>
-      <c r="L13" s="63"/>
-      <c r="M13" s="64"/>
-      <c r="N13" s="86" t="s">
-        <v>359</v>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="64"/>
+      <c r="K13" s="64"/>
+      <c r="L13" s="64"/>
+      <c r="M13" s="65"/>
+      <c r="N13" s="55" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="14" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3379,18 +3492,18 @@
       <c r="E14" s="51" t="s">
         <v>317</v>
       </c>
-      <c r="F14" s="68" t="s">
+      <c r="F14" s="72" t="s">
         <v>319</v>
       </c>
-      <c r="G14" s="63"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="63"/>
-      <c r="J14" s="63"/>
-      <c r="K14" s="63"/>
-      <c r="L14" s="63"/>
-      <c r="M14" s="64"/>
-      <c r="N14" s="86" t="s">
-        <v>360</v>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="64"/>
+      <c r="L14" s="64"/>
+      <c r="M14" s="65"/>
+      <c r="N14" s="55" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="15" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3403,18 +3516,18 @@
       <c r="E15" s="25" t="s">
         <v>309</v>
       </c>
-      <c r="F15" s="68" t="s">
+      <c r="F15" s="72" t="s">
         <v>300</v>
       </c>
-      <c r="G15" s="63"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="63"/>
-      <c r="J15" s="63"/>
-      <c r="K15" s="63"/>
-      <c r="L15" s="63"/>
-      <c r="M15" s="64"/>
-      <c r="N15" s="86" t="s">
-        <v>361</v>
+      <c r="G15" s="64"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="64"/>
+      <c r="J15" s="64"/>
+      <c r="K15" s="64"/>
+      <c r="L15" s="64"/>
+      <c r="M15" s="65"/>
+      <c r="N15" s="55" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="16" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3427,18 +3540,18 @@
       <c r="E16" s="25" t="s">
         <v>301</v>
       </c>
-      <c r="F16" s="68" t="s">
+      <c r="F16" s="72" t="s">
         <v>310</v>
       </c>
-      <c r="G16" s="63"/>
-      <c r="H16" s="63"/>
-      <c r="I16" s="63"/>
-      <c r="J16" s="63"/>
-      <c r="K16" s="63"/>
-      <c r="L16" s="63"/>
-      <c r="M16" s="64"/>
-      <c r="N16" s="86" t="s">
-        <v>362</v>
+      <c r="G16" s="64"/>
+      <c r="H16" s="64"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="64"/>
+      <c r="K16" s="64"/>
+      <c r="L16" s="64"/>
+      <c r="M16" s="65"/>
+      <c r="N16" s="55" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="17" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3451,18 +3564,18 @@
       <c r="E17" s="25" t="s">
         <v>298</v>
       </c>
-      <c r="F17" s="68" t="s">
+      <c r="F17" s="72" t="s">
         <v>298</v>
       </c>
-      <c r="G17" s="63"/>
-      <c r="H17" s="63"/>
-      <c r="I17" s="63"/>
-      <c r="J17" s="63"/>
-      <c r="K17" s="63"/>
-      <c r="L17" s="63"/>
-      <c r="M17" s="64"/>
-      <c r="N17" s="86" t="s">
-        <v>363</v>
+      <c r="G17" s="64"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="64"/>
+      <c r="K17" s="64"/>
+      <c r="L17" s="64"/>
+      <c r="M17" s="65"/>
+      <c r="N17" s="55" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="18" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3475,18 +3588,18 @@
       <c r="E18" s="25" t="s">
         <v>299</v>
       </c>
-      <c r="F18" s="68" t="s">
+      <c r="F18" s="72" t="s">
         <v>311</v>
       </c>
-      <c r="G18" s="63"/>
-      <c r="H18" s="63"/>
-      <c r="I18" s="63"/>
-      <c r="J18" s="63"/>
-      <c r="K18" s="63"/>
-      <c r="L18" s="63"/>
-      <c r="M18" s="64"/>
-      <c r="N18" s="86" t="s">
-        <v>364</v>
+      <c r="G18" s="64"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="64"/>
+      <c r="K18" s="64"/>
+      <c r="L18" s="64"/>
+      <c r="M18" s="65"/>
+      <c r="N18" s="55" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="19" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3499,18 +3612,18 @@
       <c r="E19" s="49" t="s">
         <v>107</v>
       </c>
-      <c r="F19" s="68" t="s">
+      <c r="F19" s="72" t="s">
         <v>107</v>
       </c>
-      <c r="G19" s="63"/>
-      <c r="H19" s="63"/>
-      <c r="I19" s="63"/>
-      <c r="J19" s="63"/>
-      <c r="K19" s="63"/>
-      <c r="L19" s="63"/>
-      <c r="M19" s="64"/>
-      <c r="N19" s="86" t="s">
-        <v>365</v>
+      <c r="G19" s="64"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="64"/>
+      <c r="J19" s="64"/>
+      <c r="K19" s="64"/>
+      <c r="L19" s="64"/>
+      <c r="M19" s="65"/>
+      <c r="N19" s="55" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="20" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3523,18 +3636,18 @@
       <c r="E20" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="F20" s="68" t="s">
+      <c r="F20" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="G20" s="63"/>
-      <c r="H20" s="63"/>
-      <c r="I20" s="63"/>
-      <c r="J20" s="63"/>
-      <c r="K20" s="63"/>
-      <c r="L20" s="63"/>
-      <c r="M20" s="64"/>
-      <c r="N20" s="86" t="s">
-        <v>366</v>
+      <c r="G20" s="64"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="64"/>
+      <c r="K20" s="64"/>
+      <c r="L20" s="64"/>
+      <c r="M20" s="65"/>
+      <c r="N20" s="55" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="21" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3547,18 +3660,18 @@
       <c r="E21" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F21" s="57" t="s">
+      <c r="F21" s="73" t="s">
         <v>105</v>
       </c>
-      <c r="G21" s="69"/>
-      <c r="H21" s="69"/>
-      <c r="I21" s="69"/>
-      <c r="J21" s="69"/>
-      <c r="K21" s="69"/>
-      <c r="L21" s="69"/>
-      <c r="M21" s="58"/>
-      <c r="N21" s="86" t="s">
-        <v>367</v>
+      <c r="G21" s="75"/>
+      <c r="H21" s="75"/>
+      <c r="I21" s="75"/>
+      <c r="J21" s="75"/>
+      <c r="K21" s="75"/>
+      <c r="L21" s="75"/>
+      <c r="M21" s="74"/>
+      <c r="N21" s="55" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="22" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3571,18 +3684,18 @@
       <c r="E22" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F22" s="57" t="s">
+      <c r="F22" s="73" t="s">
         <v>198</v>
       </c>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
-      <c r="J22" s="69"/>
-      <c r="K22" s="69"/>
-      <c r="L22" s="69"/>
-      <c r="M22" s="58"/>
-      <c r="N22" s="86" t="s">
-        <v>368</v>
+      <c r="G22" s="75"/>
+      <c r="H22" s="75"/>
+      <c r="I22" s="75"/>
+      <c r="J22" s="75"/>
+      <c r="K22" s="75"/>
+      <c r="L22" s="75"/>
+      <c r="M22" s="74"/>
+      <c r="N22" s="55" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="23" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3595,20 +3708,20 @@
       <c r="E23" s="52" t="s">
         <v>335</v>
       </c>
-      <c r="F23" s="65"/>
-      <c r="G23" s="66"/>
-      <c r="H23" s="66"/>
-      <c r="I23" s="66"/>
-      <c r="J23" s="66"/>
-      <c r="K23" s="67"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="67"/>
+      <c r="J23" s="67"/>
+      <c r="K23" s="68"/>
       <c r="L23" s="26" t="s">
         <v>200</v>
       </c>
       <c r="M23" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="N23" s="86" t="s">
-        <v>369</v>
+      <c r="N23" s="55" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="24" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3619,16 +3732,16 @@
         <v>96</v>
       </c>
       <c r="E24" s="6"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="55"/>
-      <c r="H24" s="55"/>
-      <c r="I24" s="55"/>
-      <c r="J24" s="55"/>
-      <c r="K24" s="55"/>
-      <c r="L24" s="55"/>
-      <c r="M24" s="56"/>
-      <c r="N24" s="86" t="s">
-        <v>370</v>
+      <c r="F24" s="69"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="71"/>
+      <c r="L24" s="71"/>
+      <c r="M24" s="70"/>
+      <c r="N24" s="55" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="25" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3639,16 +3752,16 @@
         <v>96</v>
       </c>
       <c r="E25" s="1"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="55"/>
-      <c r="H25" s="55"/>
-      <c r="I25" s="55"/>
-      <c r="J25" s="55"/>
-      <c r="K25" s="55"/>
-      <c r="L25" s="55"/>
-      <c r="M25" s="56"/>
-      <c r="N25" s="86" t="s">
-        <v>371</v>
+      <c r="F25" s="69"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="71"/>
+      <c r="K25" s="71"/>
+      <c r="L25" s="71"/>
+      <c r="M25" s="70"/>
+      <c r="N25" s="55" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="26" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3659,16 +3772,16 @@
         <v>96</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="55"/>
-      <c r="H26" s="55"/>
-      <c r="I26" s="55"/>
-      <c r="J26" s="55"/>
-      <c r="K26" s="55"/>
-      <c r="L26" s="55"/>
-      <c r="M26" s="56"/>
-      <c r="N26" s="86" t="s">
-        <v>372</v>
+      <c r="F26" s="69"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="71"/>
+      <c r="L26" s="71"/>
+      <c r="M26" s="70"/>
+      <c r="N26" s="55" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="27" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3679,16 +3792,16 @@
         <v>96</v>
       </c>
       <c r="E27" s="1"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="55"/>
-      <c r="H27" s="55"/>
-      <c r="I27" s="55"/>
-      <c r="J27" s="55"/>
-      <c r="K27" s="55"/>
-      <c r="L27" s="55"/>
-      <c r="M27" s="56"/>
-      <c r="N27" s="86" t="s">
-        <v>373</v>
+      <c r="F27" s="69"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="71"/>
+      <c r="L27" s="71"/>
+      <c r="M27" s="70"/>
+      <c r="N27" s="55" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="28" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3699,16 +3812,16 @@
         <v>96</v>
       </c>
       <c r="E28" s="1"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="55"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="55"/>
-      <c r="J28" s="55"/>
-      <c r="K28" s="55"/>
-      <c r="L28" s="55"/>
-      <c r="M28" s="56"/>
-      <c r="N28" s="86" t="s">
-        <v>374</v>
+      <c r="F28" s="69"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="71"/>
+      <c r="L28" s="71"/>
+      <c r="M28" s="70"/>
+      <c r="N28" s="55" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="29" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3719,16 +3832,16 @@
         <v>96</v>
       </c>
       <c r="E29" s="1"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="55"/>
-      <c r="H29" s="55"/>
-      <c r="I29" s="55"/>
-      <c r="J29" s="55"/>
-      <c r="K29" s="55"/>
-      <c r="L29" s="55"/>
-      <c r="M29" s="56"/>
-      <c r="N29" s="86" t="s">
-        <v>375</v>
+      <c r="F29" s="69"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="71"/>
+      <c r="K29" s="71"/>
+      <c r="L29" s="71"/>
+      <c r="M29" s="70"/>
+      <c r="N29" s="55" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="30" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3739,16 +3852,16 @@
         <v>96</v>
       </c>
       <c r="E30" s="1"/>
-      <c r="F30" s="54"/>
-      <c r="G30" s="55"/>
-      <c r="H30" s="55"/>
-      <c r="I30" s="55"/>
-      <c r="J30" s="55"/>
-      <c r="K30" s="55"/>
-      <c r="L30" s="55"/>
-      <c r="M30" s="56"/>
-      <c r="N30" s="86" t="s">
-        <v>376</v>
+      <c r="F30" s="69"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="71"/>
+      <c r="L30" s="71"/>
+      <c r="M30" s="70"/>
+      <c r="N30" s="55" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="31" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3761,18 +3874,18 @@
       <c r="E31" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="F31" s="54"/>
-      <c r="G31" s="55"/>
-      <c r="H31" s="55"/>
-      <c r="I31" s="55"/>
-      <c r="J31" s="55"/>
-      <c r="K31" s="56"/>
-      <c r="L31" s="57" t="s">
+      <c r="F31" s="69"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="70"/>
+      <c r="L31" s="73" t="s">
         <v>193</v>
       </c>
-      <c r="M31" s="58"/>
-      <c r="N31" s="86" t="s">
-        <v>377</v>
+      <c r="M31" s="74"/>
+      <c r="N31" s="55" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="32" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3785,8 +3898,8 @@
       <c r="E32" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="F32" s="54"/>
-      <c r="G32" s="56"/>
+      <c r="F32" s="69"/>
+      <c r="G32" s="70"/>
       <c r="H32" s="26" t="s">
         <v>321</v>
       </c>
@@ -3805,8 +3918,8 @@
       <c r="M32" s="47" t="s">
         <v>213</v>
       </c>
-      <c r="N32" s="86" t="s">
-        <v>378</v>
+      <c r="N32" s="55" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="33" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3819,18 +3932,18 @@
       <c r="E33" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="F33" s="59" t="s">
+      <c r="F33" s="60" t="s">
         <v>352</v>
       </c>
-      <c r="G33" s="60"/>
-      <c r="H33" s="60"/>
-      <c r="I33" s="60"/>
-      <c r="J33" s="60"/>
-      <c r="K33" s="60"/>
-      <c r="L33" s="60"/>
-      <c r="M33" s="61"/>
-      <c r="N33" s="85" t="s">
-        <v>356</v>
+      <c r="G33" s="61"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="61"/>
+      <c r="J33" s="61"/>
+      <c r="K33" s="61"/>
+      <c r="L33" s="61"/>
+      <c r="M33" s="62"/>
+      <c r="N33" s="54" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="34" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3843,22 +3956,38 @@
       <c r="E34" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="F34" s="59" t="s">
+      <c r="F34" s="60" t="s">
         <v>352</v>
       </c>
-      <c r="G34" s="60"/>
-      <c r="H34" s="60"/>
-      <c r="I34" s="60"/>
-      <c r="J34" s="60"/>
-      <c r="K34" s="60"/>
-      <c r="L34" s="60"/>
-      <c r="M34" s="61"/>
-      <c r="N34" s="85" t="s">
-        <v>356</v>
+      <c r="G34" s="61"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="61"/>
+      <c r="J34" s="61"/>
+      <c r="K34" s="61"/>
+      <c r="L34" s="61"/>
+      <c r="M34" s="62"/>
+      <c r="N34" s="54" t="s">
+        <v>355</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="F9:M9"/>
+    <mergeCell ref="F10:M10"/>
+    <mergeCell ref="F33:M33"/>
+    <mergeCell ref="F13:M13"/>
+    <mergeCell ref="F11:M11"/>
+    <mergeCell ref="F12:M12"/>
+    <mergeCell ref="F19:M19"/>
+    <mergeCell ref="F20:M20"/>
+    <mergeCell ref="F21:M21"/>
+    <mergeCell ref="F22:M22"/>
+    <mergeCell ref="F15:M15"/>
+    <mergeCell ref="F16:M16"/>
+    <mergeCell ref="F17:M17"/>
+    <mergeCell ref="F18:M18"/>
     <mergeCell ref="F34:M34"/>
     <mergeCell ref="F5:M5"/>
     <mergeCell ref="F6:M6"/>
@@ -3875,22 +4004,6 @@
     <mergeCell ref="F30:M30"/>
     <mergeCell ref="F31:K31"/>
     <mergeCell ref="F14:M14"/>
-    <mergeCell ref="F4:L4"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="F9:M9"/>
-    <mergeCell ref="F10:M10"/>
-    <mergeCell ref="F33:M33"/>
-    <mergeCell ref="F13:M13"/>
-    <mergeCell ref="F11:M11"/>
-    <mergeCell ref="F12:M12"/>
-    <mergeCell ref="F19:M19"/>
-    <mergeCell ref="F20:M20"/>
-    <mergeCell ref="F21:M21"/>
-    <mergeCell ref="F22:M22"/>
-    <mergeCell ref="F15:M15"/>
-    <mergeCell ref="F16:M16"/>
-    <mergeCell ref="F17:M17"/>
-    <mergeCell ref="F18:M18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4010,16 +4123,16 @@
       <c r="E12" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="72" t="s">
+      <c r="F12" s="76" t="s">
         <v>201</v>
       </c>
-      <c r="G12" s="73"/>
-      <c r="H12" s="73"/>
-      <c r="I12" s="73"/>
-      <c r="J12" s="73"/>
-      <c r="K12" s="73"/>
-      <c r="L12" s="73"/>
-      <c r="M12" s="74"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="77"/>
+      <c r="K12" s="77"/>
+      <c r="L12" s="77"/>
+      <c r="M12" s="78"/>
     </row>
     <row r="13" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="20" t="s">
@@ -4035,12 +4148,12 @@
       <c r="G13" s="37"/>
       <c r="H13" s="37"/>
       <c r="I13" s="38"/>
-      <c r="J13" s="72" t="s">
+      <c r="J13" s="76" t="s">
         <v>202</v>
       </c>
-      <c r="K13" s="73"/>
-      <c r="L13" s="73"/>
-      <c r="M13" s="74"/>
+      <c r="K13" s="77"/>
+      <c r="L13" s="77"/>
+      <c r="M13" s="78"/>
     </row>
     <row r="14" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="20" t="s">
@@ -4052,16 +4165,16 @@
       <c r="E14" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="72" t="s">
+      <c r="F14" s="76" t="s">
         <v>201</v>
       </c>
-      <c r="G14" s="73"/>
-      <c r="H14" s="73"/>
-      <c r="I14" s="73"/>
-      <c r="J14" s="73"/>
-      <c r="K14" s="73"/>
-      <c r="L14" s="73"/>
-      <c r="M14" s="74"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="77"/>
+      <c r="K14" s="77"/>
+      <c r="L14" s="77"/>
+      <c r="M14" s="78"/>
     </row>
     <row r="15" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="20" t="s">
@@ -4077,12 +4190,12 @@
       <c r="G15" s="37"/>
       <c r="H15" s="37"/>
       <c r="I15" s="38"/>
-      <c r="J15" s="72" t="s">
+      <c r="J15" s="76" t="s">
         <v>202</v>
       </c>
-      <c r="K15" s="73"/>
-      <c r="L15" s="73"/>
-      <c r="M15" s="74"/>
+      <c r="K15" s="77"/>
+      <c r="L15" s="77"/>
+      <c r="M15" s="78"/>
     </row>
     <row r="16" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="20" t="s">
@@ -4094,16 +4207,16 @@
       <c r="E16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="72" t="s">
+      <c r="F16" s="76" t="s">
         <v>201</v>
       </c>
-      <c r="G16" s="73"/>
-      <c r="H16" s="73"/>
-      <c r="I16" s="73"/>
-      <c r="J16" s="73"/>
-      <c r="K16" s="73"/>
-      <c r="L16" s="73"/>
-      <c r="M16" s="74"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="77"/>
+      <c r="K16" s="77"/>
+      <c r="L16" s="77"/>
+      <c r="M16" s="78"/>
     </row>
     <row r="17" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="20" t="s">
@@ -4119,12 +4232,12 @@
       <c r="G17" s="37"/>
       <c r="H17" s="37"/>
       <c r="I17" s="38"/>
-      <c r="J17" s="72" t="s">
+      <c r="J17" s="76" t="s">
         <v>202</v>
       </c>
-      <c r="K17" s="73"/>
-      <c r="L17" s="73"/>
-      <c r="M17" s="74"/>
+      <c r="K17" s="77"/>
+      <c r="L17" s="77"/>
+      <c r="M17" s="78"/>
     </row>
     <row r="18" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="20" t="s">
@@ -4139,13 +4252,13 @@
       <c r="F18" s="36"/>
       <c r="G18" s="37"/>
       <c r="H18" s="38"/>
-      <c r="I18" s="72" t="s">
+      <c r="I18" s="76" t="s">
         <v>203</v>
       </c>
-      <c r="J18" s="73"/>
-      <c r="K18" s="73"/>
-      <c r="L18" s="73"/>
-      <c r="M18" s="74"/>
+      <c r="J18" s="77"/>
+      <c r="K18" s="77"/>
+      <c r="L18" s="77"/>
+      <c r="M18" s="78"/>
     </row>
     <row r="19" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="20" t="s">
@@ -4198,12 +4311,12 @@
       <c r="I20" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="J20" s="72" t="s">
+      <c r="J20" s="76" t="s">
         <v>204</v>
       </c>
-      <c r="K20" s="73"/>
-      <c r="L20" s="73"/>
-      <c r="M20" s="74"/>
+      <c r="K20" s="77"/>
+      <c r="L20" s="77"/>
+      <c r="M20" s="78"/>
     </row>
     <row r="21" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="20" t="s">
@@ -4221,12 +4334,12 @@
       <c r="I21" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="J21" s="72" t="s">
+      <c r="J21" s="76" t="s">
         <v>204</v>
       </c>
-      <c r="K21" s="73"/>
-      <c r="L21" s="73"/>
-      <c r="M21" s="74"/>
+      <c r="K21" s="77"/>
+      <c r="L21" s="77"/>
+      <c r="M21" s="78"/>
     </row>
     <row r="22" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="20" t="s">
@@ -4244,12 +4357,12 @@
       <c r="I22" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="J22" s="72" t="s">
+      <c r="J22" s="76" t="s">
         <v>204</v>
       </c>
-      <c r="K22" s="73"/>
-      <c r="L22" s="73"/>
-      <c r="M22" s="74"/>
+      <c r="K22" s="77"/>
+      <c r="L22" s="77"/>
+      <c r="M22" s="78"/>
     </row>
     <row r="23" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="20" t="s">
@@ -4261,16 +4374,16 @@
       <c r="E23" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="F23" s="72" t="s">
+      <c r="F23" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="73"/>
-      <c r="J23" s="73"/>
-      <c r="K23" s="73"/>
-      <c r="L23" s="73"/>
-      <c r="M23" s="74"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
+      <c r="J23" s="77"/>
+      <c r="K23" s="77"/>
+      <c r="L23" s="77"/>
+      <c r="M23" s="78"/>
     </row>
     <row r="24" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="20" t="s">
@@ -4282,16 +4395,16 @@
       <c r="E24" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F24" s="72" t="s">
+      <c r="F24" s="76" t="s">
         <v>206</v>
       </c>
-      <c r="G24" s="73"/>
-      <c r="H24" s="73"/>
-      <c r="I24" s="73"/>
-      <c r="J24" s="73"/>
-      <c r="K24" s="73"/>
-      <c r="L24" s="73"/>
-      <c r="M24" s="74"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
+      <c r="J24" s="77"/>
+      <c r="K24" s="77"/>
+      <c r="L24" s="77"/>
+      <c r="M24" s="78"/>
     </row>
     <row r="25" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="20" t="s">
@@ -4307,12 +4420,12 @@
       <c r="G25" s="37"/>
       <c r="H25" s="37"/>
       <c r="I25" s="38"/>
-      <c r="J25" s="72" t="s">
+      <c r="J25" s="76" t="s">
         <v>207</v>
       </c>
-      <c r="K25" s="73"/>
-      <c r="L25" s="73"/>
-      <c r="M25" s="74"/>
+      <c r="K25" s="77"/>
+      <c r="L25" s="77"/>
+      <c r="M25" s="78"/>
     </row>
     <row r="26" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="20" t="s">
@@ -4362,16 +4475,16 @@
       <c r="E28" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="F28" s="68" t="s">
+      <c r="F28" s="72" t="s">
         <v>201</v>
       </c>
-      <c r="G28" s="70"/>
-      <c r="H28" s="70"/>
-      <c r="I28" s="70"/>
-      <c r="J28" s="70"/>
-      <c r="K28" s="70"/>
-      <c r="L28" s="70"/>
-      <c r="M28" s="71"/>
+      <c r="G28" s="79"/>
+      <c r="H28" s="79"/>
+      <c r="I28" s="79"/>
+      <c r="J28" s="79"/>
+      <c r="K28" s="79"/>
+      <c r="L28" s="79"/>
+      <c r="M28" s="80"/>
     </row>
     <row r="29" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="20" t="s">
@@ -4387,12 +4500,12 @@
       <c r="G29" s="28"/>
       <c r="H29" s="28"/>
       <c r="I29" s="29"/>
-      <c r="J29" s="68" t="s">
+      <c r="J29" s="72" t="s">
         <v>202</v>
       </c>
-      <c r="K29" s="70"/>
-      <c r="L29" s="70"/>
-      <c r="M29" s="71"/>
+      <c r="K29" s="79"/>
+      <c r="L29" s="79"/>
+      <c r="M29" s="80"/>
     </row>
     <row r="30" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="20" t="s">
@@ -4404,16 +4517,16 @@
       <c r="E30" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="F30" s="68" t="s">
+      <c r="F30" s="72" t="s">
         <v>201</v>
       </c>
-      <c r="G30" s="70"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="70"/>
-      <c r="J30" s="70"/>
-      <c r="K30" s="70"/>
-      <c r="L30" s="70"/>
-      <c r="M30" s="71"/>
+      <c r="G30" s="79"/>
+      <c r="H30" s="79"/>
+      <c r="I30" s="79"/>
+      <c r="J30" s="79"/>
+      <c r="K30" s="79"/>
+      <c r="L30" s="79"/>
+      <c r="M30" s="80"/>
     </row>
     <row r="31" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="20" t="s">
@@ -4429,12 +4542,12 @@
       <c r="G31" s="28"/>
       <c r="H31" s="28"/>
       <c r="I31" s="29"/>
-      <c r="J31" s="68" t="s">
+      <c r="J31" s="72" t="s">
         <v>202</v>
       </c>
-      <c r="K31" s="70"/>
-      <c r="L31" s="70"/>
-      <c r="M31" s="71"/>
+      <c r="K31" s="79"/>
+      <c r="L31" s="79"/>
+      <c r="M31" s="80"/>
     </row>
     <row r="32" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="20" t="s">
@@ -4446,16 +4559,16 @@
       <c r="E32" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="F32" s="68" t="s">
+      <c r="F32" s="72" t="s">
         <v>201</v>
       </c>
-      <c r="G32" s="70"/>
-      <c r="H32" s="70"/>
-      <c r="I32" s="70"/>
-      <c r="J32" s="70"/>
-      <c r="K32" s="70"/>
-      <c r="L32" s="70"/>
-      <c r="M32" s="71"/>
+      <c r="G32" s="79"/>
+      <c r="H32" s="79"/>
+      <c r="I32" s="79"/>
+      <c r="J32" s="79"/>
+      <c r="K32" s="79"/>
+      <c r="L32" s="79"/>
+      <c r="M32" s="80"/>
     </row>
     <row r="33" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="20" t="s">
@@ -4471,12 +4584,12 @@
       <c r="G33" s="28"/>
       <c r="H33" s="28"/>
       <c r="I33" s="29"/>
-      <c r="J33" s="68" t="s">
+      <c r="J33" s="72" t="s">
         <v>202</v>
       </c>
-      <c r="K33" s="70"/>
-      <c r="L33" s="70"/>
-      <c r="M33" s="71"/>
+      <c r="K33" s="79"/>
+      <c r="L33" s="79"/>
+      <c r="M33" s="80"/>
     </row>
     <row r="34" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="20" t="s">
@@ -4491,13 +4604,13 @@
       <c r="F34" s="27"/>
       <c r="G34" s="28"/>
       <c r="H34" s="29"/>
-      <c r="I34" s="68" t="s">
+      <c r="I34" s="72" t="s">
         <v>203</v>
       </c>
-      <c r="J34" s="70"/>
-      <c r="K34" s="70"/>
-      <c r="L34" s="70"/>
-      <c r="M34" s="71"/>
+      <c r="J34" s="79"/>
+      <c r="K34" s="79"/>
+      <c r="L34" s="79"/>
+      <c r="M34" s="80"/>
     </row>
     <row r="35" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="20" t="s">
@@ -4550,12 +4663,12 @@
       <c r="I36" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="J36" s="68" t="s">
+      <c r="J36" s="72" t="s">
         <v>204</v>
       </c>
-      <c r="K36" s="70"/>
-      <c r="L36" s="70"/>
-      <c r="M36" s="71"/>
+      <c r="K36" s="79"/>
+      <c r="L36" s="79"/>
+      <c r="M36" s="80"/>
     </row>
     <row r="37" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="20" t="s">
@@ -4573,12 +4686,12 @@
       <c r="I37" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="J37" s="68" t="s">
+      <c r="J37" s="72" t="s">
         <v>204</v>
       </c>
-      <c r="K37" s="70"/>
-      <c r="L37" s="70"/>
-      <c r="M37" s="71"/>
+      <c r="K37" s="79"/>
+      <c r="L37" s="79"/>
+      <c r="M37" s="80"/>
     </row>
     <row r="38" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="20" t="s">
@@ -4596,12 +4709,12 @@
       <c r="I38" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="J38" s="68" t="s">
+      <c r="J38" s="72" t="s">
         <v>204</v>
       </c>
-      <c r="K38" s="70"/>
-      <c r="L38" s="70"/>
-      <c r="M38" s="71"/>
+      <c r="K38" s="79"/>
+      <c r="L38" s="79"/>
+      <c r="M38" s="80"/>
     </row>
     <row r="39" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="20" t="s">
@@ -4613,16 +4726,16 @@
       <c r="E39" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="F39" s="68" t="s">
+      <c r="F39" s="72" t="s">
         <v>205</v>
       </c>
-      <c r="G39" s="70"/>
-      <c r="H39" s="70"/>
-      <c r="I39" s="70"/>
-      <c r="J39" s="70"/>
-      <c r="K39" s="70"/>
-      <c r="L39" s="70"/>
-      <c r="M39" s="71"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="79"/>
+      <c r="I39" s="79"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="79"/>
+      <c r="L39" s="79"/>
+      <c r="M39" s="80"/>
     </row>
     <row r="40" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="20" t="s">
@@ -4634,16 +4747,16 @@
       <c r="E40" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="F40" s="68" t="s">
+      <c r="F40" s="72" t="s">
         <v>206</v>
       </c>
-      <c r="G40" s="70"/>
-      <c r="H40" s="70"/>
-      <c r="I40" s="70"/>
-      <c r="J40" s="70"/>
-      <c r="K40" s="70"/>
-      <c r="L40" s="70"/>
-      <c r="M40" s="71"/>
+      <c r="G40" s="79"/>
+      <c r="H40" s="79"/>
+      <c r="I40" s="79"/>
+      <c r="J40" s="79"/>
+      <c r="K40" s="79"/>
+      <c r="L40" s="79"/>
+      <c r="M40" s="80"/>
     </row>
     <row r="41" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="20" t="s">
@@ -4659,12 +4772,12 @@
       <c r="G41" s="28"/>
       <c r="H41" s="28"/>
       <c r="I41" s="29"/>
-      <c r="J41" s="68" t="s">
+      <c r="J41" s="72" t="s">
         <v>207</v>
       </c>
-      <c r="K41" s="70"/>
-      <c r="L41" s="70"/>
-      <c r="M41" s="71"/>
+      <c r="K41" s="79"/>
+      <c r="L41" s="79"/>
+      <c r="M41" s="80"/>
     </row>
     <row r="42" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="20" t="s">
@@ -4699,12 +4812,12 @@
       <c r="G43" s="28"/>
       <c r="H43" s="28"/>
       <c r="I43" s="35"/>
-      <c r="J43" s="68" t="s">
+      <c r="J43" s="72" t="s">
         <v>135</v>
       </c>
-      <c r="K43" s="70"/>
-      <c r="L43" s="70"/>
-      <c r="M43" s="71"/>
+      <c r="K43" s="79"/>
+      <c r="L43" s="79"/>
+      <c r="M43" s="80"/>
     </row>
     <row r="44" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="21" t="s">
@@ -4999,12 +5112,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="J17:M17"/>
-    <mergeCell ref="F12:M12"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="F14:M14"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="F16:M16"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="J41:M41"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="I34:M34"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="F39:M39"/>
     <mergeCell ref="F32:M32"/>
     <mergeCell ref="I18:M18"/>
     <mergeCell ref="J20:M20"/>
@@ -5017,15 +5133,12 @@
     <mergeCell ref="J29:M29"/>
     <mergeCell ref="F30:M30"/>
     <mergeCell ref="J31:M31"/>
-    <mergeCell ref="F40:M40"/>
-    <mergeCell ref="J41:M41"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="I34:M34"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="F12:M12"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="F14:M14"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="F16:M16"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5109,16 +5222,16 @@
       <c r="E6" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="F6" s="57" t="s">
+      <c r="F6" s="73" t="s">
         <v>107</v>
       </c>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="58"/>
+      <c r="G6" s="75"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="75"/>
+      <c r="K6" s="75"/>
+      <c r="L6" s="75"/>
+      <c r="M6" s="74"/>
     </row>
     <row r="7" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C7" s="25" t="s">
@@ -5130,16 +5243,16 @@
       <c r="E7" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="F7" s="57" t="s">
+      <c r="F7" s="73" t="s">
         <v>197</v>
       </c>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="69"/>
-      <c r="J7" s="69"/>
-      <c r="K7" s="69"/>
-      <c r="L7" s="69"/>
-      <c r="M7" s="58"/>
+      <c r="G7" s="75"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="75"/>
+      <c r="L7" s="75"/>
+      <c r="M7" s="74"/>
     </row>
     <row r="8" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
@@ -5151,16 +5264,16 @@
       <c r="E8" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F8" s="57" t="s">
+      <c r="F8" s="73" t="s">
         <v>105</v>
       </c>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="58"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="75"/>
+      <c r="J8" s="75"/>
+      <c r="K8" s="75"/>
+      <c r="L8" s="75"/>
+      <c r="M8" s="74"/>
     </row>
     <row r="9" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
@@ -5172,16 +5285,16 @@
       <c r="E9" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F9" s="57" t="s">
+      <c r="F9" s="73" t="s">
         <v>198</v>
       </c>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
-      <c r="I9" s="69"/>
-      <c r="J9" s="69"/>
-      <c r="K9" s="69"/>
-      <c r="L9" s="69"/>
-      <c r="M9" s="58"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="75"/>
+      <c r="I9" s="75"/>
+      <c r="J9" s="75"/>
+      <c r="K9" s="75"/>
+      <c r="L9" s="75"/>
+      <c r="M9" s="74"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B19" t="s">
@@ -5243,12 +5356,12 @@
       <c r="I21" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="J21" s="57" t="s">
+      <c r="J21" s="73" t="s">
         <v>124</v>
       </c>
-      <c r="K21" s="69"/>
-      <c r="L21" s="69"/>
-      <c r="M21" s="58"/>
+      <c r="K21" s="75"/>
+      <c r="L21" s="75"/>
+      <c r="M21" s="74"/>
     </row>
     <row r="22" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="20" t="s">
@@ -5270,12 +5383,12 @@
       <c r="I22" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="J22" s="57" t="s">
+      <c r="J22" s="73" t="s">
         <v>124</v>
       </c>
-      <c r="K22" s="69"/>
-      <c r="L22" s="69"/>
-      <c r="M22" s="58"/>
+      <c r="K22" s="75"/>
+      <c r="L22" s="75"/>
+      <c r="M22" s="74"/>
     </row>
     <row r="23" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="20" t="s">
@@ -5285,18 +5398,18 @@
         <v>46</v>
       </c>
       <c r="E23" s="6"/>
-      <c r="F23" s="57" t="s">
+      <c r="F23" s="73" t="s">
         <v>125</v>
       </c>
-      <c r="G23" s="58"/>
-      <c r="H23" s="57" t="s">
+      <c r="G23" s="74"/>
+      <c r="H23" s="73" t="s">
         <v>126</v>
       </c>
-      <c r="I23" s="69"/>
-      <c r="J23" s="69"/>
-      <c r="K23" s="69"/>
-      <c r="L23" s="69"/>
-      <c r="M23" s="58"/>
+      <c r="I23" s="75"/>
+      <c r="J23" s="75"/>
+      <c r="K23" s="75"/>
+      <c r="L23" s="75"/>
+      <c r="M23" s="74"/>
     </row>
     <row r="24" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="20" t="s">
@@ -5306,10 +5419,10 @@
         <v>46</v>
       </c>
       <c r="E24" s="6"/>
-      <c r="F24" s="57" t="s">
+      <c r="F24" s="73" t="s">
         <v>125</v>
       </c>
-      <c r="G24" s="58"/>
+      <c r="G24" s="74"/>
       <c r="H24" s="19"/>
       <c r="I24" s="12" t="s">
         <v>129</v>
@@ -5317,11 +5430,11 @@
       <c r="J24" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="K24" s="57" t="s">
+      <c r="K24" s="73" t="s">
         <v>127</v>
       </c>
-      <c r="L24" s="69"/>
-      <c r="M24" s="58"/>
+      <c r="L24" s="75"/>
+      <c r="M24" s="74"/>
     </row>
     <row r="25" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="20" t="s">
@@ -5331,18 +5444,18 @@
         <v>46</v>
       </c>
       <c r="E25" s="6"/>
-      <c r="F25" s="57" t="s">
+      <c r="F25" s="73" t="s">
         <v>130</v>
       </c>
-      <c r="G25" s="69"/>
-      <c r="H25" s="69"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="57" t="s">
+      <c r="G25" s="75"/>
+      <c r="H25" s="75"/>
+      <c r="I25" s="74"/>
+      <c r="J25" s="73" t="s">
         <v>131</v>
       </c>
-      <c r="K25" s="69"/>
-      <c r="L25" s="69"/>
-      <c r="M25" s="58"/>
+      <c r="K25" s="75"/>
+      <c r="L25" s="75"/>
+      <c r="M25" s="74"/>
     </row>
     <row r="26" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="20" t="s">
@@ -5352,18 +5465,18 @@
         <v>46</v>
       </c>
       <c r="E26" s="6"/>
-      <c r="F26" s="57" t="s">
+      <c r="F26" s="73" t="s">
         <v>130</v>
       </c>
-      <c r="G26" s="69"/>
-      <c r="H26" s="69"/>
-      <c r="I26" s="58"/>
-      <c r="J26" s="57" t="s">
+      <c r="G26" s="75"/>
+      <c r="H26" s="75"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="73" t="s">
         <v>131</v>
       </c>
-      <c r="K26" s="69"/>
-      <c r="L26" s="69"/>
-      <c r="M26" s="58"/>
+      <c r="K26" s="75"/>
+      <c r="L26" s="75"/>
+      <c r="M26" s="74"/>
     </row>
     <row r="27" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="20" t="s">
@@ -5373,18 +5486,18 @@
         <v>46</v>
       </c>
       <c r="E27" s="6"/>
-      <c r="F27" s="57" t="s">
+      <c r="F27" s="73" t="s">
         <v>132</v>
       </c>
-      <c r="G27" s="69"/>
-      <c r="H27" s="69"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="57" t="s">
+      <c r="G27" s="75"/>
+      <c r="H27" s="75"/>
+      <c r="I27" s="74"/>
+      <c r="J27" s="73" t="s">
         <v>133</v>
       </c>
-      <c r="K27" s="69"/>
-      <c r="L27" s="69"/>
-      <c r="M27" s="58"/>
+      <c r="K27" s="75"/>
+      <c r="L27" s="75"/>
+      <c r="M27" s="74"/>
     </row>
     <row r="28" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C28" s="20" t="s">
@@ -5394,18 +5507,18 @@
         <v>46</v>
       </c>
       <c r="E28" s="6"/>
-      <c r="F28" s="57" t="s">
+      <c r="F28" s="73" t="s">
         <v>132</v>
       </c>
-      <c r="G28" s="69"/>
-      <c r="H28" s="69"/>
-      <c r="I28" s="58"/>
-      <c r="J28" s="57" t="s">
+      <c r="G28" s="75"/>
+      <c r="H28" s="75"/>
+      <c r="I28" s="74"/>
+      <c r="J28" s="73" t="s">
         <v>133</v>
       </c>
-      <c r="K28" s="69"/>
-      <c r="L28" s="69"/>
-      <c r="M28" s="58"/>
+      <c r="K28" s="75"/>
+      <c r="L28" s="75"/>
+      <c r="M28" s="74"/>
     </row>
     <row r="29" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="20" t="s">
@@ -5459,16 +5572,16 @@
       <c r="E31" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="F31" s="57" t="s">
+      <c r="F31" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="G31" s="69"/>
-      <c r="H31" s="69"/>
-      <c r="I31" s="69"/>
-      <c r="J31" s="69"/>
-      <c r="K31" s="69"/>
-      <c r="L31" s="69"/>
-      <c r="M31" s="58"/>
+      <c r="G31" s="75"/>
+      <c r="H31" s="75"/>
+      <c r="I31" s="75"/>
+      <c r="J31" s="75"/>
+      <c r="K31" s="75"/>
+      <c r="L31" s="75"/>
+      <c r="M31" s="74"/>
     </row>
     <row r="32" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="20" t="s">
@@ -5478,16 +5591,16 @@
         <v>46</v>
       </c>
       <c r="E32" s="6"/>
-      <c r="F32" s="57" t="s">
+      <c r="F32" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="G32" s="69"/>
-      <c r="H32" s="69"/>
-      <c r="I32" s="69"/>
-      <c r="J32" s="69"/>
-      <c r="K32" s="69"/>
-      <c r="L32" s="69"/>
-      <c r="M32" s="58"/>
+      <c r="G32" s="75"/>
+      <c r="H32" s="75"/>
+      <c r="I32" s="75"/>
+      <c r="J32" s="75"/>
+      <c r="K32" s="75"/>
+      <c r="L32" s="75"/>
+      <c r="M32" s="74"/>
     </row>
     <row r="33" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="20" t="s">
@@ -5497,16 +5610,16 @@
         <v>46</v>
       </c>
       <c r="E33" s="6"/>
-      <c r="F33" s="57" t="s">
+      <c r="F33" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="G33" s="69"/>
-      <c r="H33" s="69"/>
-      <c r="I33" s="69"/>
-      <c r="J33" s="69"/>
-      <c r="K33" s="69"/>
-      <c r="L33" s="69"/>
-      <c r="M33" s="58"/>
+      <c r="G33" s="75"/>
+      <c r="H33" s="75"/>
+      <c r="I33" s="75"/>
+      <c r="J33" s="75"/>
+      <c r="K33" s="75"/>
+      <c r="L33" s="75"/>
+      <c r="M33" s="74"/>
     </row>
     <row r="34" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="20" t="s">
@@ -5516,16 +5629,16 @@
         <v>46</v>
       </c>
       <c r="E34" s="6"/>
-      <c r="F34" s="57" t="s">
+      <c r="F34" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="G34" s="69"/>
-      <c r="H34" s="69"/>
-      <c r="I34" s="69"/>
-      <c r="J34" s="69"/>
-      <c r="K34" s="69"/>
-      <c r="L34" s="69"/>
-      <c r="M34" s="58"/>
+      <c r="G34" s="75"/>
+      <c r="H34" s="75"/>
+      <c r="I34" s="75"/>
+      <c r="J34" s="75"/>
+      <c r="K34" s="75"/>
+      <c r="L34" s="75"/>
+      <c r="M34" s="74"/>
     </row>
     <row r="35" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="20" t="s">
@@ -5535,16 +5648,16 @@
         <v>46</v>
       </c>
       <c r="E35" s="6"/>
-      <c r="F35" s="57" t="s">
+      <c r="F35" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="G35" s="69"/>
-      <c r="H35" s="69"/>
-      <c r="I35" s="69"/>
-      <c r="J35" s="69"/>
-      <c r="K35" s="69"/>
-      <c r="L35" s="69"/>
-      <c r="M35" s="58"/>
+      <c r="G35" s="75"/>
+      <c r="H35" s="75"/>
+      <c r="I35" s="75"/>
+      <c r="J35" s="75"/>
+      <c r="K35" s="75"/>
+      <c r="L35" s="75"/>
+      <c r="M35" s="74"/>
     </row>
     <row r="36" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C36" s="20" t="s">
@@ -5554,16 +5667,16 @@
         <v>46</v>
       </c>
       <c r="E36" s="6"/>
-      <c r="F36" s="57" t="s">
+      <c r="F36" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="G36" s="69"/>
-      <c r="H36" s="69"/>
-      <c r="I36" s="69"/>
-      <c r="J36" s="69"/>
-      <c r="K36" s="69"/>
-      <c r="L36" s="69"/>
-      <c r="M36" s="58"/>
+      <c r="G36" s="75"/>
+      <c r="H36" s="75"/>
+      <c r="I36" s="75"/>
+      <c r="J36" s="75"/>
+      <c r="K36" s="75"/>
+      <c r="L36" s="75"/>
+      <c r="M36" s="74"/>
     </row>
     <row r="37" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="20" t="s">
@@ -5573,16 +5686,16 @@
         <v>41</v>
       </c>
       <c r="E37" s="1"/>
-      <c r="F37" s="57" t="s">
+      <c r="F37" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="G37" s="69"/>
-      <c r="H37" s="69"/>
-      <c r="I37" s="69"/>
-      <c r="J37" s="69"/>
-      <c r="K37" s="69"/>
-      <c r="L37" s="69"/>
-      <c r="M37" s="58"/>
+      <c r="G37" s="75"/>
+      <c r="H37" s="75"/>
+      <c r="I37" s="75"/>
+      <c r="J37" s="75"/>
+      <c r="K37" s="75"/>
+      <c r="L37" s="75"/>
+      <c r="M37" s="74"/>
     </row>
     <row r="38" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="20" t="s">
@@ -5592,16 +5705,16 @@
         <v>41</v>
       </c>
       <c r="E38" s="1"/>
-      <c r="F38" s="57" t="s">
+      <c r="F38" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="G38" s="69"/>
-      <c r="H38" s="69"/>
-      <c r="I38" s="69"/>
-      <c r="J38" s="69"/>
-      <c r="K38" s="69"/>
-      <c r="L38" s="69"/>
-      <c r="M38" s="58"/>
+      <c r="G38" s="75"/>
+      <c r="H38" s="75"/>
+      <c r="I38" s="75"/>
+      <c r="J38" s="75"/>
+      <c r="K38" s="75"/>
+      <c r="L38" s="75"/>
+      <c r="M38" s="74"/>
     </row>
     <row r="39" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="20" t="s">
@@ -5611,16 +5724,16 @@
         <v>41</v>
       </c>
       <c r="E39" s="1"/>
-      <c r="F39" s="57" t="s">
+      <c r="F39" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="G39" s="69"/>
-      <c r="H39" s="69"/>
-      <c r="I39" s="69"/>
-      <c r="J39" s="69"/>
-      <c r="K39" s="69"/>
-      <c r="L39" s="69"/>
-      <c r="M39" s="58"/>
+      <c r="G39" s="75"/>
+      <c r="H39" s="75"/>
+      <c r="I39" s="75"/>
+      <c r="J39" s="75"/>
+      <c r="K39" s="75"/>
+      <c r="L39" s="75"/>
+      <c r="M39" s="74"/>
     </row>
     <row r="40" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="20" t="s">
@@ -5630,16 +5743,16 @@
         <v>41</v>
       </c>
       <c r="E40" s="1"/>
-      <c r="F40" s="57" t="s">
+      <c r="F40" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="G40" s="69"/>
-      <c r="H40" s="69"/>
-      <c r="I40" s="69"/>
-      <c r="J40" s="69"/>
-      <c r="K40" s="69"/>
-      <c r="L40" s="69"/>
-      <c r="M40" s="58"/>
+      <c r="G40" s="75"/>
+      <c r="H40" s="75"/>
+      <c r="I40" s="75"/>
+      <c r="J40" s="75"/>
+      <c r="K40" s="75"/>
+      <c r="L40" s="75"/>
+      <c r="M40" s="74"/>
     </row>
     <row r="41" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="20" t="s">
@@ -5674,11 +5787,11 @@
       <c r="I42" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J42" s="57" t="s">
+      <c r="J42" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="K42" s="69"/>
-      <c r="L42" s="58"/>
+      <c r="K42" s="75"/>
+      <c r="L42" s="74"/>
       <c r="M42" s="14" t="s">
         <v>160</v>
       </c>
@@ -5699,11 +5812,11 @@
       <c r="I43" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J43" s="57" t="s">
+      <c r="J43" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="K43" s="69"/>
-      <c r="L43" s="58"/>
+      <c r="K43" s="75"/>
+      <c r="L43" s="74"/>
       <c r="M43" s="14" t="s">
         <v>160</v>
       </c>
@@ -5724,11 +5837,11 @@
       <c r="I44" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J44" s="57" t="s">
+      <c r="J44" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="K44" s="69"/>
-      <c r="L44" s="58"/>
+      <c r="K44" s="75"/>
+      <c r="L44" s="74"/>
       <c r="M44" s="14" t="s">
         <v>160</v>
       </c>
@@ -5749,11 +5862,11 @@
       <c r="I45" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J45" s="57" t="s">
+      <c r="J45" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="K45" s="69"/>
-      <c r="L45" s="58"/>
+      <c r="K45" s="75"/>
+      <c r="L45" s="74"/>
       <c r="M45" s="14" t="s">
         <v>160</v>
       </c>
@@ -5774,11 +5887,11 @@
       <c r="I46" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J46" s="57" t="s">
+      <c r="J46" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="K46" s="69"/>
-      <c r="L46" s="58"/>
+      <c r="K46" s="75"/>
+      <c r="L46" s="74"/>
       <c r="M46" s="14" t="s">
         <v>160</v>
       </c>
@@ -5799,11 +5912,11 @@
       <c r="I47" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J47" s="57" t="s">
+      <c r="J47" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="K47" s="69"/>
-      <c r="L47" s="58"/>
+      <c r="K47" s="75"/>
+      <c r="L47" s="74"/>
       <c r="M47" s="14" t="s">
         <v>160</v>
       </c>
@@ -5824,11 +5937,11 @@
       <c r="I48" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J48" s="57" t="s">
+      <c r="J48" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="K48" s="69"/>
-      <c r="L48" s="58"/>
+      <c r="K48" s="75"/>
+      <c r="L48" s="74"/>
       <c r="M48" s="14" t="s">
         <v>160</v>
       </c>
@@ -5849,11 +5962,11 @@
       <c r="I49" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J49" s="57" t="s">
+      <c r="J49" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="K49" s="69"/>
-      <c r="L49" s="58"/>
+      <c r="K49" s="75"/>
+      <c r="L49" s="74"/>
       <c r="M49" s="14" t="s">
         <v>160</v>
       </c>
@@ -5874,11 +5987,11 @@
       <c r="I50" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J50" s="57" t="s">
+      <c r="J50" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="K50" s="69"/>
-      <c r="L50" s="58"/>
+      <c r="K50" s="75"/>
+      <c r="L50" s="74"/>
       <c r="M50" s="14" t="s">
         <v>160</v>
       </c>
@@ -5908,18 +6021,18 @@
         <v>41</v>
       </c>
       <c r="E52" s="1"/>
-      <c r="F52" s="57" t="s">
+      <c r="F52" s="73" t="s">
         <v>181</v>
       </c>
-      <c r="G52" s="69"/>
-      <c r="H52" s="69"/>
-      <c r="I52" s="58"/>
-      <c r="J52" s="57" t="s">
+      <c r="G52" s="75"/>
+      <c r="H52" s="75"/>
+      <c r="I52" s="74"/>
+      <c r="J52" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="K52" s="69"/>
-      <c r="L52" s="69"/>
-      <c r="M52" s="58"/>
+      <c r="K52" s="75"/>
+      <c r="L52" s="75"/>
+      <c r="M52" s="74"/>
     </row>
     <row r="53" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="21" t="s">
@@ -5929,18 +6042,18 @@
         <v>96</v>
       </c>
       <c r="E53" s="13"/>
-      <c r="F53" s="57" t="s">
+      <c r="F53" s="73" t="s">
         <v>181</v>
       </c>
-      <c r="G53" s="69"/>
-      <c r="H53" s="69"/>
-      <c r="I53" s="58"/>
-      <c r="J53" s="57" t="s">
+      <c r="G53" s="75"/>
+      <c r="H53" s="75"/>
+      <c r="I53" s="74"/>
+      <c r="J53" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="K53" s="69"/>
-      <c r="L53" s="69"/>
-      <c r="M53" s="58"/>
+      <c r="K53" s="75"/>
+      <c r="L53" s="75"/>
+      <c r="M53" s="74"/>
     </row>
     <row r="54" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="20" t="s">
@@ -5950,18 +6063,18 @@
         <v>41</v>
       </c>
       <c r="E54" s="1"/>
-      <c r="F54" s="57" t="s">
+      <c r="F54" s="73" t="s">
         <v>181</v>
       </c>
-      <c r="G54" s="69"/>
-      <c r="H54" s="69"/>
-      <c r="I54" s="58"/>
-      <c r="J54" s="57" t="s">
+      <c r="G54" s="75"/>
+      <c r="H54" s="75"/>
+      <c r="I54" s="74"/>
+      <c r="J54" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="K54" s="69"/>
-      <c r="L54" s="69"/>
-      <c r="M54" s="58"/>
+      <c r="K54" s="75"/>
+      <c r="L54" s="75"/>
+      <c r="M54" s="74"/>
     </row>
     <row r="55" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C55" s="20" t="s">
@@ -5971,18 +6084,18 @@
         <v>41</v>
       </c>
       <c r="E55" s="1"/>
-      <c r="F55" s="57" t="s">
+      <c r="F55" s="73" t="s">
         <v>181</v>
       </c>
-      <c r="G55" s="69"/>
-      <c r="H55" s="69"/>
-      <c r="I55" s="58"/>
-      <c r="J55" s="57" t="s">
+      <c r="G55" s="75"/>
+      <c r="H55" s="75"/>
+      <c r="I55" s="74"/>
+      <c r="J55" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="K55" s="69"/>
-      <c r="L55" s="69"/>
-      <c r="M55" s="58"/>
+      <c r="K55" s="75"/>
+      <c r="L55" s="75"/>
+      <c r="M55" s="74"/>
     </row>
     <row r="56" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="20" t="s">
@@ -5992,18 +6105,18 @@
         <v>41</v>
       </c>
       <c r="E56" s="1"/>
-      <c r="F56" s="57" t="s">
+      <c r="F56" s="73" t="s">
         <v>181</v>
       </c>
-      <c r="G56" s="69"/>
-      <c r="H56" s="69"/>
-      <c r="I56" s="58"/>
-      <c r="J56" s="57" t="s">
+      <c r="G56" s="75"/>
+      <c r="H56" s="75"/>
+      <c r="I56" s="74"/>
+      <c r="J56" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="K56" s="69"/>
-      <c r="L56" s="69"/>
-      <c r="M56" s="58"/>
+      <c r="K56" s="75"/>
+      <c r="L56" s="75"/>
+      <c r="M56" s="74"/>
     </row>
     <row r="57" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C57" s="20" t="s">
@@ -6013,18 +6126,18 @@
         <v>41</v>
       </c>
       <c r="E57" s="1"/>
-      <c r="F57" s="57" t="s">
+      <c r="F57" s="73" t="s">
         <v>181</v>
       </c>
-      <c r="G57" s="69"/>
-      <c r="H57" s="69"/>
-      <c r="I57" s="58"/>
-      <c r="J57" s="57" t="s">
+      <c r="G57" s="75"/>
+      <c r="H57" s="75"/>
+      <c r="I57" s="74"/>
+      <c r="J57" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="K57" s="69"/>
-      <c r="L57" s="69"/>
-      <c r="M57" s="58"/>
+      <c r="K57" s="75"/>
+      <c r="L57" s="75"/>
+      <c r="M57" s="74"/>
     </row>
     <row r="58" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C58" s="20" t="s">
@@ -6034,18 +6147,18 @@
         <v>41</v>
       </c>
       <c r="E58" s="1"/>
-      <c r="F58" s="57" t="s">
+      <c r="F58" s="73" t="s">
         <v>181</v>
       </c>
-      <c r="G58" s="69"/>
-      <c r="H58" s="69"/>
-      <c r="I58" s="58"/>
-      <c r="J58" s="57" t="s">
+      <c r="G58" s="75"/>
+      <c r="H58" s="75"/>
+      <c r="I58" s="74"/>
+      <c r="J58" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="K58" s="69"/>
-      <c r="L58" s="69"/>
-      <c r="M58" s="58"/>
+      <c r="K58" s="75"/>
+      <c r="L58" s="75"/>
+      <c r="M58" s="74"/>
     </row>
     <row r="59" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C59" s="20" t="s">
@@ -6055,18 +6168,18 @@
         <v>41</v>
       </c>
       <c r="E59" s="1"/>
-      <c r="F59" s="57" t="s">
+      <c r="F59" s="73" t="s">
         <v>181</v>
       </c>
-      <c r="G59" s="69"/>
-      <c r="H59" s="69"/>
-      <c r="I59" s="58"/>
-      <c r="J59" s="57" t="s">
+      <c r="G59" s="75"/>
+      <c r="H59" s="75"/>
+      <c r="I59" s="74"/>
+      <c r="J59" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="K59" s="69"/>
-      <c r="L59" s="69"/>
-      <c r="M59" s="58"/>
+      <c r="K59" s="75"/>
+      <c r="L59" s="75"/>
+      <c r="M59" s="74"/>
     </row>
     <row r="60" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C60" s="20" t="s">
@@ -6076,18 +6189,18 @@
         <v>41</v>
       </c>
       <c r="E60" s="1"/>
-      <c r="F60" s="57" t="s">
+      <c r="F60" s="73" t="s">
         <v>181</v>
       </c>
-      <c r="G60" s="69"/>
-      <c r="H60" s="69"/>
-      <c r="I60" s="58"/>
-      <c r="J60" s="57" t="s">
+      <c r="G60" s="75"/>
+      <c r="H60" s="75"/>
+      <c r="I60" s="74"/>
+      <c r="J60" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="K60" s="69"/>
-      <c r="L60" s="69"/>
-      <c r="M60" s="58"/>
+      <c r="K60" s="75"/>
+      <c r="L60" s="75"/>
+      <c r="M60" s="74"/>
     </row>
     <row r="61" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C61" s="20" t="s">
@@ -6122,10 +6235,10 @@
       <c r="I62" s="10"/>
       <c r="J62" s="10"/>
       <c r="K62" s="11"/>
-      <c r="L62" s="68" t="s">
+      <c r="L62" s="72" t="s">
         <v>193</v>
       </c>
-      <c r="M62" s="64"/>
+      <c r="M62" s="65"/>
     </row>
     <row r="63" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C63" s="20" t="s">
@@ -6143,10 +6256,10 @@
       <c r="I63" s="10"/>
       <c r="J63" s="10"/>
       <c r="K63" s="11"/>
-      <c r="L63" s="62" t="s">
+      <c r="L63" s="63" t="s">
         <v>193</v>
       </c>
-      <c r="M63" s="64"/>
+      <c r="M63" s="65"/>
     </row>
     <row r="64" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C64" s="20" t="s">
@@ -6164,10 +6277,10 @@
       <c r="I64" s="10"/>
       <c r="J64" s="10"/>
       <c r="K64" s="11"/>
-      <c r="L64" s="62" t="s">
+      <c r="L64" s="63" t="s">
         <v>193</v>
       </c>
-      <c r="M64" s="64"/>
+      <c r="M64" s="65"/>
     </row>
     <row r="65" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C65" s="20" t="s">
@@ -6185,10 +6298,10 @@
       <c r="I65" s="10"/>
       <c r="J65" s="10"/>
       <c r="K65" s="11"/>
-      <c r="L65" s="62" t="s">
+      <c r="L65" s="63" t="s">
         <v>193</v>
       </c>
-      <c r="M65" s="64"/>
+      <c r="M65" s="65"/>
     </row>
     <row r="66" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C66" s="20" t="s">
@@ -6206,10 +6319,10 @@
       <c r="I66" s="10"/>
       <c r="J66" s="10"/>
       <c r="K66" s="11"/>
-      <c r="L66" s="62" t="s">
+      <c r="L66" s="63" t="s">
         <v>193</v>
       </c>
-      <c r="M66" s="64"/>
+      <c r="M66" s="65"/>
     </row>
     <row r="67" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C67" s="20" t="s">
@@ -6227,10 +6340,10 @@
       <c r="I67" s="10"/>
       <c r="J67" s="10"/>
       <c r="K67" s="11"/>
-      <c r="L67" s="62" t="s">
+      <c r="L67" s="63" t="s">
         <v>193</v>
       </c>
-      <c r="M67" s="64"/>
+      <c r="M67" s="65"/>
     </row>
     <row r="68" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C68" s="20" t="s">
@@ -6248,10 +6361,10 @@
       <c r="I68" s="10"/>
       <c r="J68" s="10"/>
       <c r="K68" s="11"/>
-      <c r="L68" s="62" t="s">
+      <c r="L68" s="63" t="s">
         <v>193</v>
       </c>
-      <c r="M68" s="64"/>
+      <c r="M68" s="65"/>
     </row>
     <row r="69" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C69" s="20" t="s">
@@ -6269,10 +6382,10 @@
       <c r="I69" s="10"/>
       <c r="J69" s="10"/>
       <c r="K69" s="11"/>
-      <c r="L69" s="62" t="s">
+      <c r="L69" s="63" t="s">
         <v>193</v>
       </c>
-      <c r="M69" s="64"/>
+      <c r="M69" s="65"/>
     </row>
     <row r="70" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C70" s="20" t="s">
@@ -6290,10 +6403,10 @@
       <c r="I70" s="10"/>
       <c r="J70" s="10"/>
       <c r="K70" s="11"/>
-      <c r="L70" s="62" t="s">
+      <c r="L70" s="63" t="s">
         <v>193</v>
       </c>
-      <c r="M70" s="64"/>
+      <c r="M70" s="65"/>
     </row>
     <row r="71" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C71" s="20" t="s">
@@ -6314,54 +6427,6 @@
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F34:M34"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="F28:I28"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="F31:M31"/>
-    <mergeCell ref="F32:M32"/>
-    <mergeCell ref="F33:M33"/>
-    <mergeCell ref="J47:L47"/>
-    <mergeCell ref="F35:M35"/>
-    <mergeCell ref="F36:M36"/>
-    <mergeCell ref="F37:M37"/>
-    <mergeCell ref="F38:M38"/>
-    <mergeCell ref="F39:M39"/>
-    <mergeCell ref="F40:M40"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="J44:L44"/>
-    <mergeCell ref="J45:L45"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="J56:M56"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="J52:M52"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="J53:M53"/>
-    <mergeCell ref="L67:M67"/>
-    <mergeCell ref="L68:M68"/>
-    <mergeCell ref="L69:M69"/>
-    <mergeCell ref="L70:M70"/>
-    <mergeCell ref="F60:I60"/>
-    <mergeCell ref="J60:M60"/>
-    <mergeCell ref="L62:M62"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="L64:M64"/>
-    <mergeCell ref="L65:M65"/>
     <mergeCell ref="F6:M6"/>
     <mergeCell ref="F7:M7"/>
     <mergeCell ref="F8:M8"/>
@@ -6378,6 +6443,54 @@
     <mergeCell ref="F55:I55"/>
     <mergeCell ref="J55:M55"/>
     <mergeCell ref="F56:I56"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="L69:M69"/>
+    <mergeCell ref="L70:M70"/>
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="J60:M60"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="L64:M64"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="J56:M56"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="J52:M52"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="J53:M53"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="F35:M35"/>
+    <mergeCell ref="F36:M36"/>
+    <mergeCell ref="F37:M37"/>
+    <mergeCell ref="F38:M38"/>
+    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="F34:M34"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="F28:I28"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="F31:M31"/>
+    <mergeCell ref="F32:M32"/>
+    <mergeCell ref="F33:M33"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="F24:G24"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6386,10 +6499,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC57A460-A3F1-420B-B8CC-FFCC94C867CA}">
-  <dimension ref="B2:M54"/>
+  <dimension ref="B2:M56"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="5" max="5" width="39.75" customWidth="1"/>
+    <col min="2" max="2" width="5.875" customWidth="1"/>
+    <col min="3" max="3" width="6.75" customWidth="1"/>
+    <col min="4" max="4" width="5" customWidth="1"/>
+    <col min="5" max="5" width="26.75" customWidth="1"/>
     <col min="6" max="13" width="4.75" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6519,16 +6635,16 @@
       <c r="E14" s="45" t="s">
         <v>134</v>
       </c>
-      <c r="F14" s="59" t="s">
+      <c r="F14" s="60" t="s">
         <v>134</v>
       </c>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="60"/>
-      <c r="J14" s="60"/>
-      <c r="K14" s="60"/>
-      <c r="L14" s="60"/>
-      <c r="M14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="61"/>
+      <c r="L14" s="61"/>
+      <c r="M14" s="62"/>
     </row>
     <row r="15" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="20" t="s">
@@ -6540,16 +6656,16 @@
       <c r="E15" s="45" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="59" t="s">
+      <c r="F15" s="60" t="s">
         <v>245</v>
       </c>
-      <c r="G15" s="60"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="60"/>
-      <c r="K15" s="60"/>
-      <c r="L15" s="60"/>
-      <c r="M15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="61"/>
+      <c r="K15" s="61"/>
+      <c r="L15" s="61"/>
+      <c r="M15" s="62"/>
     </row>
     <row r="16" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="20" t="s">
@@ -6561,16 +6677,16 @@
       <c r="E16" s="44" t="s">
         <v>246</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="60" t="s">
         <v>246</v>
       </c>
-      <c r="G16" s="60"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="60"/>
-      <c r="K16" s="60"/>
-      <c r="L16" s="60"/>
-      <c r="M16" s="61"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="61"/>
+      <c r="K16" s="61"/>
+      <c r="L16" s="61"/>
+      <c r="M16" s="62"/>
     </row>
     <row r="17" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="20" t="s">
@@ -6589,10 +6705,10 @@
       <c r="H17" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="I17" s="47" t="s">
+      <c r="I17" s="59" t="s">
         <v>250</v>
       </c>
-      <c r="J17" s="47" t="s">
+      <c r="J17" s="59" t="s">
         <v>251</v>
       </c>
       <c r="K17" s="46"/>
@@ -6649,24 +6765,24 @@
         <v>46</v>
       </c>
       <c r="E20" s="45"/>
-      <c r="F20" s="47" t="s">
+      <c r="F20" s="59" t="s">
         <v>256</v>
       </c>
-      <c r="G20" s="47" t="s">
+      <c r="G20" s="59" t="s">
         <v>257</v>
       </c>
-      <c r="H20" s="47" t="s">
+      <c r="H20" s="59" t="s">
         <v>258</v>
       </c>
-      <c r="I20" s="47" t="s">
+      <c r="I20" s="59" t="s">
         <v>259</v>
       </c>
-      <c r="J20" s="47" t="s">
+      <c r="J20" s="59" t="s">
         <v>260</v>
       </c>
       <c r="K20" s="81"/>
       <c r="L20" s="83"/>
-      <c r="M20" s="47" t="s">
+      <c r="M20" s="59" t="s">
         <v>261</v>
       </c>
     </row>
@@ -6686,16 +6802,16 @@
       </c>
       <c r="H21" s="81"/>
       <c r="I21" s="83"/>
-      <c r="J21" s="47" t="s">
+      <c r="J21" s="59" t="s">
         <v>264</v>
       </c>
-      <c r="K21" s="47" t="s">
+      <c r="K21" s="59" t="s">
         <v>265</v>
       </c>
-      <c r="L21" s="47" t="s">
+      <c r="L21" s="59" t="s">
         <v>266</v>
       </c>
-      <c r="M21" s="47" t="s">
+      <c r="M21" s="59" t="s">
         <v>267</v>
       </c>
     </row>
@@ -6707,16 +6823,16 @@
         <v>46</v>
       </c>
       <c r="E22" s="45"/>
-      <c r="F22" s="59" t="s">
+      <c r="F22" s="84" t="s">
         <v>268</v>
       </c>
-      <c r="G22" s="60"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="60"/>
-      <c r="J22" s="60"/>
-      <c r="K22" s="60"/>
-      <c r="L22" s="60"/>
-      <c r="M22" s="61"/>
+      <c r="G22" s="85"/>
+      <c r="H22" s="85"/>
+      <c r="I22" s="85"/>
+      <c r="J22" s="85"/>
+      <c r="K22" s="85"/>
+      <c r="L22" s="85"/>
+      <c r="M22" s="86"/>
     </row>
     <row r="23" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="20" t="s">
@@ -6726,16 +6842,16 @@
         <v>46</v>
       </c>
       <c r="E23" s="44"/>
-      <c r="F23" s="59" t="s">
+      <c r="F23" s="84" t="s">
         <v>269</v>
       </c>
-      <c r="G23" s="60"/>
-      <c r="H23" s="60"/>
-      <c r="I23" s="60"/>
-      <c r="J23" s="60"/>
-      <c r="K23" s="60"/>
-      <c r="L23" s="60"/>
-      <c r="M23" s="61"/>
+      <c r="G23" s="85"/>
+      <c r="H23" s="85"/>
+      <c r="I23" s="85"/>
+      <c r="J23" s="85"/>
+      <c r="K23" s="85"/>
+      <c r="L23" s="85"/>
+      <c r="M23" s="86"/>
     </row>
     <row r="24" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="20" t="s">
@@ -6745,16 +6861,16 @@
         <v>46</v>
       </c>
       <c r="E24" s="44"/>
-      <c r="F24" s="59" t="s">
+      <c r="F24" s="84" t="s">
         <v>270</v>
       </c>
-      <c r="G24" s="60"/>
-      <c r="H24" s="60"/>
-      <c r="I24" s="60"/>
-      <c r="J24" s="60"/>
-      <c r="K24" s="60"/>
-      <c r="L24" s="60"/>
-      <c r="M24" s="61"/>
+      <c r="G24" s="85"/>
+      <c r="H24" s="85"/>
+      <c r="I24" s="85"/>
+      <c r="J24" s="85"/>
+      <c r="K24" s="85"/>
+      <c r="L24" s="85"/>
+      <c r="M24" s="86"/>
     </row>
     <row r="25" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="20" t="s">
@@ -6764,16 +6880,16 @@
         <v>46</v>
       </c>
       <c r="E25" s="44"/>
-      <c r="F25" s="59" t="s">
+      <c r="F25" s="84" t="s">
         <v>271</v>
       </c>
-      <c r="G25" s="60"/>
-      <c r="H25" s="60"/>
-      <c r="I25" s="60"/>
-      <c r="J25" s="60"/>
-      <c r="K25" s="60"/>
-      <c r="L25" s="60"/>
-      <c r="M25" s="61"/>
+      <c r="G25" s="85"/>
+      <c r="H25" s="85"/>
+      <c r="I25" s="85"/>
+      <c r="J25" s="85"/>
+      <c r="K25" s="85"/>
+      <c r="L25" s="85"/>
+      <c r="M25" s="86"/>
     </row>
     <row r="26" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="20" t="s">
@@ -6783,16 +6899,16 @@
         <v>46</v>
       </c>
       <c r="E26" s="44"/>
-      <c r="F26" s="59" t="s">
+      <c r="F26" s="84" t="s">
         <v>272</v>
       </c>
-      <c r="G26" s="60"/>
-      <c r="H26" s="60"/>
-      <c r="I26" s="60"/>
-      <c r="J26" s="60"/>
-      <c r="K26" s="60"/>
-      <c r="L26" s="60"/>
-      <c r="M26" s="61"/>
+      <c r="G26" s="85"/>
+      <c r="H26" s="85"/>
+      <c r="I26" s="85"/>
+      <c r="J26" s="85"/>
+      <c r="K26" s="85"/>
+      <c r="L26" s="85"/>
+      <c r="M26" s="86"/>
     </row>
     <row r="27" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="20" t="s">
@@ -6802,35 +6918,35 @@
         <v>46</v>
       </c>
       <c r="E27" s="44"/>
-      <c r="F27" s="59" t="s">
+      <c r="F27" s="84" t="s">
         <v>273</v>
       </c>
-      <c r="G27" s="60"/>
-      <c r="H27" s="60"/>
-      <c r="I27" s="60"/>
-      <c r="J27" s="60"/>
-      <c r="K27" s="60"/>
-      <c r="L27" s="60"/>
-      <c r="M27" s="61"/>
+      <c r="G27" s="85"/>
+      <c r="H27" s="85"/>
+      <c r="I27" s="85"/>
+      <c r="J27" s="85"/>
+      <c r="K27" s="85"/>
+      <c r="L27" s="85"/>
+      <c r="M27" s="86"/>
     </row>
     <row r="28" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C28" s="20" t="s">
         <v>146</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E28" s="44"/>
-      <c r="F28" s="59" t="s">
+      <c r="F28" s="84" t="s">
         <v>274</v>
       </c>
-      <c r="G28" s="60"/>
-      <c r="H28" s="60"/>
-      <c r="I28" s="60"/>
-      <c r="J28" s="60"/>
-      <c r="K28" s="60"/>
-      <c r="L28" s="60"/>
-      <c r="M28" s="61"/>
+      <c r="G28" s="85"/>
+      <c r="H28" s="85"/>
+      <c r="I28" s="85"/>
+      <c r="J28" s="85"/>
+      <c r="K28" s="85"/>
+      <c r="L28" s="85"/>
+      <c r="M28" s="86"/>
     </row>
     <row r="29" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="20" t="s">
@@ -6840,16 +6956,16 @@
         <v>46</v>
       </c>
       <c r="E29" s="44"/>
-      <c r="F29" s="59" t="s">
+      <c r="F29" s="84" t="s">
         <v>275</v>
       </c>
-      <c r="G29" s="60"/>
-      <c r="H29" s="60"/>
-      <c r="I29" s="60"/>
-      <c r="J29" s="60"/>
-      <c r="K29" s="60"/>
-      <c r="L29" s="60"/>
-      <c r="M29" s="61"/>
+      <c r="G29" s="85"/>
+      <c r="H29" s="85"/>
+      <c r="I29" s="85"/>
+      <c r="J29" s="85"/>
+      <c r="K29" s="85"/>
+      <c r="L29" s="85"/>
+      <c r="M29" s="86"/>
     </row>
     <row r="30" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="20" t="s">
@@ -6859,16 +6975,16 @@
         <v>46</v>
       </c>
       <c r="E30" s="44"/>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="84" t="s">
         <v>276</v>
       </c>
-      <c r="G30" s="60"/>
-      <c r="H30" s="60"/>
-      <c r="I30" s="60"/>
-      <c r="J30" s="60"/>
-      <c r="K30" s="60"/>
-      <c r="L30" s="60"/>
-      <c r="M30" s="61"/>
+      <c r="G30" s="85"/>
+      <c r="H30" s="85"/>
+      <c r="I30" s="85"/>
+      <c r="J30" s="85"/>
+      <c r="K30" s="85"/>
+      <c r="L30" s="85"/>
+      <c r="M30" s="86"/>
     </row>
     <row r="31" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="20" t="s">
@@ -6878,16 +6994,16 @@
         <v>46</v>
       </c>
       <c r="E31" s="44"/>
-      <c r="F31" s="59" t="s">
+      <c r="F31" s="84" t="s">
         <v>277</v>
       </c>
-      <c r="G31" s="60"/>
-      <c r="H31" s="60"/>
-      <c r="I31" s="60"/>
-      <c r="J31" s="60"/>
-      <c r="K31" s="60"/>
-      <c r="L31" s="60"/>
-      <c r="M31" s="61"/>
+      <c r="G31" s="85"/>
+      <c r="H31" s="85"/>
+      <c r="I31" s="85"/>
+      <c r="J31" s="85"/>
+      <c r="K31" s="85"/>
+      <c r="L31" s="85"/>
+      <c r="M31" s="86"/>
     </row>
     <row r="32" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="20" t="s">
@@ -6931,16 +7047,16 @@
         <v>46</v>
       </c>
       <c r="E34" s="44"/>
-      <c r="F34" s="59" t="s">
+      <c r="F34" s="84" t="s">
         <v>278</v>
       </c>
-      <c r="G34" s="60"/>
-      <c r="H34" s="60"/>
-      <c r="I34" s="60"/>
-      <c r="J34" s="60"/>
-      <c r="K34" s="60"/>
-      <c r="L34" s="60"/>
-      <c r="M34" s="61"/>
+      <c r="G34" s="85"/>
+      <c r="H34" s="85"/>
+      <c r="I34" s="85"/>
+      <c r="J34" s="85"/>
+      <c r="K34" s="85"/>
+      <c r="L34" s="85"/>
+      <c r="M34" s="86"/>
     </row>
     <row r="35" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="20" t="s">
@@ -6950,10 +7066,10 @@
         <v>46</v>
       </c>
       <c r="E35" s="45"/>
-      <c r="F35" s="59" t="s">
+      <c r="F35" s="84" t="s">
         <v>279</v>
       </c>
-      <c r="G35" s="61"/>
+      <c r="G35" s="86"/>
       <c r="H35" s="81"/>
       <c r="I35" s="82"/>
       <c r="J35" s="82"/>
@@ -6974,11 +7090,11 @@
       <c r="H36" s="82"/>
       <c r="I36" s="82"/>
       <c r="J36" s="83"/>
-      <c r="K36" s="59" t="s">
+      <c r="K36" s="84" t="s">
         <v>280</v>
       </c>
-      <c r="L36" s="60"/>
-      <c r="M36" s="61"/>
+      <c r="L36" s="85"/>
+      <c r="M36" s="86"/>
     </row>
     <row r="37" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="20" t="s">
@@ -6992,50 +7108,50 @@
       <c r="G37" s="82"/>
       <c r="H37" s="82"/>
       <c r="I37" s="83"/>
-      <c r="J37" s="59" t="s">
+      <c r="J37" s="84" t="s">
         <v>281</v>
       </c>
-      <c r="K37" s="60"/>
-      <c r="L37" s="60"/>
-      <c r="M37" s="61"/>
+      <c r="K37" s="85"/>
+      <c r="L37" s="85"/>
+      <c r="M37" s="86"/>
     </row>
     <row r="38" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="20" t="s">
         <v>221</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E38" s="44"/>
       <c r="F38" s="81"/>
       <c r="G38" s="82"/>
       <c r="H38" s="82"/>
       <c r="I38" s="83"/>
-      <c r="J38" s="59" t="s">
+      <c r="J38" s="84" t="s">
         <v>282</v>
       </c>
-      <c r="K38" s="60"/>
-      <c r="L38" s="60"/>
-      <c r="M38" s="61"/>
+      <c r="K38" s="85"/>
+      <c r="L38" s="85"/>
+      <c r="M38" s="86"/>
     </row>
     <row r="39" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="20" t="s">
         <v>222</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E39" s="44"/>
-      <c r="F39" s="59" t="s">
+      <c r="F39" s="84" t="s">
         <v>283</v>
       </c>
-      <c r="G39" s="60"/>
-      <c r="H39" s="60"/>
-      <c r="I39" s="60"/>
-      <c r="J39" s="60"/>
-      <c r="K39" s="60"/>
-      <c r="L39" s="60"/>
-      <c r="M39" s="61"/>
+      <c r="G39" s="85"/>
+      <c r="H39" s="85"/>
+      <c r="I39" s="85"/>
+      <c r="J39" s="85"/>
+      <c r="K39" s="85"/>
+      <c r="L39" s="85"/>
+      <c r="M39" s="86"/>
     </row>
     <row r="40" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="20" t="s">
@@ -7142,12 +7258,12 @@
       <c r="I45" s="47" t="s">
         <v>123</v>
       </c>
-      <c r="J45" s="59" t="s">
+      <c r="J45" s="60" t="s">
         <v>124</v>
       </c>
-      <c r="K45" s="60"/>
-      <c r="L45" s="60"/>
-      <c r="M45" s="61"/>
+      <c r="K45" s="61"/>
+      <c r="L45" s="61"/>
+      <c r="M45" s="62"/>
     </row>
     <row r="46" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="20" t="s">
@@ -7157,18 +7273,18 @@
         <v>46</v>
       </c>
       <c r="E46" s="45"/>
-      <c r="F46" s="59" t="s">
+      <c r="F46" s="60" t="s">
         <v>293</v>
       </c>
-      <c r="G46" s="61"/>
-      <c r="H46" s="59" t="s">
+      <c r="G46" s="62"/>
+      <c r="H46" s="60" t="s">
         <v>126</v>
       </c>
-      <c r="I46" s="60"/>
-      <c r="J46" s="60"/>
-      <c r="K46" s="60"/>
-      <c r="L46" s="60"/>
-      <c r="M46" s="61"/>
+      <c r="I46" s="61"/>
+      <c r="J46" s="61"/>
+      <c r="K46" s="61"/>
+      <c r="L46" s="61"/>
+      <c r="M46" s="62"/>
     </row>
     <row r="47" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="20" t="s">
@@ -7178,18 +7294,18 @@
         <v>46</v>
       </c>
       <c r="E47" s="45"/>
-      <c r="F47" s="75" t="s">
+      <c r="F47" s="87" t="s">
         <v>130</v>
       </c>
-      <c r="G47" s="76"/>
-      <c r="H47" s="76"/>
-      <c r="I47" s="77"/>
-      <c r="J47" s="59" t="s">
+      <c r="G47" s="88"/>
+      <c r="H47" s="88"/>
+      <c r="I47" s="89"/>
+      <c r="J47" s="60" t="s">
         <v>131</v>
       </c>
-      <c r="K47" s="60"/>
-      <c r="L47" s="60"/>
-      <c r="M47" s="61"/>
+      <c r="K47" s="61"/>
+      <c r="L47" s="61"/>
+      <c r="M47" s="62"/>
     </row>
     <row r="48" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="20" t="s">
@@ -7199,18 +7315,18 @@
         <v>46</v>
       </c>
       <c r="E48" s="6"/>
-      <c r="F48" s="59" t="s">
+      <c r="F48" s="60" t="s">
         <v>132</v>
       </c>
-      <c r="G48" s="60"/>
-      <c r="H48" s="60"/>
-      <c r="I48" s="61"/>
-      <c r="J48" s="78" t="s">
+      <c r="G48" s="61"/>
+      <c r="H48" s="61"/>
+      <c r="I48" s="62"/>
+      <c r="J48" s="90" t="s">
         <v>133</v>
       </c>
-      <c r="K48" s="79"/>
-      <c r="L48" s="79"/>
-      <c r="M48" s="80"/>
+      <c r="K48" s="91"/>
+      <c r="L48" s="91"/>
+      <c r="M48" s="92"/>
     </row>
     <row r="49" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="20" t="s">
@@ -7220,16 +7336,16 @@
         <v>46</v>
       </c>
       <c r="E49" s="6"/>
-      <c r="F49" s="57" t="s">
+      <c r="F49" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="G49" s="69"/>
-      <c r="H49" s="69"/>
-      <c r="I49" s="69"/>
-      <c r="J49" s="69"/>
-      <c r="K49" s="69"/>
-      <c r="L49" s="69"/>
-      <c r="M49" s="58"/>
+      <c r="G49" s="75"/>
+      <c r="H49" s="75"/>
+      <c r="I49" s="75"/>
+      <c r="J49" s="75"/>
+      <c r="K49" s="75"/>
+      <c r="L49" s="75"/>
+      <c r="M49" s="74"/>
     </row>
     <row r="50" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C50" s="20" t="s">
@@ -7239,20 +7355,20 @@
         <v>46</v>
       </c>
       <c r="E50" s="6"/>
-      <c r="F50" s="54"/>
-      <c r="G50" s="56"/>
+      <c r="F50" s="69"/>
+      <c r="G50" s="70"/>
       <c r="H50" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="I50" s="57" t="s">
+      <c r="I50" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="J50" s="69"/>
-      <c r="K50" s="58"/>
-      <c r="L50" s="57" t="s">
+      <c r="J50" s="75"/>
+      <c r="K50" s="74"/>
+      <c r="L50" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="M50" s="58"/>
+      <c r="M50" s="74"/>
     </row>
     <row r="51" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C51" s="20" t="s">
@@ -7295,15 +7411,15 @@
         <v>46</v>
       </c>
       <c r="E52" s="6"/>
-      <c r="F52" s="54"/>
-      <c r="G52" s="55"/>
-      <c r="H52" s="55"/>
-      <c r="I52" s="56"/>
-      <c r="J52" s="57" t="s">
+      <c r="F52" s="69"/>
+      <c r="G52" s="71"/>
+      <c r="H52" s="71"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="73" t="s">
         <v>127</v>
       </c>
-      <c r="K52" s="69"/>
-      <c r="L52" s="58"/>
+      <c r="K52" s="75"/>
+      <c r="L52" s="74"/>
       <c r="M52" s="14" t="s">
         <v>92</v>
       </c>
@@ -7324,10 +7440,10 @@
       <c r="I53" s="82"/>
       <c r="J53" s="82"/>
       <c r="K53" s="83"/>
-      <c r="L53" s="62" t="s">
+      <c r="L53" s="63" t="s">
         <v>302</v>
       </c>
-      <c r="M53" s="64"/>
+      <c r="M53" s="65"/>
     </row>
     <row r="54" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="20" t="s">
@@ -7346,8 +7462,74 @@
       <c r="L54" s="82"/>
       <c r="M54" s="83"/>
     </row>
+    <row r="55" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="56" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C56" s="57" t="s">
+        <v>379</v>
+      </c>
+      <c r="D56" t="s">
+        <v>45</v>
+      </c>
+      <c r="F56" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="G56" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="H56" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="I56" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="J56" s="58" t="s">
+        <v>385</v>
+      </c>
+      <c r="K56" s="69"/>
+      <c r="L56" s="70"/>
+      <c r="M56" s="58" t="s">
+        <v>384</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="51">
+  <mergeCells count="52">
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="F47:I47"/>
+    <mergeCell ref="J47:M47"/>
+    <mergeCell ref="F48:I48"/>
+    <mergeCell ref="J48:M48"/>
+    <mergeCell ref="F49:M49"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="F42:M42"/>
+    <mergeCell ref="F43:M43"/>
+    <mergeCell ref="F44:M44"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="F26:M26"/>
+    <mergeCell ref="F27:M27"/>
+    <mergeCell ref="F24:M24"/>
+    <mergeCell ref="F25:M25"/>
+    <mergeCell ref="F22:M22"/>
+    <mergeCell ref="F19:M19"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="F28:M28"/>
+    <mergeCell ref="F30:M30"/>
+    <mergeCell ref="F32:M32"/>
+    <mergeCell ref="F34:M34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="F36:J36"/>
+    <mergeCell ref="F23:M23"/>
+    <mergeCell ref="K56:L56"/>
     <mergeCell ref="F13:M13"/>
     <mergeCell ref="F15:M15"/>
     <mergeCell ref="F54:M54"/>
@@ -7363,42 +7545,6 @@
     <mergeCell ref="F14:M14"/>
     <mergeCell ref="F16:M16"/>
     <mergeCell ref="F18:M18"/>
-    <mergeCell ref="F19:M19"/>
-    <mergeCell ref="F22:M22"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="F28:M28"/>
-    <mergeCell ref="F30:M30"/>
-    <mergeCell ref="F32:M32"/>
-    <mergeCell ref="F34:M34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="F36:J36"/>
-    <mergeCell ref="F23:M23"/>
-    <mergeCell ref="F26:M26"/>
-    <mergeCell ref="F27:M27"/>
-    <mergeCell ref="F24:M24"/>
-    <mergeCell ref="F25:M25"/>
-    <mergeCell ref="F42:M42"/>
-    <mergeCell ref="F43:M43"/>
-    <mergeCell ref="F44:M44"/>
-    <mergeCell ref="J45:M45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="F47:I47"/>
-    <mergeCell ref="J47:M47"/>
-    <mergeCell ref="F48:I48"/>
-    <mergeCell ref="J48:M48"/>
-    <mergeCell ref="F49:M49"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="I50:K50"/>
-    <mergeCell ref="F50:G50"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc/spec/Y8960_Specifications.xlsx
+++ b/doc/spec/Y8960_Specifications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\HRA_product\Y8960_Cartridge\doc\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F968610-A728-40F1-ADF7-5A48FC638A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F32A25-D222-49CE-8A43-AC0A98D52687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1260" yWindow="1020" windowWidth="17280" windowHeight="14130" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="modules" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="398">
   <si>
     <t>Y8960 Cartridge は、MSX用のオーディオ系チップのコンボカートリッジです。</t>
     <rPh sb="21" eb="22">
@@ -1257,14 +1257,6 @@
   </si>
   <si>
     <t>T2MSK</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>EOSMSK</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>BRMSK</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1940,6 +1932,74 @@
   </si>
   <si>
     <t>BUF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>astart_b[7:0]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>astart_b[15:8]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>aend_b[7:0]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>aend_b[15:8]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>adeltan_b[7:0]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>adeltan_b[15:8]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>aeg_b</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>廃止</t>
+    <rPh sb="0" eb="2">
+      <t>ハイシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SPOFF廃止</t>
+    <rPh sb="5" eb="7">
+      <t>ハイシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FLAG CONTROL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MSKEDS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MSKBR</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ADPCMメモリの読み書き</t>
+    <rPh sb="9" eb="10">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TIMER</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2051,7 +2111,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -2376,6 +2436,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2385,7 +2465,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2566,6 +2646,51 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2575,13 +2700,19 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2593,25 +2724,10 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2623,10 +2739,22 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2638,6 +2766,15 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2647,23 +2784,20 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3239,367 +3373,367 @@
         <v>89</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="2:14" ht="27.75" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C4" s="13" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>46</v>
       </c>
       <c r="E4" s="53" t="s">
-        <v>344</v>
-      </c>
-      <c r="F4" s="69"/>
+        <v>342</v>
+      </c>
+      <c r="F4" s="70"/>
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
       <c r="I4" s="71"/>
       <c r="J4" s="71"/>
       <c r="K4" s="71"/>
-      <c r="L4" s="70"/>
+      <c r="L4" s="72"/>
       <c r="M4" s="26" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="N4" s="56" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C5" s="13" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>46</v>
       </c>
       <c r="E5" s="51" t="s">
-        <v>340</v>
-      </c>
-      <c r="F5" s="63" t="s">
-        <v>351</v>
-      </c>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
-      <c r="L5" s="64"/>
-      <c r="M5" s="65"/>
+        <v>338</v>
+      </c>
+      <c r="F5" s="81" t="s">
+        <v>349</v>
+      </c>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
+      <c r="K5" s="79"/>
+      <c r="L5" s="79"/>
+      <c r="M5" s="80"/>
       <c r="N5" s="54" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C6" s="13" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>46</v>
       </c>
       <c r="E6" s="51" t="s">
-        <v>341</v>
-      </c>
-      <c r="F6" s="63" t="s">
-        <v>351</v>
-      </c>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="65"/>
+        <v>339</v>
+      </c>
+      <c r="F6" s="81" t="s">
+        <v>349</v>
+      </c>
+      <c r="G6" s="79"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
+      <c r="J6" s="79"/>
+      <c r="K6" s="79"/>
+      <c r="L6" s="79"/>
+      <c r="M6" s="80"/>
       <c r="N6" s="54" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="7" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C7" s="13" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>46</v>
       </c>
       <c r="E7" s="51" t="s">
-        <v>342</v>
-      </c>
-      <c r="F7" s="63" t="s">
-        <v>351</v>
-      </c>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
-      <c r="L7" s="64"/>
-      <c r="M7" s="65"/>
+        <v>340</v>
+      </c>
+      <c r="F7" s="81" t="s">
+        <v>349</v>
+      </c>
+      <c r="G7" s="79"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="79"/>
+      <c r="J7" s="79"/>
+      <c r="K7" s="79"/>
+      <c r="L7" s="79"/>
+      <c r="M7" s="80"/>
       <c r="N7" s="54" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C8" s="13" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>46</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>343</v>
-      </c>
-      <c r="F8" s="63" t="s">
-        <v>351</v>
-      </c>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="64"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="64"/>
-      <c r="M8" s="65"/>
+        <v>341</v>
+      </c>
+      <c r="F8" s="81" t="s">
+        <v>349</v>
+      </c>
+      <c r="G8" s="79"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="79"/>
+      <c r="J8" s="79"/>
+      <c r="K8" s="79"/>
+      <c r="L8" s="79"/>
+      <c r="M8" s="80"/>
       <c r="N8" s="54" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C9" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="13" t="s">
         <v>338</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="F9" s="60" t="s">
-        <v>352</v>
-      </c>
-      <c r="G9" s="61"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="61"/>
-      <c r="K9" s="61"/>
-      <c r="L9" s="61"/>
-      <c r="M9" s="62"/>
+      <c r="F9" s="75" t="s">
+        <v>350</v>
+      </c>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="76"/>
+      <c r="J9" s="76"/>
+      <c r="K9" s="76"/>
+      <c r="L9" s="76"/>
+      <c r="M9" s="77"/>
       <c r="N9" s="54" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C10" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="13" t="s">
         <v>339</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="F10" s="60" t="s">
-        <v>352</v>
-      </c>
-      <c r="G10" s="61"/>
-      <c r="H10" s="61"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="61"/>
-      <c r="K10" s="61"/>
-      <c r="L10" s="61"/>
-      <c r="M10" s="62"/>
+      <c r="F10" s="75" t="s">
+        <v>350</v>
+      </c>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76"/>
+      <c r="J10" s="76"/>
+      <c r="K10" s="76"/>
+      <c r="L10" s="76"/>
+      <c r="M10" s="77"/>
       <c r="N10" s="54" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="11" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C11" s="51" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D11" s="51" t="s">
         <v>46</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="F11" s="63" t="s">
-        <v>324</v>
-      </c>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="64"/>
-      <c r="K11" s="64"/>
-      <c r="L11" s="64"/>
-      <c r="M11" s="65"/>
+        <v>322</v>
+      </c>
+      <c r="F11" s="81" t="s">
+        <v>322</v>
+      </c>
+      <c r="G11" s="79"/>
+      <c r="H11" s="79"/>
+      <c r="I11" s="79"/>
+      <c r="J11" s="79"/>
+      <c r="K11" s="79"/>
+      <c r="L11" s="79"/>
+      <c r="M11" s="80"/>
       <c r="N11" s="55" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C12" s="51" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D12" s="51" t="s">
         <v>46</v>
       </c>
       <c r="E12" s="51" t="s">
-        <v>325</v>
-      </c>
-      <c r="F12" s="63" t="s">
-        <v>325</v>
-      </c>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="64"/>
-      <c r="K12" s="64"/>
-      <c r="L12" s="64"/>
-      <c r="M12" s="65"/>
+        <v>323</v>
+      </c>
+      <c r="F12" s="81" t="s">
+        <v>323</v>
+      </c>
+      <c r="G12" s="79"/>
+      <c r="H12" s="79"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="79"/>
+      <c r="K12" s="79"/>
+      <c r="L12" s="79"/>
+      <c r="M12" s="80"/>
       <c r="N12" s="55" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="13" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="50" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D13" s="25" t="s">
         <v>46</v>
       </c>
       <c r="E13" s="50" t="s">
+        <v>314</v>
+      </c>
+      <c r="F13" s="78" t="s">
         <v>316</v>
       </c>
-      <c r="F13" s="72" t="s">
-        <v>318</v>
-      </c>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="64"/>
-      <c r="K13" s="64"/>
-      <c r="L13" s="64"/>
-      <c r="M13" s="65"/>
+      <c r="G13" s="79"/>
+      <c r="H13" s="79"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="79"/>
+      <c r="M13" s="80"/>
       <c r="N13" s="55" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="14" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="51" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D14" s="25" t="s">
         <v>46</v>
       </c>
       <c r="E14" s="51" t="s">
+        <v>315</v>
+      </c>
+      <c r="F14" s="78" t="s">
         <v>317</v>
       </c>
-      <c r="F14" s="72" t="s">
-        <v>319</v>
-      </c>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="64"/>
-      <c r="K14" s="64"/>
-      <c r="L14" s="64"/>
-      <c r="M14" s="65"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="79"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="79"/>
+      <c r="K14" s="79"/>
+      <c r="L14" s="79"/>
+      <c r="M14" s="80"/>
       <c r="N14" s="55" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="15" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="24" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D15" s="25" t="s">
         <v>46</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>309</v>
-      </c>
-      <c r="F15" s="72" t="s">
-        <v>300</v>
-      </c>
-      <c r="G15" s="64"/>
-      <c r="H15" s="64"/>
-      <c r="I15" s="64"/>
-      <c r="J15" s="64"/>
-      <c r="K15" s="64"/>
-      <c r="L15" s="64"/>
-      <c r="M15" s="65"/>
+        <v>307</v>
+      </c>
+      <c r="F15" s="78" t="s">
+        <v>298</v>
+      </c>
+      <c r="G15" s="79"/>
+      <c r="H15" s="79"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="79"/>
+      <c r="K15" s="79"/>
+      <c r="L15" s="79"/>
+      <c r="M15" s="80"/>
       <c r="N15" s="55" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="16" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="25" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D16" s="25" t="s">
         <v>46</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>301</v>
-      </c>
-      <c r="F16" s="72" t="s">
-        <v>310</v>
-      </c>
-      <c r="G16" s="64"/>
-      <c r="H16" s="64"/>
-      <c r="I16" s="64"/>
-      <c r="J16" s="64"/>
-      <c r="K16" s="64"/>
-      <c r="L16" s="64"/>
-      <c r="M16" s="65"/>
+        <v>299</v>
+      </c>
+      <c r="F16" s="78" t="s">
+        <v>308</v>
+      </c>
+      <c r="G16" s="79"/>
+      <c r="H16" s="79"/>
+      <c r="I16" s="79"/>
+      <c r="J16" s="79"/>
+      <c r="K16" s="79"/>
+      <c r="L16" s="79"/>
+      <c r="M16" s="80"/>
       <c r="N16" s="55" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="17" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="25" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D17" s="25" t="s">
         <v>46</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>298</v>
-      </c>
-      <c r="F17" s="72" t="s">
-        <v>298</v>
-      </c>
-      <c r="G17" s="64"/>
-      <c r="H17" s="64"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="64"/>
-      <c r="K17" s="64"/>
-      <c r="L17" s="64"/>
-      <c r="M17" s="65"/>
+        <v>296</v>
+      </c>
+      <c r="F17" s="78" t="s">
+        <v>296</v>
+      </c>
+      <c r="G17" s="79"/>
+      <c r="H17" s="79"/>
+      <c r="I17" s="79"/>
+      <c r="J17" s="79"/>
+      <c r="K17" s="79"/>
+      <c r="L17" s="79"/>
+      <c r="M17" s="80"/>
       <c r="N17" s="55" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="18" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="25" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D18" s="25" t="s">
         <v>46</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>299</v>
-      </c>
-      <c r="F18" s="72" t="s">
-        <v>311</v>
-      </c>
-      <c r="G18" s="64"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="64"/>
-      <c r="J18" s="64"/>
-      <c r="K18" s="64"/>
-      <c r="L18" s="64"/>
-      <c r="M18" s="65"/>
+        <v>297</v>
+      </c>
+      <c r="F18" s="78" t="s">
+        <v>309</v>
+      </c>
+      <c r="G18" s="79"/>
+      <c r="H18" s="79"/>
+      <c r="I18" s="79"/>
+      <c r="J18" s="79"/>
+      <c r="K18" s="79"/>
+      <c r="L18" s="79"/>
+      <c r="M18" s="80"/>
       <c r="N18" s="55" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="19" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3612,18 +3746,18 @@
       <c r="E19" s="49" t="s">
         <v>107</v>
       </c>
-      <c r="F19" s="72" t="s">
+      <c r="F19" s="78" t="s">
         <v>107</v>
       </c>
-      <c r="G19" s="64"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="64"/>
-      <c r="K19" s="64"/>
-      <c r="L19" s="64"/>
-      <c r="M19" s="65"/>
+      <c r="G19" s="79"/>
+      <c r="H19" s="79"/>
+      <c r="I19" s="79"/>
+      <c r="J19" s="79"/>
+      <c r="K19" s="79"/>
+      <c r="L19" s="79"/>
+      <c r="M19" s="80"/>
       <c r="N19" s="55" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="20" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3636,18 +3770,18 @@
       <c r="E20" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="F20" s="72" t="s">
+      <c r="F20" s="78" t="s">
         <v>197</v>
       </c>
-      <c r="G20" s="64"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="64"/>
-      <c r="K20" s="64"/>
-      <c r="L20" s="64"/>
-      <c r="M20" s="65"/>
+      <c r="G20" s="79"/>
+      <c r="H20" s="79"/>
+      <c r="I20" s="79"/>
+      <c r="J20" s="79"/>
+      <c r="K20" s="79"/>
+      <c r="L20" s="79"/>
+      <c r="M20" s="80"/>
       <c r="N20" s="55" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="21" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3663,15 +3797,15 @@
       <c r="F21" s="73" t="s">
         <v>105</v>
       </c>
-      <c r="G21" s="75"/>
-      <c r="H21" s="75"/>
-      <c r="I21" s="75"/>
-      <c r="J21" s="75"/>
-      <c r="K21" s="75"/>
-      <c r="L21" s="75"/>
+      <c r="G21" s="82"/>
+      <c r="H21" s="82"/>
+      <c r="I21" s="82"/>
+      <c r="J21" s="82"/>
+      <c r="K21" s="82"/>
+      <c r="L21" s="82"/>
       <c r="M21" s="74"/>
       <c r="N21" s="55" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="22" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3687,15 +3821,15 @@
       <c r="F22" s="73" t="s">
         <v>198</v>
       </c>
-      <c r="G22" s="75"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="75"/>
-      <c r="J22" s="75"/>
-      <c r="K22" s="75"/>
-      <c r="L22" s="75"/>
+      <c r="G22" s="82"/>
+      <c r="H22" s="82"/>
+      <c r="I22" s="82"/>
+      <c r="J22" s="82"/>
+      <c r="K22" s="82"/>
+      <c r="L22" s="82"/>
       <c r="M22" s="74"/>
       <c r="N22" s="55" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="23" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3706,14 +3840,14 @@
         <v>46</v>
       </c>
       <c r="E23" s="52" t="s">
-        <v>335</v>
-      </c>
-      <c r="F23" s="66"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="67"/>
-      <c r="J23" s="67"/>
-      <c r="K23" s="68"/>
+        <v>333</v>
+      </c>
+      <c r="F23" s="83"/>
+      <c r="G23" s="84"/>
+      <c r="H23" s="84"/>
+      <c r="I23" s="84"/>
+      <c r="J23" s="84"/>
+      <c r="K23" s="85"/>
       <c r="L23" s="26" t="s">
         <v>200</v>
       </c>
@@ -3721,196 +3855,198 @@
         <v>199</v>
       </c>
       <c r="N23" s="55" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="24" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E24" s="6"/>
-      <c r="F24" s="69"/>
+      <c r="F24" s="70"/>
       <c r="G24" s="71"/>
       <c r="H24" s="71"/>
       <c r="I24" s="71"/>
       <c r="J24" s="71"/>
       <c r="K24" s="71"/>
       <c r="L24" s="71"/>
-      <c r="M24" s="70"/>
+      <c r="M24" s="72"/>
       <c r="N24" s="55" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="25" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E25" s="1"/>
-      <c r="F25" s="69"/>
+      <c r="F25" s="70"/>
       <c r="G25" s="71"/>
       <c r="H25" s="71"/>
       <c r="I25" s="71"/>
       <c r="J25" s="71"/>
       <c r="K25" s="71"/>
       <c r="L25" s="71"/>
-      <c r="M25" s="70"/>
+      <c r="M25" s="72"/>
       <c r="N25" s="55" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="26" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="69"/>
+      <c r="F26" s="70"/>
       <c r="G26" s="71"/>
       <c r="H26" s="71"/>
       <c r="I26" s="71"/>
       <c r="J26" s="71"/>
       <c r="K26" s="71"/>
       <c r="L26" s="71"/>
-      <c r="M26" s="70"/>
+      <c r="M26" s="72"/>
       <c r="N26" s="55" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="27" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E27" s="1"/>
-      <c r="F27" s="69"/>
+      <c r="F27" s="70"/>
       <c r="G27" s="71"/>
       <c r="H27" s="71"/>
       <c r="I27" s="71"/>
       <c r="J27" s="71"/>
       <c r="K27" s="71"/>
       <c r="L27" s="71"/>
-      <c r="M27" s="70"/>
+      <c r="M27" s="72"/>
       <c r="N27" s="55" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="28" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E28" s="1"/>
-      <c r="F28" s="69"/>
+      <c r="F28" s="70"/>
       <c r="G28" s="71"/>
       <c r="H28" s="71"/>
       <c r="I28" s="71"/>
       <c r="J28" s="71"/>
       <c r="K28" s="71"/>
       <c r="L28" s="71"/>
-      <c r="M28" s="70"/>
+      <c r="M28" s="72"/>
       <c r="N28" s="55" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="29" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E29" s="1"/>
-      <c r="F29" s="69"/>
+      <c r="F29" s="70"/>
       <c r="G29" s="71"/>
       <c r="H29" s="71"/>
       <c r="I29" s="71"/>
       <c r="J29" s="71"/>
       <c r="K29" s="71"/>
       <c r="L29" s="71"/>
-      <c r="M29" s="70"/>
+      <c r="M29" s="72"/>
       <c r="N29" s="55" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="30" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E30" s="1"/>
-      <c r="F30" s="69"/>
+      <c r="F30" s="70"/>
       <c r="G30" s="71"/>
       <c r="H30" s="71"/>
       <c r="I30" s="71"/>
       <c r="J30" s="71"/>
       <c r="K30" s="71"/>
       <c r="L30" s="71"/>
-      <c r="M30" s="70"/>
+      <c r="M30" s="72"/>
       <c r="N30" s="55" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="31" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="F31" s="69"/>
+        <v>335</v>
+      </c>
+      <c r="F31" s="70"/>
       <c r="G31" s="71"/>
       <c r="H31" s="71"/>
       <c r="I31" s="71"/>
       <c r="J31" s="71"/>
-      <c r="K31" s="70"/>
+      <c r="K31" s="72"/>
       <c r="L31" s="73" t="s">
         <v>193</v>
       </c>
       <c r="M31" s="74"/>
       <c r="N31" s="55" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="32" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="F32" s="69"/>
-      <c r="G32" s="70"/>
+      <c r="F32" s="110" t="s">
+        <v>397</v>
+      </c>
+      <c r="G32" s="109"/>
       <c r="H32" s="26" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="I32" s="34" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J32" s="34" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K32" s="34" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="L32" s="47" t="s">
         <v>214</v>
@@ -3919,59 +4055,74 @@
         <v>213</v>
       </c>
       <c r="N32" s="55" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="33" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="13" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>46</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="F33" s="60" t="s">
-        <v>352</v>
-      </c>
-      <c r="G33" s="61"/>
-      <c r="H33" s="61"/>
-      <c r="I33" s="61"/>
-      <c r="J33" s="61"/>
-      <c r="K33" s="61"/>
-      <c r="L33" s="61"/>
-      <c r="M33" s="62"/>
+        <v>340</v>
+      </c>
+      <c r="F33" s="75" t="s">
+        <v>350</v>
+      </c>
+      <c r="G33" s="108"/>
+      <c r="H33" s="76"/>
+      <c r="I33" s="76"/>
+      <c r="J33" s="76"/>
+      <c r="K33" s="76"/>
+      <c r="L33" s="76"/>
+      <c r="M33" s="77"/>
       <c r="N33" s="54" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="34" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="F34" s="60" t="s">
-        <v>352</v>
-      </c>
-      <c r="G34" s="61"/>
-      <c r="H34" s="61"/>
-      <c r="I34" s="61"/>
-      <c r="J34" s="61"/>
-      <c r="K34" s="61"/>
-      <c r="L34" s="61"/>
-      <c r="M34" s="62"/>
+        <v>341</v>
+      </c>
+      <c r="F34" s="75" t="s">
+        <v>350</v>
+      </c>
+      <c r="G34" s="76"/>
+      <c r="H34" s="76"/>
+      <c r="I34" s="76"/>
+      <c r="J34" s="76"/>
+      <c r="K34" s="76"/>
+      <c r="L34" s="76"/>
+      <c r="M34" s="77"/>
       <c r="N34" s="54" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="31">
+    <mergeCell ref="F34:M34"/>
+    <mergeCell ref="F5:M5"/>
+    <mergeCell ref="F6:M6"/>
+    <mergeCell ref="F7:M7"/>
+    <mergeCell ref="F8:M8"/>
+    <mergeCell ref="F23:K23"/>
+    <mergeCell ref="F24:M24"/>
+    <mergeCell ref="F25:M25"/>
+    <mergeCell ref="F26:M26"/>
+    <mergeCell ref="F27:M27"/>
+    <mergeCell ref="F28:M28"/>
+    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="F30:M30"/>
+    <mergeCell ref="F31:K31"/>
+    <mergeCell ref="F14:M14"/>
     <mergeCell ref="F4:L4"/>
     <mergeCell ref="L31:M31"/>
     <mergeCell ref="F9:M9"/>
@@ -3988,22 +4139,6 @@
     <mergeCell ref="F16:M16"/>
     <mergeCell ref="F17:M17"/>
     <mergeCell ref="F18:M18"/>
-    <mergeCell ref="F34:M34"/>
-    <mergeCell ref="F5:M5"/>
-    <mergeCell ref="F6:M6"/>
-    <mergeCell ref="F7:M7"/>
-    <mergeCell ref="F8:M8"/>
-    <mergeCell ref="F23:K23"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F24:M24"/>
-    <mergeCell ref="F25:M25"/>
-    <mergeCell ref="F26:M26"/>
-    <mergeCell ref="F27:M27"/>
-    <mergeCell ref="F28:M28"/>
-    <mergeCell ref="F29:M29"/>
-    <mergeCell ref="F30:M30"/>
-    <mergeCell ref="F31:K31"/>
-    <mergeCell ref="F14:M14"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4123,16 +4258,16 @@
       <c r="E12" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="76" t="s">
+      <c r="F12" s="88" t="s">
         <v>201</v>
       </c>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="77"/>
-      <c r="K12" s="77"/>
-      <c r="L12" s="77"/>
-      <c r="M12" s="78"/>
+      <c r="G12" s="89"/>
+      <c r="H12" s="89"/>
+      <c r="I12" s="89"/>
+      <c r="J12" s="89"/>
+      <c r="K12" s="89"/>
+      <c r="L12" s="89"/>
+      <c r="M12" s="90"/>
     </row>
     <row r="13" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="20" t="s">
@@ -4148,12 +4283,12 @@
       <c r="G13" s="37"/>
       <c r="H13" s="37"/>
       <c r="I13" s="38"/>
-      <c r="J13" s="76" t="s">
+      <c r="J13" s="88" t="s">
         <v>202</v>
       </c>
-      <c r="K13" s="77"/>
-      <c r="L13" s="77"/>
-      <c r="M13" s="78"/>
+      <c r="K13" s="89"/>
+      <c r="L13" s="89"/>
+      <c r="M13" s="90"/>
     </row>
     <row r="14" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="20" t="s">
@@ -4165,16 +4300,16 @@
       <c r="E14" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="76" t="s">
+      <c r="F14" s="88" t="s">
         <v>201</v>
       </c>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
-      <c r="I14" s="77"/>
-      <c r="J14" s="77"/>
-      <c r="K14" s="77"/>
-      <c r="L14" s="77"/>
-      <c r="M14" s="78"/>
+      <c r="G14" s="89"/>
+      <c r="H14" s="89"/>
+      <c r="I14" s="89"/>
+      <c r="J14" s="89"/>
+      <c r="K14" s="89"/>
+      <c r="L14" s="89"/>
+      <c r="M14" s="90"/>
     </row>
     <row r="15" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="20" t="s">
@@ -4190,12 +4325,12 @@
       <c r="G15" s="37"/>
       <c r="H15" s="37"/>
       <c r="I15" s="38"/>
-      <c r="J15" s="76" t="s">
+      <c r="J15" s="88" t="s">
         <v>202</v>
       </c>
-      <c r="K15" s="77"/>
-      <c r="L15" s="77"/>
-      <c r="M15" s="78"/>
+      <c r="K15" s="89"/>
+      <c r="L15" s="89"/>
+      <c r="M15" s="90"/>
     </row>
     <row r="16" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="20" t="s">
@@ -4207,16 +4342,16 @@
       <c r="E16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="76" t="s">
+      <c r="F16" s="88" t="s">
         <v>201</v>
       </c>
-      <c r="G16" s="77"/>
-      <c r="H16" s="77"/>
-      <c r="I16" s="77"/>
-      <c r="J16" s="77"/>
-      <c r="K16" s="77"/>
-      <c r="L16" s="77"/>
-      <c r="M16" s="78"/>
+      <c r="G16" s="89"/>
+      <c r="H16" s="89"/>
+      <c r="I16" s="89"/>
+      <c r="J16" s="89"/>
+      <c r="K16" s="89"/>
+      <c r="L16" s="89"/>
+      <c r="M16" s="90"/>
     </row>
     <row r="17" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="20" t="s">
@@ -4232,12 +4367,12 @@
       <c r="G17" s="37"/>
       <c r="H17" s="37"/>
       <c r="I17" s="38"/>
-      <c r="J17" s="76" t="s">
+      <c r="J17" s="88" t="s">
         <v>202</v>
       </c>
-      <c r="K17" s="77"/>
-      <c r="L17" s="77"/>
-      <c r="M17" s="78"/>
+      <c r="K17" s="89"/>
+      <c r="L17" s="89"/>
+      <c r="M17" s="90"/>
     </row>
     <row r="18" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="20" t="s">
@@ -4252,13 +4387,13 @@
       <c r="F18" s="36"/>
       <c r="G18" s="37"/>
       <c r="H18" s="38"/>
-      <c r="I18" s="76" t="s">
+      <c r="I18" s="88" t="s">
         <v>203</v>
       </c>
-      <c r="J18" s="77"/>
-      <c r="K18" s="77"/>
-      <c r="L18" s="77"/>
-      <c r="M18" s="78"/>
+      <c r="J18" s="89"/>
+      <c r="K18" s="89"/>
+      <c r="L18" s="89"/>
+      <c r="M18" s="90"/>
     </row>
     <row r="19" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="20" t="s">
@@ -4311,12 +4446,12 @@
       <c r="I20" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="J20" s="76" t="s">
+      <c r="J20" s="88" t="s">
         <v>204</v>
       </c>
-      <c r="K20" s="77"/>
-      <c r="L20" s="77"/>
-      <c r="M20" s="78"/>
+      <c r="K20" s="89"/>
+      <c r="L20" s="89"/>
+      <c r="M20" s="90"/>
     </row>
     <row r="21" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="20" t="s">
@@ -4334,12 +4469,12 @@
       <c r="I21" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="J21" s="76" t="s">
+      <c r="J21" s="88" t="s">
         <v>204</v>
       </c>
-      <c r="K21" s="77"/>
-      <c r="L21" s="77"/>
-      <c r="M21" s="78"/>
+      <c r="K21" s="89"/>
+      <c r="L21" s="89"/>
+      <c r="M21" s="90"/>
     </row>
     <row r="22" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="20" t="s">
@@ -4357,12 +4492,12 @@
       <c r="I22" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="J22" s="76" t="s">
+      <c r="J22" s="88" t="s">
         <v>204</v>
       </c>
-      <c r="K22" s="77"/>
-      <c r="L22" s="77"/>
-      <c r="M22" s="78"/>
+      <c r="K22" s="89"/>
+      <c r="L22" s="89"/>
+      <c r="M22" s="90"/>
     </row>
     <row r="23" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="20" t="s">
@@ -4374,16 +4509,16 @@
       <c r="E23" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="F23" s="76" t="s">
+      <c r="F23" s="88" t="s">
         <v>205</v>
       </c>
-      <c r="G23" s="77"/>
-      <c r="H23" s="77"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="77"/>
-      <c r="K23" s="77"/>
-      <c r="L23" s="77"/>
-      <c r="M23" s="78"/>
+      <c r="G23" s="89"/>
+      <c r="H23" s="89"/>
+      <c r="I23" s="89"/>
+      <c r="J23" s="89"/>
+      <c r="K23" s="89"/>
+      <c r="L23" s="89"/>
+      <c r="M23" s="90"/>
     </row>
     <row r="24" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="20" t="s">
@@ -4395,16 +4530,16 @@
       <c r="E24" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F24" s="76" t="s">
+      <c r="F24" s="88" t="s">
         <v>206</v>
       </c>
-      <c r="G24" s="77"/>
-      <c r="H24" s="77"/>
-      <c r="I24" s="77"/>
-      <c r="J24" s="77"/>
-      <c r="K24" s="77"/>
-      <c r="L24" s="77"/>
-      <c r="M24" s="78"/>
+      <c r="G24" s="89"/>
+      <c r="H24" s="89"/>
+      <c r="I24" s="89"/>
+      <c r="J24" s="89"/>
+      <c r="K24" s="89"/>
+      <c r="L24" s="89"/>
+      <c r="M24" s="90"/>
     </row>
     <row r="25" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="20" t="s">
@@ -4420,12 +4555,12 @@
       <c r="G25" s="37"/>
       <c r="H25" s="37"/>
       <c r="I25" s="38"/>
-      <c r="J25" s="76" t="s">
+      <c r="J25" s="88" t="s">
         <v>207</v>
       </c>
-      <c r="K25" s="77"/>
-      <c r="L25" s="77"/>
-      <c r="M25" s="78"/>
+      <c r="K25" s="89"/>
+      <c r="L25" s="89"/>
+      <c r="M25" s="90"/>
     </row>
     <row r="26" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="20" t="s">
@@ -4475,16 +4610,16 @@
       <c r="E28" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="F28" s="72" t="s">
+      <c r="F28" s="78" t="s">
         <v>201</v>
       </c>
-      <c r="G28" s="79"/>
-      <c r="H28" s="79"/>
-      <c r="I28" s="79"/>
-      <c r="J28" s="79"/>
-      <c r="K28" s="79"/>
-      <c r="L28" s="79"/>
-      <c r="M28" s="80"/>
+      <c r="G28" s="86"/>
+      <c r="H28" s="86"/>
+      <c r="I28" s="86"/>
+      <c r="J28" s="86"/>
+      <c r="K28" s="86"/>
+      <c r="L28" s="86"/>
+      <c r="M28" s="87"/>
     </row>
     <row r="29" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="20" t="s">
@@ -4500,12 +4635,12 @@
       <c r="G29" s="28"/>
       <c r="H29" s="28"/>
       <c r="I29" s="29"/>
-      <c r="J29" s="72" t="s">
+      <c r="J29" s="78" t="s">
         <v>202</v>
       </c>
-      <c r="K29" s="79"/>
-      <c r="L29" s="79"/>
-      <c r="M29" s="80"/>
+      <c r="K29" s="86"/>
+      <c r="L29" s="86"/>
+      <c r="M29" s="87"/>
     </row>
     <row r="30" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="20" t="s">
@@ -4517,16 +4652,16 @@
       <c r="E30" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="F30" s="72" t="s">
+      <c r="F30" s="78" t="s">
         <v>201</v>
       </c>
-      <c r="G30" s="79"/>
-      <c r="H30" s="79"/>
-      <c r="I30" s="79"/>
-      <c r="J30" s="79"/>
-      <c r="K30" s="79"/>
-      <c r="L30" s="79"/>
-      <c r="M30" s="80"/>
+      <c r="G30" s="86"/>
+      <c r="H30" s="86"/>
+      <c r="I30" s="86"/>
+      <c r="J30" s="86"/>
+      <c r="K30" s="86"/>
+      <c r="L30" s="86"/>
+      <c r="M30" s="87"/>
     </row>
     <row r="31" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="20" t="s">
@@ -4542,12 +4677,12 @@
       <c r="G31" s="28"/>
       <c r="H31" s="28"/>
       <c r="I31" s="29"/>
-      <c r="J31" s="72" t="s">
+      <c r="J31" s="78" t="s">
         <v>202</v>
       </c>
-      <c r="K31" s="79"/>
-      <c r="L31" s="79"/>
-      <c r="M31" s="80"/>
+      <c r="K31" s="86"/>
+      <c r="L31" s="86"/>
+      <c r="M31" s="87"/>
     </row>
     <row r="32" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="20" t="s">
@@ -4559,16 +4694,16 @@
       <c r="E32" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="F32" s="72" t="s">
+      <c r="F32" s="78" t="s">
         <v>201</v>
       </c>
-      <c r="G32" s="79"/>
-      <c r="H32" s="79"/>
-      <c r="I32" s="79"/>
-      <c r="J32" s="79"/>
-      <c r="K32" s="79"/>
-      <c r="L32" s="79"/>
-      <c r="M32" s="80"/>
+      <c r="G32" s="86"/>
+      <c r="H32" s="86"/>
+      <c r="I32" s="86"/>
+      <c r="J32" s="86"/>
+      <c r="K32" s="86"/>
+      <c r="L32" s="86"/>
+      <c r="M32" s="87"/>
     </row>
     <row r="33" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="20" t="s">
@@ -4584,12 +4719,12 @@
       <c r="G33" s="28"/>
       <c r="H33" s="28"/>
       <c r="I33" s="29"/>
-      <c r="J33" s="72" t="s">
+      <c r="J33" s="78" t="s">
         <v>202</v>
       </c>
-      <c r="K33" s="79"/>
-      <c r="L33" s="79"/>
-      <c r="M33" s="80"/>
+      <c r="K33" s="86"/>
+      <c r="L33" s="86"/>
+      <c r="M33" s="87"/>
     </row>
     <row r="34" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="20" t="s">
@@ -4604,13 +4739,13 @@
       <c r="F34" s="27"/>
       <c r="G34" s="28"/>
       <c r="H34" s="29"/>
-      <c r="I34" s="72" t="s">
+      <c r="I34" s="78" t="s">
         <v>203</v>
       </c>
-      <c r="J34" s="79"/>
-      <c r="K34" s="79"/>
-      <c r="L34" s="79"/>
-      <c r="M34" s="80"/>
+      <c r="J34" s="86"/>
+      <c r="K34" s="86"/>
+      <c r="L34" s="86"/>
+      <c r="M34" s="87"/>
     </row>
     <row r="35" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="20" t="s">
@@ -4663,12 +4798,12 @@
       <c r="I36" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="J36" s="72" t="s">
+      <c r="J36" s="78" t="s">
         <v>204</v>
       </c>
-      <c r="K36" s="79"/>
-      <c r="L36" s="79"/>
-      <c r="M36" s="80"/>
+      <c r="K36" s="86"/>
+      <c r="L36" s="86"/>
+      <c r="M36" s="87"/>
     </row>
     <row r="37" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="20" t="s">
@@ -4686,12 +4821,12 @@
       <c r="I37" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="J37" s="72" t="s">
+      <c r="J37" s="78" t="s">
         <v>204</v>
       </c>
-      <c r="K37" s="79"/>
-      <c r="L37" s="79"/>
-      <c r="M37" s="80"/>
+      <c r="K37" s="86"/>
+      <c r="L37" s="86"/>
+      <c r="M37" s="87"/>
     </row>
     <row r="38" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="20" t="s">
@@ -4709,12 +4844,12 @@
       <c r="I38" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="J38" s="72" t="s">
+      <c r="J38" s="78" t="s">
         <v>204</v>
       </c>
-      <c r="K38" s="79"/>
-      <c r="L38" s="79"/>
-      <c r="M38" s="80"/>
+      <c r="K38" s="86"/>
+      <c r="L38" s="86"/>
+      <c r="M38" s="87"/>
     </row>
     <row r="39" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="20" t="s">
@@ -4726,16 +4861,16 @@
       <c r="E39" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="F39" s="72" t="s">
+      <c r="F39" s="78" t="s">
         <v>205</v>
       </c>
-      <c r="G39" s="79"/>
-      <c r="H39" s="79"/>
-      <c r="I39" s="79"/>
-      <c r="J39" s="79"/>
-      <c r="K39" s="79"/>
-      <c r="L39" s="79"/>
-      <c r="M39" s="80"/>
+      <c r="G39" s="86"/>
+      <c r="H39" s="86"/>
+      <c r="I39" s="86"/>
+      <c r="J39" s="86"/>
+      <c r="K39" s="86"/>
+      <c r="L39" s="86"/>
+      <c r="M39" s="87"/>
     </row>
     <row r="40" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="20" t="s">
@@ -4747,16 +4882,16 @@
       <c r="E40" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="F40" s="72" t="s">
+      <c r="F40" s="78" t="s">
         <v>206</v>
       </c>
-      <c r="G40" s="79"/>
-      <c r="H40" s="79"/>
-      <c r="I40" s="79"/>
-      <c r="J40" s="79"/>
-      <c r="K40" s="79"/>
-      <c r="L40" s="79"/>
-      <c r="M40" s="80"/>
+      <c r="G40" s="86"/>
+      <c r="H40" s="86"/>
+      <c r="I40" s="86"/>
+      <c r="J40" s="86"/>
+      <c r="K40" s="86"/>
+      <c r="L40" s="86"/>
+      <c r="M40" s="87"/>
     </row>
     <row r="41" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="20" t="s">
@@ -4772,12 +4907,12 @@
       <c r="G41" s="28"/>
       <c r="H41" s="28"/>
       <c r="I41" s="29"/>
-      <c r="J41" s="72" t="s">
+      <c r="J41" s="78" t="s">
         <v>207</v>
       </c>
-      <c r="K41" s="79"/>
-      <c r="L41" s="79"/>
-      <c r="M41" s="80"/>
+      <c r="K41" s="86"/>
+      <c r="L41" s="86"/>
+      <c r="M41" s="87"/>
     </row>
     <row r="42" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="20" t="s">
@@ -4812,12 +4947,12 @@
       <c r="G43" s="28"/>
       <c r="H43" s="28"/>
       <c r="I43" s="35"/>
-      <c r="J43" s="72" t="s">
+      <c r="J43" s="78" t="s">
         <v>135</v>
       </c>
-      <c r="K43" s="79"/>
-      <c r="L43" s="79"/>
-      <c r="M43" s="80"/>
+      <c r="K43" s="86"/>
+      <c r="L43" s="86"/>
+      <c r="M43" s="87"/>
     </row>
     <row r="44" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="21" t="s">
@@ -5112,15 +5247,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="F40:M40"/>
-    <mergeCell ref="J41:M41"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="I34:M34"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="F12:M12"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="F14:M14"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="F16:M16"/>
     <mergeCell ref="F32:M32"/>
     <mergeCell ref="I18:M18"/>
     <mergeCell ref="J20:M20"/>
@@ -5133,12 +5265,15 @@
     <mergeCell ref="J29:M29"/>
     <mergeCell ref="F30:M30"/>
     <mergeCell ref="J31:M31"/>
-    <mergeCell ref="J17:M17"/>
-    <mergeCell ref="F12:M12"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="F14:M14"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="F16:M16"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="J41:M41"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="I34:M34"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="F39:M39"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5225,12 +5360,12 @@
       <c r="F6" s="73" t="s">
         <v>107</v>
       </c>
-      <c r="G6" s="75"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
-      <c r="J6" s="75"/>
-      <c r="K6" s="75"/>
-      <c r="L6" s="75"/>
+      <c r="G6" s="82"/>
+      <c r="H6" s="82"/>
+      <c r="I6" s="82"/>
+      <c r="J6" s="82"/>
+      <c r="K6" s="82"/>
+      <c r="L6" s="82"/>
       <c r="M6" s="74"/>
     </row>
     <row r="7" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -5246,12 +5381,12 @@
       <c r="F7" s="73" t="s">
         <v>197</v>
       </c>
-      <c r="G7" s="75"/>
-      <c r="H7" s="75"/>
-      <c r="I7" s="75"/>
-      <c r="J7" s="75"/>
-      <c r="K7" s="75"/>
-      <c r="L7" s="75"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="82"/>
+      <c r="J7" s="82"/>
+      <c r="K7" s="82"/>
+      <c r="L7" s="82"/>
       <c r="M7" s="74"/>
     </row>
     <row r="8" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -5267,12 +5402,12 @@
       <c r="F8" s="73" t="s">
         <v>105</v>
       </c>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="75"/>
-      <c r="J8" s="75"/>
-      <c r="K8" s="75"/>
-      <c r="L8" s="75"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="82"/>
+      <c r="I8" s="82"/>
+      <c r="J8" s="82"/>
+      <c r="K8" s="82"/>
+      <c r="L8" s="82"/>
       <c r="M8" s="74"/>
     </row>
     <row r="9" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -5288,12 +5423,12 @@
       <c r="F9" s="73" t="s">
         <v>198</v>
       </c>
-      <c r="G9" s="75"/>
-      <c r="H9" s="75"/>
-      <c r="I9" s="75"/>
-      <c r="J9" s="75"/>
-      <c r="K9" s="75"/>
-      <c r="L9" s="75"/>
+      <c r="G9" s="82"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="82"/>
+      <c r="J9" s="82"/>
+      <c r="K9" s="82"/>
+      <c r="L9" s="82"/>
       <c r="M9" s="74"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.15">
@@ -5359,8 +5494,8 @@
       <c r="J21" s="73" t="s">
         <v>124</v>
       </c>
-      <c r="K21" s="75"/>
-      <c r="L21" s="75"/>
+      <c r="K21" s="82"/>
+      <c r="L21" s="82"/>
       <c r="M21" s="74"/>
     </row>
     <row r="22" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -5386,8 +5521,8 @@
       <c r="J22" s="73" t="s">
         <v>124</v>
       </c>
-      <c r="K22" s="75"/>
-      <c r="L22" s="75"/>
+      <c r="K22" s="82"/>
+      <c r="L22" s="82"/>
       <c r="M22" s="74"/>
     </row>
     <row r="23" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -5405,10 +5540,10 @@
       <c r="H23" s="73" t="s">
         <v>126</v>
       </c>
-      <c r="I23" s="75"/>
-      <c r="J23" s="75"/>
-      <c r="K23" s="75"/>
-      <c r="L23" s="75"/>
+      <c r="I23" s="82"/>
+      <c r="J23" s="82"/>
+      <c r="K23" s="82"/>
+      <c r="L23" s="82"/>
       <c r="M23" s="74"/>
     </row>
     <row r="24" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -5433,7 +5568,7 @@
       <c r="K24" s="73" t="s">
         <v>127</v>
       </c>
-      <c r="L24" s="75"/>
+      <c r="L24" s="82"/>
       <c r="M24" s="74"/>
     </row>
     <row r="25" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -5447,14 +5582,14 @@
       <c r="F25" s="73" t="s">
         <v>130</v>
       </c>
-      <c r="G25" s="75"/>
-      <c r="H25" s="75"/>
+      <c r="G25" s="82"/>
+      <c r="H25" s="82"/>
       <c r="I25" s="74"/>
       <c r="J25" s="73" t="s">
         <v>131</v>
       </c>
-      <c r="K25" s="75"/>
-      <c r="L25" s="75"/>
+      <c r="K25" s="82"/>
+      <c r="L25" s="82"/>
       <c r="M25" s="74"/>
     </row>
     <row r="26" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -5468,14 +5603,14 @@
       <c r="F26" s="73" t="s">
         <v>130</v>
       </c>
-      <c r="G26" s="75"/>
-      <c r="H26" s="75"/>
+      <c r="G26" s="82"/>
+      <c r="H26" s="82"/>
       <c r="I26" s="74"/>
       <c r="J26" s="73" t="s">
         <v>131</v>
       </c>
-      <c r="K26" s="75"/>
-      <c r="L26" s="75"/>
+      <c r="K26" s="82"/>
+      <c r="L26" s="82"/>
       <c r="M26" s="74"/>
     </row>
     <row r="27" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -5489,14 +5624,14 @@
       <c r="F27" s="73" t="s">
         <v>132</v>
       </c>
-      <c r="G27" s="75"/>
-      <c r="H27" s="75"/>
+      <c r="G27" s="82"/>
+      <c r="H27" s="82"/>
       <c r="I27" s="74"/>
       <c r="J27" s="73" t="s">
         <v>133</v>
       </c>
-      <c r="K27" s="75"/>
-      <c r="L27" s="75"/>
+      <c r="K27" s="82"/>
+      <c r="L27" s="82"/>
       <c r="M27" s="74"/>
     </row>
     <row r="28" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -5510,14 +5645,14 @@
       <c r="F28" s="73" t="s">
         <v>132</v>
       </c>
-      <c r="G28" s="75"/>
-      <c r="H28" s="75"/>
+      <c r="G28" s="82"/>
+      <c r="H28" s="82"/>
       <c r="I28" s="74"/>
       <c r="J28" s="73" t="s">
         <v>133</v>
       </c>
-      <c r="K28" s="75"/>
-      <c r="L28" s="75"/>
+      <c r="K28" s="82"/>
+      <c r="L28" s="82"/>
       <c r="M28" s="74"/>
     </row>
     <row r="29" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -5575,12 +5710,12 @@
       <c r="F31" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="G31" s="75"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="75"/>
-      <c r="J31" s="75"/>
-      <c r="K31" s="75"/>
-      <c r="L31" s="75"/>
+      <c r="G31" s="82"/>
+      <c r="H31" s="82"/>
+      <c r="I31" s="82"/>
+      <c r="J31" s="82"/>
+      <c r="K31" s="82"/>
+      <c r="L31" s="82"/>
       <c r="M31" s="74"/>
     </row>
     <row r="32" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -5594,12 +5729,12 @@
       <c r="F32" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
-      <c r="I32" s="75"/>
-      <c r="J32" s="75"/>
-      <c r="K32" s="75"/>
-      <c r="L32" s="75"/>
+      <c r="G32" s="82"/>
+      <c r="H32" s="82"/>
+      <c r="I32" s="82"/>
+      <c r="J32" s="82"/>
+      <c r="K32" s="82"/>
+      <c r="L32" s="82"/>
       <c r="M32" s="74"/>
     </row>
     <row r="33" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -5613,12 +5748,12 @@
       <c r="F33" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="G33" s="75"/>
-      <c r="H33" s="75"/>
-      <c r="I33" s="75"/>
-      <c r="J33" s="75"/>
-      <c r="K33" s="75"/>
-      <c r="L33" s="75"/>
+      <c r="G33" s="82"/>
+      <c r="H33" s="82"/>
+      <c r="I33" s="82"/>
+      <c r="J33" s="82"/>
+      <c r="K33" s="82"/>
+      <c r="L33" s="82"/>
       <c r="M33" s="74"/>
     </row>
     <row r="34" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -5632,12 +5767,12 @@
       <c r="F34" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="G34" s="75"/>
-      <c r="H34" s="75"/>
-      <c r="I34" s="75"/>
-      <c r="J34" s="75"/>
-      <c r="K34" s="75"/>
-      <c r="L34" s="75"/>
+      <c r="G34" s="82"/>
+      <c r="H34" s="82"/>
+      <c r="I34" s="82"/>
+      <c r="J34" s="82"/>
+      <c r="K34" s="82"/>
+      <c r="L34" s="82"/>
       <c r="M34" s="74"/>
     </row>
     <row r="35" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -5651,12 +5786,12 @@
       <c r="F35" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="G35" s="75"/>
-      <c r="H35" s="75"/>
-      <c r="I35" s="75"/>
-      <c r="J35" s="75"/>
-      <c r="K35" s="75"/>
-      <c r="L35" s="75"/>
+      <c r="G35" s="82"/>
+      <c r="H35" s="82"/>
+      <c r="I35" s="82"/>
+      <c r="J35" s="82"/>
+      <c r="K35" s="82"/>
+      <c r="L35" s="82"/>
       <c r="M35" s="74"/>
     </row>
     <row r="36" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -5670,12 +5805,12 @@
       <c r="F36" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="G36" s="75"/>
-      <c r="H36" s="75"/>
-      <c r="I36" s="75"/>
-      <c r="J36" s="75"/>
-      <c r="K36" s="75"/>
-      <c r="L36" s="75"/>
+      <c r="G36" s="82"/>
+      <c r="H36" s="82"/>
+      <c r="I36" s="82"/>
+      <c r="J36" s="82"/>
+      <c r="K36" s="82"/>
+      <c r="L36" s="82"/>
       <c r="M36" s="74"/>
     </row>
     <row r="37" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -5689,12 +5824,12 @@
       <c r="F37" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="G37" s="75"/>
-      <c r="H37" s="75"/>
-      <c r="I37" s="75"/>
-      <c r="J37" s="75"/>
-      <c r="K37" s="75"/>
-      <c r="L37" s="75"/>
+      <c r="G37" s="82"/>
+      <c r="H37" s="82"/>
+      <c r="I37" s="82"/>
+      <c r="J37" s="82"/>
+      <c r="K37" s="82"/>
+      <c r="L37" s="82"/>
       <c r="M37" s="74"/>
     </row>
     <row r="38" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -5708,12 +5843,12 @@
       <c r="F38" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="G38" s="75"/>
-      <c r="H38" s="75"/>
-      <c r="I38" s="75"/>
-      <c r="J38" s="75"/>
-      <c r="K38" s="75"/>
-      <c r="L38" s="75"/>
+      <c r="G38" s="82"/>
+      <c r="H38" s="82"/>
+      <c r="I38" s="82"/>
+      <c r="J38" s="82"/>
+      <c r="K38" s="82"/>
+      <c r="L38" s="82"/>
       <c r="M38" s="74"/>
     </row>
     <row r="39" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -5727,12 +5862,12 @@
       <c r="F39" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="G39" s="75"/>
-      <c r="H39" s="75"/>
-      <c r="I39" s="75"/>
-      <c r="J39" s="75"/>
-      <c r="K39" s="75"/>
-      <c r="L39" s="75"/>
+      <c r="G39" s="82"/>
+      <c r="H39" s="82"/>
+      <c r="I39" s="82"/>
+      <c r="J39" s="82"/>
+      <c r="K39" s="82"/>
+      <c r="L39" s="82"/>
       <c r="M39" s="74"/>
     </row>
     <row r="40" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -5746,12 +5881,12 @@
       <c r="F40" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="G40" s="75"/>
-      <c r="H40" s="75"/>
-      <c r="I40" s="75"/>
-      <c r="J40" s="75"/>
-      <c r="K40" s="75"/>
-      <c r="L40" s="75"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="82"/>
+      <c r="I40" s="82"/>
+      <c r="J40" s="82"/>
+      <c r="K40" s="82"/>
+      <c r="L40" s="82"/>
       <c r="M40" s="74"/>
     </row>
     <row r="41" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -5790,7 +5925,7 @@
       <c r="J42" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="K42" s="75"/>
+      <c r="K42" s="82"/>
       <c r="L42" s="74"/>
       <c r="M42" s="14" t="s">
         <v>160</v>
@@ -5815,7 +5950,7 @@
       <c r="J43" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="K43" s="75"/>
+      <c r="K43" s="82"/>
       <c r="L43" s="74"/>
       <c r="M43" s="14" t="s">
         <v>160</v>
@@ -5840,7 +5975,7 @@
       <c r="J44" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="K44" s="75"/>
+      <c r="K44" s="82"/>
       <c r="L44" s="74"/>
       <c r="M44" s="14" t="s">
         <v>160</v>
@@ -5865,7 +6000,7 @@
       <c r="J45" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="K45" s="75"/>
+      <c r="K45" s="82"/>
       <c r="L45" s="74"/>
       <c r="M45" s="14" t="s">
         <v>160</v>
@@ -5890,7 +6025,7 @@
       <c r="J46" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="K46" s="75"/>
+      <c r="K46" s="82"/>
       <c r="L46" s="74"/>
       <c r="M46" s="14" t="s">
         <v>160</v>
@@ -5915,7 +6050,7 @@
       <c r="J47" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="K47" s="75"/>
+      <c r="K47" s="82"/>
       <c r="L47" s="74"/>
       <c r="M47" s="14" t="s">
         <v>160</v>
@@ -5940,7 +6075,7 @@
       <c r="J48" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="K48" s="75"/>
+      <c r="K48" s="82"/>
       <c r="L48" s="74"/>
       <c r="M48" s="14" t="s">
         <v>160</v>
@@ -5965,7 +6100,7 @@
       <c r="J49" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="K49" s="75"/>
+      <c r="K49" s="82"/>
       <c r="L49" s="74"/>
       <c r="M49" s="14" t="s">
         <v>160</v>
@@ -5990,7 +6125,7 @@
       <c r="J50" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="K50" s="75"/>
+      <c r="K50" s="82"/>
       <c r="L50" s="74"/>
       <c r="M50" s="14" t="s">
         <v>160</v>
@@ -6024,14 +6159,14 @@
       <c r="F52" s="73" t="s">
         <v>181</v>
       </c>
-      <c r="G52" s="75"/>
-      <c r="H52" s="75"/>
+      <c r="G52" s="82"/>
+      <c r="H52" s="82"/>
       <c r="I52" s="74"/>
       <c r="J52" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="K52" s="75"/>
-      <c r="L52" s="75"/>
+      <c r="K52" s="82"/>
+      <c r="L52" s="82"/>
       <c r="M52" s="74"/>
     </row>
     <row r="53" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -6045,14 +6180,14 @@
       <c r="F53" s="73" t="s">
         <v>181</v>
       </c>
-      <c r="G53" s="75"/>
-      <c r="H53" s="75"/>
+      <c r="G53" s="82"/>
+      <c r="H53" s="82"/>
       <c r="I53" s="74"/>
       <c r="J53" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="K53" s="75"/>
-      <c r="L53" s="75"/>
+      <c r="K53" s="82"/>
+      <c r="L53" s="82"/>
       <c r="M53" s="74"/>
     </row>
     <row r="54" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -6066,14 +6201,14 @@
       <c r="F54" s="73" t="s">
         <v>181</v>
       </c>
-      <c r="G54" s="75"/>
-      <c r="H54" s="75"/>
+      <c r="G54" s="82"/>
+      <c r="H54" s="82"/>
       <c r="I54" s="74"/>
       <c r="J54" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="K54" s="75"/>
-      <c r="L54" s="75"/>
+      <c r="K54" s="82"/>
+      <c r="L54" s="82"/>
       <c r="M54" s="74"/>
     </row>
     <row r="55" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -6087,14 +6222,14 @@
       <c r="F55" s="73" t="s">
         <v>181</v>
       </c>
-      <c r="G55" s="75"/>
-      <c r="H55" s="75"/>
+      <c r="G55" s="82"/>
+      <c r="H55" s="82"/>
       <c r="I55" s="74"/>
       <c r="J55" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="K55" s="75"/>
-      <c r="L55" s="75"/>
+      <c r="K55" s="82"/>
+      <c r="L55" s="82"/>
       <c r="M55" s="74"/>
     </row>
     <row r="56" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -6108,14 +6243,14 @@
       <c r="F56" s="73" t="s">
         <v>181</v>
       </c>
-      <c r="G56" s="75"/>
-      <c r="H56" s="75"/>
+      <c r="G56" s="82"/>
+      <c r="H56" s="82"/>
       <c r="I56" s="74"/>
       <c r="J56" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="K56" s="75"/>
-      <c r="L56" s="75"/>
+      <c r="K56" s="82"/>
+      <c r="L56" s="82"/>
       <c r="M56" s="74"/>
     </row>
     <row r="57" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -6129,14 +6264,14 @@
       <c r="F57" s="73" t="s">
         <v>181</v>
       </c>
-      <c r="G57" s="75"/>
-      <c r="H57" s="75"/>
+      <c r="G57" s="82"/>
+      <c r="H57" s="82"/>
       <c r="I57" s="74"/>
       <c r="J57" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="K57" s="75"/>
-      <c r="L57" s="75"/>
+      <c r="K57" s="82"/>
+      <c r="L57" s="82"/>
       <c r="M57" s="74"/>
     </row>
     <row r="58" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -6150,14 +6285,14 @@
       <c r="F58" s="73" t="s">
         <v>181</v>
       </c>
-      <c r="G58" s="75"/>
-      <c r="H58" s="75"/>
+      <c r="G58" s="82"/>
+      <c r="H58" s="82"/>
       <c r="I58" s="74"/>
       <c r="J58" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="K58" s="75"/>
-      <c r="L58" s="75"/>
+      <c r="K58" s="82"/>
+      <c r="L58" s="82"/>
       <c r="M58" s="74"/>
     </row>
     <row r="59" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -6171,14 +6306,14 @@
       <c r="F59" s="73" t="s">
         <v>181</v>
       </c>
-      <c r="G59" s="75"/>
-      <c r="H59" s="75"/>
+      <c r="G59" s="82"/>
+      <c r="H59" s="82"/>
       <c r="I59" s="74"/>
       <c r="J59" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="K59" s="75"/>
-      <c r="L59" s="75"/>
+      <c r="K59" s="82"/>
+      <c r="L59" s="82"/>
       <c r="M59" s="74"/>
     </row>
     <row r="60" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -6192,14 +6327,14 @@
       <c r="F60" s="73" t="s">
         <v>181</v>
       </c>
-      <c r="G60" s="75"/>
-      <c r="H60" s="75"/>
+      <c r="G60" s="82"/>
+      <c r="H60" s="82"/>
       <c r="I60" s="74"/>
       <c r="J60" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="K60" s="75"/>
-      <c r="L60" s="75"/>
+      <c r="K60" s="82"/>
+      <c r="L60" s="82"/>
       <c r="M60" s="74"/>
     </row>
     <row r="61" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -6235,10 +6370,10 @@
       <c r="I62" s="10"/>
       <c r="J62" s="10"/>
       <c r="K62" s="11"/>
-      <c r="L62" s="72" t="s">
+      <c r="L62" s="78" t="s">
         <v>193</v>
       </c>
-      <c r="M62" s="65"/>
+      <c r="M62" s="80"/>
     </row>
     <row r="63" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C63" s="20" t="s">
@@ -6256,10 +6391,10 @@
       <c r="I63" s="10"/>
       <c r="J63" s="10"/>
       <c r="K63" s="11"/>
-      <c r="L63" s="63" t="s">
+      <c r="L63" s="81" t="s">
         <v>193</v>
       </c>
-      <c r="M63" s="65"/>
+      <c r="M63" s="80"/>
     </row>
     <row r="64" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C64" s="20" t="s">
@@ -6277,10 +6412,10 @@
       <c r="I64" s="10"/>
       <c r="J64" s="10"/>
       <c r="K64" s="11"/>
-      <c r="L64" s="63" t="s">
+      <c r="L64" s="81" t="s">
         <v>193</v>
       </c>
-      <c r="M64" s="65"/>
+      <c r="M64" s="80"/>
     </row>
     <row r="65" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C65" s="20" t="s">
@@ -6298,10 +6433,10 @@
       <c r="I65" s="10"/>
       <c r="J65" s="10"/>
       <c r="K65" s="11"/>
-      <c r="L65" s="63" t="s">
+      <c r="L65" s="81" t="s">
         <v>193</v>
       </c>
-      <c r="M65" s="65"/>
+      <c r="M65" s="80"/>
     </row>
     <row r="66" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C66" s="20" t="s">
@@ -6319,10 +6454,10 @@
       <c r="I66" s="10"/>
       <c r="J66" s="10"/>
       <c r="K66" s="11"/>
-      <c r="L66" s="63" t="s">
+      <c r="L66" s="81" t="s">
         <v>193</v>
       </c>
-      <c r="M66" s="65"/>
+      <c r="M66" s="80"/>
     </row>
     <row r="67" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C67" s="20" t="s">
@@ -6340,10 +6475,10 @@
       <c r="I67" s="10"/>
       <c r="J67" s="10"/>
       <c r="K67" s="11"/>
-      <c r="L67" s="63" t="s">
+      <c r="L67" s="81" t="s">
         <v>193</v>
       </c>
-      <c r="M67" s="65"/>
+      <c r="M67" s="80"/>
     </row>
     <row r="68" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C68" s="20" t="s">
@@ -6361,10 +6496,10 @@
       <c r="I68" s="10"/>
       <c r="J68" s="10"/>
       <c r="K68" s="11"/>
-      <c r="L68" s="63" t="s">
+      <c r="L68" s="81" t="s">
         <v>193</v>
       </c>
-      <c r="M68" s="65"/>
+      <c r="M68" s="80"/>
     </row>
     <row r="69" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C69" s="20" t="s">
@@ -6382,10 +6517,10 @@
       <c r="I69" s="10"/>
       <c r="J69" s="10"/>
       <c r="K69" s="11"/>
-      <c r="L69" s="63" t="s">
+      <c r="L69" s="81" t="s">
         <v>193</v>
       </c>
-      <c r="M69" s="65"/>
+      <c r="M69" s="80"/>
     </row>
     <row r="70" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C70" s="20" t="s">
@@ -6403,10 +6538,10 @@
       <c r="I70" s="10"/>
       <c r="J70" s="10"/>
       <c r="K70" s="11"/>
-      <c r="L70" s="63" t="s">
+      <c r="L70" s="81" t="s">
         <v>193</v>
       </c>
-      <c r="M70" s="65"/>
+      <c r="M70" s="80"/>
     </row>
     <row r="71" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C71" s="20" t="s">
@@ -6427,6 +6562,54 @@
     </row>
   </sheetData>
   <mergeCells count="64">
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F34:M34"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="F28:I28"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="F31:M31"/>
+    <mergeCell ref="F32:M32"/>
+    <mergeCell ref="F33:M33"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="F35:M35"/>
+    <mergeCell ref="F36:M36"/>
+    <mergeCell ref="F37:M37"/>
+    <mergeCell ref="F38:M38"/>
+    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="J56:M56"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="J52:M52"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="J53:M53"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="L69:M69"/>
+    <mergeCell ref="L70:M70"/>
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="J60:M60"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="L64:M64"/>
+    <mergeCell ref="L65:M65"/>
     <mergeCell ref="F6:M6"/>
     <mergeCell ref="F7:M7"/>
     <mergeCell ref="F8:M8"/>
@@ -6443,54 +6626,6 @@
     <mergeCell ref="F55:I55"/>
     <mergeCell ref="J55:M55"/>
     <mergeCell ref="F56:I56"/>
-    <mergeCell ref="L67:M67"/>
-    <mergeCell ref="L68:M68"/>
-    <mergeCell ref="L69:M69"/>
-    <mergeCell ref="L70:M70"/>
-    <mergeCell ref="F60:I60"/>
-    <mergeCell ref="J60:M60"/>
-    <mergeCell ref="L62:M62"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="L64:M64"/>
-    <mergeCell ref="L65:M65"/>
-    <mergeCell ref="J56:M56"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="J52:M52"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="J53:M53"/>
-    <mergeCell ref="J47:L47"/>
-    <mergeCell ref="F35:M35"/>
-    <mergeCell ref="F36:M36"/>
-    <mergeCell ref="F37:M37"/>
-    <mergeCell ref="F38:M38"/>
-    <mergeCell ref="F39:M39"/>
-    <mergeCell ref="F40:M40"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="J44:L44"/>
-    <mergeCell ref="J45:L45"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="F34:M34"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="F28:I28"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="F31:M31"/>
-    <mergeCell ref="F32:M32"/>
-    <mergeCell ref="F33:M33"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="F24:G24"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6499,7 +6634,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC57A460-A3F1-420B-B8CC-FFCC94C867CA}">
-  <dimension ref="B2:M56"/>
+  <dimension ref="B2:N56"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="5.875" customWidth="1"/>
@@ -6507,6 +6642,7 @@
     <col min="4" max="4" width="5" customWidth="1"/>
     <col min="5" max="5" width="26.75" customWidth="1"/>
     <col min="6" max="13" width="4.75" customWidth="1"/>
+    <col min="14" max="14" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.15">
@@ -6536,7 +6672,7 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.15">
@@ -6545,7 +6681,7 @@
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.15">
@@ -6554,7 +6690,7 @@
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.15">
@@ -6563,7 +6699,7 @@
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.15">
@@ -6607,23 +6743,23 @@
       </c>
     </row>
     <row r="13" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="64" t="s">
         <v>136</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13" s="45" t="s">
+      <c r="D13" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="67" t="s">
         <v>244</v>
       </c>
-      <c r="F13" s="81"/>
-      <c r="G13" s="82"/>
-      <c r="H13" s="82"/>
-      <c r="I13" s="82"/>
-      <c r="J13" s="82"/>
-      <c r="K13" s="82"/>
-      <c r="L13" s="82"/>
-      <c r="M13" s="83"/>
+      <c r="F13" s="97"/>
+      <c r="G13" s="98"/>
+      <c r="H13" s="98"/>
+      <c r="I13" s="98"/>
+      <c r="J13" s="98"/>
+      <c r="K13" s="98"/>
+      <c r="L13" s="98"/>
+      <c r="M13" s="99"/>
     </row>
     <row r="14" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="20" t="s">
@@ -6635,16 +6771,16 @@
       <c r="E14" s="45" t="s">
         <v>134</v>
       </c>
-      <c r="F14" s="60" t="s">
+      <c r="F14" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="G14" s="61"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="61"/>
-      <c r="K14" s="61"/>
-      <c r="L14" s="61"/>
-      <c r="M14" s="62"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="76"/>
+      <c r="I14" s="76"/>
+      <c r="J14" s="76"/>
+      <c r="K14" s="76"/>
+      <c r="L14" s="76"/>
+      <c r="M14" s="77"/>
     </row>
     <row r="15" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="20" t="s">
@@ -6656,16 +6792,16 @@
       <c r="E15" s="45" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="60" t="s">
+      <c r="F15" s="75" t="s">
         <v>245</v>
       </c>
-      <c r="G15" s="61"/>
-      <c r="H15" s="61"/>
-      <c r="I15" s="61"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="61"/>
-      <c r="L15" s="61"/>
-      <c r="M15" s="62"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="76"/>
+      <c r="I15" s="76"/>
+      <c r="J15" s="76"/>
+      <c r="K15" s="76"/>
+      <c r="L15" s="76"/>
+      <c r="M15" s="77"/>
     </row>
     <row r="16" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="20" t="s">
@@ -6677,25 +6813,27 @@
       <c r="E16" s="44" t="s">
         <v>246</v>
       </c>
-      <c r="F16" s="60" t="s">
+      <c r="F16" s="75" t="s">
         <v>246</v>
       </c>
-      <c r="G16" s="61"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="61"/>
-      <c r="J16" s="61"/>
-      <c r="K16" s="61"/>
-      <c r="L16" s="61"/>
-      <c r="M16" s="62"/>
-    </row>
-    <row r="17" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="G16" s="76"/>
+      <c r="H16" s="76"/>
+      <c r="I16" s="76"/>
+      <c r="J16" s="76"/>
+      <c r="K16" s="76"/>
+      <c r="L16" s="76"/>
+      <c r="M16" s="77"/>
+    </row>
+    <row r="17" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="20" t="s">
         <v>140</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="45"/>
+      <c r="E17" s="45" t="s">
+        <v>393</v>
+      </c>
       <c r="F17" s="47" t="s">
         <v>247</v>
       </c>
@@ -6706,58 +6844,64 @@
         <v>249</v>
       </c>
       <c r="I17" s="59" t="s">
-        <v>250</v>
+        <v>394</v>
       </c>
       <c r="J17" s="59" t="s">
-        <v>251</v>
+        <v>395</v>
       </c>
       <c r="K17" s="46"/>
       <c r="L17" s="47" t="s">
+        <v>250</v>
+      </c>
+      <c r="M17" s="47" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C18" s="64" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="67"/>
+      <c r="F18" s="100" t="s">
         <v>252</v>
       </c>
-      <c r="M17" s="47" t="s">
+      <c r="G18" s="101"/>
+      <c r="H18" s="101"/>
+      <c r="I18" s="101"/>
+      <c r="J18" s="101"/>
+      <c r="K18" s="101"/>
+      <c r="L18" s="101"/>
+      <c r="M18" s="102"/>
+      <c r="N18" s="61" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C19" s="64" t="s">
+        <v>142</v>
+      </c>
+      <c r="D19" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="67"/>
+      <c r="F19" s="100" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" s="45"/>
-      <c r="F18" s="81" t="s">
-        <v>254</v>
-      </c>
-      <c r="G18" s="82"/>
-      <c r="H18" s="82"/>
-      <c r="I18" s="82"/>
-      <c r="J18" s="82"/>
-      <c r="K18" s="82"/>
-      <c r="L18" s="82"/>
-      <c r="M18" s="83"/>
-    </row>
-    <row r="19" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C19" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E19" s="45"/>
-      <c r="F19" s="81" t="s">
-        <v>255</v>
-      </c>
-      <c r="G19" s="82"/>
-      <c r="H19" s="82"/>
-      <c r="I19" s="82"/>
-      <c r="J19" s="82"/>
-      <c r="K19" s="82"/>
-      <c r="L19" s="82"/>
-      <c r="M19" s="83"/>
-    </row>
-    <row r="20" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="G19" s="101"/>
+      <c r="H19" s="101"/>
+      <c r="I19" s="101"/>
+      <c r="J19" s="101"/>
+      <c r="K19" s="101"/>
+      <c r="L19" s="101"/>
+      <c r="M19" s="102"/>
+      <c r="N19" s="61" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="20" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="20" t="s">
         <v>143</v>
       </c>
@@ -6766,27 +6910,30 @@
       </c>
       <c r="E20" s="45"/>
       <c r="F20" s="59" t="s">
+        <v>254</v>
+      </c>
+      <c r="G20" s="59" t="s">
+        <v>255</v>
+      </c>
+      <c r="H20" s="59" t="s">
         <v>256</v>
       </c>
-      <c r="G20" s="59" t="s">
+      <c r="I20" s="59" t="s">
         <v>257</v>
       </c>
-      <c r="H20" s="59" t="s">
+      <c r="J20" s="60" t="s">
         <v>258</v>
       </c>
-      <c r="I20" s="59" t="s">
+      <c r="K20" s="97"/>
+      <c r="L20" s="99"/>
+      <c r="M20" s="59" t="s">
         <v>259</v>
       </c>
-      <c r="J20" s="59" t="s">
-        <v>260</v>
-      </c>
-      <c r="K20" s="81"/>
-      <c r="L20" s="83"/>
-      <c r="M20" s="59" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="21" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="N20" s="62" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="20" t="s">
         <v>215</v>
       </c>
@@ -6795,27 +6942,27 @@
       </c>
       <c r="E21" s="45"/>
       <c r="F21" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="G21" s="47" t="s">
+        <v>261</v>
+      </c>
+      <c r="H21" s="97"/>
+      <c r="I21" s="99"/>
+      <c r="J21" s="60" t="s">
         <v>262</v>
       </c>
-      <c r="G21" s="47" t="s">
+      <c r="K21" s="60" t="s">
         <v>263</v>
       </c>
-      <c r="H21" s="81"/>
-      <c r="I21" s="83"/>
-      <c r="J21" s="59" t="s">
+      <c r="L21" s="60" t="s">
         <v>264</v>
       </c>
-      <c r="K21" s="59" t="s">
+      <c r="M21" s="60" t="s">
         <v>265</v>
       </c>
-      <c r="L21" s="59" t="s">
-        <v>266</v>
-      </c>
-      <c r="M21" s="59" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="22" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="20" t="s">
         <v>216</v>
       </c>
@@ -6823,18 +6970,21 @@
         <v>46</v>
       </c>
       <c r="E22" s="45"/>
-      <c r="F22" s="84" t="s">
-        <v>268</v>
-      </c>
-      <c r="G22" s="85"/>
-      <c r="H22" s="85"/>
-      <c r="I22" s="85"/>
-      <c r="J22" s="85"/>
-      <c r="K22" s="85"/>
-      <c r="L22" s="85"/>
-      <c r="M22" s="86"/>
-    </row>
-    <row r="23" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="F22" s="103" t="s">
+        <v>266</v>
+      </c>
+      <c r="G22" s="104"/>
+      <c r="H22" s="104"/>
+      <c r="I22" s="104"/>
+      <c r="J22" s="104"/>
+      <c r="K22" s="104"/>
+      <c r="L22" s="104"/>
+      <c r="M22" s="105"/>
+      <c r="N22" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="20" t="s">
         <v>217</v>
       </c>
@@ -6842,18 +6992,21 @@
         <v>46</v>
       </c>
       <c r="E23" s="44"/>
-      <c r="F23" s="84" t="s">
-        <v>269</v>
-      </c>
-      <c r="G23" s="85"/>
-      <c r="H23" s="85"/>
-      <c r="I23" s="85"/>
-      <c r="J23" s="85"/>
-      <c r="K23" s="85"/>
-      <c r="L23" s="85"/>
-      <c r="M23" s="86"/>
-    </row>
-    <row r="24" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="F23" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="G23" s="104"/>
+      <c r="H23" s="104"/>
+      <c r="I23" s="104"/>
+      <c r="J23" s="104"/>
+      <c r="K23" s="104"/>
+      <c r="L23" s="104"/>
+      <c r="M23" s="105"/>
+      <c r="N23" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="20" t="s">
         <v>218</v>
       </c>
@@ -6861,18 +7014,21 @@
         <v>46</v>
       </c>
       <c r="E24" s="44"/>
-      <c r="F24" s="84" t="s">
-        <v>270</v>
-      </c>
-      <c r="G24" s="85"/>
-      <c r="H24" s="85"/>
-      <c r="I24" s="85"/>
-      <c r="J24" s="85"/>
-      <c r="K24" s="85"/>
-      <c r="L24" s="85"/>
-      <c r="M24" s="86"/>
-    </row>
-    <row r="25" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="F24" s="103" t="s">
+        <v>268</v>
+      </c>
+      <c r="G24" s="104"/>
+      <c r="H24" s="104"/>
+      <c r="I24" s="104"/>
+      <c r="J24" s="104"/>
+      <c r="K24" s="104"/>
+      <c r="L24" s="104"/>
+      <c r="M24" s="105"/>
+      <c r="N24" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="20" t="s">
         <v>219</v>
       </c>
@@ -6880,75 +7036,87 @@
         <v>46</v>
       </c>
       <c r="E25" s="44"/>
-      <c r="F25" s="84" t="s">
+      <c r="F25" s="103" t="s">
+        <v>269</v>
+      </c>
+      <c r="G25" s="104"/>
+      <c r="H25" s="104"/>
+      <c r="I25" s="104"/>
+      <c r="J25" s="104"/>
+      <c r="K25" s="104"/>
+      <c r="L25" s="104"/>
+      <c r="M25" s="105"/>
+      <c r="N25" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C26" s="64" t="s">
+        <v>220</v>
+      </c>
+      <c r="D26" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="66"/>
+      <c r="F26" s="100" t="s">
+        <v>270</v>
+      </c>
+      <c r="G26" s="101"/>
+      <c r="H26" s="101"/>
+      <c r="I26" s="101"/>
+      <c r="J26" s="101"/>
+      <c r="K26" s="101"/>
+      <c r="L26" s="101"/>
+      <c r="M26" s="102"/>
+      <c r="N26" s="63" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C27" s="64" t="s">
+        <v>145</v>
+      </c>
+      <c r="D27" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" s="66"/>
+      <c r="F27" s="97"/>
+      <c r="G27" s="98"/>
+      <c r="H27" s="98"/>
+      <c r="I27" s="98"/>
+      <c r="J27" s="99"/>
+      <c r="K27" s="100" t="s">
         <v>271</v>
       </c>
-      <c r="G25" s="85"/>
-      <c r="H25" s="85"/>
-      <c r="I25" s="85"/>
-      <c r="J25" s="85"/>
-      <c r="K25" s="85"/>
-      <c r="L25" s="85"/>
-      <c r="M25" s="86"/>
-    </row>
-    <row r="26" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C26" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E26" s="44"/>
-      <c r="F26" s="84" t="s">
-        <v>272</v>
-      </c>
-      <c r="G26" s="85"/>
-      <c r="H26" s="85"/>
-      <c r="I26" s="85"/>
-      <c r="J26" s="85"/>
-      <c r="K26" s="85"/>
-      <c r="L26" s="85"/>
-      <c r="M26" s="86"/>
-    </row>
-    <row r="27" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C27" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E27" s="44"/>
-      <c r="F27" s="84" t="s">
-        <v>273</v>
-      </c>
-      <c r="G27" s="85"/>
-      <c r="H27" s="85"/>
-      <c r="I27" s="85"/>
-      <c r="J27" s="85"/>
-      <c r="K27" s="85"/>
-      <c r="L27" s="85"/>
-      <c r="M27" s="86"/>
-    </row>
-    <row r="28" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="L27" s="101"/>
+      <c r="M27" s="102"/>
+      <c r="N27" s="61" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C28" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="69" t="s">
         <v>41</v>
       </c>
       <c r="E28" s="44"/>
-      <c r="F28" s="84" t="s">
-        <v>274</v>
-      </c>
-      <c r="G28" s="85"/>
-      <c r="H28" s="85"/>
-      <c r="I28" s="85"/>
-      <c r="J28" s="85"/>
-      <c r="K28" s="85"/>
-      <c r="L28" s="85"/>
-      <c r="M28" s="86"/>
-    </row>
-    <row r="29" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="F28" s="103" t="s">
+        <v>272</v>
+      </c>
+      <c r="G28" s="104"/>
+      <c r="H28" s="104"/>
+      <c r="I28" s="104"/>
+      <c r="J28" s="104"/>
+      <c r="K28" s="106"/>
+      <c r="L28" s="106"/>
+      <c r="M28" s="107"/>
+      <c r="N28" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="20" t="s">
         <v>147</v>
       </c>
@@ -6956,18 +7124,21 @@
         <v>46</v>
       </c>
       <c r="E29" s="44"/>
-      <c r="F29" s="84" t="s">
-        <v>275</v>
-      </c>
-      <c r="G29" s="85"/>
-      <c r="H29" s="85"/>
-      <c r="I29" s="85"/>
-      <c r="J29" s="85"/>
-      <c r="K29" s="85"/>
-      <c r="L29" s="85"/>
-      <c r="M29" s="86"/>
-    </row>
-    <row r="30" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="F29" s="103" t="s">
+        <v>273</v>
+      </c>
+      <c r="G29" s="104"/>
+      <c r="H29" s="104"/>
+      <c r="I29" s="104"/>
+      <c r="J29" s="104"/>
+      <c r="K29" s="104"/>
+      <c r="L29" s="104"/>
+      <c r="M29" s="105"/>
+      <c r="N29" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="20" t="s">
         <v>148</v>
       </c>
@@ -6975,18 +7146,21 @@
         <v>46</v>
       </c>
       <c r="E30" s="44"/>
-      <c r="F30" s="84" t="s">
-        <v>276</v>
-      </c>
-      <c r="G30" s="85"/>
-      <c r="H30" s="85"/>
-      <c r="I30" s="85"/>
-      <c r="J30" s="85"/>
-      <c r="K30" s="85"/>
-      <c r="L30" s="85"/>
-      <c r="M30" s="86"/>
-    </row>
-    <row r="31" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="F30" s="103" t="s">
+        <v>274</v>
+      </c>
+      <c r="G30" s="104"/>
+      <c r="H30" s="104"/>
+      <c r="I30" s="104"/>
+      <c r="J30" s="104"/>
+      <c r="K30" s="104"/>
+      <c r="L30" s="104"/>
+      <c r="M30" s="105"/>
+      <c r="N30" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="20" t="s">
         <v>149</v>
       </c>
@@ -6994,253 +7168,274 @@
         <v>46</v>
       </c>
       <c r="E31" s="44"/>
-      <c r="F31" s="84" t="s">
+      <c r="F31" s="103" t="s">
+        <v>275</v>
+      </c>
+      <c r="G31" s="104"/>
+      <c r="H31" s="104"/>
+      <c r="I31" s="104"/>
+      <c r="J31" s="104"/>
+      <c r="K31" s="104"/>
+      <c r="L31" s="104"/>
+      <c r="M31" s="105"/>
+      <c r="N31" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C32" s="64" t="s">
+        <v>150</v>
+      </c>
+      <c r="D32" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" s="66"/>
+      <c r="F32" s="97"/>
+      <c r="G32" s="98"/>
+      <c r="H32" s="98"/>
+      <c r="I32" s="98"/>
+      <c r="J32" s="98"/>
+      <c r="K32" s="98"/>
+      <c r="L32" s="98"/>
+      <c r="M32" s="99"/>
+    </row>
+    <row r="33" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C33" s="64" t="s">
+        <v>151</v>
+      </c>
+      <c r="D33" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" s="66"/>
+      <c r="F33" s="97"/>
+      <c r="G33" s="98"/>
+      <c r="H33" s="98"/>
+      <c r="I33" s="98"/>
+      <c r="J33" s="98"/>
+      <c r="K33" s="98"/>
+      <c r="L33" s="98"/>
+      <c r="M33" s="99"/>
+    </row>
+    <row r="34" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C34" s="64" t="s">
+        <v>152</v>
+      </c>
+      <c r="D34" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" s="66"/>
+      <c r="F34" s="100" t="s">
+        <v>276</v>
+      </c>
+      <c r="G34" s="101"/>
+      <c r="H34" s="101"/>
+      <c r="I34" s="101"/>
+      <c r="J34" s="101"/>
+      <c r="K34" s="101"/>
+      <c r="L34" s="101"/>
+      <c r="M34" s="102"/>
+      <c r="N34" s="61" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="35" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C35" s="64" t="s">
+        <v>153</v>
+      </c>
+      <c r="D35" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="E35" s="67"/>
+      <c r="F35" s="100" t="s">
         <v>277</v>
       </c>
-      <c r="G31" s="85"/>
-      <c r="H31" s="85"/>
-      <c r="I31" s="85"/>
-      <c r="J31" s="85"/>
-      <c r="K31" s="85"/>
-      <c r="L31" s="85"/>
-      <c r="M31" s="86"/>
-    </row>
-    <row r="32" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C32" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E32" s="44"/>
-      <c r="F32" s="81"/>
-      <c r="G32" s="82"/>
-      <c r="H32" s="82"/>
-      <c r="I32" s="82"/>
-      <c r="J32" s="82"/>
-      <c r="K32" s="82"/>
-      <c r="L32" s="82"/>
-      <c r="M32" s="83"/>
-    </row>
-    <row r="33" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C33" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E33" s="44"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="82"/>
-      <c r="H33" s="82"/>
-      <c r="I33" s="82"/>
-      <c r="J33" s="82"/>
-      <c r="K33" s="82"/>
-      <c r="L33" s="82"/>
-      <c r="M33" s="83"/>
-    </row>
-    <row r="34" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C34" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E34" s="44"/>
-      <c r="F34" s="84" t="s">
+      <c r="G35" s="102"/>
+      <c r="H35" s="97"/>
+      <c r="I35" s="98"/>
+      <c r="J35" s="98"/>
+      <c r="K35" s="98"/>
+      <c r="L35" s="98"/>
+      <c r="M35" s="99"/>
+      <c r="N35" s="61" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="36" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C36" s="64" t="s">
+        <v>154</v>
+      </c>
+      <c r="D36" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" s="67"/>
+      <c r="F36" s="97"/>
+      <c r="G36" s="98"/>
+      <c r="H36" s="98"/>
+      <c r="I36" s="98"/>
+      <c r="J36" s="99"/>
+      <c r="K36" s="100" t="s">
         <v>278</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="85"/>
-      <c r="I34" s="85"/>
-      <c r="J34" s="85"/>
-      <c r="K34" s="85"/>
-      <c r="L34" s="85"/>
-      <c r="M34" s="86"/>
-    </row>
-    <row r="35" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C35" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E35" s="45"/>
-      <c r="F35" s="84" t="s">
+      <c r="L36" s="101"/>
+      <c r="M36" s="102"/>
+      <c r="N36" s="61" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="37" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C37" s="64" t="s">
+        <v>155</v>
+      </c>
+      <c r="D37" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="E37" s="66"/>
+      <c r="F37" s="97"/>
+      <c r="G37" s="98"/>
+      <c r="H37" s="98"/>
+      <c r="I37" s="99"/>
+      <c r="J37" s="100" t="s">
         <v>279</v>
       </c>
-      <c r="G35" s="86"/>
-      <c r="H35" s="81"/>
-      <c r="I35" s="82"/>
-      <c r="J35" s="82"/>
-      <c r="K35" s="82"/>
-      <c r="L35" s="82"/>
-      <c r="M35" s="83"/>
-    </row>
-    <row r="36" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C36" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E36" s="45"/>
-      <c r="F36" s="81"/>
-      <c r="G36" s="82"/>
-      <c r="H36" s="82"/>
-      <c r="I36" s="82"/>
-      <c r="J36" s="83"/>
-      <c r="K36" s="84" t="s">
+      <c r="K37" s="101"/>
+      <c r="L37" s="101"/>
+      <c r="M37" s="102"/>
+      <c r="N37" s="61" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="38" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C38" s="64" t="s">
+        <v>221</v>
+      </c>
+      <c r="D38" s="65" t="s">
+        <v>41</v>
+      </c>
+      <c r="E38" s="66"/>
+      <c r="F38" s="97"/>
+      <c r="G38" s="98"/>
+      <c r="H38" s="98"/>
+      <c r="I38" s="99"/>
+      <c r="J38" s="100" t="s">
         <v>280</v>
       </c>
-      <c r="L36" s="85"/>
-      <c r="M36" s="86"/>
-    </row>
-    <row r="37" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C37" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E37" s="44"/>
-      <c r="F37" s="81"/>
-      <c r="G37" s="82"/>
-      <c r="H37" s="82"/>
-      <c r="I37" s="83"/>
-      <c r="J37" s="84" t="s">
+      <c r="K38" s="101"/>
+      <c r="L38" s="101"/>
+      <c r="M38" s="102"/>
+      <c r="N38" s="61" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="39" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C39" s="64" t="s">
+        <v>222</v>
+      </c>
+      <c r="D39" s="65" t="s">
+        <v>41</v>
+      </c>
+      <c r="E39" s="66"/>
+      <c r="F39" s="100" t="s">
         <v>281</v>
       </c>
-      <c r="K37" s="85"/>
-      <c r="L37" s="85"/>
-      <c r="M37" s="86"/>
-    </row>
-    <row r="38" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C38" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E38" s="44"/>
-      <c r="F38" s="81"/>
-      <c r="G38" s="82"/>
-      <c r="H38" s="82"/>
-      <c r="I38" s="83"/>
-      <c r="J38" s="84" t="s">
+      <c r="G39" s="101"/>
+      <c r="H39" s="101"/>
+      <c r="I39" s="101"/>
+      <c r="J39" s="101"/>
+      <c r="K39" s="101"/>
+      <c r="L39" s="101"/>
+      <c r="M39" s="102"/>
+      <c r="N39" s="61" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="40" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C40" s="64" t="s">
+        <v>223</v>
+      </c>
+      <c r="D40" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="E40" s="66"/>
+      <c r="F40" s="97"/>
+      <c r="G40" s="98"/>
+      <c r="H40" s="98"/>
+      <c r="I40" s="98"/>
+      <c r="J40" s="98"/>
+      <c r="K40" s="98"/>
+      <c r="L40" s="98"/>
+      <c r="M40" s="99"/>
+    </row>
+    <row r="41" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C41" s="64" t="s">
+        <v>224</v>
+      </c>
+      <c r="D41" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="E41" s="66"/>
+      <c r="F41" s="97"/>
+      <c r="G41" s="98"/>
+      <c r="H41" s="98"/>
+      <c r="I41" s="98"/>
+      <c r="J41" s="98"/>
+      <c r="K41" s="98"/>
+      <c r="L41" s="98"/>
+      <c r="M41" s="99"/>
+    </row>
+    <row r="42" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C42" s="64" t="s">
+        <v>225</v>
+      </c>
+      <c r="D42" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="E42" s="66"/>
+      <c r="F42" s="97"/>
+      <c r="G42" s="98"/>
+      <c r="H42" s="98"/>
+      <c r="I42" s="98"/>
+      <c r="J42" s="98"/>
+      <c r="K42" s="98"/>
+      <c r="L42" s="98"/>
+      <c r="M42" s="99"/>
+    </row>
+    <row r="43" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C43" s="64" t="s">
+        <v>226</v>
+      </c>
+      <c r="D43" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="E43" s="66"/>
+      <c r="F43" s="97"/>
+      <c r="G43" s="98"/>
+      <c r="H43" s="98"/>
+      <c r="I43" s="98"/>
+      <c r="J43" s="98"/>
+      <c r="K43" s="98"/>
+      <c r="L43" s="98"/>
+      <c r="M43" s="99"/>
+    </row>
+    <row r="44" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C44" s="64" t="s">
+        <v>227</v>
+      </c>
+      <c r="D44" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="E44" s="66"/>
+      <c r="F44" s="97"/>
+      <c r="G44" s="98"/>
+      <c r="H44" s="98"/>
+      <c r="I44" s="98"/>
+      <c r="J44" s="98"/>
+      <c r="K44" s="98"/>
+      <c r="L44" s="98"/>
+      <c r="M44" s="99"/>
+    </row>
+    <row r="45" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C45" s="21" t="s">
         <v>282</v>
-      </c>
-      <c r="K38" s="85"/>
-      <c r="L38" s="85"/>
-      <c r="M38" s="86"/>
-    </row>
-    <row r="39" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C39" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E39" s="44"/>
-      <c r="F39" s="84" t="s">
-        <v>283</v>
-      </c>
-      <c r="G39" s="85"/>
-      <c r="H39" s="85"/>
-      <c r="I39" s="85"/>
-      <c r="J39" s="85"/>
-      <c r="K39" s="85"/>
-      <c r="L39" s="85"/>
-      <c r="M39" s="86"/>
-    </row>
-    <row r="40" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C40" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E40" s="44"/>
-      <c r="F40" s="81"/>
-      <c r="G40" s="82"/>
-      <c r="H40" s="82"/>
-      <c r="I40" s="82"/>
-      <c r="J40" s="82"/>
-      <c r="K40" s="82"/>
-      <c r="L40" s="82"/>
-      <c r="M40" s="83"/>
-    </row>
-    <row r="41" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C41" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E41" s="44"/>
-      <c r="F41" s="81"/>
-      <c r="G41" s="82"/>
-      <c r="H41" s="82"/>
-      <c r="I41" s="82"/>
-      <c r="J41" s="82"/>
-      <c r="K41" s="82"/>
-      <c r="L41" s="82"/>
-      <c r="M41" s="83"/>
-    </row>
-    <row r="42" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C42" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E42" s="44"/>
-      <c r="F42" s="81"/>
-      <c r="G42" s="82"/>
-      <c r="H42" s="82"/>
-      <c r="I42" s="82"/>
-      <c r="J42" s="82"/>
-      <c r="K42" s="82"/>
-      <c r="L42" s="82"/>
-      <c r="M42" s="83"/>
-    </row>
-    <row r="43" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C43" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E43" s="44"/>
-      <c r="F43" s="81"/>
-      <c r="G43" s="82"/>
-      <c r="H43" s="82"/>
-      <c r="I43" s="82"/>
-      <c r="J43" s="82"/>
-      <c r="K43" s="82"/>
-      <c r="L43" s="82"/>
-      <c r="M43" s="83"/>
-    </row>
-    <row r="44" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C44" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E44" s="44"/>
-      <c r="F44" s="81"/>
-      <c r="G44" s="82"/>
-      <c r="H44" s="82"/>
-      <c r="I44" s="82"/>
-      <c r="J44" s="82"/>
-      <c r="K44" s="82"/>
-      <c r="L44" s="82"/>
-      <c r="M44" s="83"/>
-    </row>
-    <row r="45" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C45" s="21" t="s">
-        <v>284</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>46</v>
@@ -7253,84 +7448,84 @@
         <v>121</v>
       </c>
       <c r="H45" s="47" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I45" s="47" t="s">
         <v>123</v>
       </c>
-      <c r="J45" s="60" t="s">
+      <c r="J45" s="75" t="s">
         <v>124</v>
       </c>
-      <c r="K45" s="61"/>
-      <c r="L45" s="61"/>
-      <c r="M45" s="62"/>
-    </row>
-    <row r="46" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="K45" s="76"/>
+      <c r="L45" s="76"/>
+      <c r="M45" s="77"/>
+    </row>
+    <row r="46" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E46" s="45"/>
+      <c r="F46" s="75" t="s">
+        <v>291</v>
+      </c>
+      <c r="G46" s="77"/>
+      <c r="H46" s="75" t="s">
+        <v>126</v>
+      </c>
+      <c r="I46" s="76"/>
+      <c r="J46" s="76"/>
+      <c r="K46" s="76"/>
+      <c r="L46" s="76"/>
+      <c r="M46" s="77"/>
+    </row>
+    <row r="47" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C47" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E47" s="45"/>
+      <c r="F47" s="91" t="s">
+        <v>130</v>
+      </c>
+      <c r="G47" s="92"/>
+      <c r="H47" s="92"/>
+      <c r="I47" s="93"/>
+      <c r="J47" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="K47" s="76"/>
+      <c r="L47" s="76"/>
+      <c r="M47" s="77"/>
+    </row>
+    <row r="48" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C48" s="20" t="s">
         <v>285</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E46" s="45"/>
-      <c r="F46" s="60" t="s">
-        <v>293</v>
-      </c>
-      <c r="G46" s="62"/>
-      <c r="H46" s="60" t="s">
-        <v>126</v>
-      </c>
-      <c r="I46" s="61"/>
-      <c r="J46" s="61"/>
-      <c r="K46" s="61"/>
-      <c r="L46" s="61"/>
-      <c r="M46" s="62"/>
-    </row>
-    <row r="47" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C47" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E47" s="45"/>
-      <c r="F47" s="87" t="s">
-        <v>130</v>
-      </c>
-      <c r="G47" s="88"/>
-      <c r="H47" s="88"/>
-      <c r="I47" s="89"/>
-      <c r="J47" s="60" t="s">
-        <v>131</v>
-      </c>
-      <c r="K47" s="61"/>
-      <c r="L47" s="61"/>
-      <c r="M47" s="62"/>
-    </row>
-    <row r="48" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C48" s="20" t="s">
-        <v>287</v>
-      </c>
       <c r="D48" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E48" s="6"/>
-      <c r="F48" s="60" t="s">
+      <c r="F48" s="75" t="s">
         <v>132</v>
       </c>
-      <c r="G48" s="61"/>
-      <c r="H48" s="61"/>
-      <c r="I48" s="62"/>
-      <c r="J48" s="90" t="s">
+      <c r="G48" s="76"/>
+      <c r="H48" s="76"/>
+      <c r="I48" s="77"/>
+      <c r="J48" s="94" t="s">
         <v>133</v>
       </c>
-      <c r="K48" s="91"/>
-      <c r="L48" s="91"/>
-      <c r="M48" s="92"/>
+      <c r="K48" s="95"/>
+      <c r="L48" s="95"/>
+      <c r="M48" s="96"/>
     </row>
     <row r="49" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="20" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>46</v>
@@ -7339,31 +7534,31 @@
       <c r="F49" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="G49" s="75"/>
-      <c r="H49" s="75"/>
-      <c r="I49" s="75"/>
-      <c r="J49" s="75"/>
-      <c r="K49" s="75"/>
-      <c r="L49" s="75"/>
+      <c r="G49" s="82"/>
+      <c r="H49" s="82"/>
+      <c r="I49" s="82"/>
+      <c r="J49" s="82"/>
+      <c r="K49" s="82"/>
+      <c r="L49" s="82"/>
       <c r="M49" s="74"/>
     </row>
     <row r="50" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C50" s="20" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E50" s="6"/>
-      <c r="F50" s="69"/>
-      <c r="G50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="72"/>
       <c r="H50" s="12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="I50" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="J50" s="75"/>
+      <c r="J50" s="82"/>
       <c r="K50" s="74"/>
       <c r="L50" s="73" t="s">
         <v>160</v>
@@ -7379,10 +7574,10 @@
       </c>
       <c r="E51" s="6"/>
       <c r="F51" s="12" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="H51" s="12" t="s">
         <v>116</v>
@@ -7394,7 +7589,7 @@
         <v>118</v>
       </c>
       <c r="K51" s="12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L51" s="12" t="s">
         <v>94</v>
@@ -7405,20 +7600,20 @@
     </row>
     <row r="52" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="20" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E52" s="6"/>
-      <c r="F52" s="69"/>
+      <c r="F52" s="70"/>
       <c r="G52" s="71"/>
       <c r="H52" s="71"/>
-      <c r="I52" s="70"/>
+      <c r="I52" s="72"/>
       <c r="J52" s="73" t="s">
         <v>127</v>
       </c>
-      <c r="K52" s="75"/>
+      <c r="K52" s="82"/>
       <c r="L52" s="74"/>
       <c r="M52" s="14" t="s">
         <v>92</v>
@@ -7426,93 +7621,89 @@
     </row>
     <row r="53" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="20" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>304</v>
-      </c>
-      <c r="F53" s="81"/>
-      <c r="G53" s="82"/>
-      <c r="H53" s="82"/>
-      <c r="I53" s="82"/>
-      <c r="J53" s="82"/>
-      <c r="K53" s="83"/>
-      <c r="L53" s="63" t="s">
         <v>302</v>
       </c>
-      <c r="M53" s="65"/>
+      <c r="F53" s="97"/>
+      <c r="G53" s="98"/>
+      <c r="H53" s="98"/>
+      <c r="I53" s="98"/>
+      <c r="J53" s="98"/>
+      <c r="K53" s="99"/>
+      <c r="L53" s="81" t="s">
+        <v>300</v>
+      </c>
+      <c r="M53" s="80"/>
     </row>
     <row r="54" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C54" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E54" s="6"/>
-      <c r="F54" s="81"/>
-      <c r="G54" s="82"/>
-      <c r="H54" s="82"/>
-      <c r="I54" s="82"/>
-      <c r="J54" s="82"/>
-      <c r="K54" s="82"/>
-      <c r="L54" s="82"/>
-      <c r="M54" s="83"/>
+      <c r="C54" s="64" t="s">
+        <v>289</v>
+      </c>
+      <c r="D54" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="E54" s="68"/>
+      <c r="F54" s="97"/>
+      <c r="G54" s="98"/>
+      <c r="H54" s="98"/>
+      <c r="I54" s="98"/>
+      <c r="J54" s="98"/>
+      <c r="K54" s="98"/>
+      <c r="L54" s="98"/>
+      <c r="M54" s="99"/>
     </row>
     <row r="55" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="56" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="57" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D56" t="s">
         <v>45</v>
       </c>
       <c r="F56" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="G56" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="H56" s="12" t="s">
         <v>380</v>
       </c>
-      <c r="G56" s="12" t="s">
+      <c r="I56" s="12" t="s">
         <v>381</v>
       </c>
-      <c r="H56" s="12" t="s">
+      <c r="J56" s="58" t="s">
+        <v>383</v>
+      </c>
+      <c r="K56" s="70"/>
+      <c r="L56" s="72"/>
+      <c r="M56" s="58" t="s">
         <v>382</v>
       </c>
-      <c r="I56" s="12" t="s">
-        <v>383</v>
-      </c>
-      <c r="J56" s="58" t="s">
-        <v>385</v>
-      </c>
-      <c r="K56" s="69"/>
-      <c r="L56" s="70"/>
-      <c r="M56" s="58" t="s">
-        <v>384</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="52">
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="F47:I47"/>
-    <mergeCell ref="J47:M47"/>
-    <mergeCell ref="F48:I48"/>
-    <mergeCell ref="J48:M48"/>
-    <mergeCell ref="F49:M49"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="I50:K50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="F42:M42"/>
-    <mergeCell ref="F43:M43"/>
-    <mergeCell ref="F44:M44"/>
-    <mergeCell ref="J45:M45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="F26:M26"/>
-    <mergeCell ref="F27:M27"/>
-    <mergeCell ref="F24:M24"/>
-    <mergeCell ref="F25:M25"/>
-    <mergeCell ref="F22:M22"/>
+  <mergeCells count="53">
+    <mergeCell ref="K56:L56"/>
+    <mergeCell ref="F13:M13"/>
+    <mergeCell ref="F15:M15"/>
+    <mergeCell ref="F54:M54"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="F53:K53"/>
+    <mergeCell ref="J52:L52"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="F41:M41"/>
+    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="F31:M31"/>
+    <mergeCell ref="F33:M33"/>
+    <mergeCell ref="F14:M14"/>
+    <mergeCell ref="F16:M16"/>
+    <mergeCell ref="F18:M18"/>
     <mergeCell ref="F19:M19"/>
     <mergeCell ref="F38:I38"/>
     <mergeCell ref="F28:M28"/>
@@ -7529,25 +7720,31 @@
     <mergeCell ref="K20:L20"/>
     <mergeCell ref="F36:J36"/>
     <mergeCell ref="F23:M23"/>
-    <mergeCell ref="K56:L56"/>
-    <mergeCell ref="F13:M13"/>
-    <mergeCell ref="F15:M15"/>
-    <mergeCell ref="F54:M54"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="F53:K53"/>
-    <mergeCell ref="J52:L52"/>
-    <mergeCell ref="F40:M40"/>
-    <mergeCell ref="F41:M41"/>
-    <mergeCell ref="F39:M39"/>
-    <mergeCell ref="F29:M29"/>
-    <mergeCell ref="F31:M31"/>
-    <mergeCell ref="F33:M33"/>
-    <mergeCell ref="F14:M14"/>
-    <mergeCell ref="F16:M16"/>
-    <mergeCell ref="F18:M18"/>
+    <mergeCell ref="F26:M26"/>
+    <mergeCell ref="F24:M24"/>
+    <mergeCell ref="F25:M25"/>
+    <mergeCell ref="F22:M22"/>
+    <mergeCell ref="K27:M27"/>
+    <mergeCell ref="F27:J27"/>
+    <mergeCell ref="F42:M42"/>
+    <mergeCell ref="F43:M43"/>
+    <mergeCell ref="F44:M44"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="F47:I47"/>
+    <mergeCell ref="J47:M47"/>
+    <mergeCell ref="F48:I48"/>
+    <mergeCell ref="J48:M48"/>
+    <mergeCell ref="F49:M49"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="F50:G50"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/doc/spec/Y8960_Specifications.xlsx
+++ b/doc/spec/Y8960_Specifications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\HRA_product\Y8960_Cartridge\doc\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F32A25-D222-49CE-8A43-AC0A98D52687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DEECFC2-3733-4E1D-9E7C-F7D0A43D5EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="396">
   <si>
     <t>Y8960 Cartridge は、MSX用のオーディオ系チップのコンボカートリッジです。</t>
     <rPh sb="21" eb="22">
@@ -1535,14 +1535,6 @@
   </si>
   <si>
     <t>DCSG1 Access</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>SSG1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>SSG2</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -2007,7 +1999,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2067,6 +2059,22 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -2465,7 +2473,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2676,6 +2684,15 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2700,6 +2717,9 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2789,15 +2809,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3373,293 +3384,293 @@
         <v>89</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="2:14" ht="27.75" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C4" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="53" t="s">
+        <v>340</v>
+      </c>
+      <c r="F4" s="73"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="74"/>
+      <c r="K4" s="74"/>
+      <c r="L4" s="75"/>
+      <c r="M4" s="26" t="s">
+        <v>346</v>
+      </c>
+      <c r="N4" s="56" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C5" s="70" t="s">
+        <v>341</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="F5" s="85" t="s">
         <v>347</v>
       </c>
-      <c r="D4" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="53" t="s">
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="83"/>
+      <c r="K5" s="83"/>
+      <c r="L5" s="83"/>
+      <c r="M5" s="84"/>
+      <c r="N5" s="54" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C6" s="71" t="s">
         <v>342</v>
       </c>
-      <c r="F4" s="70"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="26" t="s">
+      <c r="D6" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="51" t="s">
+        <v>337</v>
+      </c>
+      <c r="F6" s="85" t="s">
+        <v>347</v>
+      </c>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="83"/>
+      <c r="L6" s="83"/>
+      <c r="M6" s="84"/>
+      <c r="N6" s="54" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="71" t="s">
+        <v>343</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="51" t="s">
+        <v>338</v>
+      </c>
+      <c r="F7" s="85" t="s">
+        <v>347</v>
+      </c>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="83"/>
+      <c r="J7" s="83"/>
+      <c r="K7" s="83"/>
+      <c r="L7" s="83"/>
+      <c r="M7" s="84"/>
+      <c r="N7" s="54" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C8" s="71" t="s">
+        <v>344</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="F8" s="85" t="s">
+        <v>347</v>
+      </c>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="83"/>
+      <c r="K8" s="83"/>
+      <c r="L8" s="83"/>
+      <c r="M8" s="84"/>
+      <c r="N8" s="54" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C9" s="71" t="s">
+        <v>334</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="F9" s="78" t="s">
         <v>348</v>
       </c>
-      <c r="N4" s="56" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="5" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C5" s="13" t="s">
-        <v>343</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E5" s="51" t="s">
-        <v>338</v>
-      </c>
-      <c r="F5" s="81" t="s">
-        <v>349</v>
-      </c>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="79"/>
-      <c r="K5" s="79"/>
-      <c r="L5" s="79"/>
-      <c r="M5" s="80"/>
-      <c r="N5" s="54" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C6" s="13" t="s">
-        <v>344</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="51" t="s">
-        <v>339</v>
-      </c>
-      <c r="F6" s="81" t="s">
-        <v>349</v>
-      </c>
-      <c r="G6" s="79"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="79"/>
-      <c r="K6" s="79"/>
-      <c r="L6" s="79"/>
-      <c r="M6" s="80"/>
-      <c r="N6" s="54" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C7" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" s="51" t="s">
-        <v>340</v>
-      </c>
-      <c r="F7" s="81" t="s">
-        <v>349</v>
-      </c>
-      <c r="G7" s="79"/>
-      <c r="H7" s="79"/>
-      <c r="I7" s="79"/>
-      <c r="J7" s="79"/>
-      <c r="K7" s="79"/>
-      <c r="L7" s="79"/>
-      <c r="M7" s="80"/>
-      <c r="N7" s="54" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C8" s="13" t="s">
-        <v>346</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>341</v>
-      </c>
-      <c r="F8" s="81" t="s">
-        <v>349</v>
-      </c>
-      <c r="G8" s="79"/>
-      <c r="H8" s="79"/>
-      <c r="I8" s="79"/>
-      <c r="J8" s="79"/>
-      <c r="K8" s="79"/>
-      <c r="L8" s="79"/>
-      <c r="M8" s="80"/>
-      <c r="N8" s="54" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C9" s="13" t="s">
-        <v>336</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="F9" s="75" t="s">
-        <v>350</v>
-      </c>
-      <c r="G9" s="76"/>
-      <c r="H9" s="76"/>
-      <c r="I9" s="76"/>
-      <c r="J9" s="76"/>
-      <c r="K9" s="76"/>
-      <c r="L9" s="76"/>
-      <c r="M9" s="77"/>
+      <c r="G9" s="79"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="79"/>
+      <c r="J9" s="79"/>
+      <c r="K9" s="79"/>
+      <c r="L9" s="79"/>
+      <c r="M9" s="80"/>
       <c r="N9" s="54" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="71" t="s">
+        <v>335</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="13" t="s">
         <v>337</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="F10" s="75" t="s">
-        <v>350</v>
-      </c>
-      <c r="G10" s="76"/>
-      <c r="H10" s="76"/>
-      <c r="I10" s="76"/>
-      <c r="J10" s="76"/>
-      <c r="K10" s="76"/>
-      <c r="L10" s="76"/>
-      <c r="M10" s="77"/>
+      <c r="F10" s="78" t="s">
+        <v>348</v>
+      </c>
+      <c r="G10" s="79"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="79"/>
+      <c r="J10" s="79"/>
+      <c r="K10" s="79"/>
+      <c r="L10" s="79"/>
+      <c r="M10" s="80"/>
       <c r="N10" s="54" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C11" s="51" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D11" s="51" t="s">
         <v>46</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="F11" s="81" t="s">
-        <v>322</v>
-      </c>
-      <c r="G11" s="79"/>
-      <c r="H11" s="79"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="79"/>
-      <c r="K11" s="79"/>
-      <c r="L11" s="79"/>
-      <c r="M11" s="80"/>
+        <v>320</v>
+      </c>
+      <c r="F11" s="85" t="s">
+        <v>320</v>
+      </c>
+      <c r="G11" s="83"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="83"/>
+      <c r="J11" s="83"/>
+      <c r="K11" s="83"/>
+      <c r="L11" s="83"/>
+      <c r="M11" s="84"/>
       <c r="N11" s="55" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="12" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C12" s="51" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D12" s="51" t="s">
         <v>46</v>
       </c>
       <c r="E12" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F12" s="81" t="s">
-        <v>323</v>
-      </c>
-      <c r="G12" s="79"/>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="79"/>
-      <c r="K12" s="79"/>
-      <c r="L12" s="79"/>
-      <c r="M12" s="80"/>
+        <v>321</v>
+      </c>
+      <c r="F12" s="85" t="s">
+        <v>321</v>
+      </c>
+      <c r="G12" s="83"/>
+      <c r="H12" s="83"/>
+      <c r="I12" s="83"/>
+      <c r="J12" s="83"/>
+      <c r="K12" s="83"/>
+      <c r="L12" s="83"/>
+      <c r="M12" s="84"/>
       <c r="N12" s="55" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="13" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C13" s="50" t="s">
+      <c r="C13" s="24" t="s">
         <v>311</v>
       </c>
       <c r="D13" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="50" t="s">
-        <v>314</v>
-      </c>
-      <c r="F13" s="78" t="s">
-        <v>316</v>
-      </c>
-      <c r="G13" s="79"/>
-      <c r="H13" s="79"/>
-      <c r="I13" s="79"/>
-      <c r="J13" s="79"/>
-      <c r="K13" s="79"/>
-      <c r="L13" s="79"/>
-      <c r="M13" s="80"/>
+      <c r="E13" s="25" t="s">
+        <v>307</v>
+      </c>
+      <c r="F13" s="82" t="s">
+        <v>298</v>
+      </c>
+      <c r="G13" s="83"/>
+      <c r="H13" s="83"/>
+      <c r="I13" s="83"/>
+      <c r="J13" s="83"/>
+      <c r="K13" s="83"/>
+      <c r="L13" s="83"/>
+      <c r="M13" s="84"/>
       <c r="N13" s="55" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="14" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C14" s="51" t="s">
+      <c r="C14" s="25" t="s">
         <v>310</v>
       </c>
       <c r="D14" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="51" t="s">
-        <v>315</v>
-      </c>
-      <c r="F14" s="78" t="s">
-        <v>317</v>
-      </c>
-      <c r="G14" s="79"/>
-      <c r="H14" s="79"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="79"/>
-      <c r="K14" s="79"/>
-      <c r="L14" s="79"/>
-      <c r="M14" s="80"/>
+      <c r="E14" s="25" t="s">
+        <v>299</v>
+      </c>
+      <c r="F14" s="82" t="s">
+        <v>308</v>
+      </c>
+      <c r="G14" s="83"/>
+      <c r="H14" s="83"/>
+      <c r="I14" s="83"/>
+      <c r="J14" s="83"/>
+      <c r="K14" s="83"/>
+      <c r="L14" s="83"/>
+      <c r="M14" s="84"/>
       <c r="N14" s="55" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="15" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="25" t="s">
         <v>303</v>
       </c>
       <c r="D15" s="25" t="s">
         <v>46</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>307</v>
-      </c>
-      <c r="F15" s="78" t="s">
-        <v>298</v>
-      </c>
-      <c r="G15" s="79"/>
-      <c r="H15" s="79"/>
-      <c r="I15" s="79"/>
-      <c r="J15" s="79"/>
-      <c r="K15" s="79"/>
-      <c r="L15" s="79"/>
-      <c r="M15" s="80"/>
+        <v>296</v>
+      </c>
+      <c r="F15" s="82" t="s">
+        <v>296</v>
+      </c>
+      <c r="G15" s="83"/>
+      <c r="H15" s="83"/>
+      <c r="I15" s="83"/>
+      <c r="J15" s="83"/>
+      <c r="K15" s="83"/>
+      <c r="L15" s="83"/>
+      <c r="M15" s="84"/>
       <c r="N15" s="55" t="s">
         <v>358</v>
       </c>
@@ -3672,68 +3683,68 @@
         <v>46</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>299</v>
-      </c>
-      <c r="F16" s="78" t="s">
-        <v>308</v>
-      </c>
-      <c r="G16" s="79"/>
-      <c r="H16" s="79"/>
-      <c r="I16" s="79"/>
-      <c r="J16" s="79"/>
-      <c r="K16" s="79"/>
-      <c r="L16" s="79"/>
-      <c r="M16" s="80"/>
+        <v>297</v>
+      </c>
+      <c r="F16" s="82" t="s">
+        <v>309</v>
+      </c>
+      <c r="G16" s="83"/>
+      <c r="H16" s="83"/>
+      <c r="I16" s="83"/>
+      <c r="J16" s="83"/>
+      <c r="K16" s="83"/>
+      <c r="L16" s="83"/>
+      <c r="M16" s="84"/>
       <c r="N16" s="55" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="17" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="50" t="s">
         <v>305</v>
       </c>
       <c r="D17" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="25" t="s">
-        <v>296</v>
-      </c>
-      <c r="F17" s="78" t="s">
-        <v>296</v>
-      </c>
-      <c r="G17" s="79"/>
-      <c r="H17" s="79"/>
-      <c r="I17" s="79"/>
-      <c r="J17" s="79"/>
-      <c r="K17" s="79"/>
-      <c r="L17" s="79"/>
-      <c r="M17" s="80"/>
+      <c r="E17" s="50" t="s">
+        <v>314</v>
+      </c>
+      <c r="F17" s="82" t="s">
+        <v>316</v>
+      </c>
+      <c r="G17" s="83"/>
+      <c r="H17" s="83"/>
+      <c r="I17" s="83"/>
+      <c r="J17" s="83"/>
+      <c r="K17" s="83"/>
+      <c r="L17" s="83"/>
+      <c r="M17" s="84"/>
       <c r="N17" s="55" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
     <row r="18" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="51" t="s">
         <v>306</v>
       </c>
       <c r="D18" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="E18" s="25" t="s">
-        <v>297</v>
-      </c>
-      <c r="F18" s="78" t="s">
-        <v>309</v>
-      </c>
-      <c r="G18" s="79"/>
-      <c r="H18" s="79"/>
-      <c r="I18" s="79"/>
-      <c r="J18" s="79"/>
-      <c r="K18" s="79"/>
-      <c r="L18" s="79"/>
-      <c r="M18" s="80"/>
+      <c r="E18" s="51" t="s">
+        <v>315</v>
+      </c>
+      <c r="F18" s="82" t="s">
+        <v>317</v>
+      </c>
+      <c r="G18" s="83"/>
+      <c r="H18" s="83"/>
+      <c r="I18" s="83"/>
+      <c r="J18" s="83"/>
+      <c r="K18" s="83"/>
+      <c r="L18" s="83"/>
+      <c r="M18" s="84"/>
       <c r="N18" s="55" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="19" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3746,18 +3757,18 @@
       <c r="E19" s="49" t="s">
         <v>107</v>
       </c>
-      <c r="F19" s="78" t="s">
+      <c r="F19" s="82" t="s">
         <v>107</v>
       </c>
-      <c r="G19" s="79"/>
-      <c r="H19" s="79"/>
-      <c r="I19" s="79"/>
-      <c r="J19" s="79"/>
-      <c r="K19" s="79"/>
-      <c r="L19" s="79"/>
-      <c r="M19" s="80"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="83"/>
+      <c r="I19" s="83"/>
+      <c r="J19" s="83"/>
+      <c r="K19" s="83"/>
+      <c r="L19" s="83"/>
+      <c r="M19" s="84"/>
       <c r="N19" s="55" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="20" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3770,18 +3781,18 @@
       <c r="E20" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="F20" s="78" t="s">
+      <c r="F20" s="82" t="s">
         <v>197</v>
       </c>
-      <c r="G20" s="79"/>
-      <c r="H20" s="79"/>
-      <c r="I20" s="79"/>
-      <c r="J20" s="79"/>
-      <c r="K20" s="79"/>
-      <c r="L20" s="79"/>
-      <c r="M20" s="80"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="83"/>
+      <c r="I20" s="83"/>
+      <c r="J20" s="83"/>
+      <c r="K20" s="83"/>
+      <c r="L20" s="83"/>
+      <c r="M20" s="84"/>
       <c r="N20" s="55" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="21" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3794,18 +3805,18 @@
       <c r="E21" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F21" s="73" t="s">
+      <c r="F21" s="76" t="s">
         <v>105</v>
       </c>
-      <c r="G21" s="82"/>
-      <c r="H21" s="82"/>
-      <c r="I21" s="82"/>
-      <c r="J21" s="82"/>
-      <c r="K21" s="82"/>
-      <c r="L21" s="82"/>
-      <c r="M21" s="74"/>
+      <c r="G21" s="86"/>
+      <c r="H21" s="86"/>
+      <c r="I21" s="86"/>
+      <c r="J21" s="86"/>
+      <c r="K21" s="86"/>
+      <c r="L21" s="86"/>
+      <c r="M21" s="77"/>
       <c r="N21" s="55" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="22" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3818,18 +3829,18 @@
       <c r="E22" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F22" s="73" t="s">
+      <c r="F22" s="76" t="s">
         <v>198</v>
       </c>
-      <c r="G22" s="82"/>
-      <c r="H22" s="82"/>
-      <c r="I22" s="82"/>
-      <c r="J22" s="82"/>
-      <c r="K22" s="82"/>
-      <c r="L22" s="82"/>
-      <c r="M22" s="74"/>
+      <c r="G22" s="86"/>
+      <c r="H22" s="86"/>
+      <c r="I22" s="86"/>
+      <c r="J22" s="86"/>
+      <c r="K22" s="86"/>
+      <c r="L22" s="86"/>
+      <c r="M22" s="77"/>
       <c r="N22" s="55" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="23" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -3840,14 +3851,14 @@
         <v>46</v>
       </c>
       <c r="E23" s="52" t="s">
-        <v>333</v>
-      </c>
-      <c r="F23" s="83"/>
-      <c r="G23" s="84"/>
-      <c r="H23" s="84"/>
-      <c r="I23" s="84"/>
-      <c r="J23" s="84"/>
-      <c r="K23" s="85"/>
+        <v>331</v>
+      </c>
+      <c r="F23" s="87"/>
+      <c r="G23" s="88"/>
+      <c r="H23" s="88"/>
+      <c r="I23" s="88"/>
+      <c r="J23" s="88"/>
+      <c r="K23" s="89"/>
       <c r="L23" s="26" t="s">
         <v>200</v>
       </c>
@@ -3855,192 +3866,190 @@
         <v>199</v>
       </c>
       <c r="N23" s="55" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="24" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E24" s="6"/>
-      <c r="F24" s="70"/>
-      <c r="G24" s="71"/>
-      <c r="H24" s="71"/>
-      <c r="I24" s="71"/>
-      <c r="J24" s="71"/>
-      <c r="K24" s="71"/>
-      <c r="L24" s="71"/>
-      <c r="M24" s="72"/>
+      <c r="F24" s="73"/>
+      <c r="G24" s="74"/>
+      <c r="H24" s="74"/>
+      <c r="I24" s="74"/>
+      <c r="J24" s="74"/>
+      <c r="K24" s="74"/>
+      <c r="L24" s="74"/>
+      <c r="M24" s="75"/>
       <c r="N24" s="55" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="25" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E25" s="1"/>
-      <c r="F25" s="70"/>
-      <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="71"/>
-      <c r="J25" s="71"/>
-      <c r="K25" s="71"/>
-      <c r="L25" s="71"/>
-      <c r="M25" s="72"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="74"/>
+      <c r="H25" s="74"/>
+      <c r="I25" s="74"/>
+      <c r="J25" s="74"/>
+      <c r="K25" s="74"/>
+      <c r="L25" s="74"/>
+      <c r="M25" s="75"/>
       <c r="N25" s="55" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="26" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="70"/>
-      <c r="G26" s="71"/>
-      <c r="H26" s="71"/>
-      <c r="I26" s="71"/>
-      <c r="J26" s="71"/>
-      <c r="K26" s="71"/>
-      <c r="L26" s="71"/>
-      <c r="M26" s="72"/>
+      <c r="F26" s="73"/>
+      <c r="G26" s="74"/>
+      <c r="H26" s="74"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="74"/>
+      <c r="K26" s="74"/>
+      <c r="L26" s="74"/>
+      <c r="M26" s="75"/>
       <c r="N26" s="55" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="27" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E27" s="1"/>
-      <c r="F27" s="70"/>
-      <c r="G27" s="71"/>
-      <c r="H27" s="71"/>
-      <c r="I27" s="71"/>
-      <c r="J27" s="71"/>
-      <c r="K27" s="71"/>
-      <c r="L27" s="71"/>
-      <c r="M27" s="72"/>
+      <c r="F27" s="73"/>
+      <c r="G27" s="74"/>
+      <c r="H27" s="74"/>
+      <c r="I27" s="74"/>
+      <c r="J27" s="74"/>
+      <c r="K27" s="74"/>
+      <c r="L27" s="74"/>
+      <c r="M27" s="75"/>
       <c r="N27" s="55" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="28" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E28" s="1"/>
-      <c r="F28" s="70"/>
-      <c r="G28" s="71"/>
-      <c r="H28" s="71"/>
-      <c r="I28" s="71"/>
-      <c r="J28" s="71"/>
-      <c r="K28" s="71"/>
-      <c r="L28" s="71"/>
-      <c r="M28" s="72"/>
+      <c r="F28" s="73"/>
+      <c r="G28" s="74"/>
+      <c r="H28" s="74"/>
+      <c r="I28" s="74"/>
+      <c r="J28" s="74"/>
+      <c r="K28" s="74"/>
+      <c r="L28" s="74"/>
+      <c r="M28" s="75"/>
       <c r="N28" s="55" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="29" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E29" s="1"/>
-      <c r="F29" s="70"/>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
-      <c r="I29" s="71"/>
-      <c r="J29" s="71"/>
-      <c r="K29" s="71"/>
-      <c r="L29" s="71"/>
-      <c r="M29" s="72"/>
+      <c r="F29" s="73"/>
+      <c r="G29" s="74"/>
+      <c r="H29" s="74"/>
+      <c r="I29" s="74"/>
+      <c r="J29" s="74"/>
+      <c r="K29" s="74"/>
+      <c r="L29" s="74"/>
+      <c r="M29" s="75"/>
       <c r="N29" s="55" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="30" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E30" s="1"/>
-      <c r="F30" s="70"/>
-      <c r="G30" s="71"/>
-      <c r="H30" s="71"/>
-      <c r="I30" s="71"/>
-      <c r="J30" s="71"/>
-      <c r="K30" s="71"/>
-      <c r="L30" s="71"/>
-      <c r="M30" s="72"/>
+      <c r="F30" s="73"/>
+      <c r="G30" s="74"/>
+      <c r="H30" s="74"/>
+      <c r="I30" s="74"/>
+      <c r="J30" s="74"/>
+      <c r="K30" s="74"/>
+      <c r="L30" s="74"/>
+      <c r="M30" s="75"/>
       <c r="N30" s="55" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="31" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="F31" s="70"/>
-      <c r="G31" s="71"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="71"/>
-      <c r="J31" s="71"/>
-      <c r="K31" s="72"/>
-      <c r="L31" s="73" t="s">
+        <v>333</v>
+      </c>
+      <c r="F31" s="73"/>
+      <c r="G31" s="74"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="74"/>
+      <c r="J31" s="74"/>
+      <c r="K31" s="75"/>
+      <c r="L31" s="76" t="s">
         <v>193</v>
       </c>
-      <c r="M31" s="74"/>
+      <c r="M31" s="77"/>
       <c r="N31" s="55" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="32" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="F32" s="110" t="s">
-        <v>397</v>
-      </c>
-      <c r="G32" s="109"/>
-      <c r="H32" s="26" t="s">
-        <v>319</v>
-      </c>
+      <c r="F32" s="26" t="s">
+        <v>395</v>
+      </c>
+      <c r="G32" s="73"/>
+      <c r="H32" s="75"/>
       <c r="I32" s="34" t="s">
-        <v>318</v>
+        <v>4</v>
       </c>
       <c r="J32" s="34" t="s">
         <v>312</v>
@@ -4055,59 +4064,59 @@
         <v>213</v>
       </c>
       <c r="N32" s="55" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="33" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C33" s="13" t="s">
-        <v>336</v>
+      <c r="C33" s="70" t="s">
+        <v>334</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>46</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="F33" s="75" t="s">
-        <v>350</v>
-      </c>
-      <c r="G33" s="108"/>
-      <c r="H33" s="76"/>
-      <c r="I33" s="76"/>
-      <c r="J33" s="76"/>
-      <c r="K33" s="76"/>
-      <c r="L33" s="76"/>
-      <c r="M33" s="77"/>
+        <v>338</v>
+      </c>
+      <c r="F33" s="78" t="s">
+        <v>348</v>
+      </c>
+      <c r="G33" s="81"/>
+      <c r="H33" s="79"/>
+      <c r="I33" s="79"/>
+      <c r="J33" s="79"/>
+      <c r="K33" s="79"/>
+      <c r="L33" s="79"/>
+      <c r="M33" s="80"/>
       <c r="N33" s="54" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="34" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C34" s="1" t="s">
-        <v>337</v>
+      <c r="C34" s="72" t="s">
+        <v>335</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="F34" s="75" t="s">
-        <v>350</v>
-      </c>
-      <c r="G34" s="76"/>
-      <c r="H34" s="76"/>
-      <c r="I34" s="76"/>
-      <c r="J34" s="76"/>
-      <c r="K34" s="76"/>
-      <c r="L34" s="76"/>
-      <c r="M34" s="77"/>
+        <v>339</v>
+      </c>
+      <c r="F34" s="78" t="s">
+        <v>348</v>
+      </c>
+      <c r="G34" s="79"/>
+      <c r="H34" s="79"/>
+      <c r="I34" s="79"/>
+      <c r="J34" s="79"/>
+      <c r="K34" s="79"/>
+      <c r="L34" s="79"/>
+      <c r="M34" s="80"/>
       <c r="N34" s="54" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="32">
     <mergeCell ref="F34:M34"/>
     <mergeCell ref="F5:M5"/>
     <mergeCell ref="F6:M6"/>
@@ -4122,23 +4131,24 @@
     <mergeCell ref="F29:M29"/>
     <mergeCell ref="F30:M30"/>
     <mergeCell ref="F31:K31"/>
-    <mergeCell ref="F14:M14"/>
+    <mergeCell ref="F18:M18"/>
+    <mergeCell ref="G32:H32"/>
     <mergeCell ref="F4:L4"/>
     <mergeCell ref="L31:M31"/>
     <mergeCell ref="F9:M9"/>
     <mergeCell ref="F10:M10"/>
     <mergeCell ref="F33:M33"/>
-    <mergeCell ref="F13:M13"/>
+    <mergeCell ref="F17:M17"/>
     <mergeCell ref="F11:M11"/>
     <mergeCell ref="F12:M12"/>
     <mergeCell ref="F19:M19"/>
     <mergeCell ref="F20:M20"/>
     <mergeCell ref="F21:M21"/>
     <mergeCell ref="F22:M22"/>
+    <mergeCell ref="F13:M13"/>
+    <mergeCell ref="F14:M14"/>
     <mergeCell ref="F15:M15"/>
     <mergeCell ref="F16:M16"/>
-    <mergeCell ref="F17:M17"/>
-    <mergeCell ref="F18:M18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4258,16 +4268,16 @@
       <c r="E12" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="88" t="s">
+      <c r="F12" s="92" t="s">
         <v>201</v>
       </c>
-      <c r="G12" s="89"/>
-      <c r="H12" s="89"/>
-      <c r="I12" s="89"/>
-      <c r="J12" s="89"/>
-      <c r="K12" s="89"/>
-      <c r="L12" s="89"/>
-      <c r="M12" s="90"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="93"/>
+      <c r="K12" s="93"/>
+      <c r="L12" s="93"/>
+      <c r="M12" s="94"/>
     </row>
     <row r="13" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="20" t="s">
@@ -4283,12 +4293,12 @@
       <c r="G13" s="37"/>
       <c r="H13" s="37"/>
       <c r="I13" s="38"/>
-      <c r="J13" s="88" t="s">
+      <c r="J13" s="92" t="s">
         <v>202</v>
       </c>
-      <c r="K13" s="89"/>
-      <c r="L13" s="89"/>
-      <c r="M13" s="90"/>
+      <c r="K13" s="93"/>
+      <c r="L13" s="93"/>
+      <c r="M13" s="94"/>
     </row>
     <row r="14" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="20" t="s">
@@ -4300,16 +4310,16 @@
       <c r="E14" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="88" t="s">
+      <c r="F14" s="92" t="s">
         <v>201</v>
       </c>
-      <c r="G14" s="89"/>
-      <c r="H14" s="89"/>
-      <c r="I14" s="89"/>
-      <c r="J14" s="89"/>
-      <c r="K14" s="89"/>
-      <c r="L14" s="89"/>
-      <c r="M14" s="90"/>
+      <c r="G14" s="93"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="93"/>
+      <c r="J14" s="93"/>
+      <c r="K14" s="93"/>
+      <c r="L14" s="93"/>
+      <c r="M14" s="94"/>
     </row>
     <row r="15" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="20" t="s">
@@ -4325,12 +4335,12 @@
       <c r="G15" s="37"/>
       <c r="H15" s="37"/>
       <c r="I15" s="38"/>
-      <c r="J15" s="88" t="s">
+      <c r="J15" s="92" t="s">
         <v>202</v>
       </c>
-      <c r="K15" s="89"/>
-      <c r="L15" s="89"/>
-      <c r="M15" s="90"/>
+      <c r="K15" s="93"/>
+      <c r="L15" s="93"/>
+      <c r="M15" s="94"/>
     </row>
     <row r="16" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="20" t="s">
@@ -4342,16 +4352,16 @@
       <c r="E16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="88" t="s">
+      <c r="F16" s="92" t="s">
         <v>201</v>
       </c>
-      <c r="G16" s="89"/>
-      <c r="H16" s="89"/>
-      <c r="I16" s="89"/>
-      <c r="J16" s="89"/>
-      <c r="K16" s="89"/>
-      <c r="L16" s="89"/>
-      <c r="M16" s="90"/>
+      <c r="G16" s="93"/>
+      <c r="H16" s="93"/>
+      <c r="I16" s="93"/>
+      <c r="J16" s="93"/>
+      <c r="K16" s="93"/>
+      <c r="L16" s="93"/>
+      <c r="M16" s="94"/>
     </row>
     <row r="17" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="20" t="s">
@@ -4367,12 +4377,12 @@
       <c r="G17" s="37"/>
       <c r="H17" s="37"/>
       <c r="I17" s="38"/>
-      <c r="J17" s="88" t="s">
+      <c r="J17" s="92" t="s">
         <v>202</v>
       </c>
-      <c r="K17" s="89"/>
-      <c r="L17" s="89"/>
-      <c r="M17" s="90"/>
+      <c r="K17" s="93"/>
+      <c r="L17" s="93"/>
+      <c r="M17" s="94"/>
     </row>
     <row r="18" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="20" t="s">
@@ -4387,13 +4397,13 @@
       <c r="F18" s="36"/>
       <c r="G18" s="37"/>
       <c r="H18" s="38"/>
-      <c r="I18" s="88" t="s">
+      <c r="I18" s="92" t="s">
         <v>203</v>
       </c>
-      <c r="J18" s="89"/>
-      <c r="K18" s="89"/>
-      <c r="L18" s="89"/>
-      <c r="M18" s="90"/>
+      <c r="J18" s="93"/>
+      <c r="K18" s="93"/>
+      <c r="L18" s="93"/>
+      <c r="M18" s="94"/>
     </row>
     <row r="19" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="20" t="s">
@@ -4446,12 +4456,12 @@
       <c r="I20" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="J20" s="88" t="s">
+      <c r="J20" s="92" t="s">
         <v>204</v>
       </c>
-      <c r="K20" s="89"/>
-      <c r="L20" s="89"/>
-      <c r="M20" s="90"/>
+      <c r="K20" s="93"/>
+      <c r="L20" s="93"/>
+      <c r="M20" s="94"/>
     </row>
     <row r="21" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="20" t="s">
@@ -4469,12 +4479,12 @@
       <c r="I21" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="J21" s="88" t="s">
+      <c r="J21" s="92" t="s">
         <v>204</v>
       </c>
-      <c r="K21" s="89"/>
-      <c r="L21" s="89"/>
-      <c r="M21" s="90"/>
+      <c r="K21" s="93"/>
+      <c r="L21" s="93"/>
+      <c r="M21" s="94"/>
     </row>
     <row r="22" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="20" t="s">
@@ -4492,12 +4502,12 @@
       <c r="I22" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="J22" s="88" t="s">
+      <c r="J22" s="92" t="s">
         <v>204</v>
       </c>
-      <c r="K22" s="89"/>
-      <c r="L22" s="89"/>
-      <c r="M22" s="90"/>
+      <c r="K22" s="93"/>
+      <c r="L22" s="93"/>
+      <c r="M22" s="94"/>
     </row>
     <row r="23" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="20" t="s">
@@ -4509,16 +4519,16 @@
       <c r="E23" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="F23" s="88" t="s">
+      <c r="F23" s="92" t="s">
         <v>205</v>
       </c>
-      <c r="G23" s="89"/>
-      <c r="H23" s="89"/>
-      <c r="I23" s="89"/>
-      <c r="J23" s="89"/>
-      <c r="K23" s="89"/>
-      <c r="L23" s="89"/>
-      <c r="M23" s="90"/>
+      <c r="G23" s="93"/>
+      <c r="H23" s="93"/>
+      <c r="I23" s="93"/>
+      <c r="J23" s="93"/>
+      <c r="K23" s="93"/>
+      <c r="L23" s="93"/>
+      <c r="M23" s="94"/>
     </row>
     <row r="24" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="20" t="s">
@@ -4530,16 +4540,16 @@
       <c r="E24" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F24" s="88" t="s">
+      <c r="F24" s="92" t="s">
         <v>206</v>
       </c>
-      <c r="G24" s="89"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="89"/>
-      <c r="J24" s="89"/>
-      <c r="K24" s="89"/>
-      <c r="L24" s="89"/>
-      <c r="M24" s="90"/>
+      <c r="G24" s="93"/>
+      <c r="H24" s="93"/>
+      <c r="I24" s="93"/>
+      <c r="J24" s="93"/>
+      <c r="K24" s="93"/>
+      <c r="L24" s="93"/>
+      <c r="M24" s="94"/>
     </row>
     <row r="25" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="20" t="s">
@@ -4555,12 +4565,12 @@
       <c r="G25" s="37"/>
       <c r="H25" s="37"/>
       <c r="I25" s="38"/>
-      <c r="J25" s="88" t="s">
+      <c r="J25" s="92" t="s">
         <v>207</v>
       </c>
-      <c r="K25" s="89"/>
-      <c r="L25" s="89"/>
-      <c r="M25" s="90"/>
+      <c r="K25" s="93"/>
+      <c r="L25" s="93"/>
+      <c r="M25" s="94"/>
     </row>
     <row r="26" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="20" t="s">
@@ -4610,16 +4620,16 @@
       <c r="E28" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="F28" s="78" t="s">
+      <c r="F28" s="82" t="s">
         <v>201</v>
       </c>
-      <c r="G28" s="86"/>
-      <c r="H28" s="86"/>
-      <c r="I28" s="86"/>
-      <c r="J28" s="86"/>
-      <c r="K28" s="86"/>
-      <c r="L28" s="86"/>
-      <c r="M28" s="87"/>
+      <c r="G28" s="90"/>
+      <c r="H28" s="90"/>
+      <c r="I28" s="90"/>
+      <c r="J28" s="90"/>
+      <c r="K28" s="90"/>
+      <c r="L28" s="90"/>
+      <c r="M28" s="91"/>
     </row>
     <row r="29" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="20" t="s">
@@ -4635,12 +4645,12 @@
       <c r="G29" s="28"/>
       <c r="H29" s="28"/>
       <c r="I29" s="29"/>
-      <c r="J29" s="78" t="s">
+      <c r="J29" s="82" t="s">
         <v>202</v>
       </c>
-      <c r="K29" s="86"/>
-      <c r="L29" s="86"/>
-      <c r="M29" s="87"/>
+      <c r="K29" s="90"/>
+      <c r="L29" s="90"/>
+      <c r="M29" s="91"/>
     </row>
     <row r="30" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="20" t="s">
@@ -4652,16 +4662,16 @@
       <c r="E30" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="F30" s="78" t="s">
+      <c r="F30" s="82" t="s">
         <v>201</v>
       </c>
-      <c r="G30" s="86"/>
-      <c r="H30" s="86"/>
-      <c r="I30" s="86"/>
-      <c r="J30" s="86"/>
-      <c r="K30" s="86"/>
-      <c r="L30" s="86"/>
-      <c r="M30" s="87"/>
+      <c r="G30" s="90"/>
+      <c r="H30" s="90"/>
+      <c r="I30" s="90"/>
+      <c r="J30" s="90"/>
+      <c r="K30" s="90"/>
+      <c r="L30" s="90"/>
+      <c r="M30" s="91"/>
     </row>
     <row r="31" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="20" t="s">
@@ -4677,12 +4687,12 @@
       <c r="G31" s="28"/>
       <c r="H31" s="28"/>
       <c r="I31" s="29"/>
-      <c r="J31" s="78" t="s">
+      <c r="J31" s="82" t="s">
         <v>202</v>
       </c>
-      <c r="K31" s="86"/>
-      <c r="L31" s="86"/>
-      <c r="M31" s="87"/>
+      <c r="K31" s="90"/>
+      <c r="L31" s="90"/>
+      <c r="M31" s="91"/>
     </row>
     <row r="32" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="20" t="s">
@@ -4694,16 +4704,16 @@
       <c r="E32" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="F32" s="78" t="s">
+      <c r="F32" s="82" t="s">
         <v>201</v>
       </c>
-      <c r="G32" s="86"/>
-      <c r="H32" s="86"/>
-      <c r="I32" s="86"/>
-      <c r="J32" s="86"/>
-      <c r="K32" s="86"/>
-      <c r="L32" s="86"/>
-      <c r="M32" s="87"/>
+      <c r="G32" s="90"/>
+      <c r="H32" s="90"/>
+      <c r="I32" s="90"/>
+      <c r="J32" s="90"/>
+      <c r="K32" s="90"/>
+      <c r="L32" s="90"/>
+      <c r="M32" s="91"/>
     </row>
     <row r="33" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="20" t="s">
@@ -4719,12 +4729,12 @@
       <c r="G33" s="28"/>
       <c r="H33" s="28"/>
       <c r="I33" s="29"/>
-      <c r="J33" s="78" t="s">
+      <c r="J33" s="82" t="s">
         <v>202</v>
       </c>
-      <c r="K33" s="86"/>
-      <c r="L33" s="86"/>
-      <c r="M33" s="87"/>
+      <c r="K33" s="90"/>
+      <c r="L33" s="90"/>
+      <c r="M33" s="91"/>
     </row>
     <row r="34" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="20" t="s">
@@ -4739,13 +4749,13 @@
       <c r="F34" s="27"/>
       <c r="G34" s="28"/>
       <c r="H34" s="29"/>
-      <c r="I34" s="78" t="s">
+      <c r="I34" s="82" t="s">
         <v>203</v>
       </c>
-      <c r="J34" s="86"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="86"/>
-      <c r="M34" s="87"/>
+      <c r="J34" s="90"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="90"/>
+      <c r="M34" s="91"/>
     </row>
     <row r="35" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="20" t="s">
@@ -4798,12 +4808,12 @@
       <c r="I36" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="J36" s="78" t="s">
+      <c r="J36" s="82" t="s">
         <v>204</v>
       </c>
-      <c r="K36" s="86"/>
-      <c r="L36" s="86"/>
-      <c r="M36" s="87"/>
+      <c r="K36" s="90"/>
+      <c r="L36" s="90"/>
+      <c r="M36" s="91"/>
     </row>
     <row r="37" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="20" t="s">
@@ -4821,12 +4831,12 @@
       <c r="I37" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="J37" s="78" t="s">
+      <c r="J37" s="82" t="s">
         <v>204</v>
       </c>
-      <c r="K37" s="86"/>
-      <c r="L37" s="86"/>
-      <c r="M37" s="87"/>
+      <c r="K37" s="90"/>
+      <c r="L37" s="90"/>
+      <c r="M37" s="91"/>
     </row>
     <row r="38" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="20" t="s">
@@ -4844,12 +4854,12 @@
       <c r="I38" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="J38" s="78" t="s">
+      <c r="J38" s="82" t="s">
         <v>204</v>
       </c>
-      <c r="K38" s="86"/>
-      <c r="L38" s="86"/>
-      <c r="M38" s="87"/>
+      <c r="K38" s="90"/>
+      <c r="L38" s="90"/>
+      <c r="M38" s="91"/>
     </row>
     <row r="39" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="20" t="s">
@@ -4861,16 +4871,16 @@
       <c r="E39" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="F39" s="78" t="s">
+      <c r="F39" s="82" t="s">
         <v>205</v>
       </c>
-      <c r="G39" s="86"/>
-      <c r="H39" s="86"/>
-      <c r="I39" s="86"/>
-      <c r="J39" s="86"/>
-      <c r="K39" s="86"/>
-      <c r="L39" s="86"/>
-      <c r="M39" s="87"/>
+      <c r="G39" s="90"/>
+      <c r="H39" s="90"/>
+      <c r="I39" s="90"/>
+      <c r="J39" s="90"/>
+      <c r="K39" s="90"/>
+      <c r="L39" s="90"/>
+      <c r="M39" s="91"/>
     </row>
     <row r="40" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="20" t="s">
@@ -4882,16 +4892,16 @@
       <c r="E40" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="F40" s="78" t="s">
+      <c r="F40" s="82" t="s">
         <v>206</v>
       </c>
-      <c r="G40" s="86"/>
-      <c r="H40" s="86"/>
-      <c r="I40" s="86"/>
-      <c r="J40" s="86"/>
-      <c r="K40" s="86"/>
-      <c r="L40" s="86"/>
-      <c r="M40" s="87"/>
+      <c r="G40" s="90"/>
+      <c r="H40" s="90"/>
+      <c r="I40" s="90"/>
+      <c r="J40" s="90"/>
+      <c r="K40" s="90"/>
+      <c r="L40" s="90"/>
+      <c r="M40" s="91"/>
     </row>
     <row r="41" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="20" t="s">
@@ -4907,12 +4917,12 @@
       <c r="G41" s="28"/>
       <c r="H41" s="28"/>
       <c r="I41" s="29"/>
-      <c r="J41" s="78" t="s">
+      <c r="J41" s="82" t="s">
         <v>207</v>
       </c>
-      <c r="K41" s="86"/>
-      <c r="L41" s="86"/>
-      <c r="M41" s="87"/>
+      <c r="K41" s="90"/>
+      <c r="L41" s="90"/>
+      <c r="M41" s="91"/>
     </row>
     <row r="42" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="20" t="s">
@@ -4947,12 +4957,12 @@
       <c r="G43" s="28"/>
       <c r="H43" s="28"/>
       <c r="I43" s="35"/>
-      <c r="J43" s="78" t="s">
+      <c r="J43" s="82" t="s">
         <v>135</v>
       </c>
-      <c r="K43" s="86"/>
-      <c r="L43" s="86"/>
-      <c r="M43" s="87"/>
+      <c r="K43" s="90"/>
+      <c r="L43" s="90"/>
+      <c r="M43" s="91"/>
     </row>
     <row r="44" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="21" t="s">
@@ -5357,16 +5367,16 @@
       <c r="E6" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="F6" s="73" t="s">
+      <c r="F6" s="76" t="s">
         <v>107</v>
       </c>
-      <c r="G6" s="82"/>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
-      <c r="J6" s="82"/>
-      <c r="K6" s="82"/>
-      <c r="L6" s="82"/>
-      <c r="M6" s="74"/>
+      <c r="G6" s="86"/>
+      <c r="H6" s="86"/>
+      <c r="I6" s="86"/>
+      <c r="J6" s="86"/>
+      <c r="K6" s="86"/>
+      <c r="L6" s="86"/>
+      <c r="M6" s="77"/>
     </row>
     <row r="7" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C7" s="25" t="s">
@@ -5378,16 +5388,16 @@
       <c r="E7" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="F7" s="73" t="s">
+      <c r="F7" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="G7" s="82"/>
-      <c r="H7" s="82"/>
-      <c r="I7" s="82"/>
-      <c r="J7" s="82"/>
-      <c r="K7" s="82"/>
-      <c r="L7" s="82"/>
-      <c r="M7" s="74"/>
+      <c r="G7" s="86"/>
+      <c r="H7" s="86"/>
+      <c r="I7" s="86"/>
+      <c r="J7" s="86"/>
+      <c r="K7" s="86"/>
+      <c r="L7" s="86"/>
+      <c r="M7" s="77"/>
     </row>
     <row r="8" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
@@ -5399,16 +5409,16 @@
       <c r="E8" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F8" s="73" t="s">
+      <c r="F8" s="76" t="s">
         <v>105</v>
       </c>
-      <c r="G8" s="82"/>
-      <c r="H8" s="82"/>
-      <c r="I8" s="82"/>
-      <c r="J8" s="82"/>
-      <c r="K8" s="82"/>
-      <c r="L8" s="82"/>
-      <c r="M8" s="74"/>
+      <c r="G8" s="86"/>
+      <c r="H8" s="86"/>
+      <c r="I8" s="86"/>
+      <c r="J8" s="86"/>
+      <c r="K8" s="86"/>
+      <c r="L8" s="86"/>
+      <c r="M8" s="77"/>
     </row>
     <row r="9" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
@@ -5420,16 +5430,16 @@
       <c r="E9" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F9" s="73" t="s">
+      <c r="F9" s="76" t="s">
         <v>198</v>
       </c>
-      <c r="G9" s="82"/>
-      <c r="H9" s="82"/>
-      <c r="I9" s="82"/>
-      <c r="J9" s="82"/>
-      <c r="K9" s="82"/>
-      <c r="L9" s="82"/>
-      <c r="M9" s="74"/>
+      <c r="G9" s="86"/>
+      <c r="H9" s="86"/>
+      <c r="I9" s="86"/>
+      <c r="J9" s="86"/>
+      <c r="K9" s="86"/>
+      <c r="L9" s="86"/>
+      <c r="M9" s="77"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B19" t="s">
@@ -5491,12 +5501,12 @@
       <c r="I21" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="J21" s="73" t="s">
+      <c r="J21" s="76" t="s">
         <v>124</v>
       </c>
-      <c r="K21" s="82"/>
-      <c r="L21" s="82"/>
-      <c r="M21" s="74"/>
+      <c r="K21" s="86"/>
+      <c r="L21" s="86"/>
+      <c r="M21" s="77"/>
     </row>
     <row r="22" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="20" t="s">
@@ -5518,12 +5528,12 @@
       <c r="I22" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="J22" s="73" t="s">
+      <c r="J22" s="76" t="s">
         <v>124</v>
       </c>
-      <c r="K22" s="82"/>
-      <c r="L22" s="82"/>
-      <c r="M22" s="74"/>
+      <c r="K22" s="86"/>
+      <c r="L22" s="86"/>
+      <c r="M22" s="77"/>
     </row>
     <row r="23" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="20" t="s">
@@ -5533,18 +5543,18 @@
         <v>46</v>
       </c>
       <c r="E23" s="6"/>
-      <c r="F23" s="73" t="s">
+      <c r="F23" s="76" t="s">
         <v>125</v>
       </c>
-      <c r="G23" s="74"/>
-      <c r="H23" s="73" t="s">
+      <c r="G23" s="77"/>
+      <c r="H23" s="76" t="s">
         <v>126</v>
       </c>
-      <c r="I23" s="82"/>
-      <c r="J23" s="82"/>
-      <c r="K23" s="82"/>
-      <c r="L23" s="82"/>
-      <c r="M23" s="74"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="86"/>
+      <c r="K23" s="86"/>
+      <c r="L23" s="86"/>
+      <c r="M23" s="77"/>
     </row>
     <row r="24" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="20" t="s">
@@ -5554,10 +5564,10 @@
         <v>46</v>
       </c>
       <c r="E24" s="6"/>
-      <c r="F24" s="73" t="s">
+      <c r="F24" s="76" t="s">
         <v>125</v>
       </c>
-      <c r="G24" s="74"/>
+      <c r="G24" s="77"/>
       <c r="H24" s="19"/>
       <c r="I24" s="12" t="s">
         <v>129</v>
@@ -5565,11 +5575,11 @@
       <c r="J24" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="K24" s="73" t="s">
+      <c r="K24" s="76" t="s">
         <v>127</v>
       </c>
-      <c r="L24" s="82"/>
-      <c r="M24" s="74"/>
+      <c r="L24" s="86"/>
+      <c r="M24" s="77"/>
     </row>
     <row r="25" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="20" t="s">
@@ -5579,18 +5589,18 @@
         <v>46</v>
       </c>
       <c r="E25" s="6"/>
-      <c r="F25" s="73" t="s">
+      <c r="F25" s="76" t="s">
         <v>130</v>
       </c>
-      <c r="G25" s="82"/>
-      <c r="H25" s="82"/>
-      <c r="I25" s="74"/>
-      <c r="J25" s="73" t="s">
+      <c r="G25" s="86"/>
+      <c r="H25" s="86"/>
+      <c r="I25" s="77"/>
+      <c r="J25" s="76" t="s">
         <v>131</v>
       </c>
-      <c r="K25" s="82"/>
-      <c r="L25" s="82"/>
-      <c r="M25" s="74"/>
+      <c r="K25" s="86"/>
+      <c r="L25" s="86"/>
+      <c r="M25" s="77"/>
     </row>
     <row r="26" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="20" t="s">
@@ -5600,18 +5610,18 @@
         <v>46</v>
       </c>
       <c r="E26" s="6"/>
-      <c r="F26" s="73" t="s">
+      <c r="F26" s="76" t="s">
         <v>130</v>
       </c>
-      <c r="G26" s="82"/>
-      <c r="H26" s="82"/>
-      <c r="I26" s="74"/>
-      <c r="J26" s="73" t="s">
+      <c r="G26" s="86"/>
+      <c r="H26" s="86"/>
+      <c r="I26" s="77"/>
+      <c r="J26" s="76" t="s">
         <v>131</v>
       </c>
-      <c r="K26" s="82"/>
-      <c r="L26" s="82"/>
-      <c r="M26" s="74"/>
+      <c r="K26" s="86"/>
+      <c r="L26" s="86"/>
+      <c r="M26" s="77"/>
     </row>
     <row r="27" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="20" t="s">
@@ -5621,18 +5631,18 @@
         <v>46</v>
       </c>
       <c r="E27" s="6"/>
-      <c r="F27" s="73" t="s">
+      <c r="F27" s="76" t="s">
         <v>132</v>
       </c>
-      <c r="G27" s="82"/>
-      <c r="H27" s="82"/>
-      <c r="I27" s="74"/>
-      <c r="J27" s="73" t="s">
+      <c r="G27" s="86"/>
+      <c r="H27" s="86"/>
+      <c r="I27" s="77"/>
+      <c r="J27" s="76" t="s">
         <v>133</v>
       </c>
-      <c r="K27" s="82"/>
-      <c r="L27" s="82"/>
-      <c r="M27" s="74"/>
+      <c r="K27" s="86"/>
+      <c r="L27" s="86"/>
+      <c r="M27" s="77"/>
     </row>
     <row r="28" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C28" s="20" t="s">
@@ -5642,18 +5652,18 @@
         <v>46</v>
       </c>
       <c r="E28" s="6"/>
-      <c r="F28" s="73" t="s">
+      <c r="F28" s="76" t="s">
         <v>132</v>
       </c>
-      <c r="G28" s="82"/>
-      <c r="H28" s="82"/>
-      <c r="I28" s="74"/>
-      <c r="J28" s="73" t="s">
+      <c r="G28" s="86"/>
+      <c r="H28" s="86"/>
+      <c r="I28" s="77"/>
+      <c r="J28" s="76" t="s">
         <v>133</v>
       </c>
-      <c r="K28" s="82"/>
-      <c r="L28" s="82"/>
-      <c r="M28" s="74"/>
+      <c r="K28" s="86"/>
+      <c r="L28" s="86"/>
+      <c r="M28" s="77"/>
     </row>
     <row r="29" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="20" t="s">
@@ -5707,16 +5717,16 @@
       <c r="E31" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="F31" s="73" t="s">
+      <c r="F31" s="76" t="s">
         <v>160</v>
       </c>
-      <c r="G31" s="82"/>
-      <c r="H31" s="82"/>
-      <c r="I31" s="82"/>
-      <c r="J31" s="82"/>
-      <c r="K31" s="82"/>
-      <c r="L31" s="82"/>
-      <c r="M31" s="74"/>
+      <c r="G31" s="86"/>
+      <c r="H31" s="86"/>
+      <c r="I31" s="86"/>
+      <c r="J31" s="86"/>
+      <c r="K31" s="86"/>
+      <c r="L31" s="86"/>
+      <c r="M31" s="77"/>
     </row>
     <row r="32" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="20" t="s">
@@ -5726,16 +5736,16 @@
         <v>46</v>
       </c>
       <c r="E32" s="6"/>
-      <c r="F32" s="73" t="s">
+      <c r="F32" s="76" t="s">
         <v>160</v>
       </c>
-      <c r="G32" s="82"/>
-      <c r="H32" s="82"/>
-      <c r="I32" s="82"/>
-      <c r="J32" s="82"/>
-      <c r="K32" s="82"/>
-      <c r="L32" s="82"/>
-      <c r="M32" s="74"/>
+      <c r="G32" s="86"/>
+      <c r="H32" s="86"/>
+      <c r="I32" s="86"/>
+      <c r="J32" s="86"/>
+      <c r="K32" s="86"/>
+      <c r="L32" s="86"/>
+      <c r="M32" s="77"/>
     </row>
     <row r="33" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="20" t="s">
@@ -5745,16 +5755,16 @@
         <v>46</v>
       </c>
       <c r="E33" s="6"/>
-      <c r="F33" s="73" t="s">
+      <c r="F33" s="76" t="s">
         <v>160</v>
       </c>
-      <c r="G33" s="82"/>
-      <c r="H33" s="82"/>
-      <c r="I33" s="82"/>
-      <c r="J33" s="82"/>
-      <c r="K33" s="82"/>
-      <c r="L33" s="82"/>
-      <c r="M33" s="74"/>
+      <c r="G33" s="86"/>
+      <c r="H33" s="86"/>
+      <c r="I33" s="86"/>
+      <c r="J33" s="86"/>
+      <c r="K33" s="86"/>
+      <c r="L33" s="86"/>
+      <c r="M33" s="77"/>
     </row>
     <row r="34" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="20" t="s">
@@ -5764,16 +5774,16 @@
         <v>46</v>
       </c>
       <c r="E34" s="6"/>
-      <c r="F34" s="73" t="s">
+      <c r="F34" s="76" t="s">
         <v>160</v>
       </c>
-      <c r="G34" s="82"/>
-      <c r="H34" s="82"/>
-      <c r="I34" s="82"/>
-      <c r="J34" s="82"/>
-      <c r="K34" s="82"/>
-      <c r="L34" s="82"/>
-      <c r="M34" s="74"/>
+      <c r="G34" s="86"/>
+      <c r="H34" s="86"/>
+      <c r="I34" s="86"/>
+      <c r="J34" s="86"/>
+      <c r="K34" s="86"/>
+      <c r="L34" s="86"/>
+      <c r="M34" s="77"/>
     </row>
     <row r="35" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="20" t="s">
@@ -5783,16 +5793,16 @@
         <v>46</v>
       </c>
       <c r="E35" s="6"/>
-      <c r="F35" s="73" t="s">
+      <c r="F35" s="76" t="s">
         <v>160</v>
       </c>
-      <c r="G35" s="82"/>
-      <c r="H35" s="82"/>
-      <c r="I35" s="82"/>
-      <c r="J35" s="82"/>
-      <c r="K35" s="82"/>
-      <c r="L35" s="82"/>
-      <c r="M35" s="74"/>
+      <c r="G35" s="86"/>
+      <c r="H35" s="86"/>
+      <c r="I35" s="86"/>
+      <c r="J35" s="86"/>
+      <c r="K35" s="86"/>
+      <c r="L35" s="86"/>
+      <c r="M35" s="77"/>
     </row>
     <row r="36" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C36" s="20" t="s">
@@ -5802,16 +5812,16 @@
         <v>46</v>
       </c>
       <c r="E36" s="6"/>
-      <c r="F36" s="73" t="s">
+      <c r="F36" s="76" t="s">
         <v>160</v>
       </c>
-      <c r="G36" s="82"/>
-      <c r="H36" s="82"/>
-      <c r="I36" s="82"/>
-      <c r="J36" s="82"/>
-      <c r="K36" s="82"/>
-      <c r="L36" s="82"/>
-      <c r="M36" s="74"/>
+      <c r="G36" s="86"/>
+      <c r="H36" s="86"/>
+      <c r="I36" s="86"/>
+      <c r="J36" s="86"/>
+      <c r="K36" s="86"/>
+      <c r="L36" s="86"/>
+      <c r="M36" s="77"/>
     </row>
     <row r="37" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="20" t="s">
@@ -5821,16 +5831,16 @@
         <v>41</v>
       </c>
       <c r="E37" s="1"/>
-      <c r="F37" s="73" t="s">
+      <c r="F37" s="76" t="s">
         <v>160</v>
       </c>
-      <c r="G37" s="82"/>
-      <c r="H37" s="82"/>
-      <c r="I37" s="82"/>
-      <c r="J37" s="82"/>
-      <c r="K37" s="82"/>
-      <c r="L37" s="82"/>
-      <c r="M37" s="74"/>
+      <c r="G37" s="86"/>
+      <c r="H37" s="86"/>
+      <c r="I37" s="86"/>
+      <c r="J37" s="86"/>
+      <c r="K37" s="86"/>
+      <c r="L37" s="86"/>
+      <c r="M37" s="77"/>
     </row>
     <row r="38" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="20" t="s">
@@ -5840,16 +5850,16 @@
         <v>41</v>
       </c>
       <c r="E38" s="1"/>
-      <c r="F38" s="73" t="s">
+      <c r="F38" s="76" t="s">
         <v>160</v>
       </c>
-      <c r="G38" s="82"/>
-      <c r="H38" s="82"/>
-      <c r="I38" s="82"/>
-      <c r="J38" s="82"/>
-      <c r="K38" s="82"/>
-      <c r="L38" s="82"/>
-      <c r="M38" s="74"/>
+      <c r="G38" s="86"/>
+      <c r="H38" s="86"/>
+      <c r="I38" s="86"/>
+      <c r="J38" s="86"/>
+      <c r="K38" s="86"/>
+      <c r="L38" s="86"/>
+      <c r="M38" s="77"/>
     </row>
     <row r="39" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="20" t="s">
@@ -5859,16 +5869,16 @@
         <v>41</v>
       </c>
       <c r="E39" s="1"/>
-      <c r="F39" s="73" t="s">
+      <c r="F39" s="76" t="s">
         <v>160</v>
       </c>
-      <c r="G39" s="82"/>
-      <c r="H39" s="82"/>
-      <c r="I39" s="82"/>
-      <c r="J39" s="82"/>
-      <c r="K39" s="82"/>
-      <c r="L39" s="82"/>
-      <c r="M39" s="74"/>
+      <c r="G39" s="86"/>
+      <c r="H39" s="86"/>
+      <c r="I39" s="86"/>
+      <c r="J39" s="86"/>
+      <c r="K39" s="86"/>
+      <c r="L39" s="86"/>
+      <c r="M39" s="77"/>
     </row>
     <row r="40" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="20" t="s">
@@ -5878,16 +5888,16 @@
         <v>41</v>
       </c>
       <c r="E40" s="1"/>
-      <c r="F40" s="73" t="s">
+      <c r="F40" s="76" t="s">
         <v>160</v>
       </c>
-      <c r="G40" s="82"/>
-      <c r="H40" s="82"/>
-      <c r="I40" s="82"/>
-      <c r="J40" s="82"/>
-      <c r="K40" s="82"/>
-      <c r="L40" s="82"/>
-      <c r="M40" s="74"/>
+      <c r="G40" s="86"/>
+      <c r="H40" s="86"/>
+      <c r="I40" s="86"/>
+      <c r="J40" s="86"/>
+      <c r="K40" s="86"/>
+      <c r="L40" s="86"/>
+      <c r="M40" s="77"/>
     </row>
     <row r="41" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="20" t="s">
@@ -5922,11 +5932,11 @@
       <c r="I42" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J42" s="73" t="s">
+      <c r="J42" s="76" t="s">
         <v>159</v>
       </c>
-      <c r="K42" s="82"/>
-      <c r="L42" s="74"/>
+      <c r="K42" s="86"/>
+      <c r="L42" s="77"/>
       <c r="M42" s="14" t="s">
         <v>160</v>
       </c>
@@ -5947,11 +5957,11 @@
       <c r="I43" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J43" s="73" t="s">
+      <c r="J43" s="76" t="s">
         <v>159</v>
       </c>
-      <c r="K43" s="82"/>
-      <c r="L43" s="74"/>
+      <c r="K43" s="86"/>
+      <c r="L43" s="77"/>
       <c r="M43" s="14" t="s">
         <v>160</v>
       </c>
@@ -5972,11 +5982,11 @@
       <c r="I44" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J44" s="73" t="s">
+      <c r="J44" s="76" t="s">
         <v>159</v>
       </c>
-      <c r="K44" s="82"/>
-      <c r="L44" s="74"/>
+      <c r="K44" s="86"/>
+      <c r="L44" s="77"/>
       <c r="M44" s="14" t="s">
         <v>160</v>
       </c>
@@ -5997,11 +6007,11 @@
       <c r="I45" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J45" s="73" t="s">
+      <c r="J45" s="76" t="s">
         <v>159</v>
       </c>
-      <c r="K45" s="82"/>
-      <c r="L45" s="74"/>
+      <c r="K45" s="86"/>
+      <c r="L45" s="77"/>
       <c r="M45" s="14" t="s">
         <v>160</v>
       </c>
@@ -6022,11 +6032,11 @@
       <c r="I46" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J46" s="73" t="s">
+      <c r="J46" s="76" t="s">
         <v>159</v>
       </c>
-      <c r="K46" s="82"/>
-      <c r="L46" s="74"/>
+      <c r="K46" s="86"/>
+      <c r="L46" s="77"/>
       <c r="M46" s="14" t="s">
         <v>160</v>
       </c>
@@ -6047,11 +6057,11 @@
       <c r="I47" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J47" s="73" t="s">
+      <c r="J47" s="76" t="s">
         <v>159</v>
       </c>
-      <c r="K47" s="82"/>
-      <c r="L47" s="74"/>
+      <c r="K47" s="86"/>
+      <c r="L47" s="77"/>
       <c r="M47" s="14" t="s">
         <v>160</v>
       </c>
@@ -6072,11 +6082,11 @@
       <c r="I48" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J48" s="73" t="s">
+      <c r="J48" s="76" t="s">
         <v>159</v>
       </c>
-      <c r="K48" s="82"/>
-      <c r="L48" s="74"/>
+      <c r="K48" s="86"/>
+      <c r="L48" s="77"/>
       <c r="M48" s="14" t="s">
         <v>160</v>
       </c>
@@ -6097,11 +6107,11 @@
       <c r="I49" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J49" s="73" t="s">
+      <c r="J49" s="76" t="s">
         <v>159</v>
       </c>
-      <c r="K49" s="82"/>
-      <c r="L49" s="74"/>
+      <c r="K49" s="86"/>
+      <c r="L49" s="77"/>
       <c r="M49" s="14" t="s">
         <v>160</v>
       </c>
@@ -6122,11 +6132,11 @@
       <c r="I50" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J50" s="73" t="s">
+      <c r="J50" s="76" t="s">
         <v>159</v>
       </c>
-      <c r="K50" s="82"/>
-      <c r="L50" s="74"/>
+      <c r="K50" s="86"/>
+      <c r="L50" s="77"/>
       <c r="M50" s="14" t="s">
         <v>160</v>
       </c>
@@ -6156,18 +6166,18 @@
         <v>41</v>
       </c>
       <c r="E52" s="1"/>
-      <c r="F52" s="73" t="s">
+      <c r="F52" s="76" t="s">
         <v>181</v>
       </c>
-      <c r="G52" s="82"/>
-      <c r="H52" s="82"/>
-      <c r="I52" s="74"/>
-      <c r="J52" s="73" t="s">
+      <c r="G52" s="86"/>
+      <c r="H52" s="86"/>
+      <c r="I52" s="77"/>
+      <c r="J52" s="76" t="s">
         <v>182</v>
       </c>
-      <c r="K52" s="82"/>
-      <c r="L52" s="82"/>
-      <c r="M52" s="74"/>
+      <c r="K52" s="86"/>
+      <c r="L52" s="86"/>
+      <c r="M52" s="77"/>
     </row>
     <row r="53" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="21" t="s">
@@ -6177,18 +6187,18 @@
         <v>96</v>
       </c>
       <c r="E53" s="13"/>
-      <c r="F53" s="73" t="s">
+      <c r="F53" s="76" t="s">
         <v>181</v>
       </c>
-      <c r="G53" s="82"/>
-      <c r="H53" s="82"/>
-      <c r="I53" s="74"/>
-      <c r="J53" s="73" t="s">
+      <c r="G53" s="86"/>
+      <c r="H53" s="86"/>
+      <c r="I53" s="77"/>
+      <c r="J53" s="76" t="s">
         <v>182</v>
       </c>
-      <c r="K53" s="82"/>
-      <c r="L53" s="82"/>
-      <c r="M53" s="74"/>
+      <c r="K53" s="86"/>
+      <c r="L53" s="86"/>
+      <c r="M53" s="77"/>
     </row>
     <row r="54" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="20" t="s">
@@ -6198,18 +6208,18 @@
         <v>41</v>
       </c>
       <c r="E54" s="1"/>
-      <c r="F54" s="73" t="s">
+      <c r="F54" s="76" t="s">
         <v>181</v>
       </c>
-      <c r="G54" s="82"/>
-      <c r="H54" s="82"/>
-      <c r="I54" s="74"/>
-      <c r="J54" s="73" t="s">
+      <c r="G54" s="86"/>
+      <c r="H54" s="86"/>
+      <c r="I54" s="77"/>
+      <c r="J54" s="76" t="s">
         <v>182</v>
       </c>
-      <c r="K54" s="82"/>
-      <c r="L54" s="82"/>
-      <c r="M54" s="74"/>
+      <c r="K54" s="86"/>
+      <c r="L54" s="86"/>
+      <c r="M54" s="77"/>
     </row>
     <row r="55" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C55" s="20" t="s">
@@ -6219,18 +6229,18 @@
         <v>41</v>
       </c>
       <c r="E55" s="1"/>
-      <c r="F55" s="73" t="s">
+      <c r="F55" s="76" t="s">
         <v>181</v>
       </c>
-      <c r="G55" s="82"/>
-      <c r="H55" s="82"/>
-      <c r="I55" s="74"/>
-      <c r="J55" s="73" t="s">
+      <c r="G55" s="86"/>
+      <c r="H55" s="86"/>
+      <c r="I55" s="77"/>
+      <c r="J55" s="76" t="s">
         <v>182</v>
       </c>
-      <c r="K55" s="82"/>
-      <c r="L55" s="82"/>
-      <c r="M55" s="74"/>
+      <c r="K55" s="86"/>
+      <c r="L55" s="86"/>
+      <c r="M55" s="77"/>
     </row>
     <row r="56" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="20" t="s">
@@ -6240,18 +6250,18 @@
         <v>41</v>
       </c>
       <c r="E56" s="1"/>
-      <c r="F56" s="73" t="s">
+      <c r="F56" s="76" t="s">
         <v>181</v>
       </c>
-      <c r="G56" s="82"/>
-      <c r="H56" s="82"/>
-      <c r="I56" s="74"/>
-      <c r="J56" s="73" t="s">
+      <c r="G56" s="86"/>
+      <c r="H56" s="86"/>
+      <c r="I56" s="77"/>
+      <c r="J56" s="76" t="s">
         <v>182</v>
       </c>
-      <c r="K56" s="82"/>
-      <c r="L56" s="82"/>
-      <c r="M56" s="74"/>
+      <c r="K56" s="86"/>
+      <c r="L56" s="86"/>
+      <c r="M56" s="77"/>
     </row>
     <row r="57" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C57" s="20" t="s">
@@ -6261,18 +6271,18 @@
         <v>41</v>
       </c>
       <c r="E57" s="1"/>
-      <c r="F57" s="73" t="s">
+      <c r="F57" s="76" t="s">
         <v>181</v>
       </c>
-      <c r="G57" s="82"/>
-      <c r="H57" s="82"/>
-      <c r="I57" s="74"/>
-      <c r="J57" s="73" t="s">
+      <c r="G57" s="86"/>
+      <c r="H57" s="86"/>
+      <c r="I57" s="77"/>
+      <c r="J57" s="76" t="s">
         <v>182</v>
       </c>
-      <c r="K57" s="82"/>
-      <c r="L57" s="82"/>
-      <c r="M57" s="74"/>
+      <c r="K57" s="86"/>
+      <c r="L57" s="86"/>
+      <c r="M57" s="77"/>
     </row>
     <row r="58" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C58" s="20" t="s">
@@ -6282,18 +6292,18 @@
         <v>41</v>
       </c>
       <c r="E58" s="1"/>
-      <c r="F58" s="73" t="s">
+      <c r="F58" s="76" t="s">
         <v>181</v>
       </c>
-      <c r="G58" s="82"/>
-      <c r="H58" s="82"/>
-      <c r="I58" s="74"/>
-      <c r="J58" s="73" t="s">
+      <c r="G58" s="86"/>
+      <c r="H58" s="86"/>
+      <c r="I58" s="77"/>
+      <c r="J58" s="76" t="s">
         <v>182</v>
       </c>
-      <c r="K58" s="82"/>
-      <c r="L58" s="82"/>
-      <c r="M58" s="74"/>
+      <c r="K58" s="86"/>
+      <c r="L58" s="86"/>
+      <c r="M58" s="77"/>
     </row>
     <row r="59" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C59" s="20" t="s">
@@ -6303,18 +6313,18 @@
         <v>41</v>
       </c>
       <c r="E59" s="1"/>
-      <c r="F59" s="73" t="s">
+      <c r="F59" s="76" t="s">
         <v>181</v>
       </c>
-      <c r="G59" s="82"/>
-      <c r="H59" s="82"/>
-      <c r="I59" s="74"/>
-      <c r="J59" s="73" t="s">
+      <c r="G59" s="86"/>
+      <c r="H59" s="86"/>
+      <c r="I59" s="77"/>
+      <c r="J59" s="76" t="s">
         <v>182</v>
       </c>
-      <c r="K59" s="82"/>
-      <c r="L59" s="82"/>
-      <c r="M59" s="74"/>
+      <c r="K59" s="86"/>
+      <c r="L59" s="86"/>
+      <c r="M59" s="77"/>
     </row>
     <row r="60" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C60" s="20" t="s">
@@ -6324,18 +6334,18 @@
         <v>41</v>
       </c>
       <c r="E60" s="1"/>
-      <c r="F60" s="73" t="s">
+      <c r="F60" s="76" t="s">
         <v>181</v>
       </c>
-      <c r="G60" s="82"/>
-      <c r="H60" s="82"/>
-      <c r="I60" s="74"/>
-      <c r="J60" s="73" t="s">
+      <c r="G60" s="86"/>
+      <c r="H60" s="86"/>
+      <c r="I60" s="77"/>
+      <c r="J60" s="76" t="s">
         <v>182</v>
       </c>
-      <c r="K60" s="82"/>
-      <c r="L60" s="82"/>
-      <c r="M60" s="74"/>
+      <c r="K60" s="86"/>
+      <c r="L60" s="86"/>
+      <c r="M60" s="77"/>
     </row>
     <row r="61" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C61" s="20" t="s">
@@ -6370,10 +6380,10 @@
       <c r="I62" s="10"/>
       <c r="J62" s="10"/>
       <c r="K62" s="11"/>
-      <c r="L62" s="78" t="s">
+      <c r="L62" s="82" t="s">
         <v>193</v>
       </c>
-      <c r="M62" s="80"/>
+      <c r="M62" s="84"/>
     </row>
     <row r="63" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C63" s="20" t="s">
@@ -6391,10 +6401,10 @@
       <c r="I63" s="10"/>
       <c r="J63" s="10"/>
       <c r="K63" s="11"/>
-      <c r="L63" s="81" t="s">
+      <c r="L63" s="85" t="s">
         <v>193</v>
       </c>
-      <c r="M63" s="80"/>
+      <c r="M63" s="84"/>
     </row>
     <row r="64" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C64" s="20" t="s">
@@ -6412,10 +6422,10 @@
       <c r="I64" s="10"/>
       <c r="J64" s="10"/>
       <c r="K64" s="11"/>
-      <c r="L64" s="81" t="s">
+      <c r="L64" s="85" t="s">
         <v>193</v>
       </c>
-      <c r="M64" s="80"/>
+      <c r="M64" s="84"/>
     </row>
     <row r="65" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C65" s="20" t="s">
@@ -6433,10 +6443,10 @@
       <c r="I65" s="10"/>
       <c r="J65" s="10"/>
       <c r="K65" s="11"/>
-      <c r="L65" s="81" t="s">
+      <c r="L65" s="85" t="s">
         <v>193</v>
       </c>
-      <c r="M65" s="80"/>
+      <c r="M65" s="84"/>
     </row>
     <row r="66" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C66" s="20" t="s">
@@ -6454,10 +6464,10 @@
       <c r="I66" s="10"/>
       <c r="J66" s="10"/>
       <c r="K66" s="11"/>
-      <c r="L66" s="81" t="s">
+      <c r="L66" s="85" t="s">
         <v>193</v>
       </c>
-      <c r="M66" s="80"/>
+      <c r="M66" s="84"/>
     </row>
     <row r="67" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C67" s="20" t="s">
@@ -6475,10 +6485,10 @@
       <c r="I67" s="10"/>
       <c r="J67" s="10"/>
       <c r="K67" s="11"/>
-      <c r="L67" s="81" t="s">
+      <c r="L67" s="85" t="s">
         <v>193</v>
       </c>
-      <c r="M67" s="80"/>
+      <c r="M67" s="84"/>
     </row>
     <row r="68" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C68" s="20" t="s">
@@ -6496,10 +6506,10 @@
       <c r="I68" s="10"/>
       <c r="J68" s="10"/>
       <c r="K68" s="11"/>
-      <c r="L68" s="81" t="s">
+      <c r="L68" s="85" t="s">
         <v>193</v>
       </c>
-      <c r="M68" s="80"/>
+      <c r="M68" s="84"/>
     </row>
     <row r="69" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C69" s="20" t="s">
@@ -6517,10 +6527,10 @@
       <c r="I69" s="10"/>
       <c r="J69" s="10"/>
       <c r="K69" s="11"/>
-      <c r="L69" s="81" t="s">
+      <c r="L69" s="85" t="s">
         <v>193</v>
       </c>
-      <c r="M69" s="80"/>
+      <c r="M69" s="84"/>
     </row>
     <row r="70" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C70" s="20" t="s">
@@ -6538,10 +6548,10 @@
       <c r="I70" s="10"/>
       <c r="J70" s="10"/>
       <c r="K70" s="11"/>
-      <c r="L70" s="81" t="s">
+      <c r="L70" s="85" t="s">
         <v>193</v>
       </c>
-      <c r="M70" s="80"/>
+      <c r="M70" s="84"/>
     </row>
     <row r="71" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C71" s="20" t="s">
@@ -6752,14 +6762,14 @@
       <c r="E13" s="67" t="s">
         <v>244</v>
       </c>
-      <c r="F13" s="97"/>
-      <c r="G13" s="98"/>
-      <c r="H13" s="98"/>
-      <c r="I13" s="98"/>
-      <c r="J13" s="98"/>
-      <c r="K13" s="98"/>
-      <c r="L13" s="98"/>
-      <c r="M13" s="99"/>
+      <c r="F13" s="101"/>
+      <c r="G13" s="102"/>
+      <c r="H13" s="102"/>
+      <c r="I13" s="102"/>
+      <c r="J13" s="102"/>
+      <c r="K13" s="102"/>
+      <c r="L13" s="102"/>
+      <c r="M13" s="103"/>
     </row>
     <row r="14" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="20" t="s">
@@ -6771,16 +6781,16 @@
       <c r="E14" s="45" t="s">
         <v>134</v>
       </c>
-      <c r="F14" s="75" t="s">
+      <c r="F14" s="78" t="s">
         <v>134</v>
       </c>
-      <c r="G14" s="76"/>
-      <c r="H14" s="76"/>
-      <c r="I14" s="76"/>
-      <c r="J14" s="76"/>
-      <c r="K14" s="76"/>
-      <c r="L14" s="76"/>
-      <c r="M14" s="77"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="79"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="79"/>
+      <c r="K14" s="79"/>
+      <c r="L14" s="79"/>
+      <c r="M14" s="80"/>
     </row>
     <row r="15" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="20" t="s">
@@ -6792,16 +6802,16 @@
       <c r="E15" s="45" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="75" t="s">
+      <c r="F15" s="78" t="s">
         <v>245</v>
       </c>
-      <c r="G15" s="76"/>
-      <c r="H15" s="76"/>
-      <c r="I15" s="76"/>
-      <c r="J15" s="76"/>
-      <c r="K15" s="76"/>
-      <c r="L15" s="76"/>
-      <c r="M15" s="77"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="79"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="79"/>
+      <c r="K15" s="79"/>
+      <c r="L15" s="79"/>
+      <c r="M15" s="80"/>
     </row>
     <row r="16" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="20" t="s">
@@ -6813,16 +6823,16 @@
       <c r="E16" s="44" t="s">
         <v>246</v>
       </c>
-      <c r="F16" s="75" t="s">
+      <c r="F16" s="78" t="s">
         <v>246</v>
       </c>
-      <c r="G16" s="76"/>
-      <c r="H16" s="76"/>
-      <c r="I16" s="76"/>
-      <c r="J16" s="76"/>
-      <c r="K16" s="76"/>
-      <c r="L16" s="76"/>
-      <c r="M16" s="77"/>
+      <c r="G16" s="79"/>
+      <c r="H16" s="79"/>
+      <c r="I16" s="79"/>
+      <c r="J16" s="79"/>
+      <c r="K16" s="79"/>
+      <c r="L16" s="79"/>
+      <c r="M16" s="80"/>
     </row>
     <row r="17" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="20" t="s">
@@ -6832,7 +6842,7 @@
         <v>46</v>
       </c>
       <c r="E17" s="45" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F17" s="47" t="s">
         <v>247</v>
@@ -6844,10 +6854,10 @@
         <v>249</v>
       </c>
       <c r="I17" s="59" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J17" s="59" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="K17" s="46"/>
       <c r="L17" s="47" t="s">
@@ -6865,18 +6875,18 @@
         <v>46</v>
       </c>
       <c r="E18" s="67"/>
-      <c r="F18" s="100" t="s">
+      <c r="F18" s="104" t="s">
         <v>252</v>
       </c>
-      <c r="G18" s="101"/>
-      <c r="H18" s="101"/>
-      <c r="I18" s="101"/>
-      <c r="J18" s="101"/>
-      <c r="K18" s="101"/>
-      <c r="L18" s="101"/>
-      <c r="M18" s="102"/>
+      <c r="G18" s="105"/>
+      <c r="H18" s="105"/>
+      <c r="I18" s="105"/>
+      <c r="J18" s="105"/>
+      <c r="K18" s="105"/>
+      <c r="L18" s="105"/>
+      <c r="M18" s="106"/>
       <c r="N18" s="61" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="19" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -6887,18 +6897,18 @@
         <v>46</v>
       </c>
       <c r="E19" s="67"/>
-      <c r="F19" s="100" t="s">
+      <c r="F19" s="104" t="s">
         <v>253</v>
       </c>
-      <c r="G19" s="101"/>
-      <c r="H19" s="101"/>
-      <c r="I19" s="101"/>
-      <c r="J19" s="101"/>
-      <c r="K19" s="101"/>
-      <c r="L19" s="101"/>
-      <c r="M19" s="102"/>
+      <c r="G19" s="105"/>
+      <c r="H19" s="105"/>
+      <c r="I19" s="105"/>
+      <c r="J19" s="105"/>
+      <c r="K19" s="105"/>
+      <c r="L19" s="105"/>
+      <c r="M19" s="106"/>
       <c r="N19" s="61" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="20" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -6924,13 +6934,13 @@
       <c r="J20" s="60" t="s">
         <v>258</v>
       </c>
-      <c r="K20" s="97"/>
-      <c r="L20" s="99"/>
+      <c r="K20" s="101"/>
+      <c r="L20" s="103"/>
       <c r="M20" s="59" t="s">
         <v>259</v>
       </c>
       <c r="N20" s="62" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="21" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -6947,8 +6957,8 @@
       <c r="G21" s="47" t="s">
         <v>261</v>
       </c>
-      <c r="H21" s="97"/>
-      <c r="I21" s="99"/>
+      <c r="H21" s="101"/>
+      <c r="I21" s="103"/>
       <c r="J21" s="60" t="s">
         <v>262</v>
       </c>
@@ -6970,18 +6980,18 @@
         <v>46</v>
       </c>
       <c r="E22" s="45"/>
-      <c r="F22" s="103" t="s">
+      <c r="F22" s="107" t="s">
         <v>266</v>
       </c>
-      <c r="G22" s="104"/>
-      <c r="H22" s="104"/>
-      <c r="I22" s="104"/>
-      <c r="J22" s="104"/>
-      <c r="K22" s="104"/>
-      <c r="L22" s="104"/>
-      <c r="M22" s="105"/>
+      <c r="G22" s="108"/>
+      <c r="H22" s="108"/>
+      <c r="I22" s="108"/>
+      <c r="J22" s="108"/>
+      <c r="K22" s="108"/>
+      <c r="L22" s="108"/>
+      <c r="M22" s="109"/>
       <c r="N22" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="23" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -6992,18 +7002,18 @@
         <v>46</v>
       </c>
       <c r="E23" s="44"/>
-      <c r="F23" s="103" t="s">
+      <c r="F23" s="107" t="s">
         <v>267</v>
       </c>
-      <c r="G23" s="104"/>
-      <c r="H23" s="104"/>
-      <c r="I23" s="104"/>
-      <c r="J23" s="104"/>
-      <c r="K23" s="104"/>
-      <c r="L23" s="104"/>
-      <c r="M23" s="105"/>
+      <c r="G23" s="108"/>
+      <c r="H23" s="108"/>
+      <c r="I23" s="108"/>
+      <c r="J23" s="108"/>
+      <c r="K23" s="108"/>
+      <c r="L23" s="108"/>
+      <c r="M23" s="109"/>
       <c r="N23" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="24" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7014,18 +7024,18 @@
         <v>46</v>
       </c>
       <c r="E24" s="44"/>
-      <c r="F24" s="103" t="s">
+      <c r="F24" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="G24" s="104"/>
-      <c r="H24" s="104"/>
-      <c r="I24" s="104"/>
-      <c r="J24" s="104"/>
-      <c r="K24" s="104"/>
-      <c r="L24" s="104"/>
-      <c r="M24" s="105"/>
+      <c r="G24" s="108"/>
+      <c r="H24" s="108"/>
+      <c r="I24" s="108"/>
+      <c r="J24" s="108"/>
+      <c r="K24" s="108"/>
+      <c r="L24" s="108"/>
+      <c r="M24" s="109"/>
       <c r="N24" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="25" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7036,18 +7046,18 @@
         <v>46</v>
       </c>
       <c r="E25" s="44"/>
-      <c r="F25" s="103" t="s">
+      <c r="F25" s="107" t="s">
         <v>269</v>
       </c>
-      <c r="G25" s="104"/>
-      <c r="H25" s="104"/>
-      <c r="I25" s="104"/>
-      <c r="J25" s="104"/>
-      <c r="K25" s="104"/>
-      <c r="L25" s="104"/>
-      <c r="M25" s="105"/>
+      <c r="G25" s="108"/>
+      <c r="H25" s="108"/>
+      <c r="I25" s="108"/>
+      <c r="J25" s="108"/>
+      <c r="K25" s="108"/>
+      <c r="L25" s="108"/>
+      <c r="M25" s="109"/>
       <c r="N25" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="26" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7058,18 +7068,18 @@
         <v>46</v>
       </c>
       <c r="E26" s="66"/>
-      <c r="F26" s="100" t="s">
+      <c r="F26" s="104" t="s">
         <v>270</v>
       </c>
-      <c r="G26" s="101"/>
-      <c r="H26" s="101"/>
-      <c r="I26" s="101"/>
-      <c r="J26" s="101"/>
-      <c r="K26" s="101"/>
-      <c r="L26" s="101"/>
-      <c r="M26" s="102"/>
+      <c r="G26" s="105"/>
+      <c r="H26" s="105"/>
+      <c r="I26" s="105"/>
+      <c r="J26" s="105"/>
+      <c r="K26" s="105"/>
+      <c r="L26" s="105"/>
+      <c r="M26" s="106"/>
       <c r="N26" s="63" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="27" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7080,18 +7090,18 @@
         <v>46</v>
       </c>
       <c r="E27" s="66"/>
-      <c r="F27" s="97"/>
-      <c r="G27" s="98"/>
-      <c r="H27" s="98"/>
-      <c r="I27" s="98"/>
-      <c r="J27" s="99"/>
-      <c r="K27" s="100" t="s">
+      <c r="F27" s="101"/>
+      <c r="G27" s="102"/>
+      <c r="H27" s="102"/>
+      <c r="I27" s="102"/>
+      <c r="J27" s="103"/>
+      <c r="K27" s="104" t="s">
         <v>271</v>
       </c>
-      <c r="L27" s="101"/>
-      <c r="M27" s="102"/>
+      <c r="L27" s="105"/>
+      <c r="M27" s="106"/>
       <c r="N27" s="61" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="28" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7102,18 +7112,18 @@
         <v>41</v>
       </c>
       <c r="E28" s="44"/>
-      <c r="F28" s="103" t="s">
+      <c r="F28" s="107" t="s">
         <v>272</v>
       </c>
-      <c r="G28" s="104"/>
-      <c r="H28" s="104"/>
-      <c r="I28" s="104"/>
-      <c r="J28" s="104"/>
-      <c r="K28" s="106"/>
-      <c r="L28" s="106"/>
-      <c r="M28" s="107"/>
+      <c r="G28" s="108"/>
+      <c r="H28" s="108"/>
+      <c r="I28" s="108"/>
+      <c r="J28" s="108"/>
+      <c r="K28" s="110"/>
+      <c r="L28" s="110"/>
+      <c r="M28" s="111"/>
       <c r="N28" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="29" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7124,18 +7134,18 @@
         <v>46</v>
       </c>
       <c r="E29" s="44"/>
-      <c r="F29" s="103" t="s">
+      <c r="F29" s="107" t="s">
         <v>273</v>
       </c>
-      <c r="G29" s="104"/>
-      <c r="H29" s="104"/>
-      <c r="I29" s="104"/>
-      <c r="J29" s="104"/>
-      <c r="K29" s="104"/>
-      <c r="L29" s="104"/>
-      <c r="M29" s="105"/>
+      <c r="G29" s="108"/>
+      <c r="H29" s="108"/>
+      <c r="I29" s="108"/>
+      <c r="J29" s="108"/>
+      <c r="K29" s="108"/>
+      <c r="L29" s="108"/>
+      <c r="M29" s="109"/>
       <c r="N29" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="30" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7146,18 +7156,18 @@
         <v>46</v>
       </c>
       <c r="E30" s="44"/>
-      <c r="F30" s="103" t="s">
+      <c r="F30" s="107" t="s">
         <v>274</v>
       </c>
-      <c r="G30" s="104"/>
-      <c r="H30" s="104"/>
-      <c r="I30" s="104"/>
-      <c r="J30" s="104"/>
-      <c r="K30" s="104"/>
-      <c r="L30" s="104"/>
-      <c r="M30" s="105"/>
+      <c r="G30" s="108"/>
+      <c r="H30" s="108"/>
+      <c r="I30" s="108"/>
+      <c r="J30" s="108"/>
+      <c r="K30" s="108"/>
+      <c r="L30" s="108"/>
+      <c r="M30" s="109"/>
       <c r="N30" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="31" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7168,18 +7178,18 @@
         <v>46</v>
       </c>
       <c r="E31" s="44"/>
-      <c r="F31" s="103" t="s">
+      <c r="F31" s="107" t="s">
         <v>275</v>
       </c>
-      <c r="G31" s="104"/>
-      <c r="H31" s="104"/>
-      <c r="I31" s="104"/>
-      <c r="J31" s="104"/>
-      <c r="K31" s="104"/>
-      <c r="L31" s="104"/>
-      <c r="M31" s="105"/>
+      <c r="G31" s="108"/>
+      <c r="H31" s="108"/>
+      <c r="I31" s="108"/>
+      <c r="J31" s="108"/>
+      <c r="K31" s="108"/>
+      <c r="L31" s="108"/>
+      <c r="M31" s="109"/>
       <c r="N31" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="32" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7190,14 +7200,14 @@
         <v>46</v>
       </c>
       <c r="E32" s="66"/>
-      <c r="F32" s="97"/>
-      <c r="G32" s="98"/>
-      <c r="H32" s="98"/>
-      <c r="I32" s="98"/>
-      <c r="J32" s="98"/>
-      <c r="K32" s="98"/>
-      <c r="L32" s="98"/>
-      <c r="M32" s="99"/>
+      <c r="F32" s="101"/>
+      <c r="G32" s="102"/>
+      <c r="H32" s="102"/>
+      <c r="I32" s="102"/>
+      <c r="J32" s="102"/>
+      <c r="K32" s="102"/>
+      <c r="L32" s="102"/>
+      <c r="M32" s="103"/>
     </row>
     <row r="33" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="64" t="s">
@@ -7207,14 +7217,14 @@
         <v>46</v>
       </c>
       <c r="E33" s="66"/>
-      <c r="F33" s="97"/>
-      <c r="G33" s="98"/>
-      <c r="H33" s="98"/>
-      <c r="I33" s="98"/>
-      <c r="J33" s="98"/>
-      <c r="K33" s="98"/>
-      <c r="L33" s="98"/>
-      <c r="M33" s="99"/>
+      <c r="F33" s="101"/>
+      <c r="G33" s="102"/>
+      <c r="H33" s="102"/>
+      <c r="I33" s="102"/>
+      <c r="J33" s="102"/>
+      <c r="K33" s="102"/>
+      <c r="L33" s="102"/>
+      <c r="M33" s="103"/>
     </row>
     <row r="34" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="64" t="s">
@@ -7224,18 +7234,18 @@
         <v>46</v>
       </c>
       <c r="E34" s="66"/>
-      <c r="F34" s="100" t="s">
+      <c r="F34" s="104" t="s">
         <v>276</v>
       </c>
-      <c r="G34" s="101"/>
-      <c r="H34" s="101"/>
-      <c r="I34" s="101"/>
-      <c r="J34" s="101"/>
-      <c r="K34" s="101"/>
-      <c r="L34" s="101"/>
-      <c r="M34" s="102"/>
+      <c r="G34" s="105"/>
+      <c r="H34" s="105"/>
+      <c r="I34" s="105"/>
+      <c r="J34" s="105"/>
+      <c r="K34" s="105"/>
+      <c r="L34" s="105"/>
+      <c r="M34" s="106"/>
       <c r="N34" s="61" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="35" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7246,18 +7256,18 @@
         <v>46</v>
       </c>
       <c r="E35" s="67"/>
-      <c r="F35" s="100" t="s">
+      <c r="F35" s="104" t="s">
         <v>277</v>
       </c>
-      <c r="G35" s="102"/>
-      <c r="H35" s="97"/>
-      <c r="I35" s="98"/>
-      <c r="J35" s="98"/>
-      <c r="K35" s="98"/>
-      <c r="L35" s="98"/>
-      <c r="M35" s="99"/>
+      <c r="G35" s="106"/>
+      <c r="H35" s="101"/>
+      <c r="I35" s="102"/>
+      <c r="J35" s="102"/>
+      <c r="K35" s="102"/>
+      <c r="L35" s="102"/>
+      <c r="M35" s="103"/>
       <c r="N35" s="61" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="36" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7268,18 +7278,18 @@
         <v>46</v>
       </c>
       <c r="E36" s="67"/>
-      <c r="F36" s="97"/>
-      <c r="G36" s="98"/>
-      <c r="H36" s="98"/>
-      <c r="I36" s="98"/>
-      <c r="J36" s="99"/>
-      <c r="K36" s="100" t="s">
+      <c r="F36" s="101"/>
+      <c r="G36" s="102"/>
+      <c r="H36" s="102"/>
+      <c r="I36" s="102"/>
+      <c r="J36" s="103"/>
+      <c r="K36" s="104" t="s">
         <v>278</v>
       </c>
-      <c r="L36" s="101"/>
-      <c r="M36" s="102"/>
+      <c r="L36" s="105"/>
+      <c r="M36" s="106"/>
       <c r="N36" s="61" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="37" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7290,18 +7300,18 @@
         <v>46</v>
       </c>
       <c r="E37" s="66"/>
-      <c r="F37" s="97"/>
-      <c r="G37" s="98"/>
-      <c r="H37" s="98"/>
-      <c r="I37" s="99"/>
-      <c r="J37" s="100" t="s">
+      <c r="F37" s="101"/>
+      <c r="G37" s="102"/>
+      <c r="H37" s="102"/>
+      <c r="I37" s="103"/>
+      <c r="J37" s="104" t="s">
         <v>279</v>
       </c>
-      <c r="K37" s="101"/>
-      <c r="L37" s="101"/>
-      <c r="M37" s="102"/>
+      <c r="K37" s="105"/>
+      <c r="L37" s="105"/>
+      <c r="M37" s="106"/>
       <c r="N37" s="61" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="38" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7312,18 +7322,18 @@
         <v>41</v>
       </c>
       <c r="E38" s="66"/>
-      <c r="F38" s="97"/>
-      <c r="G38" s="98"/>
-      <c r="H38" s="98"/>
-      <c r="I38" s="99"/>
-      <c r="J38" s="100" t="s">
+      <c r="F38" s="101"/>
+      <c r="G38" s="102"/>
+      <c r="H38" s="102"/>
+      <c r="I38" s="103"/>
+      <c r="J38" s="104" t="s">
         <v>280</v>
       </c>
-      <c r="K38" s="101"/>
-      <c r="L38" s="101"/>
-      <c r="M38" s="102"/>
+      <c r="K38" s="105"/>
+      <c r="L38" s="105"/>
+      <c r="M38" s="106"/>
       <c r="N38" s="61" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="39" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7334,18 +7344,18 @@
         <v>41</v>
       </c>
       <c r="E39" s="66"/>
-      <c r="F39" s="100" t="s">
+      <c r="F39" s="104" t="s">
         <v>281</v>
       </c>
-      <c r="G39" s="101"/>
-      <c r="H39" s="101"/>
-      <c r="I39" s="101"/>
-      <c r="J39" s="101"/>
-      <c r="K39" s="101"/>
-      <c r="L39" s="101"/>
-      <c r="M39" s="102"/>
+      <c r="G39" s="105"/>
+      <c r="H39" s="105"/>
+      <c r="I39" s="105"/>
+      <c r="J39" s="105"/>
+      <c r="K39" s="105"/>
+      <c r="L39" s="105"/>
+      <c r="M39" s="106"/>
       <c r="N39" s="61" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="40" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7356,14 +7366,14 @@
         <v>46</v>
       </c>
       <c r="E40" s="66"/>
-      <c r="F40" s="97"/>
-      <c r="G40" s="98"/>
-      <c r="H40" s="98"/>
-      <c r="I40" s="98"/>
-      <c r="J40" s="98"/>
-      <c r="K40" s="98"/>
-      <c r="L40" s="98"/>
-      <c r="M40" s="99"/>
+      <c r="F40" s="101"/>
+      <c r="G40" s="102"/>
+      <c r="H40" s="102"/>
+      <c r="I40" s="102"/>
+      <c r="J40" s="102"/>
+      <c r="K40" s="102"/>
+      <c r="L40" s="102"/>
+      <c r="M40" s="103"/>
     </row>
     <row r="41" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="64" t="s">
@@ -7373,14 +7383,14 @@
         <v>46</v>
       </c>
       <c r="E41" s="66"/>
-      <c r="F41" s="97"/>
-      <c r="G41" s="98"/>
-      <c r="H41" s="98"/>
-      <c r="I41" s="98"/>
-      <c r="J41" s="98"/>
-      <c r="K41" s="98"/>
-      <c r="L41" s="98"/>
-      <c r="M41" s="99"/>
+      <c r="F41" s="101"/>
+      <c r="G41" s="102"/>
+      <c r="H41" s="102"/>
+      <c r="I41" s="102"/>
+      <c r="J41" s="102"/>
+      <c r="K41" s="102"/>
+      <c r="L41" s="102"/>
+      <c r="M41" s="103"/>
     </row>
     <row r="42" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="64" t="s">
@@ -7390,14 +7400,14 @@
         <v>46</v>
       </c>
       <c r="E42" s="66"/>
-      <c r="F42" s="97"/>
-      <c r="G42" s="98"/>
-      <c r="H42" s="98"/>
-      <c r="I42" s="98"/>
-      <c r="J42" s="98"/>
-      <c r="K42" s="98"/>
-      <c r="L42" s="98"/>
-      <c r="M42" s="99"/>
+      <c r="F42" s="101"/>
+      <c r="G42" s="102"/>
+      <c r="H42" s="102"/>
+      <c r="I42" s="102"/>
+      <c r="J42" s="102"/>
+      <c r="K42" s="102"/>
+      <c r="L42" s="102"/>
+      <c r="M42" s="103"/>
     </row>
     <row r="43" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C43" s="64" t="s">
@@ -7407,14 +7417,14 @@
         <v>46</v>
       </c>
       <c r="E43" s="66"/>
-      <c r="F43" s="97"/>
-      <c r="G43" s="98"/>
-      <c r="H43" s="98"/>
-      <c r="I43" s="98"/>
-      <c r="J43" s="98"/>
-      <c r="K43" s="98"/>
-      <c r="L43" s="98"/>
-      <c r="M43" s="99"/>
+      <c r="F43" s="101"/>
+      <c r="G43" s="102"/>
+      <c r="H43" s="102"/>
+      <c r="I43" s="102"/>
+      <c r="J43" s="102"/>
+      <c r="K43" s="102"/>
+      <c r="L43" s="102"/>
+      <c r="M43" s="103"/>
     </row>
     <row r="44" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="64" t="s">
@@ -7424,14 +7434,14 @@
         <v>46</v>
       </c>
       <c r="E44" s="66"/>
-      <c r="F44" s="97"/>
-      <c r="G44" s="98"/>
-      <c r="H44" s="98"/>
-      <c r="I44" s="98"/>
-      <c r="J44" s="98"/>
-      <c r="K44" s="98"/>
-      <c r="L44" s="98"/>
-      <c r="M44" s="99"/>
+      <c r="F44" s="101"/>
+      <c r="G44" s="102"/>
+      <c r="H44" s="102"/>
+      <c r="I44" s="102"/>
+      <c r="J44" s="102"/>
+      <c r="K44" s="102"/>
+      <c r="L44" s="102"/>
+      <c r="M44" s="103"/>
     </row>
     <row r="45" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C45" s="21" t="s">
@@ -7453,12 +7463,12 @@
       <c r="I45" s="47" t="s">
         <v>123</v>
       </c>
-      <c r="J45" s="75" t="s">
+      <c r="J45" s="78" t="s">
         <v>124</v>
       </c>
-      <c r="K45" s="76"/>
-      <c r="L45" s="76"/>
-      <c r="M45" s="77"/>
+      <c r="K45" s="79"/>
+      <c r="L45" s="79"/>
+      <c r="M45" s="80"/>
     </row>
     <row r="46" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="20" t="s">
@@ -7468,18 +7478,18 @@
         <v>46</v>
       </c>
       <c r="E46" s="45"/>
-      <c r="F46" s="75" t="s">
+      <c r="F46" s="78" t="s">
         <v>291</v>
       </c>
-      <c r="G46" s="77"/>
-      <c r="H46" s="75" t="s">
+      <c r="G46" s="80"/>
+      <c r="H46" s="78" t="s">
         <v>126</v>
       </c>
-      <c r="I46" s="76"/>
-      <c r="J46" s="76"/>
-      <c r="K46" s="76"/>
-      <c r="L46" s="76"/>
-      <c r="M46" s="77"/>
+      <c r="I46" s="79"/>
+      <c r="J46" s="79"/>
+      <c r="K46" s="79"/>
+      <c r="L46" s="79"/>
+      <c r="M46" s="80"/>
     </row>
     <row r="47" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="20" t="s">
@@ -7489,18 +7499,18 @@
         <v>46</v>
       </c>
       <c r="E47" s="45"/>
-      <c r="F47" s="91" t="s">
+      <c r="F47" s="95" t="s">
         <v>130</v>
       </c>
-      <c r="G47" s="92"/>
-      <c r="H47" s="92"/>
-      <c r="I47" s="93"/>
-      <c r="J47" s="75" t="s">
+      <c r="G47" s="96"/>
+      <c r="H47" s="96"/>
+      <c r="I47" s="97"/>
+      <c r="J47" s="78" t="s">
         <v>131</v>
       </c>
-      <c r="K47" s="76"/>
-      <c r="L47" s="76"/>
-      <c r="M47" s="77"/>
+      <c r="K47" s="79"/>
+      <c r="L47" s="79"/>
+      <c r="M47" s="80"/>
     </row>
     <row r="48" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="20" t="s">
@@ -7510,18 +7520,18 @@
         <v>46</v>
       </c>
       <c r="E48" s="6"/>
-      <c r="F48" s="75" t="s">
+      <c r="F48" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="G48" s="76"/>
-      <c r="H48" s="76"/>
-      <c r="I48" s="77"/>
-      <c r="J48" s="94" t="s">
+      <c r="G48" s="79"/>
+      <c r="H48" s="79"/>
+      <c r="I48" s="80"/>
+      <c r="J48" s="98" t="s">
         <v>133</v>
       </c>
-      <c r="K48" s="95"/>
-      <c r="L48" s="95"/>
-      <c r="M48" s="96"/>
+      <c r="K48" s="99"/>
+      <c r="L48" s="99"/>
+      <c r="M48" s="100"/>
     </row>
     <row r="49" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="20" t="s">
@@ -7531,16 +7541,16 @@
         <v>46</v>
       </c>
       <c r="E49" s="6"/>
-      <c r="F49" s="73" t="s">
+      <c r="F49" s="76" t="s">
         <v>160</v>
       </c>
-      <c r="G49" s="82"/>
-      <c r="H49" s="82"/>
-      <c r="I49" s="82"/>
-      <c r="J49" s="82"/>
-      <c r="K49" s="82"/>
-      <c r="L49" s="82"/>
-      <c r="M49" s="74"/>
+      <c r="G49" s="86"/>
+      <c r="H49" s="86"/>
+      <c r="I49" s="86"/>
+      <c r="J49" s="86"/>
+      <c r="K49" s="86"/>
+      <c r="L49" s="86"/>
+      <c r="M49" s="77"/>
     </row>
     <row r="50" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C50" s="20" t="s">
@@ -7550,20 +7560,20 @@
         <v>46</v>
       </c>
       <c r="E50" s="6"/>
-      <c r="F50" s="70"/>
-      <c r="G50" s="72"/>
+      <c r="F50" s="73"/>
+      <c r="G50" s="75"/>
       <c r="H50" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="I50" s="73" t="s">
+      <c r="I50" s="76" t="s">
         <v>159</v>
       </c>
-      <c r="J50" s="82"/>
-      <c r="K50" s="74"/>
-      <c r="L50" s="73" t="s">
+      <c r="J50" s="86"/>
+      <c r="K50" s="77"/>
+      <c r="L50" s="76" t="s">
         <v>160</v>
       </c>
-      <c r="M50" s="74"/>
+      <c r="M50" s="77"/>
     </row>
     <row r="51" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C51" s="20" t="s">
@@ -7606,15 +7616,15 @@
         <v>46</v>
       </c>
       <c r="E52" s="6"/>
-      <c r="F52" s="70"/>
-      <c r="G52" s="71"/>
-      <c r="H52" s="71"/>
-      <c r="I52" s="72"/>
-      <c r="J52" s="73" t="s">
+      <c r="F52" s="73"/>
+      <c r="G52" s="74"/>
+      <c r="H52" s="74"/>
+      <c r="I52" s="75"/>
+      <c r="J52" s="76" t="s">
         <v>127</v>
       </c>
-      <c r="K52" s="82"/>
-      <c r="L52" s="74"/>
+      <c r="K52" s="86"/>
+      <c r="L52" s="77"/>
       <c r="M52" s="14" t="s">
         <v>92</v>
       </c>
@@ -7629,16 +7639,16 @@
       <c r="E53" s="22" t="s">
         <v>302</v>
       </c>
-      <c r="F53" s="97"/>
-      <c r="G53" s="98"/>
-      <c r="H53" s="98"/>
-      <c r="I53" s="98"/>
-      <c r="J53" s="98"/>
-      <c r="K53" s="99"/>
-      <c r="L53" s="81" t="s">
+      <c r="F53" s="101"/>
+      <c r="G53" s="102"/>
+      <c r="H53" s="102"/>
+      <c r="I53" s="102"/>
+      <c r="J53" s="102"/>
+      <c r="K53" s="103"/>
+      <c r="L53" s="85" t="s">
         <v>300</v>
       </c>
-      <c r="M53" s="80"/>
+      <c r="M53" s="84"/>
     </row>
     <row r="54" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="64" t="s">
@@ -7648,42 +7658,42 @@
         <v>46</v>
       </c>
       <c r="E54" s="68"/>
-      <c r="F54" s="97"/>
-      <c r="G54" s="98"/>
-      <c r="H54" s="98"/>
-      <c r="I54" s="98"/>
-      <c r="J54" s="98"/>
-      <c r="K54" s="98"/>
-      <c r="L54" s="98"/>
-      <c r="M54" s="99"/>
+      <c r="F54" s="101"/>
+      <c r="G54" s="102"/>
+      <c r="H54" s="102"/>
+      <c r="I54" s="102"/>
+      <c r="J54" s="102"/>
+      <c r="K54" s="102"/>
+      <c r="L54" s="102"/>
+      <c r="M54" s="103"/>
     </row>
     <row r="55" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="56" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="57" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D56" t="s">
         <v>45</v>
       </c>
       <c r="F56" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="G56" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="H56" s="12" t="s">
         <v>378</v>
       </c>
-      <c r="G56" s="12" t="s">
+      <c r="I56" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="H56" s="12" t="s">
+      <c r="J56" s="58" t="s">
+        <v>381</v>
+      </c>
+      <c r="K56" s="73"/>
+      <c r="L56" s="75"/>
+      <c r="M56" s="58" t="s">
         <v>380</v>
-      </c>
-      <c r="I56" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="J56" s="58" t="s">
-        <v>383</v>
-      </c>
-      <c r="K56" s="70"/>
-      <c r="L56" s="72"/>
-      <c r="M56" s="58" t="s">
-        <v>382</v>
       </c>
     </row>
   </sheetData>

--- a/doc/spec/Y8960_Specifications.xlsx
+++ b/doc/spec/Y8960_Specifications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\HRA_product\Y8960_Cartridge\doc\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DEECFC2-3733-4E1D-9E7C-F7D0A43D5EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE5874A0-A514-48B9-BC0F-3AF79DC3CAA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11010" yWindow="0" windowWidth="17895" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="modules" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="391">
   <si>
     <t>Y8960 Cartridge は、MSX用のオーディオ系チップのコンボカートリッジです。</t>
     <rPh sb="21" eb="22">
@@ -1598,10 +1598,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Bank selecter(Mirror 3FFEh)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>5000-57FFh</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1765,62 +1761,6 @@
   </si>
   <si>
     <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#27) のときのみ利用可能</t>
-    <rPh sb="47" eb="51">
-      <t>リヨウカノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#28) のときのみ利用可能</t>
-    <rPh sb="47" eb="51">
-      <t>リヨウカノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#29) のときのみ利用可能</t>
-    <rPh sb="47" eb="51">
-      <t>リヨウカノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#30) のときのみ利用可能</t>
-    <rPh sb="47" eb="51">
-      <t>リヨウカノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#31) のときのみ利用可能</t>
-    <rPh sb="47" eb="51">
-      <t>リヨウカノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#32) のときのみ利用可能</t>
-    <rPh sb="47" eb="51">
-      <t>リヨウカノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#33) のときのみ利用可能</t>
-    <rPh sb="47" eb="51">
-      <t>リヨウカノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#34) のときのみ利用可能</t>
-    <rPh sb="47" eb="51">
-      <t>リヨウカノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#35) のときのみ利用可能</t>
     <rPh sb="47" eb="51">
       <t>リヨウカノウ</t>
     </rPh>
@@ -1992,6 +1932,22 @@
   </si>
   <si>
     <t>TIMER</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9000-97FFh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B000-B7FFh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Register Module</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MSX SLOT</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2081,7 +2037,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2115,6 +2071,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2421,17 +2383,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -2464,6 +2415,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2473,7 +2435,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2633,16 +2595,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -2660,7 +2616,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2702,39 +2658,39 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2807,8 +2763,23 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3334,276 +3305,308 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F17AAC-1091-414B-9A6F-EA5ABE92574A}">
-  <dimension ref="B2:N34"/>
+  <dimension ref="B2:O34"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
+    <col min="1" max="1" width="2.75" customWidth="1"/>
     <col min="2" max="2" width="3.25" customWidth="1"/>
     <col min="3" max="3" width="15.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="4" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="14" max="14" width="65.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.625" customWidth="1"/>
+    <col min="15" max="15" width="65.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="3" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C3" s="7" t="s">
         <v>38</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="G3" s="114" t="s">
         <v>82</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="J3" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="K3" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="L3" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="N3" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="O3" s="5" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" ht="27.75" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C4" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>339</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="71"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="110" t="s">
+        <v>345</v>
+      </c>
+      <c r="O4" s="54" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C5" s="68" t="s">
+        <v>340</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>335</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="111" t="s">
+        <v>346</v>
+      </c>
+      <c r="H5" s="112"/>
+      <c r="I5" s="112"/>
+      <c r="J5" s="112"/>
+      <c r="K5" s="112"/>
+      <c r="L5" s="112"/>
+      <c r="M5" s="112"/>
+      <c r="N5" s="113"/>
+      <c r="O5" s="52" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="4" spans="2:14" ht="27.75" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C4" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="53" t="s">
-        <v>340</v>
-      </c>
-      <c r="F4" s="73"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74"/>
-      <c r="K4" s="74"/>
-      <c r="L4" s="75"/>
-      <c r="M4" s="26" t="s">
+    <row r="6" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C6" s="69" t="s">
+        <v>341</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>336</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="111" t="s">
         <v>346</v>
       </c>
-      <c r="N4" s="56" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="5" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C5" s="70" t="s">
-        <v>341</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E5" s="51" t="s">
+      <c r="H6" s="112"/>
+      <c r="I6" s="112"/>
+      <c r="J6" s="112"/>
+      <c r="K6" s="112"/>
+      <c r="L6" s="112"/>
+      <c r="M6" s="112"/>
+      <c r="N6" s="113"/>
+      <c r="O6" s="52" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="69" t="s">
+        <v>342</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>337</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="111" t="s">
+        <v>346</v>
+      </c>
+      <c r="H7" s="112"/>
+      <c r="I7" s="112"/>
+      <c r="J7" s="112"/>
+      <c r="K7" s="112"/>
+      <c r="L7" s="112"/>
+      <c r="M7" s="112"/>
+      <c r="N7" s="113"/>
+      <c r="O7" s="52" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C8" s="69" t="s">
+        <v>343</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>338</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="111" t="s">
+        <v>346</v>
+      </c>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="112"/>
+      <c r="K8" s="112"/>
+      <c r="L8" s="112"/>
+      <c r="M8" s="112"/>
+      <c r="N8" s="113"/>
+      <c r="O8" s="52" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C9" s="69" t="s">
+        <v>333</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="74" t="s">
+        <v>347</v>
+      </c>
+      <c r="H9" s="75"/>
+      <c r="I9" s="75"/>
+      <c r="J9" s="75"/>
+      <c r="K9" s="75"/>
+      <c r="L9" s="75"/>
+      <c r="M9" s="75"/>
+      <c r="N9" s="76"/>
+      <c r="O9" s="52" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C10" s="69" t="s">
+        <v>334</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="F5" s="85" t="s">
+      <c r="F10" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="74" t="s">
         <v>347</v>
       </c>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="83"/>
-      <c r="J5" s="83"/>
-      <c r="K5" s="83"/>
-      <c r="L5" s="83"/>
-      <c r="M5" s="84"/>
-      <c r="N5" s="54" t="s">
+      <c r="H10" s="75"/>
+      <c r="I10" s="75"/>
+      <c r="J10" s="75"/>
+      <c r="K10" s="75"/>
+      <c r="L10" s="75"/>
+      <c r="M10" s="75"/>
+      <c r="N10" s="76"/>
+      <c r="O10" s="52" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C6" s="71" t="s">
-        <v>342</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="51" t="s">
-        <v>337</v>
-      </c>
-      <c r="F6" s="85" t="s">
-        <v>347</v>
-      </c>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="83"/>
-      <c r="K6" s="83"/>
-      <c r="L6" s="83"/>
-      <c r="M6" s="84"/>
-      <c r="N6" s="54" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C7" s="71" t="s">
-        <v>343</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" s="51" t="s">
-        <v>338</v>
-      </c>
-      <c r="F7" s="85" t="s">
-        <v>347</v>
-      </c>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="83"/>
-      <c r="K7" s="83"/>
-      <c r="L7" s="83"/>
-      <c r="M7" s="84"/>
-      <c r="N7" s="54" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C8" s="71" t="s">
-        <v>344</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>339</v>
-      </c>
-      <c r="F8" s="85" t="s">
-        <v>347</v>
-      </c>
-      <c r="G8" s="83"/>
-      <c r="H8" s="83"/>
-      <c r="I8" s="83"/>
-      <c r="J8" s="83"/>
-      <c r="K8" s="83"/>
-      <c r="L8" s="83"/>
-      <c r="M8" s="84"/>
-      <c r="N8" s="54" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C9" s="71" t="s">
-        <v>334</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>336</v>
-      </c>
-      <c r="F9" s="78" t="s">
-        <v>348</v>
-      </c>
-      <c r="G9" s="79"/>
-      <c r="H9" s="79"/>
-      <c r="I9" s="79"/>
-      <c r="J9" s="79"/>
-      <c r="K9" s="79"/>
-      <c r="L9" s="79"/>
-      <c r="M9" s="80"/>
-      <c r="N9" s="54" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C10" s="71" t="s">
-        <v>335</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="F10" s="78" t="s">
-        <v>348</v>
-      </c>
-      <c r="G10" s="79"/>
-      <c r="H10" s="79"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="79"/>
-      <c r="K10" s="79"/>
-      <c r="L10" s="79"/>
-      <c r="M10" s="80"/>
-      <c r="N10" s="54" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C11" s="51" t="s">
         <v>319</v>
       </c>
       <c r="D11" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="51" t="s">
+      <c r="E11" s="25" t="s">
         <v>320</v>
       </c>
-      <c r="F11" s="85" t="s">
+      <c r="F11" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="G11" s="81" t="s">
         <v>320</v>
       </c>
-      <c r="G11" s="83"/>
-      <c r="H11" s="83"/>
-      <c r="I11" s="83"/>
-      <c r="J11" s="83"/>
-      <c r="K11" s="83"/>
-      <c r="L11" s="83"/>
-      <c r="M11" s="84"/>
-      <c r="N11" s="55" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="12" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="H11" s="79"/>
+      <c r="I11" s="79"/>
+      <c r="J11" s="79"/>
+      <c r="K11" s="79"/>
+      <c r="L11" s="79"/>
+      <c r="M11" s="79"/>
+      <c r="N11" s="80"/>
+      <c r="O11" s="53" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C12" s="51" t="s">
         <v>318</v>
       </c>
       <c r="D12" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="51" t="s">
+      <c r="E12" s="25" t="s">
         <v>321</v>
       </c>
-      <c r="F12" s="85" t="s">
+      <c r="F12" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="G12" s="81" t="s">
         <v>321</v>
       </c>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
-      <c r="I12" s="83"/>
-      <c r="J12" s="83"/>
-      <c r="K12" s="83"/>
-      <c r="L12" s="83"/>
-      <c r="M12" s="84"/>
-      <c r="N12" s="55" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="13" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="H12" s="79"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="79"/>
+      <c r="K12" s="79"/>
+      <c r="L12" s="79"/>
+      <c r="M12" s="79"/>
+      <c r="N12" s="80"/>
+      <c r="O12" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="24" t="s">
         <v>311</v>
       </c>
@@ -3613,21 +3616,24 @@
       <c r="E13" s="25" t="s">
         <v>307</v>
       </c>
-      <c r="F13" s="82" t="s">
+      <c r="F13" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="G13" s="78" t="s">
         <v>298</v>
       </c>
-      <c r="G13" s="83"/>
-      <c r="H13" s="83"/>
-      <c r="I13" s="83"/>
-      <c r="J13" s="83"/>
-      <c r="K13" s="83"/>
-      <c r="L13" s="83"/>
-      <c r="M13" s="84"/>
-      <c r="N13" s="55" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="14" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="H13" s="79"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="79"/>
+      <c r="M13" s="79"/>
+      <c r="N13" s="80"/>
+      <c r="O13" s="53" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="25" t="s">
         <v>310</v>
       </c>
@@ -3637,21 +3643,24 @@
       <c r="E14" s="25" t="s">
         <v>299</v>
       </c>
-      <c r="F14" s="82" t="s">
+      <c r="F14" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="G14" s="78" t="s">
         <v>308</v>
       </c>
-      <c r="G14" s="83"/>
-      <c r="H14" s="83"/>
-      <c r="I14" s="83"/>
-      <c r="J14" s="83"/>
-      <c r="K14" s="83"/>
-      <c r="L14" s="83"/>
-      <c r="M14" s="84"/>
-      <c r="N14" s="55" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="H14" s="79"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="79"/>
+      <c r="K14" s="79"/>
+      <c r="L14" s="79"/>
+      <c r="M14" s="79"/>
+      <c r="N14" s="80"/>
+      <c r="O14" s="53" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="25" t="s">
         <v>303</v>
       </c>
@@ -3661,21 +3670,24 @@
       <c r="E15" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="F15" s="82" t="s">
+      <c r="F15" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="G15" s="78" t="s">
         <v>296</v>
       </c>
-      <c r="G15" s="83"/>
-      <c r="H15" s="83"/>
-      <c r="I15" s="83"/>
-      <c r="J15" s="83"/>
-      <c r="K15" s="83"/>
-      <c r="L15" s="83"/>
-      <c r="M15" s="84"/>
-      <c r="N15" s="55" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="16" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="H15" s="79"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="79"/>
+      <c r="K15" s="79"/>
+      <c r="L15" s="79"/>
+      <c r="M15" s="79"/>
+      <c r="N15" s="80"/>
+      <c r="O15" s="53" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="25" t="s">
         <v>304</v>
       </c>
@@ -3685,93 +3697,105 @@
       <c r="E16" s="25" t="s">
         <v>297</v>
       </c>
-      <c r="F16" s="82" t="s">
+      <c r="F16" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="G16" s="78" t="s">
         <v>309</v>
       </c>
-      <c r="G16" s="83"/>
-      <c r="H16" s="83"/>
-      <c r="I16" s="83"/>
-      <c r="J16" s="83"/>
-      <c r="K16" s="83"/>
-      <c r="L16" s="83"/>
-      <c r="M16" s="84"/>
-      <c r="N16" s="55" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="17" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="H16" s="79"/>
+      <c r="I16" s="79"/>
+      <c r="J16" s="79"/>
+      <c r="K16" s="79"/>
+      <c r="L16" s="79"/>
+      <c r="M16" s="79"/>
+      <c r="N16" s="80"/>
+      <c r="O16" s="53" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="17" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="50" t="s">
         <v>305</v>
       </c>
       <c r="D17" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="50" t="s">
+      <c r="E17" s="24" t="s">
         <v>314</v>
       </c>
-      <c r="F17" s="82" t="s">
+      <c r="F17" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="G17" s="78" t="s">
         <v>316</v>
       </c>
-      <c r="G17" s="83"/>
-      <c r="H17" s="83"/>
-      <c r="I17" s="83"/>
-      <c r="J17" s="83"/>
-      <c r="K17" s="83"/>
-      <c r="L17" s="83"/>
-      <c r="M17" s="84"/>
-      <c r="N17" s="55" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="18" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="H17" s="79"/>
+      <c r="I17" s="79"/>
+      <c r="J17" s="79"/>
+      <c r="K17" s="79"/>
+      <c r="L17" s="79"/>
+      <c r="M17" s="79"/>
+      <c r="N17" s="80"/>
+      <c r="O17" s="53" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="51" t="s">
         <v>306</v>
       </c>
       <c r="D18" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="E18" s="51" t="s">
+      <c r="E18" s="25" t="s">
         <v>315</v>
       </c>
-      <c r="F18" s="82" t="s">
+      <c r="F18" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="G18" s="78" t="s">
         <v>317</v>
       </c>
-      <c r="G18" s="83"/>
-      <c r="H18" s="83"/>
-      <c r="I18" s="83"/>
-      <c r="J18" s="83"/>
-      <c r="K18" s="83"/>
-      <c r="L18" s="83"/>
-      <c r="M18" s="84"/>
-      <c r="N18" s="55" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="19" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="H18" s="79"/>
+      <c r="I18" s="79"/>
+      <c r="J18" s="79"/>
+      <c r="K18" s="79"/>
+      <c r="L18" s="79"/>
+      <c r="M18" s="79"/>
+      <c r="N18" s="80"/>
+      <c r="O18" s="53" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="48" t="s">
         <v>113</v>
       </c>
       <c r="D19" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="E19" s="49" t="s">
+      <c r="E19" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="F19" s="82" t="s">
+      <c r="F19" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="G19" s="78" t="s">
         <v>107</v>
       </c>
-      <c r="G19" s="83"/>
-      <c r="H19" s="83"/>
-      <c r="I19" s="83"/>
-      <c r="J19" s="83"/>
-      <c r="K19" s="83"/>
-      <c r="L19" s="83"/>
-      <c r="M19" s="84"/>
-      <c r="N19" s="55" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="20" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="H19" s="79"/>
+      <c r="I19" s="79"/>
+      <c r="J19" s="79"/>
+      <c r="K19" s="79"/>
+      <c r="L19" s="79"/>
+      <c r="M19" s="79"/>
+      <c r="N19" s="80"/>
+      <c r="O19" s="53" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="20" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="25" t="s">
         <v>112</v>
       </c>
@@ -3781,21 +3805,24 @@
       <c r="E20" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="F20" s="82" t="s">
+      <c r="F20" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="G20" s="78" t="s">
         <v>197</v>
       </c>
-      <c r="G20" s="83"/>
-      <c r="H20" s="83"/>
-      <c r="I20" s="83"/>
-      <c r="J20" s="83"/>
-      <c r="K20" s="83"/>
-      <c r="L20" s="83"/>
-      <c r="M20" s="84"/>
-      <c r="N20" s="55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="21" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="H20" s="79"/>
+      <c r="I20" s="79"/>
+      <c r="J20" s="79"/>
+      <c r="K20" s="79"/>
+      <c r="L20" s="79"/>
+      <c r="M20" s="79"/>
+      <c r="N20" s="80"/>
+      <c r="O20" s="53" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>110</v>
       </c>
@@ -3805,21 +3832,24 @@
       <c r="E21" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F21" s="76" t="s">
+      <c r="F21" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="G21" s="82" t="s">
         <v>105</v>
       </c>
-      <c r="G21" s="86"/>
-      <c r="H21" s="86"/>
-      <c r="I21" s="86"/>
-      <c r="J21" s="86"/>
-      <c r="K21" s="86"/>
-      <c r="L21" s="86"/>
-      <c r="M21" s="77"/>
-      <c r="N21" s="55" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="22" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="H21" s="83"/>
+      <c r="I21" s="83"/>
+      <c r="J21" s="83"/>
+      <c r="K21" s="83"/>
+      <c r="L21" s="83"/>
+      <c r="M21" s="83"/>
+      <c r="N21" s="84"/>
+      <c r="O21" s="53" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>111</v>
       </c>
@@ -3829,67 +3859,72 @@
       <c r="E22" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F22" s="76" t="s">
+      <c r="F22" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="G22" s="82" t="s">
         <v>198</v>
       </c>
-      <c r="G22" s="86"/>
-      <c r="H22" s="86"/>
-      <c r="I22" s="86"/>
-      <c r="J22" s="86"/>
-      <c r="K22" s="86"/>
-      <c r="L22" s="86"/>
-      <c r="M22" s="77"/>
-      <c r="N22" s="55" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="23" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="H22" s="83"/>
+      <c r="I22" s="83"/>
+      <c r="J22" s="83"/>
+      <c r="K22" s="83"/>
+      <c r="L22" s="83"/>
+      <c r="M22" s="83"/>
+      <c r="N22" s="84"/>
+      <c r="O22" s="53" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="13" t="s">
         <v>114</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E23" s="52" t="s">
+      <c r="E23" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="F23" s="87"/>
-      <c r="G23" s="88"/>
-      <c r="H23" s="88"/>
-      <c r="I23" s="88"/>
-      <c r="J23" s="88"/>
-      <c r="K23" s="89"/>
-      <c r="L23" s="26" t="s">
+      <c r="F23" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="G23" s="85"/>
+      <c r="H23" s="86"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="86"/>
+      <c r="K23" s="86"/>
+      <c r="L23" s="87"/>
+      <c r="M23" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="M23" s="12" t="s">
+      <c r="N23" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="N23" s="55" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="24" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="O23" s="53" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>322</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E24" s="6"/>
-      <c r="F24" s="73"/>
-      <c r="G24" s="74"/>
-      <c r="H24" s="74"/>
-      <c r="I24" s="74"/>
-      <c r="J24" s="74"/>
-      <c r="K24" s="74"/>
-      <c r="L24" s="74"/>
-      <c r="M24" s="75"/>
-      <c r="N24" s="55" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="25" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="E24" s="1"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="72"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="72"/>
+      <c r="M24" s="72"/>
+      <c r="N24" s="73"/>
+      <c r="O24" s="53"/>
+    </row>
+    <row r="25" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>323</v>
       </c>
@@ -3897,19 +3932,18 @@
         <v>96</v>
       </c>
       <c r="E25" s="1"/>
-      <c r="F25" s="73"/>
-      <c r="G25" s="74"/>
-      <c r="H25" s="74"/>
-      <c r="I25" s="74"/>
-      <c r="J25" s="74"/>
-      <c r="K25" s="74"/>
-      <c r="L25" s="74"/>
-      <c r="M25" s="75"/>
-      <c r="N25" s="55" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="26" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="F25" s="22"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="72"/>
+      <c r="I25" s="72"/>
+      <c r="J25" s="72"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="72"/>
+      <c r="M25" s="72"/>
+      <c r="N25" s="73"/>
+      <c r="O25" s="53"/>
+    </row>
+    <row r="26" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>324</v>
       </c>
@@ -3917,19 +3951,18 @@
         <v>96</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="73"/>
-      <c r="G26" s="74"/>
-      <c r="H26" s="74"/>
-      <c r="I26" s="74"/>
-      <c r="J26" s="74"/>
-      <c r="K26" s="74"/>
-      <c r="L26" s="74"/>
-      <c r="M26" s="75"/>
-      <c r="N26" s="55" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="27" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="F26" s="22"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="72"/>
+      <c r="I26" s="72"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="72"/>
+      <c r="M26" s="72"/>
+      <c r="N26" s="73"/>
+      <c r="O26" s="53"/>
+    </row>
+    <row r="27" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>325</v>
       </c>
@@ -3937,19 +3970,18 @@
         <v>96</v>
       </c>
       <c r="E27" s="1"/>
-      <c r="F27" s="73"/>
-      <c r="G27" s="74"/>
-      <c r="H27" s="74"/>
-      <c r="I27" s="74"/>
-      <c r="J27" s="74"/>
-      <c r="K27" s="74"/>
-      <c r="L27" s="74"/>
-      <c r="M27" s="75"/>
-      <c r="N27" s="55" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="28" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="F27" s="22"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="72"/>
+      <c r="I27" s="72"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="72"/>
+      <c r="M27" s="72"/>
+      <c r="N27" s="73"/>
+      <c r="O27" s="53"/>
+    </row>
+    <row r="28" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>326</v>
       </c>
@@ -3957,19 +3989,18 @@
         <v>96</v>
       </c>
       <c r="E28" s="1"/>
-      <c r="F28" s="73"/>
-      <c r="G28" s="74"/>
-      <c r="H28" s="74"/>
-      <c r="I28" s="74"/>
-      <c r="J28" s="74"/>
-      <c r="K28" s="74"/>
-      <c r="L28" s="74"/>
-      <c r="M28" s="75"/>
-      <c r="N28" s="55" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="29" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="F28" s="22"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="72"/>
+      <c r="I28" s="72"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="72"/>
+      <c r="M28" s="72"/>
+      <c r="N28" s="73"/>
+      <c r="O28" s="53"/>
+    </row>
+    <row r="29" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>327</v>
       </c>
@@ -3977,19 +4008,18 @@
         <v>96</v>
       </c>
       <c r="E29" s="1"/>
-      <c r="F29" s="73"/>
-      <c r="G29" s="74"/>
-      <c r="H29" s="74"/>
-      <c r="I29" s="74"/>
-      <c r="J29" s="74"/>
-      <c r="K29" s="74"/>
-      <c r="L29" s="74"/>
-      <c r="M29" s="75"/>
-      <c r="N29" s="55" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="30" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="F29" s="22"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="72"/>
+      <c r="I29" s="72"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="72"/>
+      <c r="M29" s="72"/>
+      <c r="N29" s="73"/>
+      <c r="O29" s="53"/>
+    </row>
+    <row r="30" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>328</v>
       </c>
@@ -3997,158 +4027,160 @@
         <v>96</v>
       </c>
       <c r="E30" s="1"/>
-      <c r="F30" s="73"/>
-      <c r="G30" s="74"/>
-      <c r="H30" s="74"/>
-      <c r="I30" s="74"/>
-      <c r="J30" s="74"/>
-      <c r="K30" s="74"/>
-      <c r="L30" s="74"/>
-      <c r="M30" s="75"/>
-      <c r="N30" s="55" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="31" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="F30" s="22"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="72"/>
+      <c r="I30" s="72"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="72"/>
+      <c r="M30" s="72"/>
+      <c r="N30" s="73"/>
+      <c r="O30" s="53"/>
+    </row>
+    <row r="31" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>329</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="F31" s="73"/>
-      <c r="G31" s="74"/>
-      <c r="H31" s="74"/>
-      <c r="I31" s="74"/>
-      <c r="J31" s="74"/>
-      <c r="K31" s="75"/>
-      <c r="L31" s="76" t="s">
-        <v>193</v>
-      </c>
-      <c r="M31" s="77"/>
-      <c r="N31" s="55" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="32" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+      <c r="E31" s="1"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="72"/>
+      <c r="I31" s="72"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="72"/>
+      <c r="M31" s="72"/>
+      <c r="N31" s="73"/>
+      <c r="O31" s="53"/>
+    </row>
+    <row r="32" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>330</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="F32" s="26" t="s">
-        <v>395</v>
-      </c>
-      <c r="G32" s="73"/>
-      <c r="H32" s="75"/>
-      <c r="I32" s="34" t="s">
+      <c r="F32" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="G32" s="26" t="s">
+        <v>386</v>
+      </c>
+      <c r="H32" s="71"/>
+      <c r="I32" s="73"/>
+      <c r="J32" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="J32" s="34" t="s">
+      <c r="K32" s="34" t="s">
         <v>312</v>
       </c>
-      <c r="K32" s="34" t="s">
+      <c r="L32" s="34" t="s">
         <v>313</v>
       </c>
-      <c r="L32" s="47" t="s">
+      <c r="M32" s="47" t="s">
         <v>214</v>
       </c>
-      <c r="M32" s="47" t="s">
+      <c r="N32" s="47" t="s">
         <v>213</v>
       </c>
-      <c r="N32" s="55" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="33" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C33" s="70" t="s">
-        <v>334</v>
+      <c r="O32" s="53" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="33" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C33" s="68" t="s">
+        <v>387</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E33" s="13" t="s">
+      <c r="E33" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F33" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="74" t="s">
+        <v>347</v>
+      </c>
+      <c r="H33" s="77"/>
+      <c r="I33" s="75"/>
+      <c r="J33" s="75"/>
+      <c r="K33" s="75"/>
+      <c r="L33" s="75"/>
+      <c r="M33" s="75"/>
+      <c r="N33" s="76"/>
+      <c r="O33" s="52" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="34" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C34" s="70" t="s">
+        <v>388</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="F33" s="78" t="s">
-        <v>348</v>
-      </c>
-      <c r="G33" s="81"/>
-      <c r="H33" s="79"/>
-      <c r="I33" s="79"/>
-      <c r="J33" s="79"/>
-      <c r="K33" s="79"/>
-      <c r="L33" s="79"/>
-      <c r="M33" s="80"/>
-      <c r="N33" s="54" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="34" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C34" s="72" t="s">
-        <v>335</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="F34" s="78" t="s">
-        <v>348</v>
-      </c>
-      <c r="G34" s="79"/>
-      <c r="H34" s="79"/>
-      <c r="I34" s="79"/>
-      <c r="J34" s="79"/>
-      <c r="K34" s="79"/>
-      <c r="L34" s="79"/>
-      <c r="M34" s="80"/>
-      <c r="N34" s="54" t="s">
-        <v>351</v>
+      <c r="F34" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="74" t="s">
+        <v>347</v>
+      </c>
+      <c r="H34" s="75"/>
+      <c r="I34" s="75"/>
+      <c r="J34" s="75"/>
+      <c r="K34" s="75"/>
+      <c r="L34" s="75"/>
+      <c r="M34" s="75"/>
+      <c r="N34" s="76"/>
+      <c r="O34" s="52" t="s">
+        <v>350</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="F34:M34"/>
-    <mergeCell ref="F5:M5"/>
-    <mergeCell ref="F6:M6"/>
-    <mergeCell ref="F7:M7"/>
-    <mergeCell ref="F8:M8"/>
-    <mergeCell ref="F23:K23"/>
-    <mergeCell ref="F24:M24"/>
-    <mergeCell ref="F25:M25"/>
-    <mergeCell ref="F26:M26"/>
-    <mergeCell ref="F27:M27"/>
-    <mergeCell ref="F28:M28"/>
-    <mergeCell ref="F29:M29"/>
-    <mergeCell ref="F30:M30"/>
-    <mergeCell ref="F31:K31"/>
-    <mergeCell ref="F18:M18"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="F4:L4"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="F9:M9"/>
-    <mergeCell ref="F10:M10"/>
-    <mergeCell ref="F33:M33"/>
-    <mergeCell ref="F17:M17"/>
-    <mergeCell ref="F11:M11"/>
-    <mergeCell ref="F12:M12"/>
-    <mergeCell ref="F19:M19"/>
-    <mergeCell ref="F20:M20"/>
-    <mergeCell ref="F21:M21"/>
-    <mergeCell ref="F22:M22"/>
-    <mergeCell ref="F13:M13"/>
-    <mergeCell ref="F14:M14"/>
-    <mergeCell ref="F15:M15"/>
-    <mergeCell ref="F16:M16"/>
+  <mergeCells count="31">
+    <mergeCell ref="G34:N34"/>
+    <mergeCell ref="G5:N5"/>
+    <mergeCell ref="G6:N6"/>
+    <mergeCell ref="G7:N7"/>
+    <mergeCell ref="G8:N8"/>
+    <mergeCell ref="G23:L23"/>
+    <mergeCell ref="G24:N24"/>
+    <mergeCell ref="G25:N25"/>
+    <mergeCell ref="G26:N26"/>
+    <mergeCell ref="G27:N27"/>
+    <mergeCell ref="G28:N28"/>
+    <mergeCell ref="G29:N29"/>
+    <mergeCell ref="G30:N30"/>
+    <mergeCell ref="G18:N18"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="G31:N31"/>
+    <mergeCell ref="G4:M4"/>
+    <mergeCell ref="G9:N9"/>
+    <mergeCell ref="G10:N10"/>
+    <mergeCell ref="G33:N33"/>
+    <mergeCell ref="G17:N17"/>
+    <mergeCell ref="G11:N11"/>
+    <mergeCell ref="G12:N12"/>
+    <mergeCell ref="G19:N19"/>
+    <mergeCell ref="G20:N20"/>
+    <mergeCell ref="G21:N21"/>
+    <mergeCell ref="G22:N22"/>
+    <mergeCell ref="G13:N13"/>
+    <mergeCell ref="G14:N14"/>
+    <mergeCell ref="G15:N15"/>
+    <mergeCell ref="G16:N16"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4268,16 +4300,16 @@
       <c r="E12" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="92" t="s">
+      <c r="F12" s="90" t="s">
         <v>201</v>
       </c>
-      <c r="G12" s="93"/>
-      <c r="H12" s="93"/>
-      <c r="I12" s="93"/>
-      <c r="J12" s="93"/>
-      <c r="K12" s="93"/>
-      <c r="L12" s="93"/>
-      <c r="M12" s="94"/>
+      <c r="G12" s="91"/>
+      <c r="H12" s="91"/>
+      <c r="I12" s="91"/>
+      <c r="J12" s="91"/>
+      <c r="K12" s="91"/>
+      <c r="L12" s="91"/>
+      <c r="M12" s="92"/>
     </row>
     <row r="13" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="20" t="s">
@@ -4293,12 +4325,12 @@
       <c r="G13" s="37"/>
       <c r="H13" s="37"/>
       <c r="I13" s="38"/>
-      <c r="J13" s="92" t="s">
+      <c r="J13" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="K13" s="93"/>
-      <c r="L13" s="93"/>
-      <c r="M13" s="94"/>
+      <c r="K13" s="91"/>
+      <c r="L13" s="91"/>
+      <c r="M13" s="92"/>
     </row>
     <row r="14" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="20" t="s">
@@ -4310,16 +4342,16 @@
       <c r="E14" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="92" t="s">
+      <c r="F14" s="90" t="s">
         <v>201</v>
       </c>
-      <c r="G14" s="93"/>
-      <c r="H14" s="93"/>
-      <c r="I14" s="93"/>
-      <c r="J14" s="93"/>
-      <c r="K14" s="93"/>
-      <c r="L14" s="93"/>
-      <c r="M14" s="94"/>
+      <c r="G14" s="91"/>
+      <c r="H14" s="91"/>
+      <c r="I14" s="91"/>
+      <c r="J14" s="91"/>
+      <c r="K14" s="91"/>
+      <c r="L14" s="91"/>
+      <c r="M14" s="92"/>
     </row>
     <row r="15" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="20" t="s">
@@ -4335,12 +4367,12 @@
       <c r="G15" s="37"/>
       <c r="H15" s="37"/>
       <c r="I15" s="38"/>
-      <c r="J15" s="92" t="s">
+      <c r="J15" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="K15" s="93"/>
-      <c r="L15" s="93"/>
-      <c r="M15" s="94"/>
+      <c r="K15" s="91"/>
+      <c r="L15" s="91"/>
+      <c r="M15" s="92"/>
     </row>
     <row r="16" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="20" t="s">
@@ -4352,16 +4384,16 @@
       <c r="E16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="92" t="s">
+      <c r="F16" s="90" t="s">
         <v>201</v>
       </c>
-      <c r="G16" s="93"/>
-      <c r="H16" s="93"/>
-      <c r="I16" s="93"/>
-      <c r="J16" s="93"/>
-      <c r="K16" s="93"/>
-      <c r="L16" s="93"/>
-      <c r="M16" s="94"/>
+      <c r="G16" s="91"/>
+      <c r="H16" s="91"/>
+      <c r="I16" s="91"/>
+      <c r="J16" s="91"/>
+      <c r="K16" s="91"/>
+      <c r="L16" s="91"/>
+      <c r="M16" s="92"/>
     </row>
     <row r="17" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="20" t="s">
@@ -4377,12 +4409,12 @@
       <c r="G17" s="37"/>
       <c r="H17" s="37"/>
       <c r="I17" s="38"/>
-      <c r="J17" s="92" t="s">
+      <c r="J17" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="K17" s="93"/>
-      <c r="L17" s="93"/>
-      <c r="M17" s="94"/>
+      <c r="K17" s="91"/>
+      <c r="L17" s="91"/>
+      <c r="M17" s="92"/>
     </row>
     <row r="18" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="20" t="s">
@@ -4397,13 +4429,13 @@
       <c r="F18" s="36"/>
       <c r="G18" s="37"/>
       <c r="H18" s="38"/>
-      <c r="I18" s="92" t="s">
+      <c r="I18" s="90" t="s">
         <v>203</v>
       </c>
-      <c r="J18" s="93"/>
-      <c r="K18" s="93"/>
-      <c r="L18" s="93"/>
-      <c r="M18" s="94"/>
+      <c r="J18" s="91"/>
+      <c r="K18" s="91"/>
+      <c r="L18" s="91"/>
+      <c r="M18" s="92"/>
     </row>
     <row r="19" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="20" t="s">
@@ -4456,12 +4488,12 @@
       <c r="I20" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="J20" s="92" t="s">
+      <c r="J20" s="90" t="s">
         <v>204</v>
       </c>
-      <c r="K20" s="93"/>
-      <c r="L20" s="93"/>
-      <c r="M20" s="94"/>
+      <c r="K20" s="91"/>
+      <c r="L20" s="91"/>
+      <c r="M20" s="92"/>
     </row>
     <row r="21" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="20" t="s">
@@ -4479,12 +4511,12 @@
       <c r="I21" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="J21" s="92" t="s">
+      <c r="J21" s="90" t="s">
         <v>204</v>
       </c>
-      <c r="K21" s="93"/>
-      <c r="L21" s="93"/>
-      <c r="M21" s="94"/>
+      <c r="K21" s="91"/>
+      <c r="L21" s="91"/>
+      <c r="M21" s="92"/>
     </row>
     <row r="22" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="20" t="s">
@@ -4502,12 +4534,12 @@
       <c r="I22" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="J22" s="92" t="s">
+      <c r="J22" s="90" t="s">
         <v>204</v>
       </c>
-      <c r="K22" s="93"/>
-      <c r="L22" s="93"/>
-      <c r="M22" s="94"/>
+      <c r="K22" s="91"/>
+      <c r="L22" s="91"/>
+      <c r="M22" s="92"/>
     </row>
     <row r="23" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="20" t="s">
@@ -4519,16 +4551,16 @@
       <c r="E23" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="F23" s="92" t="s">
+      <c r="F23" s="90" t="s">
         <v>205</v>
       </c>
-      <c r="G23" s="93"/>
-      <c r="H23" s="93"/>
-      <c r="I23" s="93"/>
-      <c r="J23" s="93"/>
-      <c r="K23" s="93"/>
-      <c r="L23" s="93"/>
-      <c r="M23" s="94"/>
+      <c r="G23" s="91"/>
+      <c r="H23" s="91"/>
+      <c r="I23" s="91"/>
+      <c r="J23" s="91"/>
+      <c r="K23" s="91"/>
+      <c r="L23" s="91"/>
+      <c r="M23" s="92"/>
     </row>
     <row r="24" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="20" t="s">
@@ -4540,16 +4572,16 @@
       <c r="E24" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F24" s="92" t="s">
+      <c r="F24" s="90" t="s">
         <v>206</v>
       </c>
-      <c r="G24" s="93"/>
-      <c r="H24" s="93"/>
-      <c r="I24" s="93"/>
-      <c r="J24" s="93"/>
-      <c r="K24" s="93"/>
-      <c r="L24" s="93"/>
-      <c r="M24" s="94"/>
+      <c r="G24" s="91"/>
+      <c r="H24" s="91"/>
+      <c r="I24" s="91"/>
+      <c r="J24" s="91"/>
+      <c r="K24" s="91"/>
+      <c r="L24" s="91"/>
+      <c r="M24" s="92"/>
     </row>
     <row r="25" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="20" t="s">
@@ -4565,12 +4597,12 @@
       <c r="G25" s="37"/>
       <c r="H25" s="37"/>
       <c r="I25" s="38"/>
-      <c r="J25" s="92" t="s">
+      <c r="J25" s="90" t="s">
         <v>207</v>
       </c>
-      <c r="K25" s="93"/>
-      <c r="L25" s="93"/>
-      <c r="M25" s="94"/>
+      <c r="K25" s="91"/>
+      <c r="L25" s="91"/>
+      <c r="M25" s="92"/>
     </row>
     <row r="26" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="20" t="s">
@@ -4620,16 +4652,16 @@
       <c r="E28" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="F28" s="82" t="s">
+      <c r="F28" s="78" t="s">
         <v>201</v>
       </c>
-      <c r="G28" s="90"/>
-      <c r="H28" s="90"/>
-      <c r="I28" s="90"/>
-      <c r="J28" s="90"/>
-      <c r="K28" s="90"/>
-      <c r="L28" s="90"/>
-      <c r="M28" s="91"/>
+      <c r="G28" s="88"/>
+      <c r="H28" s="88"/>
+      <c r="I28" s="88"/>
+      <c r="J28" s="88"/>
+      <c r="K28" s="88"/>
+      <c r="L28" s="88"/>
+      <c r="M28" s="89"/>
     </row>
     <row r="29" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="20" t="s">
@@ -4645,12 +4677,12 @@
       <c r="G29" s="28"/>
       <c r="H29" s="28"/>
       <c r="I29" s="29"/>
-      <c r="J29" s="82" t="s">
+      <c r="J29" s="78" t="s">
         <v>202</v>
       </c>
-      <c r="K29" s="90"/>
-      <c r="L29" s="90"/>
-      <c r="M29" s="91"/>
+      <c r="K29" s="88"/>
+      <c r="L29" s="88"/>
+      <c r="M29" s="89"/>
     </row>
     <row r="30" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="20" t="s">
@@ -4662,16 +4694,16 @@
       <c r="E30" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="F30" s="82" t="s">
+      <c r="F30" s="78" t="s">
         <v>201</v>
       </c>
-      <c r="G30" s="90"/>
-      <c r="H30" s="90"/>
-      <c r="I30" s="90"/>
-      <c r="J30" s="90"/>
-      <c r="K30" s="90"/>
-      <c r="L30" s="90"/>
-      <c r="M30" s="91"/>
+      <c r="G30" s="88"/>
+      <c r="H30" s="88"/>
+      <c r="I30" s="88"/>
+      <c r="J30" s="88"/>
+      <c r="K30" s="88"/>
+      <c r="L30" s="88"/>
+      <c r="M30" s="89"/>
     </row>
     <row r="31" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="20" t="s">
@@ -4687,12 +4719,12 @@
       <c r="G31" s="28"/>
       <c r="H31" s="28"/>
       <c r="I31" s="29"/>
-      <c r="J31" s="82" t="s">
+      <c r="J31" s="78" t="s">
         <v>202</v>
       </c>
-      <c r="K31" s="90"/>
-      <c r="L31" s="90"/>
-      <c r="M31" s="91"/>
+      <c r="K31" s="88"/>
+      <c r="L31" s="88"/>
+      <c r="M31" s="89"/>
     </row>
     <row r="32" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="20" t="s">
@@ -4704,16 +4736,16 @@
       <c r="E32" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="F32" s="82" t="s">
+      <c r="F32" s="78" t="s">
         <v>201</v>
       </c>
-      <c r="G32" s="90"/>
-      <c r="H32" s="90"/>
-      <c r="I32" s="90"/>
-      <c r="J32" s="90"/>
-      <c r="K32" s="90"/>
-      <c r="L32" s="90"/>
-      <c r="M32" s="91"/>
+      <c r="G32" s="88"/>
+      <c r="H32" s="88"/>
+      <c r="I32" s="88"/>
+      <c r="J32" s="88"/>
+      <c r="K32" s="88"/>
+      <c r="L32" s="88"/>
+      <c r="M32" s="89"/>
     </row>
     <row r="33" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="20" t="s">
@@ -4729,12 +4761,12 @@
       <c r="G33" s="28"/>
       <c r="H33" s="28"/>
       <c r="I33" s="29"/>
-      <c r="J33" s="82" t="s">
+      <c r="J33" s="78" t="s">
         <v>202</v>
       </c>
-      <c r="K33" s="90"/>
-      <c r="L33" s="90"/>
-      <c r="M33" s="91"/>
+      <c r="K33" s="88"/>
+      <c r="L33" s="88"/>
+      <c r="M33" s="89"/>
     </row>
     <row r="34" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="20" t="s">
@@ -4749,13 +4781,13 @@
       <c r="F34" s="27"/>
       <c r="G34" s="28"/>
       <c r="H34" s="29"/>
-      <c r="I34" s="82" t="s">
+      <c r="I34" s="78" t="s">
         <v>203</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="90"/>
-      <c r="L34" s="90"/>
-      <c r="M34" s="91"/>
+      <c r="J34" s="88"/>
+      <c r="K34" s="88"/>
+      <c r="L34" s="88"/>
+      <c r="M34" s="89"/>
     </row>
     <row r="35" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="20" t="s">
@@ -4808,12 +4840,12 @@
       <c r="I36" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="J36" s="82" t="s">
+      <c r="J36" s="78" t="s">
         <v>204</v>
       </c>
-      <c r="K36" s="90"/>
-      <c r="L36" s="90"/>
-      <c r="M36" s="91"/>
+      <c r="K36" s="88"/>
+      <c r="L36" s="88"/>
+      <c r="M36" s="89"/>
     </row>
     <row r="37" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="20" t="s">
@@ -4831,12 +4863,12 @@
       <c r="I37" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="J37" s="82" t="s">
+      <c r="J37" s="78" t="s">
         <v>204</v>
       </c>
-      <c r="K37" s="90"/>
-      <c r="L37" s="90"/>
-      <c r="M37" s="91"/>
+      <c r="K37" s="88"/>
+      <c r="L37" s="88"/>
+      <c r="M37" s="89"/>
     </row>
     <row r="38" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="20" t="s">
@@ -4854,12 +4886,12 @@
       <c r="I38" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="J38" s="82" t="s">
+      <c r="J38" s="78" t="s">
         <v>204</v>
       </c>
-      <c r="K38" s="90"/>
-      <c r="L38" s="90"/>
-      <c r="M38" s="91"/>
+      <c r="K38" s="88"/>
+      <c r="L38" s="88"/>
+      <c r="M38" s="89"/>
     </row>
     <row r="39" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="20" t="s">
@@ -4871,16 +4903,16 @@
       <c r="E39" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="F39" s="82" t="s">
+      <c r="F39" s="78" t="s">
         <v>205</v>
       </c>
-      <c r="G39" s="90"/>
-      <c r="H39" s="90"/>
-      <c r="I39" s="90"/>
-      <c r="J39" s="90"/>
-      <c r="K39" s="90"/>
-      <c r="L39" s="90"/>
-      <c r="M39" s="91"/>
+      <c r="G39" s="88"/>
+      <c r="H39" s="88"/>
+      <c r="I39" s="88"/>
+      <c r="J39" s="88"/>
+      <c r="K39" s="88"/>
+      <c r="L39" s="88"/>
+      <c r="M39" s="89"/>
     </row>
     <row r="40" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="20" t="s">
@@ -4892,16 +4924,16 @@
       <c r="E40" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="F40" s="82" t="s">
+      <c r="F40" s="78" t="s">
         <v>206</v>
       </c>
-      <c r="G40" s="90"/>
-      <c r="H40" s="90"/>
-      <c r="I40" s="90"/>
-      <c r="J40" s="90"/>
-      <c r="K40" s="90"/>
-      <c r="L40" s="90"/>
-      <c r="M40" s="91"/>
+      <c r="G40" s="88"/>
+      <c r="H40" s="88"/>
+      <c r="I40" s="88"/>
+      <c r="J40" s="88"/>
+      <c r="K40" s="88"/>
+      <c r="L40" s="88"/>
+      <c r="M40" s="89"/>
     </row>
     <row r="41" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="20" t="s">
@@ -4917,12 +4949,12 @@
       <c r="G41" s="28"/>
       <c r="H41" s="28"/>
       <c r="I41" s="29"/>
-      <c r="J41" s="82" t="s">
+      <c r="J41" s="78" t="s">
         <v>207</v>
       </c>
-      <c r="K41" s="90"/>
-      <c r="L41" s="90"/>
-      <c r="M41" s="91"/>
+      <c r="K41" s="88"/>
+      <c r="L41" s="88"/>
+      <c r="M41" s="89"/>
     </row>
     <row r="42" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="20" t="s">
@@ -4957,12 +4989,12 @@
       <c r="G43" s="28"/>
       <c r="H43" s="28"/>
       <c r="I43" s="35"/>
-      <c r="J43" s="82" t="s">
+      <c r="J43" s="78" t="s">
         <v>135</v>
       </c>
-      <c r="K43" s="90"/>
-      <c r="L43" s="90"/>
-      <c r="M43" s="91"/>
+      <c r="K43" s="88"/>
+      <c r="L43" s="88"/>
+      <c r="M43" s="89"/>
     </row>
     <row r="44" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="21" t="s">
@@ -5367,16 +5399,16 @@
       <c r="E6" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="F6" s="76" t="s">
+      <c r="F6" s="82" t="s">
         <v>107</v>
       </c>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86"/>
-      <c r="I6" s="86"/>
-      <c r="J6" s="86"/>
-      <c r="K6" s="86"/>
-      <c r="L6" s="86"/>
-      <c r="M6" s="77"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="83"/>
+      <c r="L6" s="83"/>
+      <c r="M6" s="84"/>
     </row>
     <row r="7" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C7" s="25" t="s">
@@ -5388,16 +5420,16 @@
       <c r="E7" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="F7" s="76" t="s">
+      <c r="F7" s="82" t="s">
         <v>197</v>
       </c>
-      <c r="G7" s="86"/>
-      <c r="H7" s="86"/>
-      <c r="I7" s="86"/>
-      <c r="J7" s="86"/>
-      <c r="K7" s="86"/>
-      <c r="L7" s="86"/>
-      <c r="M7" s="77"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="83"/>
+      <c r="J7" s="83"/>
+      <c r="K7" s="83"/>
+      <c r="L7" s="83"/>
+      <c r="M7" s="84"/>
     </row>
     <row r="8" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
@@ -5409,16 +5441,16 @@
       <c r="E8" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F8" s="76" t="s">
+      <c r="F8" s="82" t="s">
         <v>105</v>
       </c>
-      <c r="G8" s="86"/>
-      <c r="H8" s="86"/>
-      <c r="I8" s="86"/>
-      <c r="J8" s="86"/>
-      <c r="K8" s="86"/>
-      <c r="L8" s="86"/>
-      <c r="M8" s="77"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="83"/>
+      <c r="K8" s="83"/>
+      <c r="L8" s="83"/>
+      <c r="M8" s="84"/>
     </row>
     <row r="9" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
@@ -5430,16 +5462,16 @@
       <c r="E9" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F9" s="76" t="s">
+      <c r="F9" s="82" t="s">
         <v>198</v>
       </c>
-      <c r="G9" s="86"/>
-      <c r="H9" s="86"/>
-      <c r="I9" s="86"/>
-      <c r="J9" s="86"/>
-      <c r="K9" s="86"/>
-      <c r="L9" s="86"/>
-      <c r="M9" s="77"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
+      <c r="J9" s="83"/>
+      <c r="K9" s="83"/>
+      <c r="L9" s="83"/>
+      <c r="M9" s="84"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B19" t="s">
@@ -5501,12 +5533,12 @@
       <c r="I21" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="J21" s="76" t="s">
+      <c r="J21" s="82" t="s">
         <v>124</v>
       </c>
-      <c r="K21" s="86"/>
-      <c r="L21" s="86"/>
-      <c r="M21" s="77"/>
+      <c r="K21" s="83"/>
+      <c r="L21" s="83"/>
+      <c r="M21" s="84"/>
     </row>
     <row r="22" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="20" t="s">
@@ -5528,12 +5560,12 @@
       <c r="I22" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="J22" s="76" t="s">
+      <c r="J22" s="82" t="s">
         <v>124</v>
       </c>
-      <c r="K22" s="86"/>
-      <c r="L22" s="86"/>
-      <c r="M22" s="77"/>
+      <c r="K22" s="83"/>
+      <c r="L22" s="83"/>
+      <c r="M22" s="84"/>
     </row>
     <row r="23" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="20" t="s">
@@ -5543,18 +5575,18 @@
         <v>46</v>
       </c>
       <c r="E23" s="6"/>
-      <c r="F23" s="76" t="s">
+      <c r="F23" s="82" t="s">
         <v>125</v>
       </c>
-      <c r="G23" s="77"/>
-      <c r="H23" s="76" t="s">
+      <c r="G23" s="84"/>
+      <c r="H23" s="82" t="s">
         <v>126</v>
       </c>
-      <c r="I23" s="86"/>
-      <c r="J23" s="86"/>
-      <c r="K23" s="86"/>
-      <c r="L23" s="86"/>
-      <c r="M23" s="77"/>
+      <c r="I23" s="83"/>
+      <c r="J23" s="83"/>
+      <c r="K23" s="83"/>
+      <c r="L23" s="83"/>
+      <c r="M23" s="84"/>
     </row>
     <row r="24" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="20" t="s">
@@ -5564,10 +5596,10 @@
         <v>46</v>
       </c>
       <c r="E24" s="6"/>
-      <c r="F24" s="76" t="s">
+      <c r="F24" s="82" t="s">
         <v>125</v>
       </c>
-      <c r="G24" s="77"/>
+      <c r="G24" s="84"/>
       <c r="H24" s="19"/>
       <c r="I24" s="12" t="s">
         <v>129</v>
@@ -5575,11 +5607,11 @@
       <c r="J24" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="K24" s="76" t="s">
+      <c r="K24" s="82" t="s">
         <v>127</v>
       </c>
-      <c r="L24" s="86"/>
-      <c r="M24" s="77"/>
+      <c r="L24" s="83"/>
+      <c r="M24" s="84"/>
     </row>
     <row r="25" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="20" t="s">
@@ -5589,18 +5621,18 @@
         <v>46</v>
       </c>
       <c r="E25" s="6"/>
-      <c r="F25" s="76" t="s">
+      <c r="F25" s="82" t="s">
         <v>130</v>
       </c>
-      <c r="G25" s="86"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="77"/>
-      <c r="J25" s="76" t="s">
+      <c r="G25" s="83"/>
+      <c r="H25" s="83"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="82" t="s">
         <v>131</v>
       </c>
-      <c r="K25" s="86"/>
-      <c r="L25" s="86"/>
-      <c r="M25" s="77"/>
+      <c r="K25" s="83"/>
+      <c r="L25" s="83"/>
+      <c r="M25" s="84"/>
     </row>
     <row r="26" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="20" t="s">
@@ -5610,18 +5642,18 @@
         <v>46</v>
       </c>
       <c r="E26" s="6"/>
-      <c r="F26" s="76" t="s">
+      <c r="F26" s="82" t="s">
         <v>130</v>
       </c>
-      <c r="G26" s="86"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="77"/>
-      <c r="J26" s="76" t="s">
+      <c r="G26" s="83"/>
+      <c r="H26" s="83"/>
+      <c r="I26" s="84"/>
+      <c r="J26" s="82" t="s">
         <v>131</v>
       </c>
-      <c r="K26" s="86"/>
-      <c r="L26" s="86"/>
-      <c r="M26" s="77"/>
+      <c r="K26" s="83"/>
+      <c r="L26" s="83"/>
+      <c r="M26" s="84"/>
     </row>
     <row r="27" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="20" t="s">
@@ -5631,18 +5663,18 @@
         <v>46</v>
       </c>
       <c r="E27" s="6"/>
-      <c r="F27" s="76" t="s">
+      <c r="F27" s="82" t="s">
         <v>132</v>
       </c>
-      <c r="G27" s="86"/>
-      <c r="H27" s="86"/>
-      <c r="I27" s="77"/>
-      <c r="J27" s="76" t="s">
+      <c r="G27" s="83"/>
+      <c r="H27" s="83"/>
+      <c r="I27" s="84"/>
+      <c r="J27" s="82" t="s">
         <v>133</v>
       </c>
-      <c r="K27" s="86"/>
-      <c r="L27" s="86"/>
-      <c r="M27" s="77"/>
+      <c r="K27" s="83"/>
+      <c r="L27" s="83"/>
+      <c r="M27" s="84"/>
     </row>
     <row r="28" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C28" s="20" t="s">
@@ -5652,18 +5684,18 @@
         <v>46</v>
       </c>
       <c r="E28" s="6"/>
-      <c r="F28" s="76" t="s">
+      <c r="F28" s="82" t="s">
         <v>132</v>
       </c>
-      <c r="G28" s="86"/>
-      <c r="H28" s="86"/>
-      <c r="I28" s="77"/>
-      <c r="J28" s="76" t="s">
+      <c r="G28" s="83"/>
+      <c r="H28" s="83"/>
+      <c r="I28" s="84"/>
+      <c r="J28" s="82" t="s">
         <v>133</v>
       </c>
-      <c r="K28" s="86"/>
-      <c r="L28" s="86"/>
-      <c r="M28" s="77"/>
+      <c r="K28" s="83"/>
+      <c r="L28" s="83"/>
+      <c r="M28" s="84"/>
     </row>
     <row r="29" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="20" t="s">
@@ -5717,16 +5749,16 @@
       <c r="E31" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="F31" s="76" t="s">
+      <c r="F31" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="G31" s="86"/>
-      <c r="H31" s="86"/>
-      <c r="I31" s="86"/>
-      <c r="J31" s="86"/>
-      <c r="K31" s="86"/>
-      <c r="L31" s="86"/>
-      <c r="M31" s="77"/>
+      <c r="G31" s="83"/>
+      <c r="H31" s="83"/>
+      <c r="I31" s="83"/>
+      <c r="J31" s="83"/>
+      <c r="K31" s="83"/>
+      <c r="L31" s="83"/>
+      <c r="M31" s="84"/>
     </row>
     <row r="32" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="20" t="s">
@@ -5736,16 +5768,16 @@
         <v>46</v>
       </c>
       <c r="E32" s="6"/>
-      <c r="F32" s="76" t="s">
+      <c r="F32" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="G32" s="86"/>
-      <c r="H32" s="86"/>
-      <c r="I32" s="86"/>
-      <c r="J32" s="86"/>
-      <c r="K32" s="86"/>
-      <c r="L32" s="86"/>
-      <c r="M32" s="77"/>
+      <c r="G32" s="83"/>
+      <c r="H32" s="83"/>
+      <c r="I32" s="83"/>
+      <c r="J32" s="83"/>
+      <c r="K32" s="83"/>
+      <c r="L32" s="83"/>
+      <c r="M32" s="84"/>
     </row>
     <row r="33" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="20" t="s">
@@ -5755,16 +5787,16 @@
         <v>46</v>
       </c>
       <c r="E33" s="6"/>
-      <c r="F33" s="76" t="s">
+      <c r="F33" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="G33" s="86"/>
-      <c r="H33" s="86"/>
-      <c r="I33" s="86"/>
-      <c r="J33" s="86"/>
-      <c r="K33" s="86"/>
-      <c r="L33" s="86"/>
-      <c r="M33" s="77"/>
+      <c r="G33" s="83"/>
+      <c r="H33" s="83"/>
+      <c r="I33" s="83"/>
+      <c r="J33" s="83"/>
+      <c r="K33" s="83"/>
+      <c r="L33" s="83"/>
+      <c r="M33" s="84"/>
     </row>
     <row r="34" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="20" t="s">
@@ -5774,16 +5806,16 @@
         <v>46</v>
       </c>
       <c r="E34" s="6"/>
-      <c r="F34" s="76" t="s">
+      <c r="F34" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="G34" s="86"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="86"/>
-      <c r="J34" s="86"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="86"/>
-      <c r="M34" s="77"/>
+      <c r="G34" s="83"/>
+      <c r="H34" s="83"/>
+      <c r="I34" s="83"/>
+      <c r="J34" s="83"/>
+      <c r="K34" s="83"/>
+      <c r="L34" s="83"/>
+      <c r="M34" s="84"/>
     </row>
     <row r="35" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="20" t="s">
@@ -5793,16 +5825,16 @@
         <v>46</v>
       </c>
       <c r="E35" s="6"/>
-      <c r="F35" s="76" t="s">
+      <c r="F35" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="G35" s="86"/>
-      <c r="H35" s="86"/>
-      <c r="I35" s="86"/>
-      <c r="J35" s="86"/>
-      <c r="K35" s="86"/>
-      <c r="L35" s="86"/>
-      <c r="M35" s="77"/>
+      <c r="G35" s="83"/>
+      <c r="H35" s="83"/>
+      <c r="I35" s="83"/>
+      <c r="J35" s="83"/>
+      <c r="K35" s="83"/>
+      <c r="L35" s="83"/>
+      <c r="M35" s="84"/>
     </row>
     <row r="36" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C36" s="20" t="s">
@@ -5812,16 +5844,16 @@
         <v>46</v>
       </c>
       <c r="E36" s="6"/>
-      <c r="F36" s="76" t="s">
+      <c r="F36" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="G36" s="86"/>
-      <c r="H36" s="86"/>
-      <c r="I36" s="86"/>
-      <c r="J36" s="86"/>
-      <c r="K36" s="86"/>
-      <c r="L36" s="86"/>
-      <c r="M36" s="77"/>
+      <c r="G36" s="83"/>
+      <c r="H36" s="83"/>
+      <c r="I36" s="83"/>
+      <c r="J36" s="83"/>
+      <c r="K36" s="83"/>
+      <c r="L36" s="83"/>
+      <c r="M36" s="84"/>
     </row>
     <row r="37" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="20" t="s">
@@ -5831,16 +5863,16 @@
         <v>41</v>
       </c>
       <c r="E37" s="1"/>
-      <c r="F37" s="76" t="s">
+      <c r="F37" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="G37" s="86"/>
-      <c r="H37" s="86"/>
-      <c r="I37" s="86"/>
-      <c r="J37" s="86"/>
-      <c r="K37" s="86"/>
-      <c r="L37" s="86"/>
-      <c r="M37" s="77"/>
+      <c r="G37" s="83"/>
+      <c r="H37" s="83"/>
+      <c r="I37" s="83"/>
+      <c r="J37" s="83"/>
+      <c r="K37" s="83"/>
+      <c r="L37" s="83"/>
+      <c r="M37" s="84"/>
     </row>
     <row r="38" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="20" t="s">
@@ -5850,16 +5882,16 @@
         <v>41</v>
       </c>
       <c r="E38" s="1"/>
-      <c r="F38" s="76" t="s">
+      <c r="F38" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="G38" s="86"/>
-      <c r="H38" s="86"/>
-      <c r="I38" s="86"/>
-      <c r="J38" s="86"/>
-      <c r="K38" s="86"/>
-      <c r="L38" s="86"/>
-      <c r="M38" s="77"/>
+      <c r="G38" s="83"/>
+      <c r="H38" s="83"/>
+      <c r="I38" s="83"/>
+      <c r="J38" s="83"/>
+      <c r="K38" s="83"/>
+      <c r="L38" s="83"/>
+      <c r="M38" s="84"/>
     </row>
     <row r="39" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="20" t="s">
@@ -5869,16 +5901,16 @@
         <v>41</v>
       </c>
       <c r="E39" s="1"/>
-      <c r="F39" s="76" t="s">
+      <c r="F39" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="G39" s="86"/>
-      <c r="H39" s="86"/>
-      <c r="I39" s="86"/>
-      <c r="J39" s="86"/>
-      <c r="K39" s="86"/>
-      <c r="L39" s="86"/>
-      <c r="M39" s="77"/>
+      <c r="G39" s="83"/>
+      <c r="H39" s="83"/>
+      <c r="I39" s="83"/>
+      <c r="J39" s="83"/>
+      <c r="K39" s="83"/>
+      <c r="L39" s="83"/>
+      <c r="M39" s="84"/>
     </row>
     <row r="40" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="20" t="s">
@@ -5888,16 +5920,16 @@
         <v>41</v>
       </c>
       <c r="E40" s="1"/>
-      <c r="F40" s="76" t="s">
+      <c r="F40" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="G40" s="86"/>
-      <c r="H40" s="86"/>
-      <c r="I40" s="86"/>
-      <c r="J40" s="86"/>
-      <c r="K40" s="86"/>
-      <c r="L40" s="86"/>
-      <c r="M40" s="77"/>
+      <c r="G40" s="83"/>
+      <c r="H40" s="83"/>
+      <c r="I40" s="83"/>
+      <c r="J40" s="83"/>
+      <c r="K40" s="83"/>
+      <c r="L40" s="83"/>
+      <c r="M40" s="84"/>
     </row>
     <row r="41" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="20" t="s">
@@ -5932,11 +5964,11 @@
       <c r="I42" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J42" s="76" t="s">
+      <c r="J42" s="82" t="s">
         <v>159</v>
       </c>
-      <c r="K42" s="86"/>
-      <c r="L42" s="77"/>
+      <c r="K42" s="83"/>
+      <c r="L42" s="84"/>
       <c r="M42" s="14" t="s">
         <v>160</v>
       </c>
@@ -5957,11 +5989,11 @@
       <c r="I43" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J43" s="76" t="s">
+      <c r="J43" s="82" t="s">
         <v>159</v>
       </c>
-      <c r="K43" s="86"/>
-      <c r="L43" s="77"/>
+      <c r="K43" s="83"/>
+      <c r="L43" s="84"/>
       <c r="M43" s="14" t="s">
         <v>160</v>
       </c>
@@ -5982,11 +6014,11 @@
       <c r="I44" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J44" s="76" t="s">
+      <c r="J44" s="82" t="s">
         <v>159</v>
       </c>
-      <c r="K44" s="86"/>
-      <c r="L44" s="77"/>
+      <c r="K44" s="83"/>
+      <c r="L44" s="84"/>
       <c r="M44" s="14" t="s">
         <v>160</v>
       </c>
@@ -6007,11 +6039,11 @@
       <c r="I45" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J45" s="76" t="s">
+      <c r="J45" s="82" t="s">
         <v>159</v>
       </c>
-      <c r="K45" s="86"/>
-      <c r="L45" s="77"/>
+      <c r="K45" s="83"/>
+      <c r="L45" s="84"/>
       <c r="M45" s="14" t="s">
         <v>160</v>
       </c>
@@ -6032,11 +6064,11 @@
       <c r="I46" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J46" s="76" t="s">
+      <c r="J46" s="82" t="s">
         <v>159</v>
       </c>
-      <c r="K46" s="86"/>
-      <c r="L46" s="77"/>
+      <c r="K46" s="83"/>
+      <c r="L46" s="84"/>
       <c r="M46" s="14" t="s">
         <v>160</v>
       </c>
@@ -6057,11 +6089,11 @@
       <c r="I47" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J47" s="76" t="s">
+      <c r="J47" s="82" t="s">
         <v>159</v>
       </c>
-      <c r="K47" s="86"/>
-      <c r="L47" s="77"/>
+      <c r="K47" s="83"/>
+      <c r="L47" s="84"/>
       <c r="M47" s="14" t="s">
         <v>160</v>
       </c>
@@ -6082,11 +6114,11 @@
       <c r="I48" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J48" s="76" t="s">
+      <c r="J48" s="82" t="s">
         <v>159</v>
       </c>
-      <c r="K48" s="86"/>
-      <c r="L48" s="77"/>
+      <c r="K48" s="83"/>
+      <c r="L48" s="84"/>
       <c r="M48" s="14" t="s">
         <v>160</v>
       </c>
@@ -6107,11 +6139,11 @@
       <c r="I49" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J49" s="76" t="s">
+      <c r="J49" s="82" t="s">
         <v>159</v>
       </c>
-      <c r="K49" s="86"/>
-      <c r="L49" s="77"/>
+      <c r="K49" s="83"/>
+      <c r="L49" s="84"/>
       <c r="M49" s="14" t="s">
         <v>160</v>
       </c>
@@ -6132,11 +6164,11 @@
       <c r="I50" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J50" s="76" t="s">
+      <c r="J50" s="82" t="s">
         <v>159</v>
       </c>
-      <c r="K50" s="86"/>
-      <c r="L50" s="77"/>
+      <c r="K50" s="83"/>
+      <c r="L50" s="84"/>
       <c r="M50" s="14" t="s">
         <v>160</v>
       </c>
@@ -6166,18 +6198,18 @@
         <v>41</v>
       </c>
       <c r="E52" s="1"/>
-      <c r="F52" s="76" t="s">
+      <c r="F52" s="82" t="s">
         <v>181</v>
       </c>
-      <c r="G52" s="86"/>
-      <c r="H52" s="86"/>
-      <c r="I52" s="77"/>
-      <c r="J52" s="76" t="s">
+      <c r="G52" s="83"/>
+      <c r="H52" s="83"/>
+      <c r="I52" s="84"/>
+      <c r="J52" s="82" t="s">
         <v>182</v>
       </c>
-      <c r="K52" s="86"/>
-      <c r="L52" s="86"/>
-      <c r="M52" s="77"/>
+      <c r="K52" s="83"/>
+      <c r="L52" s="83"/>
+      <c r="M52" s="84"/>
     </row>
     <row r="53" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="21" t="s">
@@ -6187,18 +6219,18 @@
         <v>96</v>
       </c>
       <c r="E53" s="13"/>
-      <c r="F53" s="76" t="s">
+      <c r="F53" s="82" t="s">
         <v>181</v>
       </c>
-      <c r="G53" s="86"/>
-      <c r="H53" s="86"/>
-      <c r="I53" s="77"/>
-      <c r="J53" s="76" t="s">
+      <c r="G53" s="83"/>
+      <c r="H53" s="83"/>
+      <c r="I53" s="84"/>
+      <c r="J53" s="82" t="s">
         <v>182</v>
       </c>
-      <c r="K53" s="86"/>
-      <c r="L53" s="86"/>
-      <c r="M53" s="77"/>
+      <c r="K53" s="83"/>
+      <c r="L53" s="83"/>
+      <c r="M53" s="84"/>
     </row>
     <row r="54" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="20" t="s">
@@ -6208,18 +6240,18 @@
         <v>41</v>
       </c>
       <c r="E54" s="1"/>
-      <c r="F54" s="76" t="s">
+      <c r="F54" s="82" t="s">
         <v>181</v>
       </c>
-      <c r="G54" s="86"/>
-      <c r="H54" s="86"/>
-      <c r="I54" s="77"/>
-      <c r="J54" s="76" t="s">
+      <c r="G54" s="83"/>
+      <c r="H54" s="83"/>
+      <c r="I54" s="84"/>
+      <c r="J54" s="82" t="s">
         <v>182</v>
       </c>
-      <c r="K54" s="86"/>
-      <c r="L54" s="86"/>
-      <c r="M54" s="77"/>
+      <c r="K54" s="83"/>
+      <c r="L54" s="83"/>
+      <c r="M54" s="84"/>
     </row>
     <row r="55" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C55" s="20" t="s">
@@ -6229,18 +6261,18 @@
         <v>41</v>
       </c>
       <c r="E55" s="1"/>
-      <c r="F55" s="76" t="s">
+      <c r="F55" s="82" t="s">
         <v>181</v>
       </c>
-      <c r="G55" s="86"/>
-      <c r="H55" s="86"/>
-      <c r="I55" s="77"/>
-      <c r="J55" s="76" t="s">
+      <c r="G55" s="83"/>
+      <c r="H55" s="83"/>
+      <c r="I55" s="84"/>
+      <c r="J55" s="82" t="s">
         <v>182</v>
       </c>
-      <c r="K55" s="86"/>
-      <c r="L55" s="86"/>
-      <c r="M55" s="77"/>
+      <c r="K55" s="83"/>
+      <c r="L55" s="83"/>
+      <c r="M55" s="84"/>
     </row>
     <row r="56" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="20" t="s">
@@ -6250,18 +6282,18 @@
         <v>41</v>
       </c>
       <c r="E56" s="1"/>
-      <c r="F56" s="76" t="s">
+      <c r="F56" s="82" t="s">
         <v>181</v>
       </c>
-      <c r="G56" s="86"/>
-      <c r="H56" s="86"/>
-      <c r="I56" s="77"/>
-      <c r="J56" s="76" t="s">
+      <c r="G56" s="83"/>
+      <c r="H56" s="83"/>
+      <c r="I56" s="84"/>
+      <c r="J56" s="82" t="s">
         <v>182</v>
       </c>
-      <c r="K56" s="86"/>
-      <c r="L56" s="86"/>
-      <c r="M56" s="77"/>
+      <c r="K56" s="83"/>
+      <c r="L56" s="83"/>
+      <c r="M56" s="84"/>
     </row>
     <row r="57" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C57" s="20" t="s">
@@ -6271,18 +6303,18 @@
         <v>41</v>
       </c>
       <c r="E57" s="1"/>
-      <c r="F57" s="76" t="s">
+      <c r="F57" s="82" t="s">
         <v>181</v>
       </c>
-      <c r="G57" s="86"/>
-      <c r="H57" s="86"/>
-      <c r="I57" s="77"/>
-      <c r="J57" s="76" t="s">
+      <c r="G57" s="83"/>
+      <c r="H57" s="83"/>
+      <c r="I57" s="84"/>
+      <c r="J57" s="82" t="s">
         <v>182</v>
       </c>
-      <c r="K57" s="86"/>
-      <c r="L57" s="86"/>
-      <c r="M57" s="77"/>
+      <c r="K57" s="83"/>
+      <c r="L57" s="83"/>
+      <c r="M57" s="84"/>
     </row>
     <row r="58" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C58" s="20" t="s">
@@ -6292,18 +6324,18 @@
         <v>41</v>
       </c>
       <c r="E58" s="1"/>
-      <c r="F58" s="76" t="s">
+      <c r="F58" s="82" t="s">
         <v>181</v>
       </c>
-      <c r="G58" s="86"/>
-      <c r="H58" s="86"/>
-      <c r="I58" s="77"/>
-      <c r="J58" s="76" t="s">
+      <c r="G58" s="83"/>
+      <c r="H58" s="83"/>
+      <c r="I58" s="84"/>
+      <c r="J58" s="82" t="s">
         <v>182</v>
       </c>
-      <c r="K58" s="86"/>
-      <c r="L58" s="86"/>
-      <c r="M58" s="77"/>
+      <c r="K58" s="83"/>
+      <c r="L58" s="83"/>
+      <c r="M58" s="84"/>
     </row>
     <row r="59" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C59" s="20" t="s">
@@ -6313,18 +6345,18 @@
         <v>41</v>
       </c>
       <c r="E59" s="1"/>
-      <c r="F59" s="76" t="s">
+      <c r="F59" s="82" t="s">
         <v>181</v>
       </c>
-      <c r="G59" s="86"/>
-      <c r="H59" s="86"/>
-      <c r="I59" s="77"/>
-      <c r="J59" s="76" t="s">
+      <c r="G59" s="83"/>
+      <c r="H59" s="83"/>
+      <c r="I59" s="84"/>
+      <c r="J59" s="82" t="s">
         <v>182</v>
       </c>
-      <c r="K59" s="86"/>
-      <c r="L59" s="86"/>
-      <c r="M59" s="77"/>
+      <c r="K59" s="83"/>
+      <c r="L59" s="83"/>
+      <c r="M59" s="84"/>
     </row>
     <row r="60" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C60" s="20" t="s">
@@ -6334,18 +6366,18 @@
         <v>41</v>
       </c>
       <c r="E60" s="1"/>
-      <c r="F60" s="76" t="s">
+      <c r="F60" s="82" t="s">
         <v>181</v>
       </c>
-      <c r="G60" s="86"/>
-      <c r="H60" s="86"/>
-      <c r="I60" s="77"/>
-      <c r="J60" s="76" t="s">
+      <c r="G60" s="83"/>
+      <c r="H60" s="83"/>
+      <c r="I60" s="84"/>
+      <c r="J60" s="82" t="s">
         <v>182</v>
       </c>
-      <c r="K60" s="86"/>
-      <c r="L60" s="86"/>
-      <c r="M60" s="77"/>
+      <c r="K60" s="83"/>
+      <c r="L60" s="83"/>
+      <c r="M60" s="84"/>
     </row>
     <row r="61" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C61" s="20" t="s">
@@ -6380,10 +6412,10 @@
       <c r="I62" s="10"/>
       <c r="J62" s="10"/>
       <c r="K62" s="11"/>
-      <c r="L62" s="82" t="s">
+      <c r="L62" s="78" t="s">
         <v>193</v>
       </c>
-      <c r="M62" s="84"/>
+      <c r="M62" s="80"/>
     </row>
     <row r="63" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C63" s="20" t="s">
@@ -6401,10 +6433,10 @@
       <c r="I63" s="10"/>
       <c r="J63" s="10"/>
       <c r="K63" s="11"/>
-      <c r="L63" s="85" t="s">
+      <c r="L63" s="81" t="s">
         <v>193</v>
       </c>
-      <c r="M63" s="84"/>
+      <c r="M63" s="80"/>
     </row>
     <row r="64" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C64" s="20" t="s">
@@ -6422,10 +6454,10 @@
       <c r="I64" s="10"/>
       <c r="J64" s="10"/>
       <c r="K64" s="11"/>
-      <c r="L64" s="85" t="s">
+      <c r="L64" s="81" t="s">
         <v>193</v>
       </c>
-      <c r="M64" s="84"/>
+      <c r="M64" s="80"/>
     </row>
     <row r="65" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C65" s="20" t="s">
@@ -6443,10 +6475,10 @@
       <c r="I65" s="10"/>
       <c r="J65" s="10"/>
       <c r="K65" s="11"/>
-      <c r="L65" s="85" t="s">
+      <c r="L65" s="81" t="s">
         <v>193</v>
       </c>
-      <c r="M65" s="84"/>
+      <c r="M65" s="80"/>
     </row>
     <row r="66" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C66" s="20" t="s">
@@ -6464,10 +6496,10 @@
       <c r="I66" s="10"/>
       <c r="J66" s="10"/>
       <c r="K66" s="11"/>
-      <c r="L66" s="85" t="s">
+      <c r="L66" s="81" t="s">
         <v>193</v>
       </c>
-      <c r="M66" s="84"/>
+      <c r="M66" s="80"/>
     </row>
     <row r="67" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C67" s="20" t="s">
@@ -6485,10 +6517,10 @@
       <c r="I67" s="10"/>
       <c r="J67" s="10"/>
       <c r="K67" s="11"/>
-      <c r="L67" s="85" t="s">
+      <c r="L67" s="81" t="s">
         <v>193</v>
       </c>
-      <c r="M67" s="84"/>
+      <c r="M67" s="80"/>
     </row>
     <row r="68" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C68" s="20" t="s">
@@ -6506,10 +6538,10 @@
       <c r="I68" s="10"/>
       <c r="J68" s="10"/>
       <c r="K68" s="11"/>
-      <c r="L68" s="85" t="s">
+      <c r="L68" s="81" t="s">
         <v>193</v>
       </c>
-      <c r="M68" s="84"/>
+      <c r="M68" s="80"/>
     </row>
     <row r="69" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C69" s="20" t="s">
@@ -6527,10 +6559,10 @@
       <c r="I69" s="10"/>
       <c r="J69" s="10"/>
       <c r="K69" s="11"/>
-      <c r="L69" s="85" t="s">
+      <c r="L69" s="81" t="s">
         <v>193</v>
       </c>
-      <c r="M69" s="84"/>
+      <c r="M69" s="80"/>
     </row>
     <row r="70" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C70" s="20" t="s">
@@ -6548,10 +6580,10 @@
       <c r="I70" s="10"/>
       <c r="J70" s="10"/>
       <c r="K70" s="11"/>
-      <c r="L70" s="85" t="s">
+      <c r="L70" s="81" t="s">
         <v>193</v>
       </c>
-      <c r="M70" s="84"/>
+      <c r="M70" s="80"/>
     </row>
     <row r="71" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C71" s="20" t="s">
@@ -6753,23 +6785,23 @@
       </c>
     </row>
     <row r="13" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C13" s="64" t="s">
+      <c r="C13" s="62" t="s">
         <v>136</v>
       </c>
-      <c r="D13" s="65" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13" s="67" t="s">
+      <c r="D13" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="65" t="s">
         <v>244</v>
       </c>
-      <c r="F13" s="101"/>
-      <c r="G13" s="102"/>
-      <c r="H13" s="102"/>
-      <c r="I13" s="102"/>
-      <c r="J13" s="102"/>
-      <c r="K13" s="102"/>
-      <c r="L13" s="102"/>
-      <c r="M13" s="103"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="100"/>
+      <c r="H13" s="100"/>
+      <c r="I13" s="100"/>
+      <c r="J13" s="100"/>
+      <c r="K13" s="100"/>
+      <c r="L13" s="100"/>
+      <c r="M13" s="101"/>
     </row>
     <row r="14" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="20" t="s">
@@ -6781,16 +6813,16 @@
       <c r="E14" s="45" t="s">
         <v>134</v>
       </c>
-      <c r="F14" s="78" t="s">
+      <c r="F14" s="74" t="s">
         <v>134</v>
       </c>
-      <c r="G14" s="79"/>
-      <c r="H14" s="79"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="79"/>
-      <c r="K14" s="79"/>
-      <c r="L14" s="79"/>
-      <c r="M14" s="80"/>
+      <c r="G14" s="75"/>
+      <c r="H14" s="75"/>
+      <c r="I14" s="75"/>
+      <c r="J14" s="75"/>
+      <c r="K14" s="75"/>
+      <c r="L14" s="75"/>
+      <c r="M14" s="76"/>
     </row>
     <row r="15" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="20" t="s">
@@ -6802,16 +6834,16 @@
       <c r="E15" s="45" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="78" t="s">
+      <c r="F15" s="74" t="s">
         <v>245</v>
       </c>
-      <c r="G15" s="79"/>
-      <c r="H15" s="79"/>
-      <c r="I15" s="79"/>
-      <c r="J15" s="79"/>
-      <c r="K15" s="79"/>
-      <c r="L15" s="79"/>
-      <c r="M15" s="80"/>
+      <c r="G15" s="75"/>
+      <c r="H15" s="75"/>
+      <c r="I15" s="75"/>
+      <c r="J15" s="75"/>
+      <c r="K15" s="75"/>
+      <c r="L15" s="75"/>
+      <c r="M15" s="76"/>
     </row>
     <row r="16" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="20" t="s">
@@ -6823,16 +6855,16 @@
       <c r="E16" s="44" t="s">
         <v>246</v>
       </c>
-      <c r="F16" s="78" t="s">
+      <c r="F16" s="74" t="s">
         <v>246</v>
       </c>
-      <c r="G16" s="79"/>
-      <c r="H16" s="79"/>
-      <c r="I16" s="79"/>
-      <c r="J16" s="79"/>
-      <c r="K16" s="79"/>
-      <c r="L16" s="79"/>
-      <c r="M16" s="80"/>
+      <c r="G16" s="75"/>
+      <c r="H16" s="75"/>
+      <c r="I16" s="75"/>
+      <c r="J16" s="75"/>
+      <c r="K16" s="75"/>
+      <c r="L16" s="75"/>
+      <c r="M16" s="76"/>
     </row>
     <row r="17" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="20" t="s">
@@ -6842,7 +6874,7 @@
         <v>46</v>
       </c>
       <c r="E17" s="45" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="F17" s="47" t="s">
         <v>247</v>
@@ -6853,11 +6885,11 @@
       <c r="H17" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="I17" s="59" t="s">
-        <v>392</v>
-      </c>
-      <c r="J17" s="59" t="s">
-        <v>393</v>
+      <c r="I17" s="57" t="s">
+        <v>383</v>
+      </c>
+      <c r="J17" s="57" t="s">
+        <v>384</v>
       </c>
       <c r="K17" s="46"/>
       <c r="L17" s="47" t="s">
@@ -6868,47 +6900,47 @@
       </c>
     </row>
     <row r="18" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="64" t="s">
+      <c r="C18" s="62" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="65" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" s="67"/>
-      <c r="F18" s="104" t="s">
+      <c r="D18" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="65"/>
+      <c r="F18" s="102" t="s">
         <v>252</v>
       </c>
-      <c r="G18" s="105"/>
-      <c r="H18" s="105"/>
-      <c r="I18" s="105"/>
-      <c r="J18" s="105"/>
-      <c r="K18" s="105"/>
-      <c r="L18" s="105"/>
-      <c r="M18" s="106"/>
-      <c r="N18" s="61" t="s">
-        <v>389</v>
+      <c r="G18" s="103"/>
+      <c r="H18" s="103"/>
+      <c r="I18" s="103"/>
+      <c r="J18" s="103"/>
+      <c r="K18" s="103"/>
+      <c r="L18" s="103"/>
+      <c r="M18" s="104"/>
+      <c r="N18" s="59" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="19" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C19" s="64" t="s">
+      <c r="C19" s="62" t="s">
         <v>142</v>
       </c>
-      <c r="D19" s="65" t="s">
-        <v>46</v>
-      </c>
-      <c r="E19" s="67"/>
-      <c r="F19" s="104" t="s">
+      <c r="D19" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="65"/>
+      <c r="F19" s="102" t="s">
         <v>253</v>
       </c>
-      <c r="G19" s="105"/>
-      <c r="H19" s="105"/>
-      <c r="I19" s="105"/>
-      <c r="J19" s="105"/>
-      <c r="K19" s="105"/>
-      <c r="L19" s="105"/>
-      <c r="M19" s="106"/>
-      <c r="N19" s="61" t="s">
-        <v>389</v>
+      <c r="G19" s="103"/>
+      <c r="H19" s="103"/>
+      <c r="I19" s="103"/>
+      <c r="J19" s="103"/>
+      <c r="K19" s="103"/>
+      <c r="L19" s="103"/>
+      <c r="M19" s="104"/>
+      <c r="N19" s="59" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="20" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -6919,28 +6951,28 @@
         <v>46</v>
       </c>
       <c r="E20" s="45"/>
-      <c r="F20" s="59" t="s">
+      <c r="F20" s="57" t="s">
         <v>254</v>
       </c>
-      <c r="G20" s="59" t="s">
+      <c r="G20" s="57" t="s">
         <v>255</v>
       </c>
-      <c r="H20" s="59" t="s">
+      <c r="H20" s="57" t="s">
         <v>256</v>
       </c>
-      <c r="I20" s="59" t="s">
+      <c r="I20" s="57" t="s">
         <v>257</v>
       </c>
-      <c r="J20" s="60" t="s">
+      <c r="J20" s="58" t="s">
         <v>258</v>
       </c>
-      <c r="K20" s="101"/>
-      <c r="L20" s="103"/>
-      <c r="M20" s="59" t="s">
+      <c r="K20" s="99"/>
+      <c r="L20" s="101"/>
+      <c r="M20" s="57" t="s">
         <v>259</v>
       </c>
-      <c r="N20" s="62" t="s">
-        <v>390</v>
+      <c r="N20" s="60" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="21" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -6957,18 +6989,18 @@
       <c r="G21" s="47" t="s">
         <v>261</v>
       </c>
-      <c r="H21" s="101"/>
-      <c r="I21" s="103"/>
-      <c r="J21" s="60" t="s">
+      <c r="H21" s="99"/>
+      <c r="I21" s="101"/>
+      <c r="J21" s="58" t="s">
         <v>262</v>
       </c>
-      <c r="K21" s="60" t="s">
+      <c r="K21" s="58" t="s">
         <v>263</v>
       </c>
-      <c r="L21" s="60" t="s">
+      <c r="L21" s="58" t="s">
         <v>264</v>
       </c>
-      <c r="M21" s="60" t="s">
+      <c r="M21" s="58" t="s">
         <v>265</v>
       </c>
     </row>
@@ -6980,18 +7012,18 @@
         <v>46</v>
       </c>
       <c r="E22" s="45"/>
-      <c r="F22" s="107" t="s">
+      <c r="F22" s="105" t="s">
         <v>266</v>
       </c>
-      <c r="G22" s="108"/>
-      <c r="H22" s="108"/>
-      <c r="I22" s="108"/>
-      <c r="J22" s="108"/>
-      <c r="K22" s="108"/>
-      <c r="L22" s="108"/>
-      <c r="M22" s="109"/>
+      <c r="G22" s="106"/>
+      <c r="H22" s="106"/>
+      <c r="I22" s="106"/>
+      <c r="J22" s="106"/>
+      <c r="K22" s="106"/>
+      <c r="L22" s="106"/>
+      <c r="M22" s="107"/>
       <c r="N22" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
     </row>
     <row r="23" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7002,18 +7034,18 @@
         <v>46</v>
       </c>
       <c r="E23" s="44"/>
-      <c r="F23" s="107" t="s">
+      <c r="F23" s="105" t="s">
         <v>267</v>
       </c>
-      <c r="G23" s="108"/>
-      <c r="H23" s="108"/>
-      <c r="I23" s="108"/>
-      <c r="J23" s="108"/>
-      <c r="K23" s="108"/>
-      <c r="L23" s="108"/>
-      <c r="M23" s="109"/>
+      <c r="G23" s="106"/>
+      <c r="H23" s="106"/>
+      <c r="I23" s="106"/>
+      <c r="J23" s="106"/>
+      <c r="K23" s="106"/>
+      <c r="L23" s="106"/>
+      <c r="M23" s="107"/>
       <c r="N23" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
     </row>
     <row r="24" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7024,18 +7056,18 @@
         <v>46</v>
       </c>
       <c r="E24" s="44"/>
-      <c r="F24" s="107" t="s">
+      <c r="F24" s="105" t="s">
         <v>268</v>
       </c>
-      <c r="G24" s="108"/>
-      <c r="H24" s="108"/>
-      <c r="I24" s="108"/>
-      <c r="J24" s="108"/>
-      <c r="K24" s="108"/>
-      <c r="L24" s="108"/>
-      <c r="M24" s="109"/>
+      <c r="G24" s="106"/>
+      <c r="H24" s="106"/>
+      <c r="I24" s="106"/>
+      <c r="J24" s="106"/>
+      <c r="K24" s="106"/>
+      <c r="L24" s="106"/>
+      <c r="M24" s="107"/>
       <c r="N24" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
     </row>
     <row r="25" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7046,84 +7078,84 @@
         <v>46</v>
       </c>
       <c r="E25" s="44"/>
-      <c r="F25" s="107" t="s">
+      <c r="F25" s="105" t="s">
         <v>269</v>
       </c>
-      <c r="G25" s="108"/>
-      <c r="H25" s="108"/>
-      <c r="I25" s="108"/>
-      <c r="J25" s="108"/>
-      <c r="K25" s="108"/>
-      <c r="L25" s="108"/>
-      <c r="M25" s="109"/>
+      <c r="G25" s="106"/>
+      <c r="H25" s="106"/>
+      <c r="I25" s="106"/>
+      <c r="J25" s="106"/>
+      <c r="K25" s="106"/>
+      <c r="L25" s="106"/>
+      <c r="M25" s="107"/>
       <c r="N25" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
     </row>
     <row r="26" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C26" s="64" t="s">
+      <c r="C26" s="62" t="s">
         <v>220</v>
       </c>
-      <c r="D26" s="65" t="s">
-        <v>46</v>
-      </c>
-      <c r="E26" s="66"/>
-      <c r="F26" s="104" t="s">
+      <c r="D26" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="64"/>
+      <c r="F26" s="102" t="s">
         <v>270</v>
       </c>
-      <c r="G26" s="105"/>
-      <c r="H26" s="105"/>
-      <c r="I26" s="105"/>
-      <c r="J26" s="105"/>
-      <c r="K26" s="105"/>
-      <c r="L26" s="105"/>
-      <c r="M26" s="106"/>
-      <c r="N26" s="63" t="s">
-        <v>389</v>
+      <c r="G26" s="103"/>
+      <c r="H26" s="103"/>
+      <c r="I26" s="103"/>
+      <c r="J26" s="103"/>
+      <c r="K26" s="103"/>
+      <c r="L26" s="103"/>
+      <c r="M26" s="104"/>
+      <c r="N26" s="61" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="27" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C27" s="64" t="s">
+      <c r="C27" s="62" t="s">
         <v>145</v>
       </c>
-      <c r="D27" s="65" t="s">
-        <v>46</v>
-      </c>
-      <c r="E27" s="66"/>
-      <c r="F27" s="101"/>
-      <c r="G27" s="102"/>
-      <c r="H27" s="102"/>
-      <c r="I27" s="102"/>
-      <c r="J27" s="103"/>
-      <c r="K27" s="104" t="s">
+      <c r="D27" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" s="64"/>
+      <c r="F27" s="99"/>
+      <c r="G27" s="100"/>
+      <c r="H27" s="100"/>
+      <c r="I27" s="100"/>
+      <c r="J27" s="101"/>
+      <c r="K27" s="102" t="s">
         <v>271</v>
       </c>
-      <c r="L27" s="105"/>
-      <c r="M27" s="106"/>
-      <c r="N27" s="61" t="s">
-        <v>389</v>
+      <c r="L27" s="103"/>
+      <c r="M27" s="104"/>
+      <c r="N27" s="59" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="28" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C28" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="D28" s="69" t="s">
+      <c r="D28" s="67" t="s">
         <v>41</v>
       </c>
       <c r="E28" s="44"/>
-      <c r="F28" s="107" t="s">
+      <c r="F28" s="105" t="s">
         <v>272</v>
       </c>
-      <c r="G28" s="108"/>
-      <c r="H28" s="108"/>
-      <c r="I28" s="108"/>
-      <c r="J28" s="108"/>
-      <c r="K28" s="110"/>
-      <c r="L28" s="110"/>
-      <c r="M28" s="111"/>
+      <c r="G28" s="106"/>
+      <c r="H28" s="106"/>
+      <c r="I28" s="106"/>
+      <c r="J28" s="106"/>
+      <c r="K28" s="108"/>
+      <c r="L28" s="108"/>
+      <c r="M28" s="109"/>
       <c r="N28" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
     </row>
     <row r="29" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7134,18 +7166,18 @@
         <v>46</v>
       </c>
       <c r="E29" s="44"/>
-      <c r="F29" s="107" t="s">
+      <c r="F29" s="105" t="s">
         <v>273</v>
       </c>
-      <c r="G29" s="108"/>
-      <c r="H29" s="108"/>
-      <c r="I29" s="108"/>
-      <c r="J29" s="108"/>
-      <c r="K29" s="108"/>
-      <c r="L29" s="108"/>
-      <c r="M29" s="109"/>
+      <c r="G29" s="106"/>
+      <c r="H29" s="106"/>
+      <c r="I29" s="106"/>
+      <c r="J29" s="106"/>
+      <c r="K29" s="106"/>
+      <c r="L29" s="106"/>
+      <c r="M29" s="107"/>
       <c r="N29" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
     </row>
     <row r="30" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7156,18 +7188,18 @@
         <v>46</v>
       </c>
       <c r="E30" s="44"/>
-      <c r="F30" s="107" t="s">
+      <c r="F30" s="105" t="s">
         <v>274</v>
       </c>
-      <c r="G30" s="108"/>
-      <c r="H30" s="108"/>
-      <c r="I30" s="108"/>
-      <c r="J30" s="108"/>
-      <c r="K30" s="108"/>
-      <c r="L30" s="108"/>
-      <c r="M30" s="109"/>
+      <c r="G30" s="106"/>
+      <c r="H30" s="106"/>
+      <c r="I30" s="106"/>
+      <c r="J30" s="106"/>
+      <c r="K30" s="106"/>
+      <c r="L30" s="106"/>
+      <c r="M30" s="107"/>
       <c r="N30" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
     </row>
     <row r="31" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7178,270 +7210,270 @@
         <v>46</v>
       </c>
       <c r="E31" s="44"/>
-      <c r="F31" s="107" t="s">
+      <c r="F31" s="105" t="s">
         <v>275</v>
       </c>
-      <c r="G31" s="108"/>
-      <c r="H31" s="108"/>
-      <c r="I31" s="108"/>
-      <c r="J31" s="108"/>
-      <c r="K31" s="108"/>
-      <c r="L31" s="108"/>
-      <c r="M31" s="109"/>
+      <c r="G31" s="106"/>
+      <c r="H31" s="106"/>
+      <c r="I31" s="106"/>
+      <c r="J31" s="106"/>
+      <c r="K31" s="106"/>
+      <c r="L31" s="106"/>
+      <c r="M31" s="107"/>
       <c r="N31" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
     </row>
     <row r="32" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C32" s="64" t="s">
+      <c r="C32" s="62" t="s">
         <v>150</v>
       </c>
-      <c r="D32" s="65" t="s">
-        <v>46</v>
-      </c>
-      <c r="E32" s="66"/>
-      <c r="F32" s="101"/>
-      <c r="G32" s="102"/>
-      <c r="H32" s="102"/>
-      <c r="I32" s="102"/>
-      <c r="J32" s="102"/>
-      <c r="K32" s="102"/>
-      <c r="L32" s="102"/>
-      <c r="M32" s="103"/>
+      <c r="D32" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" s="64"/>
+      <c r="F32" s="99"/>
+      <c r="G32" s="100"/>
+      <c r="H32" s="100"/>
+      <c r="I32" s="100"/>
+      <c r="J32" s="100"/>
+      <c r="K32" s="100"/>
+      <c r="L32" s="100"/>
+      <c r="M32" s="101"/>
     </row>
     <row r="33" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C33" s="64" t="s">
+      <c r="C33" s="62" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="65" t="s">
-        <v>46</v>
-      </c>
-      <c r="E33" s="66"/>
-      <c r="F33" s="101"/>
-      <c r="G33" s="102"/>
-      <c r="H33" s="102"/>
-      <c r="I33" s="102"/>
-      <c r="J33" s="102"/>
-      <c r="K33" s="102"/>
-      <c r="L33" s="102"/>
-      <c r="M33" s="103"/>
+      <c r="D33" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" s="64"/>
+      <c r="F33" s="99"/>
+      <c r="G33" s="100"/>
+      <c r="H33" s="100"/>
+      <c r="I33" s="100"/>
+      <c r="J33" s="100"/>
+      <c r="K33" s="100"/>
+      <c r="L33" s="100"/>
+      <c r="M33" s="101"/>
     </row>
     <row r="34" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C34" s="64" t="s">
+      <c r="C34" s="62" t="s">
         <v>152</v>
       </c>
-      <c r="D34" s="65" t="s">
-        <v>46</v>
-      </c>
-      <c r="E34" s="66"/>
-      <c r="F34" s="104" t="s">
+      <c r="D34" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" s="64"/>
+      <c r="F34" s="102" t="s">
         <v>276</v>
       </c>
-      <c r="G34" s="105"/>
-      <c r="H34" s="105"/>
-      <c r="I34" s="105"/>
-      <c r="J34" s="105"/>
-      <c r="K34" s="105"/>
-      <c r="L34" s="105"/>
-      <c r="M34" s="106"/>
-      <c r="N34" s="61" t="s">
-        <v>389</v>
+      <c r="G34" s="103"/>
+      <c r="H34" s="103"/>
+      <c r="I34" s="103"/>
+      <c r="J34" s="103"/>
+      <c r="K34" s="103"/>
+      <c r="L34" s="103"/>
+      <c r="M34" s="104"/>
+      <c r="N34" s="59" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="35" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C35" s="64" t="s">
+      <c r="C35" s="62" t="s">
         <v>153</v>
       </c>
-      <c r="D35" s="65" t="s">
-        <v>46</v>
-      </c>
-      <c r="E35" s="67"/>
-      <c r="F35" s="104" t="s">
+      <c r="D35" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="E35" s="65"/>
+      <c r="F35" s="102" t="s">
         <v>277</v>
       </c>
-      <c r="G35" s="106"/>
-      <c r="H35" s="101"/>
-      <c r="I35" s="102"/>
-      <c r="J35" s="102"/>
-      <c r="K35" s="102"/>
-      <c r="L35" s="102"/>
-      <c r="M35" s="103"/>
-      <c r="N35" s="61" t="s">
-        <v>389</v>
+      <c r="G35" s="104"/>
+      <c r="H35" s="99"/>
+      <c r="I35" s="100"/>
+      <c r="J35" s="100"/>
+      <c r="K35" s="100"/>
+      <c r="L35" s="100"/>
+      <c r="M35" s="101"/>
+      <c r="N35" s="59" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="36" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C36" s="64" t="s">
+      <c r="C36" s="62" t="s">
         <v>154</v>
       </c>
-      <c r="D36" s="65" t="s">
-        <v>46</v>
-      </c>
-      <c r="E36" s="67"/>
-      <c r="F36" s="101"/>
-      <c r="G36" s="102"/>
-      <c r="H36" s="102"/>
-      <c r="I36" s="102"/>
-      <c r="J36" s="103"/>
-      <c r="K36" s="104" t="s">
+      <c r="D36" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" s="65"/>
+      <c r="F36" s="99"/>
+      <c r="G36" s="100"/>
+      <c r="H36" s="100"/>
+      <c r="I36" s="100"/>
+      <c r="J36" s="101"/>
+      <c r="K36" s="102" t="s">
         <v>278</v>
       </c>
-      <c r="L36" s="105"/>
-      <c r="M36" s="106"/>
-      <c r="N36" s="61" t="s">
-        <v>389</v>
+      <c r="L36" s="103"/>
+      <c r="M36" s="104"/>
+      <c r="N36" s="59" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="37" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C37" s="64" t="s">
+      <c r="C37" s="62" t="s">
         <v>155</v>
       </c>
-      <c r="D37" s="65" t="s">
-        <v>46</v>
-      </c>
-      <c r="E37" s="66"/>
-      <c r="F37" s="101"/>
-      <c r="G37" s="102"/>
-      <c r="H37" s="102"/>
-      <c r="I37" s="103"/>
-      <c r="J37" s="104" t="s">
+      <c r="D37" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="E37" s="64"/>
+      <c r="F37" s="99"/>
+      <c r="G37" s="100"/>
+      <c r="H37" s="100"/>
+      <c r="I37" s="101"/>
+      <c r="J37" s="102" t="s">
         <v>279</v>
       </c>
-      <c r="K37" s="105"/>
-      <c r="L37" s="105"/>
-      <c r="M37" s="106"/>
-      <c r="N37" s="61" t="s">
-        <v>389</v>
+      <c r="K37" s="103"/>
+      <c r="L37" s="103"/>
+      <c r="M37" s="104"/>
+      <c r="N37" s="59" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="38" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C38" s="64" t="s">
+      <c r="C38" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="D38" s="65" t="s">
+      <c r="D38" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="E38" s="66"/>
-      <c r="F38" s="101"/>
-      <c r="G38" s="102"/>
-      <c r="H38" s="102"/>
-      <c r="I38" s="103"/>
-      <c r="J38" s="104" t="s">
+      <c r="E38" s="64"/>
+      <c r="F38" s="99"/>
+      <c r="G38" s="100"/>
+      <c r="H38" s="100"/>
+      <c r="I38" s="101"/>
+      <c r="J38" s="102" t="s">
         <v>280</v>
       </c>
-      <c r="K38" s="105"/>
-      <c r="L38" s="105"/>
-      <c r="M38" s="106"/>
-      <c r="N38" s="61" t="s">
-        <v>389</v>
+      <c r="K38" s="103"/>
+      <c r="L38" s="103"/>
+      <c r="M38" s="104"/>
+      <c r="N38" s="59" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="39" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C39" s="64" t="s">
+      <c r="C39" s="62" t="s">
         <v>222</v>
       </c>
-      <c r="D39" s="65" t="s">
+      <c r="D39" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="E39" s="66"/>
-      <c r="F39" s="104" t="s">
+      <c r="E39" s="64"/>
+      <c r="F39" s="102" t="s">
         <v>281</v>
       </c>
-      <c r="G39" s="105"/>
-      <c r="H39" s="105"/>
-      <c r="I39" s="105"/>
-      <c r="J39" s="105"/>
-      <c r="K39" s="105"/>
-      <c r="L39" s="105"/>
-      <c r="M39" s="106"/>
-      <c r="N39" s="61" t="s">
-        <v>389</v>
+      <c r="G39" s="103"/>
+      <c r="H39" s="103"/>
+      <c r="I39" s="103"/>
+      <c r="J39" s="103"/>
+      <c r="K39" s="103"/>
+      <c r="L39" s="103"/>
+      <c r="M39" s="104"/>
+      <c r="N39" s="59" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="40" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C40" s="64" t="s">
+      <c r="C40" s="62" t="s">
         <v>223</v>
       </c>
-      <c r="D40" s="65" t="s">
-        <v>46</v>
-      </c>
-      <c r="E40" s="66"/>
-      <c r="F40" s="101"/>
-      <c r="G40" s="102"/>
-      <c r="H40" s="102"/>
-      <c r="I40" s="102"/>
-      <c r="J40" s="102"/>
-      <c r="K40" s="102"/>
-      <c r="L40" s="102"/>
-      <c r="M40" s="103"/>
+      <c r="D40" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="E40" s="64"/>
+      <c r="F40" s="99"/>
+      <c r="G40" s="100"/>
+      <c r="H40" s="100"/>
+      <c r="I40" s="100"/>
+      <c r="J40" s="100"/>
+      <c r="K40" s="100"/>
+      <c r="L40" s="100"/>
+      <c r="M40" s="101"/>
     </row>
     <row r="41" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C41" s="64" t="s">
+      <c r="C41" s="62" t="s">
         <v>224</v>
       </c>
-      <c r="D41" s="65" t="s">
-        <v>46</v>
-      </c>
-      <c r="E41" s="66"/>
-      <c r="F41" s="101"/>
-      <c r="G41" s="102"/>
-      <c r="H41" s="102"/>
-      <c r="I41" s="102"/>
-      <c r="J41" s="102"/>
-      <c r="K41" s="102"/>
-      <c r="L41" s="102"/>
-      <c r="M41" s="103"/>
+      <c r="D41" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="E41" s="64"/>
+      <c r="F41" s="99"/>
+      <c r="G41" s="100"/>
+      <c r="H41" s="100"/>
+      <c r="I41" s="100"/>
+      <c r="J41" s="100"/>
+      <c r="K41" s="100"/>
+      <c r="L41" s="100"/>
+      <c r="M41" s="101"/>
     </row>
     <row r="42" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C42" s="64" t="s">
+      <c r="C42" s="62" t="s">
         <v>225</v>
       </c>
-      <c r="D42" s="65" t="s">
-        <v>46</v>
-      </c>
-      <c r="E42" s="66"/>
-      <c r="F42" s="101"/>
-      <c r="G42" s="102"/>
-      <c r="H42" s="102"/>
-      <c r="I42" s="102"/>
-      <c r="J42" s="102"/>
-      <c r="K42" s="102"/>
-      <c r="L42" s="102"/>
-      <c r="M42" s="103"/>
+      <c r="D42" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="E42" s="64"/>
+      <c r="F42" s="99"/>
+      <c r="G42" s="100"/>
+      <c r="H42" s="100"/>
+      <c r="I42" s="100"/>
+      <c r="J42" s="100"/>
+      <c r="K42" s="100"/>
+      <c r="L42" s="100"/>
+      <c r="M42" s="101"/>
     </row>
     <row r="43" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C43" s="64" t="s">
+      <c r="C43" s="62" t="s">
         <v>226</v>
       </c>
-      <c r="D43" s="65" t="s">
-        <v>46</v>
-      </c>
-      <c r="E43" s="66"/>
-      <c r="F43" s="101"/>
-      <c r="G43" s="102"/>
-      <c r="H43" s="102"/>
-      <c r="I43" s="102"/>
-      <c r="J43" s="102"/>
-      <c r="K43" s="102"/>
-      <c r="L43" s="102"/>
-      <c r="M43" s="103"/>
+      <c r="D43" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="E43" s="64"/>
+      <c r="F43" s="99"/>
+      <c r="G43" s="100"/>
+      <c r="H43" s="100"/>
+      <c r="I43" s="100"/>
+      <c r="J43" s="100"/>
+      <c r="K43" s="100"/>
+      <c r="L43" s="100"/>
+      <c r="M43" s="101"/>
     </row>
     <row r="44" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C44" s="64" t="s">
+      <c r="C44" s="62" t="s">
         <v>227</v>
       </c>
-      <c r="D44" s="65" t="s">
-        <v>46</v>
-      </c>
-      <c r="E44" s="66"/>
-      <c r="F44" s="101"/>
-      <c r="G44" s="102"/>
-      <c r="H44" s="102"/>
-      <c r="I44" s="102"/>
-      <c r="J44" s="102"/>
-      <c r="K44" s="102"/>
-      <c r="L44" s="102"/>
-      <c r="M44" s="103"/>
+      <c r="D44" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="E44" s="64"/>
+      <c r="F44" s="99"/>
+      <c r="G44" s="100"/>
+      <c r="H44" s="100"/>
+      <c r="I44" s="100"/>
+      <c r="J44" s="100"/>
+      <c r="K44" s="100"/>
+      <c r="L44" s="100"/>
+      <c r="M44" s="101"/>
     </row>
     <row r="45" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C45" s="21" t="s">
@@ -7463,12 +7495,12 @@
       <c r="I45" s="47" t="s">
         <v>123</v>
       </c>
-      <c r="J45" s="78" t="s">
+      <c r="J45" s="74" t="s">
         <v>124</v>
       </c>
-      <c r="K45" s="79"/>
-      <c r="L45" s="79"/>
-      <c r="M45" s="80"/>
+      <c r="K45" s="75"/>
+      <c r="L45" s="75"/>
+      <c r="M45" s="76"/>
     </row>
     <row r="46" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="20" t="s">
@@ -7478,18 +7510,18 @@
         <v>46</v>
       </c>
       <c r="E46" s="45"/>
-      <c r="F46" s="78" t="s">
+      <c r="F46" s="74" t="s">
         <v>291</v>
       </c>
-      <c r="G46" s="80"/>
-      <c r="H46" s="78" t="s">
+      <c r="G46" s="76"/>
+      <c r="H46" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="I46" s="79"/>
-      <c r="J46" s="79"/>
-      <c r="K46" s="79"/>
-      <c r="L46" s="79"/>
-      <c r="M46" s="80"/>
+      <c r="I46" s="75"/>
+      <c r="J46" s="75"/>
+      <c r="K46" s="75"/>
+      <c r="L46" s="75"/>
+      <c r="M46" s="76"/>
     </row>
     <row r="47" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="20" t="s">
@@ -7499,18 +7531,18 @@
         <v>46</v>
       </c>
       <c r="E47" s="45"/>
-      <c r="F47" s="95" t="s">
+      <c r="F47" s="93" t="s">
         <v>130</v>
       </c>
-      <c r="G47" s="96"/>
-      <c r="H47" s="96"/>
-      <c r="I47" s="97"/>
-      <c r="J47" s="78" t="s">
+      <c r="G47" s="94"/>
+      <c r="H47" s="94"/>
+      <c r="I47" s="95"/>
+      <c r="J47" s="74" t="s">
         <v>131</v>
       </c>
-      <c r="K47" s="79"/>
-      <c r="L47" s="79"/>
-      <c r="M47" s="80"/>
+      <c r="K47" s="75"/>
+      <c r="L47" s="75"/>
+      <c r="M47" s="76"/>
     </row>
     <row r="48" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="20" t="s">
@@ -7520,18 +7552,18 @@
         <v>46</v>
       </c>
       <c r="E48" s="6"/>
-      <c r="F48" s="78" t="s">
+      <c r="F48" s="74" t="s">
         <v>132</v>
       </c>
-      <c r="G48" s="79"/>
-      <c r="H48" s="79"/>
-      <c r="I48" s="80"/>
-      <c r="J48" s="98" t="s">
+      <c r="G48" s="75"/>
+      <c r="H48" s="75"/>
+      <c r="I48" s="76"/>
+      <c r="J48" s="96" t="s">
         <v>133</v>
       </c>
-      <c r="K48" s="99"/>
-      <c r="L48" s="99"/>
-      <c r="M48" s="100"/>
+      <c r="K48" s="97"/>
+      <c r="L48" s="97"/>
+      <c r="M48" s="98"/>
     </row>
     <row r="49" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="20" t="s">
@@ -7541,16 +7573,16 @@
         <v>46</v>
       </c>
       <c r="E49" s="6"/>
-      <c r="F49" s="76" t="s">
+      <c r="F49" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="G49" s="86"/>
-      <c r="H49" s="86"/>
-      <c r="I49" s="86"/>
-      <c r="J49" s="86"/>
-      <c r="K49" s="86"/>
-      <c r="L49" s="86"/>
-      <c r="M49" s="77"/>
+      <c r="G49" s="83"/>
+      <c r="H49" s="83"/>
+      <c r="I49" s="83"/>
+      <c r="J49" s="83"/>
+      <c r="K49" s="83"/>
+      <c r="L49" s="83"/>
+      <c r="M49" s="84"/>
     </row>
     <row r="50" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C50" s="20" t="s">
@@ -7560,20 +7592,20 @@
         <v>46</v>
       </c>
       <c r="E50" s="6"/>
-      <c r="F50" s="73"/>
-      <c r="G50" s="75"/>
+      <c r="F50" s="71"/>
+      <c r="G50" s="73"/>
       <c r="H50" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="I50" s="76" t="s">
+      <c r="I50" s="82" t="s">
         <v>159</v>
       </c>
-      <c r="J50" s="86"/>
-      <c r="K50" s="77"/>
-      <c r="L50" s="76" t="s">
+      <c r="J50" s="83"/>
+      <c r="K50" s="84"/>
+      <c r="L50" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="M50" s="77"/>
+      <c r="M50" s="84"/>
     </row>
     <row r="51" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C51" s="20" t="s">
@@ -7616,15 +7648,15 @@
         <v>46</v>
       </c>
       <c r="E52" s="6"/>
-      <c r="F52" s="73"/>
-      <c r="G52" s="74"/>
-      <c r="H52" s="74"/>
-      <c r="I52" s="75"/>
-      <c r="J52" s="76" t="s">
+      <c r="F52" s="71"/>
+      <c r="G52" s="72"/>
+      <c r="H52" s="72"/>
+      <c r="I52" s="73"/>
+      <c r="J52" s="82" t="s">
         <v>127</v>
       </c>
-      <c r="K52" s="86"/>
-      <c r="L52" s="77"/>
+      <c r="K52" s="83"/>
+      <c r="L52" s="84"/>
       <c r="M52" s="14" t="s">
         <v>92</v>
       </c>
@@ -7639,61 +7671,61 @@
       <c r="E53" s="22" t="s">
         <v>302</v>
       </c>
-      <c r="F53" s="101"/>
-      <c r="G53" s="102"/>
-      <c r="H53" s="102"/>
-      <c r="I53" s="102"/>
-      <c r="J53" s="102"/>
-      <c r="K53" s="103"/>
-      <c r="L53" s="85" t="s">
+      <c r="F53" s="99"/>
+      <c r="G53" s="100"/>
+      <c r="H53" s="100"/>
+      <c r="I53" s="100"/>
+      <c r="J53" s="100"/>
+      <c r="K53" s="101"/>
+      <c r="L53" s="81" t="s">
         <v>300</v>
       </c>
-      <c r="M53" s="84"/>
+      <c r="M53" s="80"/>
     </row>
     <row r="54" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C54" s="64" t="s">
+      <c r="C54" s="62" t="s">
         <v>289</v>
       </c>
-      <c r="D54" s="65" t="s">
-        <v>46</v>
-      </c>
-      <c r="E54" s="68"/>
-      <c r="F54" s="101"/>
-      <c r="G54" s="102"/>
-      <c r="H54" s="102"/>
-      <c r="I54" s="102"/>
-      <c r="J54" s="102"/>
-      <c r="K54" s="102"/>
-      <c r="L54" s="102"/>
-      <c r="M54" s="103"/>
+      <c r="D54" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="E54" s="66"/>
+      <c r="F54" s="99"/>
+      <c r="G54" s="100"/>
+      <c r="H54" s="100"/>
+      <c r="I54" s="100"/>
+      <c r="J54" s="100"/>
+      <c r="K54" s="100"/>
+      <c r="L54" s="100"/>
+      <c r="M54" s="101"/>
     </row>
     <row r="55" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="56" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C56" s="57" t="s">
-        <v>375</v>
+      <c r="C56" s="55" t="s">
+        <v>366</v>
       </c>
       <c r="D56" t="s">
         <v>45</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="G56" s="12" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="I56" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="J56" s="58" t="s">
-        <v>381</v>
-      </c>
-      <c r="K56" s="73"/>
-      <c r="L56" s="75"/>
-      <c r="M56" s="58" t="s">
-        <v>380</v>
+        <v>370</v>
+      </c>
+      <c r="J56" s="56" t="s">
+        <v>372</v>
+      </c>
+      <c r="K56" s="71"/>
+      <c r="L56" s="73"/>
+      <c r="M56" s="56" t="s">
+        <v>371</v>
       </c>
     </row>
   </sheetData>

--- a/doc/spec/Y8960_Specifications.xlsx
+++ b/doc/spec/Y8960_Specifications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\HRA_product\Y8960_Cartridge\doc\spec\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hra\Documents\github\HRA_product\Y8960_Cartridge\doc\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE5874A0-A514-48B9-BC0F-3AF79DC3CAA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{066F0355-9793-4316-946C-EFE29F6DEA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11010" yWindow="0" windowWidth="17895" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="modules" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="394">
   <si>
     <t>Y8960 Cartridge は、MSX用のオーディオ系チップのコンボカートリッジです。</t>
     <rPh sb="21" eb="22">
@@ -70,10 +70,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>OPL3</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ADPCM</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -121,10 +117,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>https://github.com/gnogni/ocm-pld-dev/tree/master/ocm_sm/src_addons/sound/opl3</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>MSX Cartridge</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -150,10 +142,6 @@
   </si>
   <si>
     <t>MIT</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>MIDI</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -168,10 +156,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>https://github.com/hra1129/one-chip-msx-kai/tree/main/source/pld/src/peripheral/msx_midi</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>https://github.com/plgDavid/misc/wiki/Copyright-free-OPLL(x)-ROM-patches</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -181,10 +165,6 @@
   </si>
   <si>
     <t>sn76489_audio</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>opl3</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1948,6 +1928,37 @@
   </si>
   <si>
     <t>MSX SLOT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>opl2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPL2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://github.com/jotego/jtopl</t>
+  </si>
+  <si>
+    <t>https://github.com/jotego/jt12</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>jt12</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GPL3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SerialSRAM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SerialROM</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2435,7 +2446,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2649,6 +2660,39 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2658,27 +2702,18 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2691,13 +2726,13 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2706,13 +2741,37 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2733,52 +2792,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3065,7 +3079,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F16"/>
+  <dimension ref="B2:F17"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.75" customWidth="1"/>
@@ -3093,7 +3107,7 @@
         <v>5</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.15">
@@ -3104,10 +3118,10 @@
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F5" s="1"/>
     </row>
@@ -3119,13 +3133,13 @@
         <v>6</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.15">
@@ -3133,16 +3147,16 @@
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>7</v>
+        <v>387</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>34</v>
+        <v>386</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>391</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>19</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.15">
@@ -3150,31 +3164,33 @@
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>14</v>
+        <v>390</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="1"/>
+        <v>391</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B9" s="1">
         <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.15">
@@ -3182,16 +3198,16 @@
         <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.15">
@@ -3199,13 +3215,13 @@
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F11" s="1"/>
     </row>
@@ -3214,13 +3230,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F12" s="1"/>
     </row>
@@ -3229,13 +3245,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F13" s="1"/>
     </row>
@@ -3244,13 +3260,13 @@
         <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F14" s="1"/>
     </row>
@@ -3259,47 +3275,59 @@
         <v>11</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="F15" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B16" s="115">
+        <v>12</v>
+      </c>
+      <c r="C16" s="115" t="s">
+        <v>392</v>
+      </c>
+      <c r="D16" s="115" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="115" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B17" s="115">
+        <v>13</v>
+      </c>
+      <c r="C17" s="115" t="s">
+        <v>393</v>
+      </c>
+      <c r="D17" s="115" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="115" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B16" s="1">
-        <v>12</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>30</v>
-      </c>
+      <c r="F17" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="F6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="F10" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="F7" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="F15" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="F16" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="F9" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="F15" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="F9" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="F8" r:id="rId5" xr:uid="{D9F07537-65A1-46DF-B5B2-4D161B547953}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="67" fitToHeight="0" orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId7"/>
+  <pageSetup paperSize="9" scale="67" fitToHeight="0" orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId6"/>
 </worksheet>
 </file>
 
@@ -3319,837 +3347,852 @@
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C3" s="7" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>389</v>
-      </c>
-      <c r="G3" s="114" t="s">
+        <v>384</v>
+      </c>
+      <c r="G3" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="L3" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="N3" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="J3" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>89</v>
-      </c>
       <c r="O3" s="5" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4" spans="2:15" ht="27.75" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C4" s="13" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="71"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="72"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="73"/>
-      <c r="N4" s="110" t="s">
-        <v>345</v>
+        <v>9</v>
+      </c>
+      <c r="G4" s="82"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="83"/>
+      <c r="K4" s="83"/>
+      <c r="L4" s="83"/>
+      <c r="M4" s="84"/>
+      <c r="N4" s="71" t="s">
+        <v>340</v>
       </c>
       <c r="O4" s="54" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C5" s="68" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="111" t="s">
-        <v>346</v>
-      </c>
-      <c r="H5" s="112"/>
-      <c r="I5" s="112"/>
-      <c r="J5" s="112"/>
-      <c r="K5" s="112"/>
-      <c r="L5" s="112"/>
-      <c r="M5" s="112"/>
-      <c r="N5" s="113"/>
+        <v>9</v>
+      </c>
+      <c r="G5" s="76" t="s">
+        <v>341</v>
+      </c>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="77"/>
+      <c r="M5" s="77"/>
+      <c r="N5" s="78"/>
       <c r="O5" s="52" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C6" s="69" t="s">
+        <v>336</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>331</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="76" t="s">
         <v>341</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>336</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="111" t="s">
-        <v>346</v>
-      </c>
-      <c r="H6" s="112"/>
-      <c r="I6" s="112"/>
-      <c r="J6" s="112"/>
-      <c r="K6" s="112"/>
-      <c r="L6" s="112"/>
-      <c r="M6" s="112"/>
-      <c r="N6" s="113"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="77"/>
+      <c r="M6" s="77"/>
+      <c r="N6" s="78"/>
       <c r="O6" s="52" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C7" s="69" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="111" t="s">
-        <v>346</v>
-      </c>
-      <c r="H7" s="112"/>
-      <c r="I7" s="112"/>
-      <c r="J7" s="112"/>
-      <c r="K7" s="112"/>
-      <c r="L7" s="112"/>
-      <c r="M7" s="112"/>
-      <c r="N7" s="113"/>
+        <v>9</v>
+      </c>
+      <c r="G7" s="76" t="s">
+        <v>341</v>
+      </c>
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="77"/>
+      <c r="L7" s="77"/>
+      <c r="M7" s="77"/>
+      <c r="N7" s="78"/>
       <c r="O7" s="52" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="8" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C8" s="69" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="111" t="s">
-        <v>346</v>
-      </c>
-      <c r="H8" s="112"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="112"/>
-      <c r="K8" s="112"/>
-      <c r="L8" s="112"/>
-      <c r="M8" s="112"/>
-      <c r="N8" s="113"/>
+        <v>9</v>
+      </c>
+      <c r="G8" s="76" t="s">
+        <v>341</v>
+      </c>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
+      <c r="J8" s="77"/>
+      <c r="K8" s="77"/>
+      <c r="L8" s="77"/>
+      <c r="M8" s="77"/>
+      <c r="N8" s="78"/>
       <c r="O8" s="52" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C9" s="69" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="74" t="s">
-        <v>347</v>
-      </c>
-      <c r="H9" s="75"/>
-      <c r="I9" s="75"/>
-      <c r="J9" s="75"/>
-      <c r="K9" s="75"/>
-      <c r="L9" s="75"/>
-      <c r="M9" s="75"/>
-      <c r="N9" s="76"/>
+        <v>9</v>
+      </c>
+      <c r="G9" s="73" t="s">
+        <v>342</v>
+      </c>
+      <c r="H9" s="74"/>
+      <c r="I9" s="74"/>
+      <c r="J9" s="74"/>
+      <c r="K9" s="74"/>
+      <c r="L9" s="74"/>
+      <c r="M9" s="74"/>
+      <c r="N9" s="75"/>
       <c r="O9" s="52" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C10" s="69" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="74" t="s">
-        <v>347</v>
-      </c>
-      <c r="H10" s="75"/>
-      <c r="I10" s="75"/>
-      <c r="J10" s="75"/>
-      <c r="K10" s="75"/>
-      <c r="L10" s="75"/>
-      <c r="M10" s="75"/>
-      <c r="N10" s="76"/>
+        <v>9</v>
+      </c>
+      <c r="G10" s="73" t="s">
+        <v>342</v>
+      </c>
+      <c r="H10" s="74"/>
+      <c r="I10" s="74"/>
+      <c r="J10" s="74"/>
+      <c r="K10" s="74"/>
+      <c r="L10" s="74"/>
+      <c r="M10" s="74"/>
+      <c r="N10" s="75"/>
       <c r="O10" s="52" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C11" s="51" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>390</v>
-      </c>
-      <c r="G11" s="81" t="s">
-        <v>320</v>
-      </c>
-      <c r="H11" s="79"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="79"/>
-      <c r="K11" s="79"/>
-      <c r="L11" s="79"/>
-      <c r="M11" s="79"/>
-      <c r="N11" s="80"/>
+        <v>385</v>
+      </c>
+      <c r="G11" s="89" t="s">
+        <v>315</v>
+      </c>
+      <c r="H11" s="86"/>
+      <c r="I11" s="86"/>
+      <c r="J11" s="86"/>
+      <c r="K11" s="86"/>
+      <c r="L11" s="86"/>
+      <c r="M11" s="86"/>
+      <c r="N11" s="87"/>
       <c r="O11" s="53" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
     <row r="12" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C12" s="51" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="D12" s="51" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>390</v>
-      </c>
-      <c r="G12" s="81" t="s">
-        <v>321</v>
-      </c>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="79"/>
-      <c r="K12" s="79"/>
-      <c r="L12" s="79"/>
-      <c r="M12" s="79"/>
-      <c r="N12" s="80"/>
+        <v>385</v>
+      </c>
+      <c r="G12" s="89" t="s">
+        <v>316</v>
+      </c>
+      <c r="H12" s="86"/>
+      <c r="I12" s="86"/>
+      <c r="J12" s="86"/>
+      <c r="K12" s="86"/>
+      <c r="L12" s="86"/>
+      <c r="M12" s="86"/>
+      <c r="N12" s="87"/>
       <c r="O12" s="53" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="13" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="24" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>390</v>
-      </c>
-      <c r="G13" s="78" t="s">
-        <v>298</v>
-      </c>
-      <c r="H13" s="79"/>
-      <c r="I13" s="79"/>
-      <c r="J13" s="79"/>
-      <c r="K13" s="79"/>
-      <c r="L13" s="79"/>
-      <c r="M13" s="79"/>
-      <c r="N13" s="80"/>
+        <v>385</v>
+      </c>
+      <c r="G13" s="85" t="s">
+        <v>293</v>
+      </c>
+      <c r="H13" s="86"/>
+      <c r="I13" s="86"/>
+      <c r="J13" s="86"/>
+      <c r="K13" s="86"/>
+      <c r="L13" s="86"/>
+      <c r="M13" s="86"/>
+      <c r="N13" s="87"/>
       <c r="O13" s="53" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="25" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>390</v>
-      </c>
-      <c r="G14" s="78" t="s">
-        <v>308</v>
-      </c>
-      <c r="H14" s="79"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="79"/>
-      <c r="K14" s="79"/>
-      <c r="L14" s="79"/>
-      <c r="M14" s="79"/>
-      <c r="N14" s="80"/>
+        <v>385</v>
+      </c>
+      <c r="G14" s="85" t="s">
+        <v>303</v>
+      </c>
+      <c r="H14" s="86"/>
+      <c r="I14" s="86"/>
+      <c r="J14" s="86"/>
+      <c r="K14" s="86"/>
+      <c r="L14" s="86"/>
+      <c r="M14" s="86"/>
+      <c r="N14" s="87"/>
       <c r="O14" s="53" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
     </row>
     <row r="15" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="25" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>390</v>
-      </c>
-      <c r="G15" s="78" t="s">
-        <v>296</v>
-      </c>
-      <c r="H15" s="79"/>
-      <c r="I15" s="79"/>
-      <c r="J15" s="79"/>
-      <c r="K15" s="79"/>
-      <c r="L15" s="79"/>
-      <c r="M15" s="79"/>
-      <c r="N15" s="80"/>
+        <v>385</v>
+      </c>
+      <c r="G15" s="85" t="s">
+        <v>291</v>
+      </c>
+      <c r="H15" s="86"/>
+      <c r="I15" s="86"/>
+      <c r="J15" s="86"/>
+      <c r="K15" s="86"/>
+      <c r="L15" s="86"/>
+      <c r="M15" s="86"/>
+      <c r="N15" s="87"/>
       <c r="O15" s="53" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
     </row>
     <row r="16" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="25" t="s">
+        <v>299</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>292</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>385</v>
+      </c>
+      <c r="G16" s="85" t="s">
         <v>304</v>
       </c>
-      <c r="D16" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>297</v>
-      </c>
-      <c r="F16" s="22" t="s">
-        <v>390</v>
-      </c>
-      <c r="G16" s="78" t="s">
-        <v>309</v>
-      </c>
-      <c r="H16" s="79"/>
-      <c r="I16" s="79"/>
-      <c r="J16" s="79"/>
-      <c r="K16" s="79"/>
-      <c r="L16" s="79"/>
-      <c r="M16" s="79"/>
-      <c r="N16" s="80"/>
+      <c r="H16" s="86"/>
+      <c r="I16" s="86"/>
+      <c r="J16" s="86"/>
+      <c r="K16" s="86"/>
+      <c r="L16" s="86"/>
+      <c r="M16" s="86"/>
+      <c r="N16" s="87"/>
       <c r="O16" s="53" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="17" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="50" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>390</v>
-      </c>
-      <c r="G17" s="78" t="s">
-        <v>316</v>
-      </c>
-      <c r="H17" s="79"/>
-      <c r="I17" s="79"/>
-      <c r="J17" s="79"/>
-      <c r="K17" s="79"/>
-      <c r="L17" s="79"/>
-      <c r="M17" s="79"/>
-      <c r="N17" s="80"/>
+        <v>385</v>
+      </c>
+      <c r="G17" s="85" t="s">
+        <v>311</v>
+      </c>
+      <c r="H17" s="86"/>
+      <c r="I17" s="86"/>
+      <c r="J17" s="86"/>
+      <c r="K17" s="86"/>
+      <c r="L17" s="86"/>
+      <c r="M17" s="86"/>
+      <c r="N17" s="87"/>
       <c r="O17" s="53" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="18" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="51" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>390</v>
-      </c>
-      <c r="G18" s="78" t="s">
-        <v>317</v>
-      </c>
-      <c r="H18" s="79"/>
-      <c r="I18" s="79"/>
-      <c r="J18" s="79"/>
-      <c r="K18" s="79"/>
-      <c r="L18" s="79"/>
-      <c r="M18" s="79"/>
-      <c r="N18" s="80"/>
+        <v>385</v>
+      </c>
+      <c r="G18" s="85" t="s">
+        <v>312</v>
+      </c>
+      <c r="H18" s="86"/>
+      <c r="I18" s="86"/>
+      <c r="J18" s="86"/>
+      <c r="K18" s="86"/>
+      <c r="L18" s="86"/>
+      <c r="M18" s="86"/>
+      <c r="N18" s="87"/>
       <c r="O18" s="53" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="19" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="48" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D19" s="49" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>390</v>
-      </c>
-      <c r="G19" s="78" t="s">
-        <v>107</v>
-      </c>
-      <c r="H19" s="79"/>
-      <c r="I19" s="79"/>
-      <c r="J19" s="79"/>
-      <c r="K19" s="79"/>
-      <c r="L19" s="79"/>
-      <c r="M19" s="79"/>
-      <c r="N19" s="80"/>
+        <v>385</v>
+      </c>
+      <c r="G19" s="85" t="s">
+        <v>102</v>
+      </c>
+      <c r="H19" s="86"/>
+      <c r="I19" s="86"/>
+      <c r="J19" s="86"/>
+      <c r="K19" s="86"/>
+      <c r="L19" s="86"/>
+      <c r="M19" s="86"/>
+      <c r="N19" s="87"/>
       <c r="O19" s="53" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="20" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="25" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>390</v>
-      </c>
-      <c r="G20" s="78" t="s">
-        <v>197</v>
-      </c>
-      <c r="H20" s="79"/>
-      <c r="I20" s="79"/>
-      <c r="J20" s="79"/>
-      <c r="K20" s="79"/>
-      <c r="L20" s="79"/>
-      <c r="M20" s="79"/>
-      <c r="N20" s="80"/>
+        <v>385</v>
+      </c>
+      <c r="G20" s="85" t="s">
+        <v>192</v>
+      </c>
+      <c r="H20" s="86"/>
+      <c r="I20" s="86"/>
+      <c r="J20" s="86"/>
+      <c r="K20" s="86"/>
+      <c r="L20" s="86"/>
+      <c r="M20" s="86"/>
+      <c r="N20" s="87"/>
       <c r="O20" s="53" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="21" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>390</v>
-      </c>
-      <c r="G21" s="82" t="s">
-        <v>105</v>
-      </c>
-      <c r="H21" s="83"/>
-      <c r="I21" s="83"/>
-      <c r="J21" s="83"/>
-      <c r="K21" s="83"/>
-      <c r="L21" s="83"/>
-      <c r="M21" s="83"/>
-      <c r="N21" s="84"/>
+        <v>385</v>
+      </c>
+      <c r="G21" s="90" t="s">
+        <v>100</v>
+      </c>
+      <c r="H21" s="91"/>
+      <c r="I21" s="91"/>
+      <c r="J21" s="91"/>
+      <c r="K21" s="91"/>
+      <c r="L21" s="91"/>
+      <c r="M21" s="91"/>
+      <c r="N21" s="92"/>
       <c r="O21" s="53" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
     </row>
     <row r="22" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>390</v>
-      </c>
-      <c r="G22" s="82" t="s">
-        <v>198</v>
-      </c>
-      <c r="H22" s="83"/>
-      <c r="I22" s="83"/>
-      <c r="J22" s="83"/>
-      <c r="K22" s="83"/>
-      <c r="L22" s="83"/>
-      <c r="M22" s="83"/>
-      <c r="N22" s="84"/>
+        <v>385</v>
+      </c>
+      <c r="G22" s="90" t="s">
+        <v>193</v>
+      </c>
+      <c r="H22" s="91"/>
+      <c r="I22" s="91"/>
+      <c r="J22" s="91"/>
+      <c r="K22" s="91"/>
+      <c r="L22" s="91"/>
+      <c r="M22" s="91"/>
+      <c r="N22" s="92"/>
       <c r="O22" s="53" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="23" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="13" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>390</v>
-      </c>
-      <c r="G23" s="85"/>
-      <c r="H23" s="86"/>
-      <c r="I23" s="86"/>
-      <c r="J23" s="86"/>
-      <c r="K23" s="86"/>
-      <c r="L23" s="87"/>
+        <v>385</v>
+      </c>
+      <c r="G23" s="79"/>
+      <c r="H23" s="80"/>
+      <c r="I23" s="80"/>
+      <c r="J23" s="80"/>
+      <c r="K23" s="80"/>
+      <c r="L23" s="81"/>
       <c r="M23" s="26" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="O23" s="53" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
     </row>
     <row r="24" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="22"/>
-      <c r="G24" s="71"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="72"/>
-      <c r="J24" s="72"/>
-      <c r="K24" s="72"/>
-      <c r="L24" s="72"/>
-      <c r="M24" s="72"/>
-      <c r="N24" s="73"/>
+      <c r="G24" s="82"/>
+      <c r="H24" s="83"/>
+      <c r="I24" s="83"/>
+      <c r="J24" s="83"/>
+      <c r="K24" s="83"/>
+      <c r="L24" s="83"/>
+      <c r="M24" s="83"/>
+      <c r="N24" s="84"/>
       <c r="O24" s="53"/>
     </row>
     <row r="25" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="22"/>
-      <c r="G25" s="71"/>
-      <c r="H25" s="72"/>
-      <c r="I25" s="72"/>
-      <c r="J25" s="72"/>
-      <c r="K25" s="72"/>
-      <c r="L25" s="72"/>
-      <c r="M25" s="72"/>
-      <c r="N25" s="73"/>
+      <c r="G25" s="82"/>
+      <c r="H25" s="83"/>
+      <c r="I25" s="83"/>
+      <c r="J25" s="83"/>
+      <c r="K25" s="83"/>
+      <c r="L25" s="83"/>
+      <c r="M25" s="83"/>
+      <c r="N25" s="84"/>
       <c r="O25" s="53"/>
     </row>
     <row r="26" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="22"/>
-      <c r="G26" s="71"/>
-      <c r="H26" s="72"/>
-      <c r="I26" s="72"/>
-      <c r="J26" s="72"/>
-      <c r="K26" s="72"/>
-      <c r="L26" s="72"/>
-      <c r="M26" s="72"/>
-      <c r="N26" s="73"/>
+      <c r="G26" s="82"/>
+      <c r="H26" s="83"/>
+      <c r="I26" s="83"/>
+      <c r="J26" s="83"/>
+      <c r="K26" s="83"/>
+      <c r="L26" s="83"/>
+      <c r="M26" s="83"/>
+      <c r="N26" s="84"/>
       <c r="O26" s="53"/>
     </row>
     <row r="27" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="22"/>
-      <c r="G27" s="71"/>
-      <c r="H27" s="72"/>
-      <c r="I27" s="72"/>
-      <c r="J27" s="72"/>
-      <c r="K27" s="72"/>
-      <c r="L27" s="72"/>
-      <c r="M27" s="72"/>
-      <c r="N27" s="73"/>
+      <c r="G27" s="82"/>
+      <c r="H27" s="83"/>
+      <c r="I27" s="83"/>
+      <c r="J27" s="83"/>
+      <c r="K27" s="83"/>
+      <c r="L27" s="83"/>
+      <c r="M27" s="83"/>
+      <c r="N27" s="84"/>
       <c r="O27" s="53"/>
     </row>
     <row r="28" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="22"/>
-      <c r="G28" s="71"/>
-      <c r="H28" s="72"/>
-      <c r="I28" s="72"/>
-      <c r="J28" s="72"/>
-      <c r="K28" s="72"/>
-      <c r="L28" s="72"/>
-      <c r="M28" s="72"/>
-      <c r="N28" s="73"/>
+      <c r="G28" s="82"/>
+      <c r="H28" s="83"/>
+      <c r="I28" s="83"/>
+      <c r="J28" s="83"/>
+      <c r="K28" s="83"/>
+      <c r="L28" s="83"/>
+      <c r="M28" s="83"/>
+      <c r="N28" s="84"/>
       <c r="O28" s="53"/>
     </row>
     <row r="29" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="22"/>
-      <c r="G29" s="71"/>
-      <c r="H29" s="72"/>
-      <c r="I29" s="72"/>
-      <c r="J29" s="72"/>
-      <c r="K29" s="72"/>
-      <c r="L29" s="72"/>
-      <c r="M29" s="72"/>
-      <c r="N29" s="73"/>
+      <c r="G29" s="82"/>
+      <c r="H29" s="83"/>
+      <c r="I29" s="83"/>
+      <c r="J29" s="83"/>
+      <c r="K29" s="83"/>
+      <c r="L29" s="83"/>
+      <c r="M29" s="83"/>
+      <c r="N29" s="84"/>
       <c r="O29" s="53"/>
     </row>
     <row r="30" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="22"/>
-      <c r="G30" s="71"/>
-      <c r="H30" s="72"/>
-      <c r="I30" s="72"/>
-      <c r="J30" s="72"/>
-      <c r="K30" s="72"/>
-      <c r="L30" s="72"/>
-      <c r="M30" s="72"/>
-      <c r="N30" s="73"/>
+      <c r="G30" s="82"/>
+      <c r="H30" s="83"/>
+      <c r="I30" s="83"/>
+      <c r="J30" s="83"/>
+      <c r="K30" s="83"/>
+      <c r="L30" s="83"/>
+      <c r="M30" s="83"/>
+      <c r="N30" s="84"/>
       <c r="O30" s="53"/>
     </row>
     <row r="31" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="22"/>
-      <c r="G31" s="71"/>
-      <c r="H31" s="72"/>
-      <c r="I31" s="72"/>
-      <c r="J31" s="72"/>
-      <c r="K31" s="72"/>
-      <c r="L31" s="72"/>
-      <c r="M31" s="72"/>
-      <c r="N31" s="73"/>
+      <c r="G31" s="82"/>
+      <c r="H31" s="83"/>
+      <c r="I31" s="83"/>
+      <c r="J31" s="83"/>
+      <c r="K31" s="83"/>
+      <c r="L31" s="83"/>
+      <c r="M31" s="83"/>
+      <c r="N31" s="84"/>
       <c r="O31" s="53"/>
     </row>
     <row r="32" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="G32" s="26" t="s">
-        <v>386</v>
-      </c>
-      <c r="H32" s="71"/>
-      <c r="I32" s="73"/>
+        <v>381</v>
+      </c>
+      <c r="H32" s="82"/>
+      <c r="I32" s="84"/>
       <c r="J32" s="34" t="s">
         <v>4</v>
       </c>
       <c r="K32" s="34" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="L32" s="34" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="M32" s="47" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="N32" s="47" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="O32" s="53" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="33" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="68" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" s="74" t="s">
-        <v>347</v>
-      </c>
-      <c r="H33" s="77"/>
-      <c r="I33" s="75"/>
-      <c r="J33" s="75"/>
-      <c r="K33" s="75"/>
-      <c r="L33" s="75"/>
-      <c r="M33" s="75"/>
-      <c r="N33" s="76"/>
+        <v>9</v>
+      </c>
+      <c r="G33" s="73" t="s">
+        <v>342</v>
+      </c>
+      <c r="H33" s="88"/>
+      <c r="I33" s="74"/>
+      <c r="J33" s="74"/>
+      <c r="K33" s="74"/>
+      <c r="L33" s="74"/>
+      <c r="M33" s="74"/>
+      <c r="N33" s="75"/>
       <c r="O33" s="52" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="34" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="70" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="F34" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="74" t="s">
-        <v>347</v>
-      </c>
-      <c r="H34" s="75"/>
-      <c r="I34" s="75"/>
-      <c r="J34" s="75"/>
-      <c r="K34" s="75"/>
-      <c r="L34" s="75"/>
-      <c r="M34" s="75"/>
-      <c r="N34" s="76"/>
+        <v>9</v>
+      </c>
+      <c r="G34" s="73" t="s">
+        <v>342</v>
+      </c>
+      <c r="H34" s="74"/>
+      <c r="I34" s="74"/>
+      <c r="J34" s="74"/>
+      <c r="K34" s="74"/>
+      <c r="L34" s="74"/>
+      <c r="M34" s="74"/>
+      <c r="N34" s="75"/>
       <c r="O34" s="52" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="G4:M4"/>
+    <mergeCell ref="G9:N9"/>
+    <mergeCell ref="G10:N10"/>
+    <mergeCell ref="G33:N33"/>
+    <mergeCell ref="G17:N17"/>
+    <mergeCell ref="G11:N11"/>
+    <mergeCell ref="G12:N12"/>
+    <mergeCell ref="G19:N19"/>
+    <mergeCell ref="G20:N20"/>
+    <mergeCell ref="G21:N21"/>
+    <mergeCell ref="G22:N22"/>
+    <mergeCell ref="G13:N13"/>
+    <mergeCell ref="G14:N14"/>
+    <mergeCell ref="G15:N15"/>
+    <mergeCell ref="G16:N16"/>
     <mergeCell ref="G34:N34"/>
     <mergeCell ref="G5:N5"/>
     <mergeCell ref="G6:N6"/>
@@ -4166,21 +4209,6 @@
     <mergeCell ref="G18:N18"/>
     <mergeCell ref="H32:I32"/>
     <mergeCell ref="G31:N31"/>
-    <mergeCell ref="G4:M4"/>
-    <mergeCell ref="G9:N9"/>
-    <mergeCell ref="G10:N10"/>
-    <mergeCell ref="G33:N33"/>
-    <mergeCell ref="G17:N17"/>
-    <mergeCell ref="G11:N11"/>
-    <mergeCell ref="G12:N12"/>
-    <mergeCell ref="G19:N19"/>
-    <mergeCell ref="G20:N20"/>
-    <mergeCell ref="G21:N21"/>
-    <mergeCell ref="G22:N22"/>
-    <mergeCell ref="G13:N13"/>
-    <mergeCell ref="G14:N14"/>
-    <mergeCell ref="G15:N15"/>
-    <mergeCell ref="G16:N16"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4198,421 +4226,421 @@
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C5" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C6" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C7" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C8" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C11" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F11" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="K11" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="L11" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="M11" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="12" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C12" s="20" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" s="90" t="s">
-        <v>201</v>
-      </c>
-      <c r="G12" s="91"/>
-      <c r="H12" s="91"/>
-      <c r="I12" s="91"/>
-      <c r="J12" s="91"/>
-      <c r="K12" s="91"/>
-      <c r="L12" s="91"/>
-      <c r="M12" s="92"/>
+        <v>45</v>
+      </c>
+      <c r="F12" s="93" t="s">
+        <v>196</v>
+      </c>
+      <c r="G12" s="94"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="94"/>
+      <c r="J12" s="94"/>
+      <c r="K12" s="94"/>
+      <c r="L12" s="94"/>
+      <c r="M12" s="95"/>
     </row>
     <row r="13" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="20" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>51</v>
       </c>
       <c r="F13" s="36"/>
       <c r="G13" s="37"/>
       <c r="H13" s="37"/>
       <c r="I13" s="38"/>
-      <c r="J13" s="90" t="s">
-        <v>202</v>
-      </c>
-      <c r="K13" s="91"/>
-      <c r="L13" s="91"/>
-      <c r="M13" s="92"/>
+      <c r="J13" s="93" t="s">
+        <v>197</v>
+      </c>
+      <c r="K13" s="94"/>
+      <c r="L13" s="94"/>
+      <c r="M13" s="95"/>
     </row>
     <row r="14" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="20" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F14" s="90" t="s">
-        <v>201</v>
-      </c>
-      <c r="G14" s="91"/>
-      <c r="H14" s="91"/>
-      <c r="I14" s="91"/>
-      <c r="J14" s="91"/>
-      <c r="K14" s="91"/>
-      <c r="L14" s="91"/>
-      <c r="M14" s="92"/>
+        <v>47</v>
+      </c>
+      <c r="F14" s="93" t="s">
+        <v>196</v>
+      </c>
+      <c r="G14" s="94"/>
+      <c r="H14" s="94"/>
+      <c r="I14" s="94"/>
+      <c r="J14" s="94"/>
+      <c r="K14" s="94"/>
+      <c r="L14" s="94"/>
+      <c r="M14" s="95"/>
     </row>
     <row r="15" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="20" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F15" s="36"/>
       <c r="G15" s="37"/>
       <c r="H15" s="37"/>
       <c r="I15" s="38"/>
-      <c r="J15" s="90" t="s">
-        <v>202</v>
-      </c>
-      <c r="K15" s="91"/>
-      <c r="L15" s="91"/>
-      <c r="M15" s="92"/>
+      <c r="J15" s="93" t="s">
+        <v>197</v>
+      </c>
+      <c r="K15" s="94"/>
+      <c r="L15" s="94"/>
+      <c r="M15" s="95"/>
     </row>
     <row r="16" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="20" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F16" s="90" t="s">
-        <v>201</v>
-      </c>
-      <c r="G16" s="91"/>
-      <c r="H16" s="91"/>
-      <c r="I16" s="91"/>
-      <c r="J16" s="91"/>
-      <c r="K16" s="91"/>
-      <c r="L16" s="91"/>
-      <c r="M16" s="92"/>
+        <v>49</v>
+      </c>
+      <c r="F16" s="93" t="s">
+        <v>196</v>
+      </c>
+      <c r="G16" s="94"/>
+      <c r="H16" s="94"/>
+      <c r="I16" s="94"/>
+      <c r="J16" s="94"/>
+      <c r="K16" s="94"/>
+      <c r="L16" s="94"/>
+      <c r="M16" s="95"/>
     </row>
     <row r="17" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="20" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F17" s="36"/>
       <c r="G17" s="37"/>
       <c r="H17" s="37"/>
       <c r="I17" s="38"/>
-      <c r="J17" s="90" t="s">
-        <v>202</v>
-      </c>
-      <c r="K17" s="91"/>
-      <c r="L17" s="91"/>
-      <c r="M17" s="92"/>
+      <c r="J17" s="93" t="s">
+        <v>197</v>
+      </c>
+      <c r="K17" s="94"/>
+      <c r="L17" s="94"/>
+      <c r="M17" s="95"/>
     </row>
     <row r="18" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="20" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F18" s="36"/>
       <c r="G18" s="37"/>
       <c r="H18" s="38"/>
-      <c r="I18" s="90" t="s">
-        <v>203</v>
-      </c>
-      <c r="J18" s="91"/>
-      <c r="K18" s="91"/>
-      <c r="L18" s="91"/>
-      <c r="M18" s="92"/>
+      <c r="I18" s="93" t="s">
+        <v>198</v>
+      </c>
+      <c r="J18" s="94"/>
+      <c r="K18" s="94"/>
+      <c r="L18" s="94"/>
+      <c r="M18" s="95"/>
     </row>
     <row r="19" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="20" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F19" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="H19" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="I19" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="J19" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="K19" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="L19" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="M19" s="40" t="s">
         <v>90</v>
-      </c>
-      <c r="G19" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="H19" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="I19" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="J19" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="K19" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="L19" s="41" t="s">
-        <v>93</v>
-      </c>
-      <c r="M19" s="40" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="20" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="20" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F20" s="36"/>
       <c r="G20" s="37"/>
       <c r="H20" s="38"/>
       <c r="I20" s="43" t="s">
-        <v>99</v>
-      </c>
-      <c r="J20" s="90" t="s">
-        <v>204</v>
-      </c>
-      <c r="K20" s="91"/>
-      <c r="L20" s="91"/>
-      <c r="M20" s="92"/>
+        <v>94</v>
+      </c>
+      <c r="J20" s="93" t="s">
+        <v>199</v>
+      </c>
+      <c r="K20" s="94"/>
+      <c r="L20" s="94"/>
+      <c r="M20" s="95"/>
     </row>
     <row r="21" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="20" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F21" s="36"/>
       <c r="G21" s="37"/>
       <c r="H21" s="38"/>
       <c r="I21" s="43" t="s">
-        <v>99</v>
-      </c>
-      <c r="J21" s="90" t="s">
-        <v>204</v>
-      </c>
-      <c r="K21" s="91"/>
-      <c r="L21" s="91"/>
-      <c r="M21" s="92"/>
+        <v>94</v>
+      </c>
+      <c r="J21" s="93" t="s">
+        <v>199</v>
+      </c>
+      <c r="K21" s="94"/>
+      <c r="L21" s="94"/>
+      <c r="M21" s="95"/>
     </row>
     <row r="22" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="20" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F22" s="36"/>
       <c r="G22" s="37"/>
       <c r="H22" s="38"/>
       <c r="I22" s="43" t="s">
-        <v>99</v>
-      </c>
-      <c r="J22" s="90" t="s">
-        <v>204</v>
-      </c>
-      <c r="K22" s="91"/>
-      <c r="L22" s="91"/>
-      <c r="M22" s="92"/>
+        <v>94</v>
+      </c>
+      <c r="J22" s="93" t="s">
+        <v>199</v>
+      </c>
+      <c r="K22" s="94"/>
+      <c r="L22" s="94"/>
+      <c r="M22" s="95"/>
     </row>
     <row r="23" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="20" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="F23" s="90" t="s">
-        <v>205</v>
-      </c>
-      <c r="G23" s="91"/>
-      <c r="H23" s="91"/>
-      <c r="I23" s="91"/>
-      <c r="J23" s="91"/>
-      <c r="K23" s="91"/>
-      <c r="L23" s="91"/>
-      <c r="M23" s="92"/>
+        <v>56</v>
+      </c>
+      <c r="F23" s="93" t="s">
+        <v>200</v>
+      </c>
+      <c r="G23" s="94"/>
+      <c r="H23" s="94"/>
+      <c r="I23" s="94"/>
+      <c r="J23" s="94"/>
+      <c r="K23" s="94"/>
+      <c r="L23" s="94"/>
+      <c r="M23" s="95"/>
     </row>
     <row r="24" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="20" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="F24" s="90" t="s">
-        <v>206</v>
-      </c>
-      <c r="G24" s="91"/>
-      <c r="H24" s="91"/>
-      <c r="I24" s="91"/>
-      <c r="J24" s="91"/>
-      <c r="K24" s="91"/>
-      <c r="L24" s="91"/>
-      <c r="M24" s="92"/>
+        <v>57</v>
+      </c>
+      <c r="F24" s="93" t="s">
+        <v>201</v>
+      </c>
+      <c r="G24" s="94"/>
+      <c r="H24" s="94"/>
+      <c r="I24" s="94"/>
+      <c r="J24" s="94"/>
+      <c r="K24" s="94"/>
+      <c r="L24" s="94"/>
+      <c r="M24" s="95"/>
     </row>
     <row r="25" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="20" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F25" s="36"/>
       <c r="G25" s="37"/>
       <c r="H25" s="37"/>
       <c r="I25" s="38"/>
-      <c r="J25" s="90" t="s">
-        <v>207</v>
-      </c>
-      <c r="K25" s="91"/>
-      <c r="L25" s="91"/>
-      <c r="M25" s="92"/>
+      <c r="J25" s="93" t="s">
+        <v>202</v>
+      </c>
+      <c r="K25" s="94"/>
+      <c r="L25" s="94"/>
+      <c r="M25" s="95"/>
     </row>
     <row r="26" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="20" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="10"/>
@@ -4625,13 +4653,13 @@
     </row>
     <row r="27" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="20" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F27" s="9"/>
       <c r="G27" s="10"/>
@@ -4644,327 +4672,327 @@
     </row>
     <row r="28" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C28" s="20" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="F28" s="78" t="s">
-        <v>201</v>
-      </c>
-      <c r="G28" s="88"/>
-      <c r="H28" s="88"/>
-      <c r="I28" s="88"/>
-      <c r="J28" s="88"/>
-      <c r="K28" s="88"/>
-      <c r="L28" s="88"/>
-      <c r="M28" s="89"/>
+        <v>59</v>
+      </c>
+      <c r="F28" s="85" t="s">
+        <v>196</v>
+      </c>
+      <c r="G28" s="96"/>
+      <c r="H28" s="96"/>
+      <c r="I28" s="96"/>
+      <c r="J28" s="96"/>
+      <c r="K28" s="96"/>
+      <c r="L28" s="96"/>
+      <c r="M28" s="97"/>
     </row>
     <row r="29" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="20" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F29" s="27"/>
       <c r="G29" s="28"/>
       <c r="H29" s="28"/>
       <c r="I29" s="29"/>
-      <c r="J29" s="78" t="s">
-        <v>202</v>
-      </c>
-      <c r="K29" s="88"/>
-      <c r="L29" s="88"/>
-      <c r="M29" s="89"/>
+      <c r="J29" s="85" t="s">
+        <v>197</v>
+      </c>
+      <c r="K29" s="96"/>
+      <c r="L29" s="96"/>
+      <c r="M29" s="97"/>
     </row>
     <row r="30" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="20" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E30" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="F30" s="78" t="s">
-        <v>201</v>
-      </c>
-      <c r="G30" s="88"/>
-      <c r="H30" s="88"/>
-      <c r="I30" s="88"/>
-      <c r="J30" s="88"/>
-      <c r="K30" s="88"/>
-      <c r="L30" s="88"/>
-      <c r="M30" s="89"/>
+        <v>61</v>
+      </c>
+      <c r="F30" s="85" t="s">
+        <v>196</v>
+      </c>
+      <c r="G30" s="96"/>
+      <c r="H30" s="96"/>
+      <c r="I30" s="96"/>
+      <c r="J30" s="96"/>
+      <c r="K30" s="96"/>
+      <c r="L30" s="96"/>
+      <c r="M30" s="97"/>
     </row>
     <row r="31" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="20" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E31" s="25" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F31" s="27"/>
       <c r="G31" s="28"/>
       <c r="H31" s="28"/>
       <c r="I31" s="29"/>
-      <c r="J31" s="78" t="s">
-        <v>202</v>
-      </c>
-      <c r="K31" s="88"/>
-      <c r="L31" s="88"/>
-      <c r="M31" s="89"/>
+      <c r="J31" s="85" t="s">
+        <v>197</v>
+      </c>
+      <c r="K31" s="96"/>
+      <c r="L31" s="96"/>
+      <c r="M31" s="97"/>
     </row>
     <row r="32" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="20" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E32" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="F32" s="78" t="s">
-        <v>201</v>
-      </c>
-      <c r="G32" s="88"/>
-      <c r="H32" s="88"/>
-      <c r="I32" s="88"/>
-      <c r="J32" s="88"/>
-      <c r="K32" s="88"/>
-      <c r="L32" s="88"/>
-      <c r="M32" s="89"/>
+        <v>63</v>
+      </c>
+      <c r="F32" s="85" t="s">
+        <v>196</v>
+      </c>
+      <c r="G32" s="96"/>
+      <c r="H32" s="96"/>
+      <c r="I32" s="96"/>
+      <c r="J32" s="96"/>
+      <c r="K32" s="96"/>
+      <c r="L32" s="96"/>
+      <c r="M32" s="97"/>
     </row>
     <row r="33" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="20" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E33" s="25" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F33" s="27"/>
       <c r="G33" s="28"/>
       <c r="H33" s="28"/>
       <c r="I33" s="29"/>
-      <c r="J33" s="78" t="s">
-        <v>202</v>
-      </c>
-      <c r="K33" s="88"/>
-      <c r="L33" s="88"/>
-      <c r="M33" s="89"/>
+      <c r="J33" s="85" t="s">
+        <v>197</v>
+      </c>
+      <c r="K33" s="96"/>
+      <c r="L33" s="96"/>
+      <c r="M33" s="97"/>
     </row>
     <row r="34" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="20" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E34" s="25" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F34" s="27"/>
       <c r="G34" s="28"/>
       <c r="H34" s="29"/>
-      <c r="I34" s="78" t="s">
-        <v>203</v>
-      </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="88"/>
-      <c r="M34" s="89"/>
+      <c r="I34" s="85" t="s">
+        <v>198</v>
+      </c>
+      <c r="J34" s="96"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="96"/>
+      <c r="M34" s="97"/>
     </row>
     <row r="35" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="20" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E35" s="25" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F35" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="G35" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="H35" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="I35" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="J35" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="K35" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="L35" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="M35" s="31" t="s">
         <v>90</v>
-      </c>
-      <c r="G35" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="H35" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="I35" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="J35" s="31" t="s">
-        <v>96</v>
-      </c>
-      <c r="K35" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="L35" s="32" t="s">
-        <v>93</v>
-      </c>
-      <c r="M35" s="31" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="36" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C36" s="20" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E36" s="25" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F36" s="27"/>
       <c r="G36" s="28"/>
       <c r="H36" s="29"/>
       <c r="I36" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="J36" s="78" t="s">
-        <v>204</v>
-      </c>
-      <c r="K36" s="88"/>
-      <c r="L36" s="88"/>
-      <c r="M36" s="89"/>
+        <v>94</v>
+      </c>
+      <c r="J36" s="85" t="s">
+        <v>199</v>
+      </c>
+      <c r="K36" s="96"/>
+      <c r="L36" s="96"/>
+      <c r="M36" s="97"/>
     </row>
     <row r="37" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="20" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E37" s="25" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F37" s="27"/>
       <c r="G37" s="28"/>
       <c r="H37" s="29"/>
       <c r="I37" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="J37" s="78" t="s">
-        <v>204</v>
-      </c>
-      <c r="K37" s="88"/>
-      <c r="L37" s="88"/>
-      <c r="M37" s="89"/>
+        <v>94</v>
+      </c>
+      <c r="J37" s="85" t="s">
+        <v>199</v>
+      </c>
+      <c r="K37" s="96"/>
+      <c r="L37" s="96"/>
+      <c r="M37" s="97"/>
     </row>
     <row r="38" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="20" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E38" s="25" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F38" s="27"/>
       <c r="G38" s="28"/>
       <c r="H38" s="29"/>
       <c r="I38" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="J38" s="78" t="s">
-        <v>204</v>
-      </c>
-      <c r="K38" s="88"/>
-      <c r="L38" s="88"/>
-      <c r="M38" s="89"/>
+        <v>94</v>
+      </c>
+      <c r="J38" s="85" t="s">
+        <v>199</v>
+      </c>
+      <c r="K38" s="96"/>
+      <c r="L38" s="96"/>
+      <c r="M38" s="97"/>
     </row>
     <row r="39" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="20" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E39" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="F39" s="78" t="s">
-        <v>205</v>
-      </c>
-      <c r="G39" s="88"/>
-      <c r="H39" s="88"/>
-      <c r="I39" s="88"/>
-      <c r="J39" s="88"/>
-      <c r="K39" s="88"/>
-      <c r="L39" s="88"/>
-      <c r="M39" s="89"/>
+        <v>70</v>
+      </c>
+      <c r="F39" s="85" t="s">
+        <v>200</v>
+      </c>
+      <c r="G39" s="96"/>
+      <c r="H39" s="96"/>
+      <c r="I39" s="96"/>
+      <c r="J39" s="96"/>
+      <c r="K39" s="96"/>
+      <c r="L39" s="96"/>
+      <c r="M39" s="97"/>
     </row>
     <row r="40" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="20" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E40" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="F40" s="78" t="s">
-        <v>206</v>
-      </c>
-      <c r="G40" s="88"/>
-      <c r="H40" s="88"/>
-      <c r="I40" s="88"/>
-      <c r="J40" s="88"/>
-      <c r="K40" s="88"/>
-      <c r="L40" s="88"/>
-      <c r="M40" s="89"/>
+        <v>71</v>
+      </c>
+      <c r="F40" s="85" t="s">
+        <v>201</v>
+      </c>
+      <c r="G40" s="96"/>
+      <c r="H40" s="96"/>
+      <c r="I40" s="96"/>
+      <c r="J40" s="96"/>
+      <c r="K40" s="96"/>
+      <c r="L40" s="96"/>
+      <c r="M40" s="97"/>
     </row>
     <row r="41" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="20" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E41" s="25" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F41" s="27"/>
       <c r="G41" s="28"/>
       <c r="H41" s="28"/>
       <c r="I41" s="29"/>
-      <c r="J41" s="78" t="s">
-        <v>207</v>
-      </c>
-      <c r="K41" s="88"/>
-      <c r="L41" s="88"/>
-      <c r="M41" s="89"/>
+      <c r="J41" s="85" t="s">
+        <v>202</v>
+      </c>
+      <c r="K41" s="96"/>
+      <c r="L41" s="96"/>
+      <c r="M41" s="97"/>
     </row>
     <row r="42" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="20" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E42" s="25" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F42" s="27"/>
       <c r="G42" s="28"/>
@@ -4977,34 +5005,34 @@
     </row>
     <row r="43" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C43" s="20" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E43" s="25" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="28"/>
       <c r="H43" s="28"/>
       <c r="I43" s="35"/>
-      <c r="J43" s="78" t="s">
-        <v>135</v>
-      </c>
-      <c r="K43" s="88"/>
-      <c r="L43" s="88"/>
-      <c r="M43" s="89"/>
+      <c r="J43" s="85" t="s">
+        <v>130</v>
+      </c>
+      <c r="K43" s="96"/>
+      <c r="L43" s="96"/>
+      <c r="M43" s="97"/>
     </row>
     <row r="44" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="21" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F44" s="9"/>
       <c r="G44" s="10"/>
@@ -5017,10 +5045,10 @@
     </row>
     <row r="45" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C45" s="20" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="8"/>
@@ -5034,10 +5062,10 @@
     </row>
     <row r="46" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C46" s="20" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
@@ -5051,10 +5079,10 @@
     </row>
     <row r="47" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C47" s="20" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
@@ -5068,10 +5096,10 @@
     </row>
     <row r="48" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C48" s="20" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -5085,10 +5113,10 @@
     </row>
     <row r="49" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C49" s="20" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -5102,10 +5130,10 @@
     </row>
     <row r="50" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C50" s="20" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
@@ -5119,10 +5147,10 @@
     </row>
     <row r="51" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C51" s="20" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
@@ -5136,10 +5164,10 @@
     </row>
     <row r="52" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C52" s="20" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -5153,10 +5181,10 @@
     </row>
     <row r="53" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C53" s="20" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
@@ -5170,10 +5198,10 @@
     </row>
     <row r="54" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C54" s="20" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
@@ -5187,10 +5215,10 @@
     </row>
     <row r="55" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C55" s="20" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
@@ -5204,10 +5232,10 @@
     </row>
     <row r="56" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C56" s="20" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
@@ -5221,10 +5249,10 @@
     </row>
     <row r="57" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C57" s="20" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
@@ -5238,10 +5266,10 @@
     </row>
     <row r="58" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C58" s="20" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
@@ -5255,10 +5283,10 @@
     </row>
     <row r="59" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C59" s="20" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
@@ -5272,10 +5300,10 @@
     </row>
     <row r="60" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C60" s="20" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
@@ -5289,12 +5317,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="J17:M17"/>
-    <mergeCell ref="F12:M12"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="F14:M14"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="F16:M16"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="J41:M41"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="I34:M34"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="F39:M39"/>
     <mergeCell ref="F32:M32"/>
     <mergeCell ref="I18:M18"/>
     <mergeCell ref="J20:M20"/>
@@ -5307,15 +5338,12 @@
     <mergeCell ref="J29:M29"/>
     <mergeCell ref="F30:M30"/>
     <mergeCell ref="J31:M31"/>
-    <mergeCell ref="F40:M40"/>
-    <mergeCell ref="J41:M41"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="I34:M34"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="F12:M12"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="F14:M14"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="F16:M16"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5343,366 +5371,366 @@
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C5" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F5" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="L5" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="M5" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="6" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C6" s="24" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="F6" s="82" t="s">
-        <v>107</v>
-      </c>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="83"/>
-      <c r="K6" s="83"/>
-      <c r="L6" s="83"/>
-      <c r="M6" s="84"/>
+        <v>102</v>
+      </c>
+      <c r="F6" s="90" t="s">
+        <v>102</v>
+      </c>
+      <c r="G6" s="91"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
+      <c r="J6" s="91"/>
+      <c r="K6" s="91"/>
+      <c r="L6" s="91"/>
+      <c r="M6" s="92"/>
     </row>
     <row r="7" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C7" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="D7" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="F7" s="82" t="s">
-        <v>197</v>
-      </c>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="83"/>
-      <c r="K7" s="83"/>
-      <c r="L7" s="83"/>
-      <c r="M7" s="84"/>
+      <c r="F7" s="90" t="s">
+        <v>192</v>
+      </c>
+      <c r="G7" s="91"/>
+      <c r="H7" s="91"/>
+      <c r="I7" s="91"/>
+      <c r="J7" s="91"/>
+      <c r="K7" s="91"/>
+      <c r="L7" s="91"/>
+      <c r="M7" s="92"/>
     </row>
     <row r="8" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="F8" s="82" t="s">
-        <v>105</v>
-      </c>
-      <c r="G8" s="83"/>
-      <c r="H8" s="83"/>
-      <c r="I8" s="83"/>
-      <c r="J8" s="83"/>
-      <c r="K8" s="83"/>
-      <c r="L8" s="83"/>
-      <c r="M8" s="84"/>
+        <v>100</v>
+      </c>
+      <c r="F8" s="90" t="s">
+        <v>100</v>
+      </c>
+      <c r="G8" s="91"/>
+      <c r="H8" s="91"/>
+      <c r="I8" s="91"/>
+      <c r="J8" s="91"/>
+      <c r="K8" s="91"/>
+      <c r="L8" s="91"/>
+      <c r="M8" s="92"/>
     </row>
     <row r="9" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F9" s="82" t="s">
-        <v>198</v>
-      </c>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="83"/>
-      <c r="J9" s="83"/>
-      <c r="K9" s="83"/>
-      <c r="L9" s="83"/>
-      <c r="M9" s="84"/>
+        <v>101</v>
+      </c>
+      <c r="F9" s="90" t="s">
+        <v>193</v>
+      </c>
+      <c r="G9" s="91"/>
+      <c r="H9" s="91"/>
+      <c r="I9" s="91"/>
+      <c r="J9" s="91"/>
+      <c r="K9" s="91"/>
+      <c r="L9" s="91"/>
+      <c r="M9" s="92"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B19" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F20" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="K20" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="L20" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="M20" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M20" s="7" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="21" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="20" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="12" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="J21" s="82" t="s">
-        <v>124</v>
-      </c>
-      <c r="K21" s="83"/>
-      <c r="L21" s="83"/>
-      <c r="M21" s="84"/>
+        <v>118</v>
+      </c>
+      <c r="J21" s="90" t="s">
+        <v>119</v>
+      </c>
+      <c r="K21" s="91"/>
+      <c r="L21" s="91"/>
+      <c r="M21" s="92"/>
     </row>
     <row r="22" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="20" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="12" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="J22" s="82" t="s">
-        <v>124</v>
-      </c>
-      <c r="K22" s="83"/>
-      <c r="L22" s="83"/>
-      <c r="M22" s="84"/>
+        <v>118</v>
+      </c>
+      <c r="J22" s="90" t="s">
+        <v>119</v>
+      </c>
+      <c r="K22" s="91"/>
+      <c r="L22" s="91"/>
+      <c r="M22" s="92"/>
     </row>
     <row r="23" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="20" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E23" s="6"/>
-      <c r="F23" s="82" t="s">
-        <v>125</v>
-      </c>
-      <c r="G23" s="84"/>
-      <c r="H23" s="82" t="s">
-        <v>126</v>
-      </c>
-      <c r="I23" s="83"/>
-      <c r="J23" s="83"/>
-      <c r="K23" s="83"/>
-      <c r="L23" s="83"/>
-      <c r="M23" s="84"/>
+      <c r="F23" s="90" t="s">
+        <v>120</v>
+      </c>
+      <c r="G23" s="92"/>
+      <c r="H23" s="90" t="s">
+        <v>121</v>
+      </c>
+      <c r="I23" s="91"/>
+      <c r="J23" s="91"/>
+      <c r="K23" s="91"/>
+      <c r="L23" s="91"/>
+      <c r="M23" s="92"/>
     </row>
     <row r="24" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="20" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E24" s="6"/>
-      <c r="F24" s="82" t="s">
-        <v>125</v>
-      </c>
-      <c r="G24" s="84"/>
+      <c r="F24" s="90" t="s">
+        <v>120</v>
+      </c>
+      <c r="G24" s="92"/>
       <c r="H24" s="19"/>
       <c r="I24" s="12" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="K24" s="82" t="s">
-        <v>127</v>
-      </c>
-      <c r="L24" s="83"/>
-      <c r="M24" s="84"/>
+        <v>123</v>
+      </c>
+      <c r="K24" s="90" t="s">
+        <v>122</v>
+      </c>
+      <c r="L24" s="91"/>
+      <c r="M24" s="92"/>
     </row>
     <row r="25" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="20" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E25" s="6"/>
-      <c r="F25" s="82" t="s">
-        <v>130</v>
-      </c>
-      <c r="G25" s="83"/>
-      <c r="H25" s="83"/>
-      <c r="I25" s="84"/>
-      <c r="J25" s="82" t="s">
-        <v>131</v>
-      </c>
-      <c r="K25" s="83"/>
-      <c r="L25" s="83"/>
-      <c r="M25" s="84"/>
+      <c r="F25" s="90" t="s">
+        <v>125</v>
+      </c>
+      <c r="G25" s="91"/>
+      <c r="H25" s="91"/>
+      <c r="I25" s="92"/>
+      <c r="J25" s="90" t="s">
+        <v>126</v>
+      </c>
+      <c r="K25" s="91"/>
+      <c r="L25" s="91"/>
+      <c r="M25" s="92"/>
     </row>
     <row r="26" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="20" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E26" s="6"/>
-      <c r="F26" s="82" t="s">
-        <v>130</v>
-      </c>
-      <c r="G26" s="83"/>
-      <c r="H26" s="83"/>
-      <c r="I26" s="84"/>
-      <c r="J26" s="82" t="s">
-        <v>131</v>
-      </c>
-      <c r="K26" s="83"/>
-      <c r="L26" s="83"/>
-      <c r="M26" s="84"/>
+      <c r="F26" s="90" t="s">
+        <v>125</v>
+      </c>
+      <c r="G26" s="91"/>
+      <c r="H26" s="91"/>
+      <c r="I26" s="92"/>
+      <c r="J26" s="90" t="s">
+        <v>126</v>
+      </c>
+      <c r="K26" s="91"/>
+      <c r="L26" s="91"/>
+      <c r="M26" s="92"/>
     </row>
     <row r="27" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="20" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E27" s="6"/>
-      <c r="F27" s="82" t="s">
-        <v>132</v>
-      </c>
-      <c r="G27" s="83"/>
-      <c r="H27" s="83"/>
-      <c r="I27" s="84"/>
-      <c r="J27" s="82" t="s">
-        <v>133</v>
-      </c>
-      <c r="K27" s="83"/>
-      <c r="L27" s="83"/>
-      <c r="M27" s="84"/>
+      <c r="F27" s="90" t="s">
+        <v>127</v>
+      </c>
+      <c r="G27" s="91"/>
+      <c r="H27" s="91"/>
+      <c r="I27" s="92"/>
+      <c r="J27" s="90" t="s">
+        <v>128</v>
+      </c>
+      <c r="K27" s="91"/>
+      <c r="L27" s="91"/>
+      <c r="M27" s="92"/>
     </row>
     <row r="28" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C28" s="20" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E28" s="6"/>
-      <c r="F28" s="82" t="s">
-        <v>132</v>
-      </c>
-      <c r="G28" s="83"/>
-      <c r="H28" s="83"/>
-      <c r="I28" s="84"/>
-      <c r="J28" s="82" t="s">
-        <v>133</v>
-      </c>
-      <c r="K28" s="83"/>
-      <c r="L28" s="83"/>
-      <c r="M28" s="84"/>
+      <c r="F28" s="90" t="s">
+        <v>127</v>
+      </c>
+      <c r="G28" s="91"/>
+      <c r="H28" s="91"/>
+      <c r="I28" s="92"/>
+      <c r="J28" s="90" t="s">
+        <v>128</v>
+      </c>
+      <c r="K28" s="91"/>
+      <c r="L28" s="91"/>
+      <c r="M28" s="92"/>
     </row>
     <row r="29" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="20" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E29" s="6"/>
       <c r="F29" s="9"/>
@@ -5716,227 +5744,227 @@
     </row>
     <row r="30" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="20" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="15"/>
       <c r="G30" s="16"/>
       <c r="H30" s="17" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="I30" s="18" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="J30" s="18" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K30" s="15"/>
       <c r="L30" s="16"/>
       <c r="M30" s="18" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="20" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="F31" s="82" t="s">
-        <v>160</v>
-      </c>
-      <c r="G31" s="83"/>
-      <c r="H31" s="83"/>
-      <c r="I31" s="83"/>
-      <c r="J31" s="83"/>
-      <c r="K31" s="83"/>
-      <c r="L31" s="83"/>
-      <c r="M31" s="84"/>
+        <v>110</v>
+      </c>
+      <c r="F31" s="90" t="s">
+        <v>155</v>
+      </c>
+      <c r="G31" s="91"/>
+      <c r="H31" s="91"/>
+      <c r="I31" s="91"/>
+      <c r="J31" s="91"/>
+      <c r="K31" s="91"/>
+      <c r="L31" s="91"/>
+      <c r="M31" s="92"/>
     </row>
     <row r="32" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="20" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E32" s="6"/>
-      <c r="F32" s="82" t="s">
-        <v>160</v>
-      </c>
-      <c r="G32" s="83"/>
-      <c r="H32" s="83"/>
-      <c r="I32" s="83"/>
-      <c r="J32" s="83"/>
-      <c r="K32" s="83"/>
-      <c r="L32" s="83"/>
-      <c r="M32" s="84"/>
+      <c r="F32" s="90" t="s">
+        <v>155</v>
+      </c>
+      <c r="G32" s="91"/>
+      <c r="H32" s="91"/>
+      <c r="I32" s="91"/>
+      <c r="J32" s="91"/>
+      <c r="K32" s="91"/>
+      <c r="L32" s="91"/>
+      <c r="M32" s="92"/>
     </row>
     <row r="33" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="20" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E33" s="6"/>
-      <c r="F33" s="82" t="s">
-        <v>160</v>
-      </c>
-      <c r="G33" s="83"/>
-      <c r="H33" s="83"/>
-      <c r="I33" s="83"/>
-      <c r="J33" s="83"/>
-      <c r="K33" s="83"/>
-      <c r="L33" s="83"/>
-      <c r="M33" s="84"/>
+      <c r="F33" s="90" t="s">
+        <v>155</v>
+      </c>
+      <c r="G33" s="91"/>
+      <c r="H33" s="91"/>
+      <c r="I33" s="91"/>
+      <c r="J33" s="91"/>
+      <c r="K33" s="91"/>
+      <c r="L33" s="91"/>
+      <c r="M33" s="92"/>
     </row>
     <row r="34" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="20" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E34" s="6"/>
-      <c r="F34" s="82" t="s">
-        <v>160</v>
-      </c>
-      <c r="G34" s="83"/>
-      <c r="H34" s="83"/>
-      <c r="I34" s="83"/>
-      <c r="J34" s="83"/>
-      <c r="K34" s="83"/>
-      <c r="L34" s="83"/>
-      <c r="M34" s="84"/>
+      <c r="F34" s="90" t="s">
+        <v>155</v>
+      </c>
+      <c r="G34" s="91"/>
+      <c r="H34" s="91"/>
+      <c r="I34" s="91"/>
+      <c r="J34" s="91"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="91"/>
+      <c r="M34" s="92"/>
     </row>
     <row r="35" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="20" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E35" s="6"/>
-      <c r="F35" s="82" t="s">
-        <v>160</v>
-      </c>
-      <c r="G35" s="83"/>
-      <c r="H35" s="83"/>
-      <c r="I35" s="83"/>
-      <c r="J35" s="83"/>
-      <c r="K35" s="83"/>
-      <c r="L35" s="83"/>
-      <c r="M35" s="84"/>
+      <c r="F35" s="90" t="s">
+        <v>155</v>
+      </c>
+      <c r="G35" s="91"/>
+      <c r="H35" s="91"/>
+      <c r="I35" s="91"/>
+      <c r="J35" s="91"/>
+      <c r="K35" s="91"/>
+      <c r="L35" s="91"/>
+      <c r="M35" s="92"/>
     </row>
     <row r="36" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C36" s="20" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E36" s="6"/>
-      <c r="F36" s="82" t="s">
-        <v>160</v>
-      </c>
-      <c r="G36" s="83"/>
-      <c r="H36" s="83"/>
-      <c r="I36" s="83"/>
-      <c r="J36" s="83"/>
-      <c r="K36" s="83"/>
-      <c r="L36" s="83"/>
-      <c r="M36" s="84"/>
+      <c r="F36" s="90" t="s">
+        <v>155</v>
+      </c>
+      <c r="G36" s="91"/>
+      <c r="H36" s="91"/>
+      <c r="I36" s="91"/>
+      <c r="J36" s="91"/>
+      <c r="K36" s="91"/>
+      <c r="L36" s="91"/>
+      <c r="M36" s="92"/>
     </row>
     <row r="37" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="20" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E37" s="1"/>
-      <c r="F37" s="82" t="s">
-        <v>160</v>
-      </c>
-      <c r="G37" s="83"/>
-      <c r="H37" s="83"/>
-      <c r="I37" s="83"/>
-      <c r="J37" s="83"/>
-      <c r="K37" s="83"/>
-      <c r="L37" s="83"/>
-      <c r="M37" s="84"/>
+      <c r="F37" s="90" t="s">
+        <v>155</v>
+      </c>
+      <c r="G37" s="91"/>
+      <c r="H37" s="91"/>
+      <c r="I37" s="91"/>
+      <c r="J37" s="91"/>
+      <c r="K37" s="91"/>
+      <c r="L37" s="91"/>
+      <c r="M37" s="92"/>
     </row>
     <row r="38" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="20" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E38" s="1"/>
-      <c r="F38" s="82" t="s">
-        <v>160</v>
-      </c>
-      <c r="G38" s="83"/>
-      <c r="H38" s="83"/>
-      <c r="I38" s="83"/>
-      <c r="J38" s="83"/>
-      <c r="K38" s="83"/>
-      <c r="L38" s="83"/>
-      <c r="M38" s="84"/>
+      <c r="F38" s="90" t="s">
+        <v>155</v>
+      </c>
+      <c r="G38" s="91"/>
+      <c r="H38" s="91"/>
+      <c r="I38" s="91"/>
+      <c r="J38" s="91"/>
+      <c r="K38" s="91"/>
+      <c r="L38" s="91"/>
+      <c r="M38" s="92"/>
     </row>
     <row r="39" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="20" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E39" s="1"/>
-      <c r="F39" s="82" t="s">
-        <v>160</v>
-      </c>
-      <c r="G39" s="83"/>
-      <c r="H39" s="83"/>
-      <c r="I39" s="83"/>
-      <c r="J39" s="83"/>
-      <c r="K39" s="83"/>
-      <c r="L39" s="83"/>
-      <c r="M39" s="84"/>
+      <c r="F39" s="90" t="s">
+        <v>155</v>
+      </c>
+      <c r="G39" s="91"/>
+      <c r="H39" s="91"/>
+      <c r="I39" s="91"/>
+      <c r="J39" s="91"/>
+      <c r="K39" s="91"/>
+      <c r="L39" s="91"/>
+      <c r="M39" s="92"/>
     </row>
     <row r="40" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="90" t="s">
         <v>155</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E40" s="1"/>
-      <c r="F40" s="82" t="s">
-        <v>160</v>
-      </c>
-      <c r="G40" s="83"/>
-      <c r="H40" s="83"/>
-      <c r="I40" s="83"/>
-      <c r="J40" s="83"/>
-      <c r="K40" s="83"/>
-      <c r="L40" s="83"/>
-      <c r="M40" s="84"/>
+      <c r="G40" s="91"/>
+      <c r="H40" s="91"/>
+      <c r="I40" s="91"/>
+      <c r="J40" s="91"/>
+      <c r="K40" s="91"/>
+      <c r="L40" s="91"/>
+      <c r="M40" s="92"/>
     </row>
     <row r="41" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="20" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="9"/>
@@ -5950,235 +5978,235 @@
     </row>
     <row r="42" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="20" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="9"/>
       <c r="G42" s="11"/>
       <c r="H42" s="12" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="J42" s="82" t="s">
-        <v>159</v>
-      </c>
-      <c r="K42" s="83"/>
-      <c r="L42" s="84"/>
+        <v>153</v>
+      </c>
+      <c r="J42" s="90" t="s">
+        <v>154</v>
+      </c>
+      <c r="K42" s="91"/>
+      <c r="L42" s="92"/>
       <c r="M42" s="14" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="43" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C43" s="20" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="9"/>
       <c r="G43" s="11"/>
       <c r="H43" s="12" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="J43" s="82" t="s">
-        <v>159</v>
-      </c>
-      <c r="K43" s="83"/>
-      <c r="L43" s="84"/>
+        <v>153</v>
+      </c>
+      <c r="J43" s="90" t="s">
+        <v>154</v>
+      </c>
+      <c r="K43" s="91"/>
+      <c r="L43" s="92"/>
       <c r="M43" s="14" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="20" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="9"/>
       <c r="G44" s="11"/>
       <c r="H44" s="12" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="J44" s="82" t="s">
-        <v>159</v>
-      </c>
-      <c r="K44" s="83"/>
-      <c r="L44" s="84"/>
+        <v>153</v>
+      </c>
+      <c r="J44" s="90" t="s">
+        <v>154</v>
+      </c>
+      <c r="K44" s="91"/>
+      <c r="L44" s="92"/>
       <c r="M44" s="14" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C45" s="20" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="9"/>
       <c r="G45" s="11"/>
       <c r="H45" s="12" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I45" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="J45" s="82" t="s">
-        <v>159</v>
-      </c>
-      <c r="K45" s="83"/>
-      <c r="L45" s="84"/>
+        <v>153</v>
+      </c>
+      <c r="J45" s="90" t="s">
+        <v>154</v>
+      </c>
+      <c r="K45" s="91"/>
+      <c r="L45" s="92"/>
       <c r="M45" s="14" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="20" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="9"/>
       <c r="G46" s="11"/>
       <c r="H46" s="12" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I46" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="J46" s="82" t="s">
-        <v>159</v>
-      </c>
-      <c r="K46" s="83"/>
-      <c r="L46" s="84"/>
+        <v>153</v>
+      </c>
+      <c r="J46" s="90" t="s">
+        <v>154</v>
+      </c>
+      <c r="K46" s="91"/>
+      <c r="L46" s="92"/>
       <c r="M46" s="14" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="47" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="20" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="9"/>
       <c r="G47" s="11"/>
       <c r="H47" s="12" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I47" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="J47" s="82" t="s">
-        <v>159</v>
-      </c>
-      <c r="K47" s="83"/>
-      <c r="L47" s="84"/>
+        <v>153</v>
+      </c>
+      <c r="J47" s="90" t="s">
+        <v>154</v>
+      </c>
+      <c r="K47" s="91"/>
+      <c r="L47" s="92"/>
       <c r="M47" s="14" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="48" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="20" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="9"/>
       <c r="G48" s="11"/>
       <c r="H48" s="12" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="J48" s="82" t="s">
-        <v>159</v>
-      </c>
-      <c r="K48" s="83"/>
-      <c r="L48" s="84"/>
+        <v>153</v>
+      </c>
+      <c r="J48" s="90" t="s">
+        <v>154</v>
+      </c>
+      <c r="K48" s="91"/>
+      <c r="L48" s="92"/>
       <c r="M48" s="14" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="49" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="20" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="9"/>
       <c r="G49" s="11"/>
       <c r="H49" s="12" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I49" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="J49" s="82" t="s">
-        <v>159</v>
-      </c>
-      <c r="K49" s="83"/>
-      <c r="L49" s="84"/>
+        <v>153</v>
+      </c>
+      <c r="J49" s="90" t="s">
+        <v>154</v>
+      </c>
+      <c r="K49" s="91"/>
+      <c r="L49" s="92"/>
       <c r="M49" s="14" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="50" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C50" s="20" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="9"/>
       <c r="G50" s="11"/>
       <c r="H50" s="12" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I50" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="J50" s="82" t="s">
-        <v>159</v>
-      </c>
-      <c r="K50" s="83"/>
-      <c r="L50" s="84"/>
+        <v>153</v>
+      </c>
+      <c r="J50" s="90" t="s">
+        <v>154</v>
+      </c>
+      <c r="K50" s="91"/>
+      <c r="L50" s="92"/>
       <c r="M50" s="14" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="51" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C51" s="20" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="9"/>
@@ -6192,199 +6220,199 @@
     </row>
     <row r="52" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="20" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E52" s="1"/>
-      <c r="F52" s="82" t="s">
-        <v>181</v>
-      </c>
-      <c r="G52" s="83"/>
-      <c r="H52" s="83"/>
-      <c r="I52" s="84"/>
-      <c r="J52" s="82" t="s">
-        <v>182</v>
-      </c>
-      <c r="K52" s="83"/>
-      <c r="L52" s="83"/>
-      <c r="M52" s="84"/>
+      <c r="F52" s="90" t="s">
+        <v>176</v>
+      </c>
+      <c r="G52" s="91"/>
+      <c r="H52" s="91"/>
+      <c r="I52" s="92"/>
+      <c r="J52" s="90" t="s">
+        <v>177</v>
+      </c>
+      <c r="K52" s="91"/>
+      <c r="L52" s="91"/>
+      <c r="M52" s="92"/>
     </row>
     <row r="53" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="21" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E53" s="13"/>
-      <c r="F53" s="82" t="s">
-        <v>181</v>
-      </c>
-      <c r="G53" s="83"/>
-      <c r="H53" s="83"/>
-      <c r="I53" s="84"/>
-      <c r="J53" s="82" t="s">
-        <v>182</v>
-      </c>
-      <c r="K53" s="83"/>
-      <c r="L53" s="83"/>
-      <c r="M53" s="84"/>
+      <c r="F53" s="90" t="s">
+        <v>176</v>
+      </c>
+      <c r="G53" s="91"/>
+      <c r="H53" s="91"/>
+      <c r="I53" s="92"/>
+      <c r="J53" s="90" t="s">
+        <v>177</v>
+      </c>
+      <c r="K53" s="91"/>
+      <c r="L53" s="91"/>
+      <c r="M53" s="92"/>
     </row>
     <row r="54" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="20" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E54" s="1"/>
-      <c r="F54" s="82" t="s">
-        <v>181</v>
-      </c>
-      <c r="G54" s="83"/>
-      <c r="H54" s="83"/>
-      <c r="I54" s="84"/>
-      <c r="J54" s="82" t="s">
-        <v>182</v>
-      </c>
-      <c r="K54" s="83"/>
-      <c r="L54" s="83"/>
-      <c r="M54" s="84"/>
+      <c r="F54" s="90" t="s">
+        <v>176</v>
+      </c>
+      <c r="G54" s="91"/>
+      <c r="H54" s="91"/>
+      <c r="I54" s="92"/>
+      <c r="J54" s="90" t="s">
+        <v>177</v>
+      </c>
+      <c r="K54" s="91"/>
+      <c r="L54" s="91"/>
+      <c r="M54" s="92"/>
     </row>
     <row r="55" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C55" s="20" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E55" s="1"/>
-      <c r="F55" s="82" t="s">
-        <v>181</v>
-      </c>
-      <c r="G55" s="83"/>
-      <c r="H55" s="83"/>
-      <c r="I55" s="84"/>
-      <c r="J55" s="82" t="s">
-        <v>182</v>
-      </c>
-      <c r="K55" s="83"/>
-      <c r="L55" s="83"/>
-      <c r="M55" s="84"/>
+      <c r="F55" s="90" t="s">
+        <v>176</v>
+      </c>
+      <c r="G55" s="91"/>
+      <c r="H55" s="91"/>
+      <c r="I55" s="92"/>
+      <c r="J55" s="90" t="s">
+        <v>177</v>
+      </c>
+      <c r="K55" s="91"/>
+      <c r="L55" s="91"/>
+      <c r="M55" s="92"/>
     </row>
     <row r="56" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="20" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E56" s="1"/>
-      <c r="F56" s="82" t="s">
-        <v>181</v>
-      </c>
-      <c r="G56" s="83"/>
-      <c r="H56" s="83"/>
-      <c r="I56" s="84"/>
-      <c r="J56" s="82" t="s">
-        <v>182</v>
-      </c>
-      <c r="K56" s="83"/>
-      <c r="L56" s="83"/>
-      <c r="M56" s="84"/>
+      <c r="F56" s="90" t="s">
+        <v>176</v>
+      </c>
+      <c r="G56" s="91"/>
+      <c r="H56" s="91"/>
+      <c r="I56" s="92"/>
+      <c r="J56" s="90" t="s">
+        <v>177</v>
+      </c>
+      <c r="K56" s="91"/>
+      <c r="L56" s="91"/>
+      <c r="M56" s="92"/>
     </row>
     <row r="57" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C57" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E57" s="1"/>
+      <c r="F57" s="90" t="s">
         <v>176</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E57" s="1"/>
-      <c r="F57" s="82" t="s">
-        <v>181</v>
-      </c>
-      <c r="G57" s="83"/>
-      <c r="H57" s="83"/>
-      <c r="I57" s="84"/>
-      <c r="J57" s="82" t="s">
-        <v>182</v>
-      </c>
-      <c r="K57" s="83"/>
-      <c r="L57" s="83"/>
-      <c r="M57" s="84"/>
+      <c r="G57" s="91"/>
+      <c r="H57" s="91"/>
+      <c r="I57" s="92"/>
+      <c r="J57" s="90" t="s">
+        <v>177</v>
+      </c>
+      <c r="K57" s="91"/>
+      <c r="L57" s="91"/>
+      <c r="M57" s="92"/>
     </row>
     <row r="58" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C58" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E58" s="1"/>
+      <c r="F58" s="90" t="s">
+        <v>176</v>
+      </c>
+      <c r="G58" s="91"/>
+      <c r="H58" s="91"/>
+      <c r="I58" s="92"/>
+      <c r="J58" s="90" t="s">
         <v>177</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E58" s="1"/>
-      <c r="F58" s="82" t="s">
-        <v>181</v>
-      </c>
-      <c r="G58" s="83"/>
-      <c r="H58" s="83"/>
-      <c r="I58" s="84"/>
-      <c r="J58" s="82" t="s">
-        <v>182</v>
-      </c>
-      <c r="K58" s="83"/>
-      <c r="L58" s="83"/>
-      <c r="M58" s="84"/>
+      <c r="K58" s="91"/>
+      <c r="L58" s="91"/>
+      <c r="M58" s="92"/>
     </row>
     <row r="59" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C59" s="20" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E59" s="1"/>
-      <c r="F59" s="82" t="s">
-        <v>181</v>
-      </c>
-      <c r="G59" s="83"/>
-      <c r="H59" s="83"/>
-      <c r="I59" s="84"/>
-      <c r="J59" s="82" t="s">
-        <v>182</v>
-      </c>
-      <c r="K59" s="83"/>
-      <c r="L59" s="83"/>
-      <c r="M59" s="84"/>
+      <c r="F59" s="90" t="s">
+        <v>176</v>
+      </c>
+      <c r="G59" s="91"/>
+      <c r="H59" s="91"/>
+      <c r="I59" s="92"/>
+      <c r="J59" s="90" t="s">
+        <v>177</v>
+      </c>
+      <c r="K59" s="91"/>
+      <c r="L59" s="91"/>
+      <c r="M59" s="92"/>
     </row>
     <row r="60" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C60" s="20" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E60" s="1"/>
-      <c r="F60" s="82" t="s">
-        <v>181</v>
-      </c>
-      <c r="G60" s="83"/>
-      <c r="H60" s="83"/>
-      <c r="I60" s="84"/>
-      <c r="J60" s="82" t="s">
-        <v>182</v>
-      </c>
-      <c r="K60" s="83"/>
-      <c r="L60" s="83"/>
-      <c r="M60" s="84"/>
+      <c r="F60" s="90" t="s">
+        <v>176</v>
+      </c>
+      <c r="G60" s="91"/>
+      <c r="H60" s="91"/>
+      <c r="I60" s="92"/>
+      <c r="J60" s="90" t="s">
+        <v>177</v>
+      </c>
+      <c r="K60" s="91"/>
+      <c r="L60" s="91"/>
+      <c r="M60" s="92"/>
     </row>
     <row r="61" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C61" s="20" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="9"/>
@@ -6398,13 +6426,13 @@
     </row>
     <row r="62" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C62" s="20" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E62" s="22" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F62" s="9"/>
       <c r="G62" s="10"/>
@@ -6412,20 +6440,20 @@
       <c r="I62" s="10"/>
       <c r="J62" s="10"/>
       <c r="K62" s="11"/>
-      <c r="L62" s="78" t="s">
-        <v>193</v>
-      </c>
-      <c r="M62" s="80"/>
+      <c r="L62" s="85" t="s">
+        <v>188</v>
+      </c>
+      <c r="M62" s="87"/>
     </row>
     <row r="63" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C63" s="20" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E63" s="23" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F63" s="9"/>
       <c r="G63" s="10"/>
@@ -6433,20 +6461,20 @@
       <c r="I63" s="10"/>
       <c r="J63" s="10"/>
       <c r="K63" s="11"/>
-      <c r="L63" s="81" t="s">
-        <v>193</v>
-      </c>
-      <c r="M63" s="80"/>
+      <c r="L63" s="89" t="s">
+        <v>188</v>
+      </c>
+      <c r="M63" s="87"/>
     </row>
     <row r="64" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C64" s="20" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E64" s="23" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F64" s="9"/>
       <c r="G64" s="10"/>
@@ -6454,20 +6482,20 @@
       <c r="I64" s="10"/>
       <c r="J64" s="10"/>
       <c r="K64" s="11"/>
-      <c r="L64" s="81" t="s">
-        <v>193</v>
-      </c>
-      <c r="M64" s="80"/>
+      <c r="L64" s="89" t="s">
+        <v>188</v>
+      </c>
+      <c r="M64" s="87"/>
     </row>
     <row r="65" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C65" s="20" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E65" s="23" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F65" s="9"/>
       <c r="G65" s="10"/>
@@ -6475,20 +6503,20 @@
       <c r="I65" s="10"/>
       <c r="J65" s="10"/>
       <c r="K65" s="11"/>
-      <c r="L65" s="81" t="s">
-        <v>193</v>
-      </c>
-      <c r="M65" s="80"/>
+      <c r="L65" s="89" t="s">
+        <v>188</v>
+      </c>
+      <c r="M65" s="87"/>
     </row>
     <row r="66" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C66" s="20" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E66" s="23" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F66" s="9"/>
       <c r="G66" s="10"/>
@@ -6496,20 +6524,20 @@
       <c r="I66" s="10"/>
       <c r="J66" s="10"/>
       <c r="K66" s="11"/>
-      <c r="L66" s="81" t="s">
-        <v>193</v>
-      </c>
-      <c r="M66" s="80"/>
+      <c r="L66" s="89" t="s">
+        <v>188</v>
+      </c>
+      <c r="M66" s="87"/>
     </row>
     <row r="67" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C67" s="20" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E67" s="23" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F67" s="9"/>
       <c r="G67" s="10"/>
@@ -6517,20 +6545,20 @@
       <c r="I67" s="10"/>
       <c r="J67" s="10"/>
       <c r="K67" s="11"/>
-      <c r="L67" s="81" t="s">
-        <v>193</v>
-      </c>
-      <c r="M67" s="80"/>
+      <c r="L67" s="89" t="s">
+        <v>188</v>
+      </c>
+      <c r="M67" s="87"/>
     </row>
     <row r="68" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C68" s="20" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E68" s="23" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F68" s="9"/>
       <c r="G68" s="10"/>
@@ -6538,20 +6566,20 @@
       <c r="I68" s="10"/>
       <c r="J68" s="10"/>
       <c r="K68" s="11"/>
-      <c r="L68" s="81" t="s">
-        <v>193</v>
-      </c>
-      <c r="M68" s="80"/>
+      <c r="L68" s="89" t="s">
+        <v>188</v>
+      </c>
+      <c r="M68" s="87"/>
     </row>
     <row r="69" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C69" s="20" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E69" s="23" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F69" s="9"/>
       <c r="G69" s="10"/>
@@ -6559,20 +6587,20 @@
       <c r="I69" s="10"/>
       <c r="J69" s="10"/>
       <c r="K69" s="11"/>
-      <c r="L69" s="81" t="s">
-        <v>193</v>
-      </c>
-      <c r="M69" s="80"/>
+      <c r="L69" s="89" t="s">
+        <v>188</v>
+      </c>
+      <c r="M69" s="87"/>
     </row>
     <row r="70" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C70" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E70" s="23" t="s">
         <v>191</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E70" s="23" t="s">
-        <v>196</v>
       </c>
       <c r="F70" s="9"/>
       <c r="G70" s="10"/>
@@ -6580,17 +6608,17 @@
       <c r="I70" s="10"/>
       <c r="J70" s="10"/>
       <c r="K70" s="11"/>
-      <c r="L70" s="81" t="s">
-        <v>193</v>
-      </c>
-      <c r="M70" s="80"/>
+      <c r="L70" s="89" t="s">
+        <v>188</v>
+      </c>
+      <c r="M70" s="87"/>
     </row>
     <row r="71" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C71" s="20" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="9"/>
@@ -6604,54 +6632,6 @@
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F34:M34"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="F28:I28"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="F31:M31"/>
-    <mergeCell ref="F32:M32"/>
-    <mergeCell ref="F33:M33"/>
-    <mergeCell ref="J47:L47"/>
-    <mergeCell ref="F35:M35"/>
-    <mergeCell ref="F36:M36"/>
-    <mergeCell ref="F37:M37"/>
-    <mergeCell ref="F38:M38"/>
-    <mergeCell ref="F39:M39"/>
-    <mergeCell ref="F40:M40"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="J44:L44"/>
-    <mergeCell ref="J45:L45"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="J56:M56"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="J52:M52"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="J53:M53"/>
-    <mergeCell ref="L67:M67"/>
-    <mergeCell ref="L68:M68"/>
-    <mergeCell ref="L69:M69"/>
-    <mergeCell ref="L70:M70"/>
-    <mergeCell ref="F60:I60"/>
-    <mergeCell ref="J60:M60"/>
-    <mergeCell ref="L62:M62"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="L64:M64"/>
-    <mergeCell ref="L65:M65"/>
     <mergeCell ref="F6:M6"/>
     <mergeCell ref="F7:M7"/>
     <mergeCell ref="F8:M8"/>
@@ -6668,6 +6648,54 @@
     <mergeCell ref="F55:I55"/>
     <mergeCell ref="J55:M55"/>
     <mergeCell ref="F56:I56"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="L69:M69"/>
+    <mergeCell ref="L70:M70"/>
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="J60:M60"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="L64:M64"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="J56:M56"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="J52:M52"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="J53:M53"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="F35:M35"/>
+    <mergeCell ref="F36:M36"/>
+    <mergeCell ref="F37:M37"/>
+    <mergeCell ref="F38:M38"/>
+    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="F34:M34"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="F28:I28"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="F31:M31"/>
+    <mergeCell ref="F32:M32"/>
+    <mergeCell ref="F33:M33"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="F24:G24"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6689,1047 +6717,1084 @@
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C5" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C6" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C7" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C8" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C9" s="1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C12" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F12" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="K12" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="L12" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="M12" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M12" s="7" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="13" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="62" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D13" s="63" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E13" s="65" t="s">
-        <v>244</v>
-      </c>
-      <c r="F13" s="99"/>
-      <c r="G13" s="100"/>
-      <c r="H13" s="100"/>
-      <c r="I13" s="100"/>
-      <c r="J13" s="100"/>
-      <c r="K13" s="100"/>
-      <c r="L13" s="100"/>
-      <c r="M13" s="101"/>
+        <v>239</v>
+      </c>
+      <c r="F13" s="98"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="99"/>
+      <c r="I13" s="99"/>
+      <c r="J13" s="99"/>
+      <c r="K13" s="99"/>
+      <c r="L13" s="99"/>
+      <c r="M13" s="100"/>
     </row>
     <row r="14" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="20" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E14" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="F14" s="74" t="s">
-        <v>134</v>
-      </c>
-      <c r="G14" s="75"/>
-      <c r="H14" s="75"/>
-      <c r="I14" s="75"/>
-      <c r="J14" s="75"/>
-      <c r="K14" s="75"/>
-      <c r="L14" s="75"/>
-      <c r="M14" s="76"/>
+        <v>129</v>
+      </c>
+      <c r="F14" s="73" t="s">
+        <v>129</v>
+      </c>
+      <c r="G14" s="74"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="74"/>
+      <c r="K14" s="74"/>
+      <c r="L14" s="74"/>
+      <c r="M14" s="75"/>
     </row>
     <row r="15" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="20" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E15" s="45" t="s">
-        <v>245</v>
-      </c>
-      <c r="F15" s="74" t="s">
-        <v>245</v>
-      </c>
-      <c r="G15" s="75"/>
-      <c r="H15" s="75"/>
-      <c r="I15" s="75"/>
-      <c r="J15" s="75"/>
-      <c r="K15" s="75"/>
-      <c r="L15" s="75"/>
-      <c r="M15" s="76"/>
+        <v>240</v>
+      </c>
+      <c r="F15" s="73" t="s">
+        <v>240</v>
+      </c>
+      <c r="G15" s="74"/>
+      <c r="H15" s="74"/>
+      <c r="I15" s="74"/>
+      <c r="J15" s="74"/>
+      <c r="K15" s="74"/>
+      <c r="L15" s="74"/>
+      <c r="M15" s="75"/>
     </row>
     <row r="16" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="20" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>246</v>
-      </c>
-      <c r="F16" s="74" t="s">
-        <v>246</v>
-      </c>
-      <c r="G16" s="75"/>
-      <c r="H16" s="75"/>
-      <c r="I16" s="75"/>
-      <c r="J16" s="75"/>
-      <c r="K16" s="75"/>
-      <c r="L16" s="75"/>
-      <c r="M16" s="76"/>
+        <v>241</v>
+      </c>
+      <c r="F16" s="73" t="s">
+        <v>241</v>
+      </c>
+      <c r="G16" s="74"/>
+      <c r="H16" s="74"/>
+      <c r="I16" s="74"/>
+      <c r="J16" s="74"/>
+      <c r="K16" s="74"/>
+      <c r="L16" s="74"/>
+      <c r="M16" s="75"/>
     </row>
     <row r="17" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="20" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E17" s="45" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="F17" s="47" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="G17" s="47" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H17" s="47" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="I17" s="57" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="J17" s="57" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="K17" s="46"/>
       <c r="L17" s="47" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="M17" s="47" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="18" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="62" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D18" s="63" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E18" s="65"/>
-      <c r="F18" s="102" t="s">
-        <v>252</v>
-      </c>
-      <c r="G18" s="103"/>
-      <c r="H18" s="103"/>
-      <c r="I18" s="103"/>
-      <c r="J18" s="103"/>
-      <c r="K18" s="103"/>
-      <c r="L18" s="103"/>
-      <c r="M18" s="104"/>
+      <c r="F18" s="101" t="s">
+        <v>247</v>
+      </c>
+      <c r="G18" s="102"/>
+      <c r="H18" s="102"/>
+      <c r="I18" s="102"/>
+      <c r="J18" s="102"/>
+      <c r="K18" s="102"/>
+      <c r="L18" s="102"/>
+      <c r="M18" s="103"/>
       <c r="N18" s="59" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="19" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="62" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D19" s="63" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E19" s="65"/>
-      <c r="F19" s="102" t="s">
-        <v>253</v>
-      </c>
-      <c r="G19" s="103"/>
-      <c r="H19" s="103"/>
-      <c r="I19" s="103"/>
-      <c r="J19" s="103"/>
-      <c r="K19" s="103"/>
-      <c r="L19" s="103"/>
-      <c r="M19" s="104"/>
+      <c r="F19" s="101" t="s">
+        <v>248</v>
+      </c>
+      <c r="G19" s="102"/>
+      <c r="H19" s="102"/>
+      <c r="I19" s="102"/>
+      <c r="J19" s="102"/>
+      <c r="K19" s="102"/>
+      <c r="L19" s="102"/>
+      <c r="M19" s="103"/>
       <c r="N19" s="59" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="20" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="20" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E20" s="45"/>
       <c r="F20" s="57" t="s">
+        <v>249</v>
+      </c>
+      <c r="G20" s="57" t="s">
+        <v>250</v>
+      </c>
+      <c r="H20" s="57" t="s">
+        <v>251</v>
+      </c>
+      <c r="I20" s="57" t="s">
+        <v>252</v>
+      </c>
+      <c r="J20" s="58" t="s">
+        <v>253</v>
+      </c>
+      <c r="K20" s="98"/>
+      <c r="L20" s="100"/>
+      <c r="M20" s="57" t="s">
         <v>254</v>
       </c>
-      <c r="G20" s="57" t="s">
-        <v>255</v>
-      </c>
-      <c r="H20" s="57" t="s">
-        <v>256</v>
-      </c>
-      <c r="I20" s="57" t="s">
-        <v>257</v>
-      </c>
-      <c r="J20" s="58" t="s">
-        <v>258</v>
-      </c>
-      <c r="K20" s="99"/>
-      <c r="L20" s="101"/>
-      <c r="M20" s="57" t="s">
-        <v>259</v>
-      </c>
       <c r="N20" s="60" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="21" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="20" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E21" s="45"/>
       <c r="F21" s="47" t="s">
+        <v>255</v>
+      </c>
+      <c r="G21" s="47" t="s">
+        <v>256</v>
+      </c>
+      <c r="H21" s="98"/>
+      <c r="I21" s="100"/>
+      <c r="J21" s="58" t="s">
+        <v>257</v>
+      </c>
+      <c r="K21" s="58" t="s">
+        <v>258</v>
+      </c>
+      <c r="L21" s="58" t="s">
+        <v>259</v>
+      </c>
+      <c r="M21" s="58" t="s">
         <v>260</v>
-      </c>
-      <c r="G21" s="47" t="s">
-        <v>261</v>
-      </c>
-      <c r="H21" s="99"/>
-      <c r="I21" s="101"/>
-      <c r="J21" s="58" t="s">
-        <v>262</v>
-      </c>
-      <c r="K21" s="58" t="s">
-        <v>263</v>
-      </c>
-      <c r="L21" s="58" t="s">
-        <v>264</v>
-      </c>
-      <c r="M21" s="58" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="22" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="20" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E22" s="45"/>
-      <c r="F22" s="105" t="s">
-        <v>266</v>
-      </c>
-      <c r="G22" s="106"/>
-      <c r="H22" s="106"/>
-      <c r="I22" s="106"/>
-      <c r="J22" s="106"/>
-      <c r="K22" s="106"/>
-      <c r="L22" s="106"/>
-      <c r="M22" s="107"/>
+      <c r="F22" s="104" t="s">
+        <v>261</v>
+      </c>
+      <c r="G22" s="105"/>
+      <c r="H22" s="105"/>
+      <c r="I22" s="105"/>
+      <c r="J22" s="105"/>
+      <c r="K22" s="105"/>
+      <c r="L22" s="105"/>
+      <c r="M22" s="106"/>
       <c r="N22" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="23" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="20" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E23" s="44"/>
-      <c r="F23" s="105" t="s">
-        <v>267</v>
-      </c>
-      <c r="G23" s="106"/>
-      <c r="H23" s="106"/>
-      <c r="I23" s="106"/>
-      <c r="J23" s="106"/>
-      <c r="K23" s="106"/>
-      <c r="L23" s="106"/>
-      <c r="M23" s="107"/>
+      <c r="F23" s="104" t="s">
+        <v>262</v>
+      </c>
+      <c r="G23" s="105"/>
+      <c r="H23" s="105"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="105"/>
+      <c r="K23" s="105"/>
+      <c r="L23" s="105"/>
+      <c r="M23" s="106"/>
       <c r="N23" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="24" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="20" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E24" s="44"/>
-      <c r="F24" s="105" t="s">
-        <v>268</v>
-      </c>
-      <c r="G24" s="106"/>
-      <c r="H24" s="106"/>
-      <c r="I24" s="106"/>
-      <c r="J24" s="106"/>
-      <c r="K24" s="106"/>
-      <c r="L24" s="106"/>
-      <c r="M24" s="107"/>
+      <c r="F24" s="104" t="s">
+        <v>263</v>
+      </c>
+      <c r="G24" s="105"/>
+      <c r="H24" s="105"/>
+      <c r="I24" s="105"/>
+      <c r="J24" s="105"/>
+      <c r="K24" s="105"/>
+      <c r="L24" s="105"/>
+      <c r="M24" s="106"/>
       <c r="N24" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="25" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="20" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E25" s="44"/>
-      <c r="F25" s="105" t="s">
-        <v>269</v>
-      </c>
-      <c r="G25" s="106"/>
-      <c r="H25" s="106"/>
-      <c r="I25" s="106"/>
-      <c r="J25" s="106"/>
-      <c r="K25" s="106"/>
-      <c r="L25" s="106"/>
-      <c r="M25" s="107"/>
+      <c r="F25" s="104" t="s">
+        <v>264</v>
+      </c>
+      <c r="G25" s="105"/>
+      <c r="H25" s="105"/>
+      <c r="I25" s="105"/>
+      <c r="J25" s="105"/>
+      <c r="K25" s="105"/>
+      <c r="L25" s="105"/>
+      <c r="M25" s="106"/>
       <c r="N25" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="26" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="62" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D26" s="63" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E26" s="64"/>
-      <c r="F26" s="102" t="s">
-        <v>270</v>
-      </c>
-      <c r="G26" s="103"/>
-      <c r="H26" s="103"/>
-      <c r="I26" s="103"/>
-      <c r="J26" s="103"/>
-      <c r="K26" s="103"/>
-      <c r="L26" s="103"/>
-      <c r="M26" s="104"/>
+      <c r="F26" s="101" t="s">
+        <v>265</v>
+      </c>
+      <c r="G26" s="102"/>
+      <c r="H26" s="102"/>
+      <c r="I26" s="102"/>
+      <c r="J26" s="102"/>
+      <c r="K26" s="102"/>
+      <c r="L26" s="102"/>
+      <c r="M26" s="103"/>
       <c r="N26" s="61" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="27" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="62" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D27" s="63" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E27" s="64"/>
-      <c r="F27" s="99"/>
-      <c r="G27" s="100"/>
-      <c r="H27" s="100"/>
-      <c r="I27" s="100"/>
-      <c r="J27" s="101"/>
-      <c r="K27" s="102" t="s">
-        <v>271</v>
-      </c>
-      <c r="L27" s="103"/>
-      <c r="M27" s="104"/>
+      <c r="F27" s="98"/>
+      <c r="G27" s="99"/>
+      <c r="H27" s="99"/>
+      <c r="I27" s="99"/>
+      <c r="J27" s="100"/>
+      <c r="K27" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="L27" s="102"/>
+      <c r="M27" s="103"/>
       <c r="N27" s="59" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="28" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C28" s="20" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D28" s="67" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E28" s="44"/>
-      <c r="F28" s="105" t="s">
-        <v>272</v>
-      </c>
-      <c r="G28" s="106"/>
-      <c r="H28" s="106"/>
-      <c r="I28" s="106"/>
-      <c r="J28" s="106"/>
-      <c r="K28" s="108"/>
-      <c r="L28" s="108"/>
-      <c r="M28" s="109"/>
+      <c r="F28" s="104" t="s">
+        <v>267</v>
+      </c>
+      <c r="G28" s="105"/>
+      <c r="H28" s="105"/>
+      <c r="I28" s="105"/>
+      <c r="J28" s="105"/>
+      <c r="K28" s="107"/>
+      <c r="L28" s="107"/>
+      <c r="M28" s="108"/>
       <c r="N28" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
     </row>
     <row r="29" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="20" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E29" s="44"/>
-      <c r="F29" s="105" t="s">
-        <v>273</v>
-      </c>
-      <c r="G29" s="106"/>
-      <c r="H29" s="106"/>
-      <c r="I29" s="106"/>
-      <c r="J29" s="106"/>
-      <c r="K29" s="106"/>
-      <c r="L29" s="106"/>
-      <c r="M29" s="107"/>
+      <c r="F29" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="G29" s="105"/>
+      <c r="H29" s="105"/>
+      <c r="I29" s="105"/>
+      <c r="J29" s="105"/>
+      <c r="K29" s="105"/>
+      <c r="L29" s="105"/>
+      <c r="M29" s="106"/>
       <c r="N29" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
     </row>
     <row r="30" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="20" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E30" s="44"/>
-      <c r="F30" s="105" t="s">
-        <v>274</v>
-      </c>
-      <c r="G30" s="106"/>
-      <c r="H30" s="106"/>
-      <c r="I30" s="106"/>
-      <c r="J30" s="106"/>
-      <c r="K30" s="106"/>
-      <c r="L30" s="106"/>
-      <c r="M30" s="107"/>
+      <c r="F30" s="104" t="s">
+        <v>269</v>
+      </c>
+      <c r="G30" s="105"/>
+      <c r="H30" s="105"/>
+      <c r="I30" s="105"/>
+      <c r="J30" s="105"/>
+      <c r="K30" s="105"/>
+      <c r="L30" s="105"/>
+      <c r="M30" s="106"/>
       <c r="N30" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
     </row>
     <row r="31" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="20" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E31" s="44"/>
-      <c r="F31" s="105" t="s">
-        <v>275</v>
-      </c>
-      <c r="G31" s="106"/>
-      <c r="H31" s="106"/>
-      <c r="I31" s="106"/>
-      <c r="J31" s="106"/>
-      <c r="K31" s="106"/>
-      <c r="L31" s="106"/>
-      <c r="M31" s="107"/>
+      <c r="F31" s="104" t="s">
+        <v>270</v>
+      </c>
+      <c r="G31" s="105"/>
+      <c r="H31" s="105"/>
+      <c r="I31" s="105"/>
+      <c r="J31" s="105"/>
+      <c r="K31" s="105"/>
+      <c r="L31" s="105"/>
+      <c r="M31" s="106"/>
       <c r="N31" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
     </row>
     <row r="32" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="62" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D32" s="63" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E32" s="64"/>
-      <c r="F32" s="99"/>
-      <c r="G32" s="100"/>
-      <c r="H32" s="100"/>
-      <c r="I32" s="100"/>
-      <c r="J32" s="100"/>
-      <c r="K32" s="100"/>
-      <c r="L32" s="100"/>
-      <c r="M32" s="101"/>
+      <c r="F32" s="98"/>
+      <c r="G32" s="99"/>
+      <c r="H32" s="99"/>
+      <c r="I32" s="99"/>
+      <c r="J32" s="99"/>
+      <c r="K32" s="99"/>
+      <c r="L32" s="99"/>
+      <c r="M32" s="100"/>
     </row>
     <row r="33" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="62" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D33" s="63" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E33" s="64"/>
-      <c r="F33" s="99"/>
-      <c r="G33" s="100"/>
-      <c r="H33" s="100"/>
-      <c r="I33" s="100"/>
-      <c r="J33" s="100"/>
-      <c r="K33" s="100"/>
-      <c r="L33" s="100"/>
-      <c r="M33" s="101"/>
+      <c r="F33" s="98"/>
+      <c r="G33" s="99"/>
+      <c r="H33" s="99"/>
+      <c r="I33" s="99"/>
+      <c r="J33" s="99"/>
+      <c r="K33" s="99"/>
+      <c r="L33" s="99"/>
+      <c r="M33" s="100"/>
     </row>
     <row r="34" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="62" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D34" s="63" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E34" s="64"/>
-      <c r="F34" s="102" t="s">
-        <v>276</v>
-      </c>
-      <c r="G34" s="103"/>
-      <c r="H34" s="103"/>
-      <c r="I34" s="103"/>
-      <c r="J34" s="103"/>
-      <c r="K34" s="103"/>
-      <c r="L34" s="103"/>
-      <c r="M34" s="104"/>
+      <c r="F34" s="101" t="s">
+        <v>271</v>
+      </c>
+      <c r="G34" s="102"/>
+      <c r="H34" s="102"/>
+      <c r="I34" s="102"/>
+      <c r="J34" s="102"/>
+      <c r="K34" s="102"/>
+      <c r="L34" s="102"/>
+      <c r="M34" s="103"/>
       <c r="N34" s="59" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="35" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="62" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D35" s="63" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E35" s="65"/>
-      <c r="F35" s="102" t="s">
-        <v>277</v>
-      </c>
-      <c r="G35" s="104"/>
-      <c r="H35" s="99"/>
-      <c r="I35" s="100"/>
-      <c r="J35" s="100"/>
-      <c r="K35" s="100"/>
-      <c r="L35" s="100"/>
-      <c r="M35" s="101"/>
+      <c r="F35" s="101" t="s">
+        <v>272</v>
+      </c>
+      <c r="G35" s="103"/>
+      <c r="H35" s="98"/>
+      <c r="I35" s="99"/>
+      <c r="J35" s="99"/>
+      <c r="K35" s="99"/>
+      <c r="L35" s="99"/>
+      <c r="M35" s="100"/>
       <c r="N35" s="59" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="36" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C36" s="62" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D36" s="63" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E36" s="65"/>
-      <c r="F36" s="99"/>
-      <c r="G36" s="100"/>
-      <c r="H36" s="100"/>
-      <c r="I36" s="100"/>
-      <c r="J36" s="101"/>
-      <c r="K36" s="102" t="s">
-        <v>278</v>
-      </c>
-      <c r="L36" s="103"/>
-      <c r="M36" s="104"/>
+      <c r="F36" s="98"/>
+      <c r="G36" s="99"/>
+      <c r="H36" s="99"/>
+      <c r="I36" s="99"/>
+      <c r="J36" s="100"/>
+      <c r="K36" s="101" t="s">
+        <v>273</v>
+      </c>
+      <c r="L36" s="102"/>
+      <c r="M36" s="103"/>
       <c r="N36" s="59" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="37" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="62" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D37" s="63" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E37" s="64"/>
-      <c r="F37" s="99"/>
-      <c r="G37" s="100"/>
-      <c r="H37" s="100"/>
-      <c r="I37" s="101"/>
-      <c r="J37" s="102" t="s">
-        <v>279</v>
-      </c>
-      <c r="K37" s="103"/>
-      <c r="L37" s="103"/>
-      <c r="M37" s="104"/>
+      <c r="F37" s="98"/>
+      <c r="G37" s="99"/>
+      <c r="H37" s="99"/>
+      <c r="I37" s="100"/>
+      <c r="J37" s="101" t="s">
+        <v>274</v>
+      </c>
+      <c r="K37" s="102"/>
+      <c r="L37" s="102"/>
+      <c r="M37" s="103"/>
       <c r="N37" s="59" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="38" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="62" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D38" s="63" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E38" s="64"/>
-      <c r="F38" s="99"/>
-      <c r="G38" s="100"/>
-      <c r="H38" s="100"/>
-      <c r="I38" s="101"/>
-      <c r="J38" s="102" t="s">
-        <v>280</v>
-      </c>
-      <c r="K38" s="103"/>
-      <c r="L38" s="103"/>
-      <c r="M38" s="104"/>
+      <c r="F38" s="98"/>
+      <c r="G38" s="99"/>
+      <c r="H38" s="99"/>
+      <c r="I38" s="100"/>
+      <c r="J38" s="101" t="s">
+        <v>275</v>
+      </c>
+      <c r="K38" s="102"/>
+      <c r="L38" s="102"/>
+      <c r="M38" s="103"/>
       <c r="N38" s="59" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="39" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="62" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D39" s="63" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E39" s="64"/>
-      <c r="F39" s="102" t="s">
-        <v>281</v>
-      </c>
-      <c r="G39" s="103"/>
-      <c r="H39" s="103"/>
-      <c r="I39" s="103"/>
-      <c r="J39" s="103"/>
-      <c r="K39" s="103"/>
-      <c r="L39" s="103"/>
-      <c r="M39" s="104"/>
+      <c r="F39" s="101" t="s">
+        <v>276</v>
+      </c>
+      <c r="G39" s="102"/>
+      <c r="H39" s="102"/>
+      <c r="I39" s="102"/>
+      <c r="J39" s="102"/>
+      <c r="K39" s="102"/>
+      <c r="L39" s="102"/>
+      <c r="M39" s="103"/>
       <c r="N39" s="59" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="40" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="62" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D40" s="63" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E40" s="64"/>
-      <c r="F40" s="99"/>
-      <c r="G40" s="100"/>
-      <c r="H40" s="100"/>
-      <c r="I40" s="100"/>
-      <c r="J40" s="100"/>
-      <c r="K40" s="100"/>
-      <c r="L40" s="100"/>
-      <c r="M40" s="101"/>
+      <c r="F40" s="98"/>
+      <c r="G40" s="99"/>
+      <c r="H40" s="99"/>
+      <c r="I40" s="99"/>
+      <c r="J40" s="99"/>
+      <c r="K40" s="99"/>
+      <c r="L40" s="99"/>
+      <c r="M40" s="100"/>
     </row>
     <row r="41" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="62" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D41" s="63" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E41" s="64"/>
-      <c r="F41" s="99"/>
-      <c r="G41" s="100"/>
-      <c r="H41" s="100"/>
-      <c r="I41" s="100"/>
-      <c r="J41" s="100"/>
-      <c r="K41" s="100"/>
-      <c r="L41" s="100"/>
-      <c r="M41" s="101"/>
+      <c r="F41" s="98"/>
+      <c r="G41" s="99"/>
+      <c r="H41" s="99"/>
+      <c r="I41" s="99"/>
+      <c r="J41" s="99"/>
+      <c r="K41" s="99"/>
+      <c r="L41" s="99"/>
+      <c r="M41" s="100"/>
     </row>
     <row r="42" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="62" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D42" s="63" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E42" s="64"/>
-      <c r="F42" s="99"/>
-      <c r="G42" s="100"/>
-      <c r="H42" s="100"/>
-      <c r="I42" s="100"/>
-      <c r="J42" s="100"/>
-      <c r="K42" s="100"/>
-      <c r="L42" s="100"/>
-      <c r="M42" s="101"/>
+      <c r="F42" s="98"/>
+      <c r="G42" s="99"/>
+      <c r="H42" s="99"/>
+      <c r="I42" s="99"/>
+      <c r="J42" s="99"/>
+      <c r="K42" s="99"/>
+      <c r="L42" s="99"/>
+      <c r="M42" s="100"/>
     </row>
     <row r="43" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C43" s="62" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D43" s="63" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E43" s="64"/>
-      <c r="F43" s="99"/>
-      <c r="G43" s="100"/>
-      <c r="H43" s="100"/>
-      <c r="I43" s="100"/>
-      <c r="J43" s="100"/>
-      <c r="K43" s="100"/>
-      <c r="L43" s="100"/>
-      <c r="M43" s="101"/>
+      <c r="F43" s="98"/>
+      <c r="G43" s="99"/>
+      <c r="H43" s="99"/>
+      <c r="I43" s="99"/>
+      <c r="J43" s="99"/>
+      <c r="K43" s="99"/>
+      <c r="L43" s="99"/>
+      <c r="M43" s="100"/>
     </row>
     <row r="44" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="62" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D44" s="63" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E44" s="64"/>
-      <c r="F44" s="99"/>
-      <c r="G44" s="100"/>
-      <c r="H44" s="100"/>
-      <c r="I44" s="100"/>
-      <c r="J44" s="100"/>
-      <c r="K44" s="100"/>
-      <c r="L44" s="100"/>
-      <c r="M44" s="101"/>
+      <c r="F44" s="98"/>
+      <c r="G44" s="99"/>
+      <c r="H44" s="99"/>
+      <c r="I44" s="99"/>
+      <c r="J44" s="99"/>
+      <c r="K44" s="99"/>
+      <c r="L44" s="99"/>
+      <c r="M44" s="100"/>
     </row>
     <row r="45" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C45" s="21" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E45" s="45"/>
       <c r="F45" s="47" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G45" s="47" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="H45" s="47" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="I45" s="47" t="s">
-        <v>123</v>
-      </c>
-      <c r="J45" s="74" t="s">
-        <v>124</v>
-      </c>
-      <c r="K45" s="75"/>
-      <c r="L45" s="75"/>
-      <c r="M45" s="76"/>
+        <v>118</v>
+      </c>
+      <c r="J45" s="73" t="s">
+        <v>119</v>
+      </c>
+      <c r="K45" s="74"/>
+      <c r="L45" s="74"/>
+      <c r="M45" s="75"/>
     </row>
     <row r="46" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="20" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E46" s="45"/>
-      <c r="F46" s="74" t="s">
-        <v>291</v>
-      </c>
-      <c r="G46" s="76"/>
-      <c r="H46" s="74" t="s">
-        <v>126</v>
-      </c>
-      <c r="I46" s="75"/>
-      <c r="J46" s="75"/>
-      <c r="K46" s="75"/>
-      <c r="L46" s="75"/>
-      <c r="M46" s="76"/>
+      <c r="F46" s="73" t="s">
+        <v>286</v>
+      </c>
+      <c r="G46" s="75"/>
+      <c r="H46" s="73" t="s">
+        <v>121</v>
+      </c>
+      <c r="I46" s="74"/>
+      <c r="J46" s="74"/>
+      <c r="K46" s="74"/>
+      <c r="L46" s="74"/>
+      <c r="M46" s="75"/>
     </row>
     <row r="47" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="20" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E47" s="45"/>
-      <c r="F47" s="93" t="s">
-        <v>130</v>
-      </c>
-      <c r="G47" s="94"/>
-      <c r="H47" s="94"/>
-      <c r="I47" s="95"/>
-      <c r="J47" s="74" t="s">
-        <v>131</v>
-      </c>
-      <c r="K47" s="75"/>
-      <c r="L47" s="75"/>
-      <c r="M47" s="76"/>
+      <c r="F47" s="109" t="s">
+        <v>125</v>
+      </c>
+      <c r="G47" s="110"/>
+      <c r="H47" s="110"/>
+      <c r="I47" s="111"/>
+      <c r="J47" s="73" t="s">
+        <v>126</v>
+      </c>
+      <c r="K47" s="74"/>
+      <c r="L47" s="74"/>
+      <c r="M47" s="75"/>
     </row>
     <row r="48" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="20" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E48" s="6"/>
-      <c r="F48" s="74" t="s">
-        <v>132</v>
-      </c>
-      <c r="G48" s="75"/>
-      <c r="H48" s="75"/>
-      <c r="I48" s="76"/>
-      <c r="J48" s="96" t="s">
-        <v>133</v>
-      </c>
-      <c r="K48" s="97"/>
-      <c r="L48" s="97"/>
-      <c r="M48" s="98"/>
+      <c r="F48" s="73" t="s">
+        <v>127</v>
+      </c>
+      <c r="G48" s="74"/>
+      <c r="H48" s="74"/>
+      <c r="I48" s="75"/>
+      <c r="J48" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="K48" s="113"/>
+      <c r="L48" s="113"/>
+      <c r="M48" s="114"/>
     </row>
     <row r="49" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="20" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E49" s="6"/>
-      <c r="F49" s="82" t="s">
-        <v>160</v>
-      </c>
-      <c r="G49" s="83"/>
-      <c r="H49" s="83"/>
-      <c r="I49" s="83"/>
-      <c r="J49" s="83"/>
-      <c r="K49" s="83"/>
-      <c r="L49" s="83"/>
-      <c r="M49" s="84"/>
+      <c r="F49" s="90" t="s">
+        <v>155</v>
+      </c>
+      <c r="G49" s="91"/>
+      <c r="H49" s="91"/>
+      <c r="I49" s="91"/>
+      <c r="J49" s="91"/>
+      <c r="K49" s="91"/>
+      <c r="L49" s="91"/>
+      <c r="M49" s="92"/>
     </row>
     <row r="50" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C50" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E50" s="6"/>
+      <c r="F50" s="82"/>
+      <c r="G50" s="84"/>
+      <c r="H50" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E50" s="6"/>
-      <c r="F50" s="71"/>
-      <c r="G50" s="73"/>
-      <c r="H50" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="I50" s="82" t="s">
-        <v>159</v>
-      </c>
-      <c r="J50" s="83"/>
-      <c r="K50" s="84"/>
-      <c r="L50" s="82" t="s">
-        <v>160</v>
-      </c>
-      <c r="M50" s="84"/>
+      <c r="I50" s="90" t="s">
+        <v>154</v>
+      </c>
+      <c r="J50" s="91"/>
+      <c r="K50" s="92"/>
+      <c r="L50" s="90" t="s">
+        <v>155</v>
+      </c>
+      <c r="M50" s="92"/>
     </row>
     <row r="51" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C51" s="20" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E51" s="6"/>
       <c r="F51" s="12" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="I51" s="12" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K51" s="12" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="L51" s="12" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M51" s="12" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="20" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E52" s="6"/>
-      <c r="F52" s="71"/>
-      <c r="G52" s="72"/>
-      <c r="H52" s="72"/>
-      <c r="I52" s="73"/>
-      <c r="J52" s="82" t="s">
-        <v>127</v>
-      </c>
-      <c r="K52" s="83"/>
-      <c r="L52" s="84"/>
+      <c r="F52" s="82"/>
+      <c r="G52" s="83"/>
+      <c r="H52" s="83"/>
+      <c r="I52" s="84"/>
+      <c r="J52" s="90" t="s">
+        <v>122</v>
+      </c>
+      <c r="K52" s="91"/>
+      <c r="L52" s="92"/>
       <c r="M52" s="14" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="20" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>302</v>
-      </c>
-      <c r="F53" s="99"/>
-      <c r="G53" s="100"/>
-      <c r="H53" s="100"/>
-      <c r="I53" s="100"/>
-      <c r="J53" s="100"/>
-      <c r="K53" s="101"/>
-      <c r="L53" s="81" t="s">
-        <v>300</v>
-      </c>
-      <c r="M53" s="80"/>
+        <v>297</v>
+      </c>
+      <c r="F53" s="98"/>
+      <c r="G53" s="99"/>
+      <c r="H53" s="99"/>
+      <c r="I53" s="99"/>
+      <c r="J53" s="99"/>
+      <c r="K53" s="100"/>
+      <c r="L53" s="89" t="s">
+        <v>295</v>
+      </c>
+      <c r="M53" s="87"/>
     </row>
     <row r="54" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="62" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="D54" s="63" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E54" s="66"/>
-      <c r="F54" s="99"/>
-      <c r="G54" s="100"/>
-      <c r="H54" s="100"/>
-      <c r="I54" s="100"/>
-      <c r="J54" s="100"/>
-      <c r="K54" s="100"/>
-      <c r="L54" s="100"/>
-      <c r="M54" s="101"/>
+      <c r="F54" s="98"/>
+      <c r="G54" s="99"/>
+      <c r="H54" s="99"/>
+      <c r="I54" s="99"/>
+      <c r="J54" s="99"/>
+      <c r="K54" s="99"/>
+      <c r="L54" s="99"/>
+      <c r="M54" s="100"/>
     </row>
     <row r="55" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="56" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="55" t="s">
+        <v>361</v>
+      </c>
+      <c r="D56" t="s">
+        <v>40</v>
+      </c>
+      <c r="F56" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="G56" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="H56" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="I56" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="J56" s="56" t="s">
+        <v>367</v>
+      </c>
+      <c r="K56" s="82"/>
+      <c r="L56" s="84"/>
+      <c r="M56" s="56" t="s">
         <v>366</v>
-      </c>
-      <c r="D56" t="s">
-        <v>45</v>
-      </c>
-      <c r="F56" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="G56" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="H56" s="12" t="s">
-        <v>369</v>
-      </c>
-      <c r="I56" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="J56" s="56" t="s">
-        <v>372</v>
-      </c>
-      <c r="K56" s="71"/>
-      <c r="L56" s="73"/>
-      <c r="M56" s="56" t="s">
-        <v>371</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="53">
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="F47:I47"/>
+    <mergeCell ref="J47:M47"/>
+    <mergeCell ref="F48:I48"/>
+    <mergeCell ref="J48:M48"/>
+    <mergeCell ref="F49:M49"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="F42:M42"/>
+    <mergeCell ref="F43:M43"/>
+    <mergeCell ref="F44:M44"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="F26:M26"/>
+    <mergeCell ref="F24:M24"/>
+    <mergeCell ref="F25:M25"/>
+    <mergeCell ref="F22:M22"/>
+    <mergeCell ref="K27:M27"/>
+    <mergeCell ref="F27:J27"/>
+    <mergeCell ref="F19:M19"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="F28:M28"/>
+    <mergeCell ref="F30:M30"/>
+    <mergeCell ref="F32:M32"/>
+    <mergeCell ref="F34:M34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="F36:J36"/>
+    <mergeCell ref="F23:M23"/>
     <mergeCell ref="K56:L56"/>
     <mergeCell ref="F13:M13"/>
     <mergeCell ref="F15:M15"/>
@@ -7746,43 +7811,6 @@
     <mergeCell ref="F14:M14"/>
     <mergeCell ref="F16:M16"/>
     <mergeCell ref="F18:M18"/>
-    <mergeCell ref="F19:M19"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="F28:M28"/>
-    <mergeCell ref="F30:M30"/>
-    <mergeCell ref="F32:M32"/>
-    <mergeCell ref="F34:M34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="F36:J36"/>
-    <mergeCell ref="F23:M23"/>
-    <mergeCell ref="F26:M26"/>
-    <mergeCell ref="F24:M24"/>
-    <mergeCell ref="F25:M25"/>
-    <mergeCell ref="F22:M22"/>
-    <mergeCell ref="K27:M27"/>
-    <mergeCell ref="F27:J27"/>
-    <mergeCell ref="F42:M42"/>
-    <mergeCell ref="F43:M43"/>
-    <mergeCell ref="F44:M44"/>
-    <mergeCell ref="J45:M45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="F47:I47"/>
-    <mergeCell ref="J47:M47"/>
-    <mergeCell ref="F48:I48"/>
-    <mergeCell ref="J48:M48"/>
-    <mergeCell ref="F49:M49"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="I50:K50"/>
-    <mergeCell ref="F50:G50"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc/spec/Y8960_Specifications.xlsx
+++ b/doc/spec/Y8960_Specifications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hra\Documents\github\HRA_product\Y8960_Cartridge\doc\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{066F0355-9793-4316-946C-EFE29F6DEA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4A65A8-71D1-4270-92A0-01532ED014AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="modules" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="403">
   <si>
     <t>Y8960 Cartridge は、MSX用のオーディオ系チップのコンボカートリッジです。</t>
     <rPh sb="21" eb="22">
@@ -169,10 +169,6 @@
   </si>
   <si>
     <t>BSD 3-Clause</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>SSG (YM2149) [PSG(AY-3-8910) Compatible]</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1959,6 +1955,70 @@
   </si>
   <si>
     <t>SerialROM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Register(A0h にこの Address を書くと、A1h, A2h が Description の機能に切り替わる)</t>
+    <rPh sb="26" eb="27">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Register(7Ah にこの Address を書くと7Bh が Description の機能に切り替わる、7Ch にこの Address を書くと7Dh が Description の機能に切り替わる)</t>
+    <rPh sb="26" eb="27">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SCCは、MemoryMappedI/Oのみ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3Eh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3Fh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DCSG1 Register</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DCSG2 Register</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DCSG Register</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Dual SN76489N (DCSG) </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dual SSG (YM2149) [PSG(AY-3-8910) Compatible]</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2446,7 +2506,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2666,6 +2726,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2675,6 +2744,30 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2693,37 +2786,10 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2735,10 +2801,22 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2773,27 +2851,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3147,16 +3204,16 @@
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>387</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.15">
@@ -3167,13 +3224,13 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>391</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.15">
@@ -3288,31 +3345,31 @@
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B16" s="115">
+      <c r="B16" s="1">
         <v>12</v>
       </c>
-      <c r="C16" s="115" t="s">
+      <c r="C16" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B17" s="1">
+        <v>13</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="D16" s="115" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="115" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="4"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B17" s="115">
+      <c r="D17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="115" t="s">
-        <v>393</v>
-      </c>
-      <c r="D17" s="115" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="115" t="s">
+      <c r="E17" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F17" s="4"/>
@@ -3347,852 +3404,837 @@
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="F3" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G3" s="72" t="s">
+        <v>76</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="J3" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="K3" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="L3" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="N3" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="N3" s="7" t="s">
-        <v>84</v>
-      </c>
       <c r="O3" s="5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="2:15" ht="27.75" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C4" s="13" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="82"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="83"/>
-      <c r="M4" s="84"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="74"/>
+      <c r="K4" s="74"/>
+      <c r="L4" s="74"/>
+      <c r="M4" s="75"/>
       <c r="N4" s="71" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O4" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C5" s="68" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F5" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="76" t="s">
-        <v>341</v>
-      </c>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="77"/>
-      <c r="L5" s="77"/>
-      <c r="M5" s="77"/>
-      <c r="N5" s="78"/>
+      <c r="G5" s="87" t="s">
+        <v>340</v>
+      </c>
+      <c r="H5" s="88"/>
+      <c r="I5" s="88"/>
+      <c r="J5" s="88"/>
+      <c r="K5" s="88"/>
+      <c r="L5" s="88"/>
+      <c r="M5" s="88"/>
+      <c r="N5" s="89"/>
       <c r="O5" s="52" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C6" s="69" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F6" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="76" t="s">
-        <v>341</v>
-      </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
-      <c r="J6" s="77"/>
-      <c r="K6" s="77"/>
-      <c r="L6" s="77"/>
-      <c r="M6" s="77"/>
-      <c r="N6" s="78"/>
+      <c r="G6" s="87" t="s">
+        <v>340</v>
+      </c>
+      <c r="H6" s="88"/>
+      <c r="I6" s="88"/>
+      <c r="J6" s="88"/>
+      <c r="K6" s="88"/>
+      <c r="L6" s="88"/>
+      <c r="M6" s="88"/>
+      <c r="N6" s="89"/>
       <c r="O6" s="52" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C7" s="69" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F7" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="76" t="s">
-        <v>341</v>
-      </c>
-      <c r="H7" s="77"/>
-      <c r="I7" s="77"/>
-      <c r="J7" s="77"/>
-      <c r="K7" s="77"/>
-      <c r="L7" s="77"/>
-      <c r="M7" s="77"/>
-      <c r="N7" s="78"/>
+      <c r="G7" s="87" t="s">
+        <v>340</v>
+      </c>
+      <c r="H7" s="88"/>
+      <c r="I7" s="88"/>
+      <c r="J7" s="88"/>
+      <c r="K7" s="88"/>
+      <c r="L7" s="88"/>
+      <c r="M7" s="88"/>
+      <c r="N7" s="89"/>
       <c r="O7" s="52" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C8" s="69" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F8" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="76" t="s">
-        <v>341</v>
-      </c>
-      <c r="H8" s="77"/>
-      <c r="I8" s="77"/>
-      <c r="J8" s="77"/>
-      <c r="K8" s="77"/>
-      <c r="L8" s="77"/>
-      <c r="M8" s="77"/>
-      <c r="N8" s="78"/>
+      <c r="G8" s="87" t="s">
+        <v>340</v>
+      </c>
+      <c r="H8" s="88"/>
+      <c r="I8" s="88"/>
+      <c r="J8" s="88"/>
+      <c r="K8" s="88"/>
+      <c r="L8" s="88"/>
+      <c r="M8" s="88"/>
+      <c r="N8" s="89"/>
       <c r="O8" s="52" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C9" s="69" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F9" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="73" t="s">
-        <v>342</v>
-      </c>
-      <c r="H9" s="74"/>
-      <c r="I9" s="74"/>
-      <c r="J9" s="74"/>
-      <c r="K9" s="74"/>
-      <c r="L9" s="74"/>
-      <c r="M9" s="74"/>
-      <c r="N9" s="75"/>
+      <c r="G9" s="76" t="s">
+        <v>341</v>
+      </c>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="77"/>
+      <c r="K9" s="77"/>
+      <c r="L9" s="77"/>
+      <c r="M9" s="77"/>
+      <c r="N9" s="78"/>
       <c r="O9" s="52" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C10" s="69" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F10" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="73" t="s">
-        <v>342</v>
-      </c>
-      <c r="H10" s="74"/>
-      <c r="I10" s="74"/>
-      <c r="J10" s="74"/>
-      <c r="K10" s="74"/>
-      <c r="L10" s="74"/>
-      <c r="M10" s="74"/>
-      <c r="N10" s="75"/>
+      <c r="G10" s="76" t="s">
+        <v>341</v>
+      </c>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="77"/>
+      <c r="K10" s="77"/>
+      <c r="L10" s="77"/>
+      <c r="M10" s="77"/>
+      <c r="N10" s="78"/>
       <c r="O10" s="52" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C11" s="51" t="s">
+        <v>313</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="25" t="s">
         <v>314</v>
       </c>
-      <c r="D11" s="51" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>315</v>
-      </c>
       <c r="F11" s="22" t="s">
-        <v>385</v>
-      </c>
-      <c r="G11" s="89" t="s">
-        <v>315</v>
-      </c>
-      <c r="H11" s="86"/>
-      <c r="I11" s="86"/>
-      <c r="J11" s="86"/>
-      <c r="K11" s="86"/>
-      <c r="L11" s="86"/>
-      <c r="M11" s="86"/>
-      <c r="N11" s="87"/>
+        <v>384</v>
+      </c>
+      <c r="G11" s="83" t="s">
+        <v>314</v>
+      </c>
+      <c r="H11" s="81"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="81"/>
+      <c r="K11" s="81"/>
+      <c r="L11" s="81"/>
+      <c r="M11" s="81"/>
+      <c r="N11" s="82"/>
       <c r="O11" s="53" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C12" s="51" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D12" s="51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>385</v>
-      </c>
-      <c r="G12" s="89" t="s">
-        <v>316</v>
-      </c>
-      <c r="H12" s="86"/>
-      <c r="I12" s="86"/>
-      <c r="J12" s="86"/>
-      <c r="K12" s="86"/>
-      <c r="L12" s="86"/>
-      <c r="M12" s="86"/>
-      <c r="N12" s="87"/>
+        <v>384</v>
+      </c>
+      <c r="G12" s="83" t="s">
+        <v>315</v>
+      </c>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
+      <c r="J12" s="81"/>
+      <c r="K12" s="81"/>
+      <c r="L12" s="81"/>
+      <c r="M12" s="81"/>
+      <c r="N12" s="82"/>
       <c r="O12" s="53" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="24" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>385</v>
-      </c>
-      <c r="G13" s="85" t="s">
-        <v>293</v>
-      </c>
-      <c r="H13" s="86"/>
-      <c r="I13" s="86"/>
-      <c r="J13" s="86"/>
-      <c r="K13" s="86"/>
-      <c r="L13" s="86"/>
-      <c r="M13" s="86"/>
-      <c r="N13" s="87"/>
+        <v>384</v>
+      </c>
+      <c r="G13" s="80" t="s">
+        <v>292</v>
+      </c>
+      <c r="H13" s="81"/>
+      <c r="I13" s="81"/>
+      <c r="J13" s="81"/>
+      <c r="K13" s="81"/>
+      <c r="L13" s="81"/>
+      <c r="M13" s="81"/>
+      <c r="N13" s="82"/>
       <c r="O13" s="53" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="25" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>385</v>
-      </c>
-      <c r="G14" s="85" t="s">
-        <v>303</v>
-      </c>
-      <c r="H14" s="86"/>
-      <c r="I14" s="86"/>
-      <c r="J14" s="86"/>
-      <c r="K14" s="86"/>
-      <c r="L14" s="86"/>
-      <c r="M14" s="86"/>
-      <c r="N14" s="87"/>
+        <v>384</v>
+      </c>
+      <c r="G14" s="80" t="s">
+        <v>302</v>
+      </c>
+      <c r="H14" s="81"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="81"/>
+      <c r="K14" s="81"/>
+      <c r="L14" s="81"/>
+      <c r="M14" s="81"/>
+      <c r="N14" s="82"/>
       <c r="O14" s="53" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="15" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="25" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>385</v>
-      </c>
-      <c r="G15" s="85" t="s">
-        <v>291</v>
-      </c>
-      <c r="H15" s="86"/>
-      <c r="I15" s="86"/>
-      <c r="J15" s="86"/>
-      <c r="K15" s="86"/>
-      <c r="L15" s="86"/>
-      <c r="M15" s="86"/>
-      <c r="N15" s="87"/>
+        <v>384</v>
+      </c>
+      <c r="G15" s="80" t="s">
+        <v>290</v>
+      </c>
+      <c r="H15" s="81"/>
+      <c r="I15" s="81"/>
+      <c r="J15" s="81"/>
+      <c r="K15" s="81"/>
+      <c r="L15" s="81"/>
+      <c r="M15" s="81"/>
+      <c r="N15" s="82"/>
       <c r="O15" s="53" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="16" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="25" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>385</v>
-      </c>
-      <c r="G16" s="85" t="s">
-        <v>304</v>
-      </c>
-      <c r="H16" s="86"/>
-      <c r="I16" s="86"/>
-      <c r="J16" s="86"/>
-      <c r="K16" s="86"/>
-      <c r="L16" s="86"/>
-      <c r="M16" s="86"/>
-      <c r="N16" s="87"/>
+        <v>384</v>
+      </c>
+      <c r="G16" s="80" t="s">
+        <v>303</v>
+      </c>
+      <c r="H16" s="81"/>
+      <c r="I16" s="81"/>
+      <c r="J16" s="81"/>
+      <c r="K16" s="81"/>
+      <c r="L16" s="81"/>
+      <c r="M16" s="81"/>
+      <c r="N16" s="82"/>
       <c r="O16" s="53" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="50" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>385</v>
-      </c>
-      <c r="G17" s="85" t="s">
-        <v>311</v>
-      </c>
-      <c r="H17" s="86"/>
-      <c r="I17" s="86"/>
-      <c r="J17" s="86"/>
-      <c r="K17" s="86"/>
-      <c r="L17" s="86"/>
-      <c r="M17" s="86"/>
-      <c r="N17" s="87"/>
+        <v>384</v>
+      </c>
+      <c r="G17" s="80" t="s">
+        <v>310</v>
+      </c>
+      <c r="H17" s="81"/>
+      <c r="I17" s="81"/>
+      <c r="J17" s="81"/>
+      <c r="K17" s="81"/>
+      <c r="L17" s="81"/>
+      <c r="M17" s="81"/>
+      <c r="N17" s="82"/>
       <c r="O17" s="53" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="18" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="51" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>385</v>
-      </c>
-      <c r="G18" s="85" t="s">
-        <v>312</v>
-      </c>
-      <c r="H18" s="86"/>
-      <c r="I18" s="86"/>
-      <c r="J18" s="86"/>
-      <c r="K18" s="86"/>
-      <c r="L18" s="86"/>
-      <c r="M18" s="86"/>
-      <c r="N18" s="87"/>
+        <v>384</v>
+      </c>
+      <c r="G18" s="80" t="s">
+        <v>311</v>
+      </c>
+      <c r="H18" s="81"/>
+      <c r="I18" s="81"/>
+      <c r="J18" s="81"/>
+      <c r="K18" s="81"/>
+      <c r="L18" s="81"/>
+      <c r="M18" s="81"/>
+      <c r="N18" s="82"/>
       <c r="O18" s="53" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="19" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="48" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D19" s="49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>385</v>
-      </c>
-      <c r="G19" s="85" t="s">
-        <v>102</v>
-      </c>
-      <c r="H19" s="86"/>
-      <c r="I19" s="86"/>
-      <c r="J19" s="86"/>
-      <c r="K19" s="86"/>
-      <c r="L19" s="86"/>
-      <c r="M19" s="86"/>
-      <c r="N19" s="87"/>
+        <v>384</v>
+      </c>
+      <c r="G19" s="80" t="s">
+        <v>101</v>
+      </c>
+      <c r="H19" s="81"/>
+      <c r="I19" s="81"/>
+      <c r="J19" s="81"/>
+      <c r="K19" s="81"/>
+      <c r="L19" s="81"/>
+      <c r="M19" s="81"/>
+      <c r="N19" s="82"/>
       <c r="O19" s="53" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="20" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>385</v>
-      </c>
-      <c r="G20" s="85" t="s">
-        <v>192</v>
-      </c>
-      <c r="H20" s="86"/>
-      <c r="I20" s="86"/>
-      <c r="J20" s="86"/>
-      <c r="K20" s="86"/>
-      <c r="L20" s="86"/>
-      <c r="M20" s="86"/>
-      <c r="N20" s="87"/>
+        <v>384</v>
+      </c>
+      <c r="G20" s="80" t="s">
+        <v>191</v>
+      </c>
+      <c r="H20" s="81"/>
+      <c r="I20" s="81"/>
+      <c r="J20" s="81"/>
+      <c r="K20" s="81"/>
+      <c r="L20" s="81"/>
+      <c r="M20" s="81"/>
+      <c r="N20" s="82"/>
       <c r="O20" s="53" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="21" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>385</v>
-      </c>
-      <c r="G21" s="90" t="s">
-        <v>100</v>
-      </c>
-      <c r="H21" s="91"/>
-      <c r="I21" s="91"/>
-      <c r="J21" s="91"/>
-      <c r="K21" s="91"/>
-      <c r="L21" s="91"/>
-      <c r="M21" s="91"/>
-      <c r="N21" s="92"/>
+        <v>384</v>
+      </c>
+      <c r="G21" s="84" t="s">
+        <v>99</v>
+      </c>
+      <c r="H21" s="85"/>
+      <c r="I21" s="85"/>
+      <c r="J21" s="85"/>
+      <c r="K21" s="85"/>
+      <c r="L21" s="85"/>
+      <c r="M21" s="85"/>
+      <c r="N21" s="86"/>
       <c r="O21" s="53" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="22" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>385</v>
-      </c>
-      <c r="G22" s="90" t="s">
-        <v>193</v>
-      </c>
-      <c r="H22" s="91"/>
-      <c r="I22" s="91"/>
-      <c r="J22" s="91"/>
-      <c r="K22" s="91"/>
-      <c r="L22" s="91"/>
-      <c r="M22" s="91"/>
-      <c r="N22" s="92"/>
+        <v>384</v>
+      </c>
+      <c r="G22" s="84" t="s">
+        <v>192</v>
+      </c>
+      <c r="H22" s="85"/>
+      <c r="I22" s="85"/>
+      <c r="J22" s="85"/>
+      <c r="K22" s="85"/>
+      <c r="L22" s="85"/>
+      <c r="M22" s="85"/>
+      <c r="N22" s="86"/>
       <c r="O22" s="53" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="23" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>385</v>
-      </c>
-      <c r="G23" s="79"/>
-      <c r="H23" s="80"/>
-      <c r="I23" s="80"/>
-      <c r="J23" s="80"/>
-      <c r="K23" s="80"/>
-      <c r="L23" s="81"/>
+        <v>384</v>
+      </c>
+      <c r="G23" s="90"/>
+      <c r="H23" s="91"/>
+      <c r="I23" s="91"/>
+      <c r="J23" s="91"/>
+      <c r="K23" s="91"/>
+      <c r="L23" s="92"/>
       <c r="M23" s="26" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O23" s="53" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="24" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="22"/>
-      <c r="G24" s="82"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="83"/>
-      <c r="J24" s="83"/>
-      <c r="K24" s="83"/>
-      <c r="L24" s="83"/>
-      <c r="M24" s="83"/>
-      <c r="N24" s="84"/>
+      <c r="G24" s="73"/>
+      <c r="H24" s="74"/>
+      <c r="I24" s="74"/>
+      <c r="J24" s="74"/>
+      <c r="K24" s="74"/>
+      <c r="L24" s="74"/>
+      <c r="M24" s="74"/>
+      <c r="N24" s="75"/>
       <c r="O24" s="53"/>
     </row>
     <row r="25" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="22"/>
-      <c r="G25" s="82"/>
-      <c r="H25" s="83"/>
-      <c r="I25" s="83"/>
-      <c r="J25" s="83"/>
-      <c r="K25" s="83"/>
-      <c r="L25" s="83"/>
-      <c r="M25" s="83"/>
-      <c r="N25" s="84"/>
+      <c r="G25" s="73"/>
+      <c r="H25" s="74"/>
+      <c r="I25" s="74"/>
+      <c r="J25" s="74"/>
+      <c r="K25" s="74"/>
+      <c r="L25" s="74"/>
+      <c r="M25" s="74"/>
+      <c r="N25" s="75"/>
       <c r="O25" s="53"/>
     </row>
     <row r="26" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="22"/>
-      <c r="G26" s="82"/>
-      <c r="H26" s="83"/>
-      <c r="I26" s="83"/>
-      <c r="J26" s="83"/>
-      <c r="K26" s="83"/>
-      <c r="L26" s="83"/>
-      <c r="M26" s="83"/>
-      <c r="N26" s="84"/>
+      <c r="G26" s="73"/>
+      <c r="H26" s="74"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="74"/>
+      <c r="K26" s="74"/>
+      <c r="L26" s="74"/>
+      <c r="M26" s="74"/>
+      <c r="N26" s="75"/>
       <c r="O26" s="53"/>
     </row>
     <row r="27" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="22"/>
-      <c r="G27" s="82"/>
-      <c r="H27" s="83"/>
-      <c r="I27" s="83"/>
-      <c r="J27" s="83"/>
-      <c r="K27" s="83"/>
-      <c r="L27" s="83"/>
-      <c r="M27" s="83"/>
-      <c r="N27" s="84"/>
+      <c r="G27" s="73"/>
+      <c r="H27" s="74"/>
+      <c r="I27" s="74"/>
+      <c r="J27" s="74"/>
+      <c r="K27" s="74"/>
+      <c r="L27" s="74"/>
+      <c r="M27" s="74"/>
+      <c r="N27" s="75"/>
       <c r="O27" s="53"/>
     </row>
     <row r="28" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="22"/>
-      <c r="G28" s="82"/>
-      <c r="H28" s="83"/>
-      <c r="I28" s="83"/>
-      <c r="J28" s="83"/>
-      <c r="K28" s="83"/>
-      <c r="L28" s="83"/>
-      <c r="M28" s="83"/>
-      <c r="N28" s="84"/>
+      <c r="G28" s="73"/>
+      <c r="H28" s="74"/>
+      <c r="I28" s="74"/>
+      <c r="J28" s="74"/>
+      <c r="K28" s="74"/>
+      <c r="L28" s="74"/>
+      <c r="M28" s="74"/>
+      <c r="N28" s="75"/>
       <c r="O28" s="53"/>
     </row>
     <row r="29" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="22"/>
-      <c r="G29" s="82"/>
-      <c r="H29" s="83"/>
-      <c r="I29" s="83"/>
-      <c r="J29" s="83"/>
-      <c r="K29" s="83"/>
-      <c r="L29" s="83"/>
-      <c r="M29" s="83"/>
-      <c r="N29" s="84"/>
+      <c r="G29" s="73"/>
+      <c r="H29" s="74"/>
+      <c r="I29" s="74"/>
+      <c r="J29" s="74"/>
+      <c r="K29" s="74"/>
+      <c r="L29" s="74"/>
+      <c r="M29" s="74"/>
+      <c r="N29" s="75"/>
       <c r="O29" s="53"/>
     </row>
     <row r="30" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="22"/>
-      <c r="G30" s="82"/>
-      <c r="H30" s="83"/>
-      <c r="I30" s="83"/>
-      <c r="J30" s="83"/>
-      <c r="K30" s="83"/>
-      <c r="L30" s="83"/>
-      <c r="M30" s="83"/>
-      <c r="N30" s="84"/>
+      <c r="G30" s="73"/>
+      <c r="H30" s="74"/>
+      <c r="I30" s="74"/>
+      <c r="J30" s="74"/>
+      <c r="K30" s="74"/>
+      <c r="L30" s="74"/>
+      <c r="M30" s="74"/>
+      <c r="N30" s="75"/>
       <c r="O30" s="53"/>
     </row>
     <row r="31" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="22"/>
-      <c r="G31" s="82"/>
-      <c r="H31" s="83"/>
-      <c r="I31" s="83"/>
-      <c r="J31" s="83"/>
-      <c r="K31" s="83"/>
-      <c r="L31" s="83"/>
-      <c r="M31" s="83"/>
-      <c r="N31" s="84"/>
+      <c r="G31" s="73"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="74"/>
+      <c r="J31" s="74"/>
+      <c r="K31" s="74"/>
+      <c r="L31" s="74"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="75"/>
       <c r="O31" s="53"/>
     </row>
     <row r="32" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G32" s="26" t="s">
-        <v>381</v>
-      </c>
-      <c r="H32" s="82"/>
-      <c r="I32" s="84"/>
+        <v>380</v>
+      </c>
+      <c r="H32" s="73"/>
+      <c r="I32" s="75"/>
       <c r="J32" s="34" t="s">
         <v>4</v>
       </c>
       <c r="K32" s="34" t="s">
+        <v>306</v>
+      </c>
+      <c r="L32" s="34" t="s">
         <v>307</v>
       </c>
-      <c r="L32" s="34" t="s">
-        <v>308</v>
-      </c>
       <c r="M32" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N32" s="47" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O32" s="53" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="33" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="68" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F33" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="G33" s="73" t="s">
-        <v>342</v>
-      </c>
-      <c r="H33" s="88"/>
-      <c r="I33" s="74"/>
-      <c r="J33" s="74"/>
-      <c r="K33" s="74"/>
-      <c r="L33" s="74"/>
-      <c r="M33" s="74"/>
-      <c r="N33" s="75"/>
+      <c r="G33" s="76" t="s">
+        <v>341</v>
+      </c>
+      <c r="H33" s="79"/>
+      <c r="I33" s="77"/>
+      <c r="J33" s="77"/>
+      <c r="K33" s="77"/>
+      <c r="L33" s="77"/>
+      <c r="M33" s="77"/>
+      <c r="N33" s="78"/>
       <c r="O33" s="52" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="34" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="70" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F34" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="G34" s="73" t="s">
-        <v>342</v>
-      </c>
-      <c r="H34" s="74"/>
-      <c r="I34" s="74"/>
-      <c r="J34" s="74"/>
-      <c r="K34" s="74"/>
-      <c r="L34" s="74"/>
-      <c r="M34" s="74"/>
-      <c r="N34" s="75"/>
+      <c r="G34" s="76" t="s">
+        <v>341</v>
+      </c>
+      <c r="H34" s="77"/>
+      <c r="I34" s="77"/>
+      <c r="J34" s="77"/>
+      <c r="K34" s="77"/>
+      <c r="L34" s="77"/>
+      <c r="M34" s="77"/>
+      <c r="N34" s="78"/>
       <c r="O34" s="52" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="G4:M4"/>
-    <mergeCell ref="G9:N9"/>
-    <mergeCell ref="G10:N10"/>
-    <mergeCell ref="G33:N33"/>
-    <mergeCell ref="G17:N17"/>
-    <mergeCell ref="G11:N11"/>
-    <mergeCell ref="G12:N12"/>
-    <mergeCell ref="G19:N19"/>
-    <mergeCell ref="G20:N20"/>
-    <mergeCell ref="G21:N21"/>
-    <mergeCell ref="G22:N22"/>
-    <mergeCell ref="G13:N13"/>
-    <mergeCell ref="G14:N14"/>
-    <mergeCell ref="G15:N15"/>
-    <mergeCell ref="G16:N16"/>
     <mergeCell ref="G34:N34"/>
     <mergeCell ref="G5:N5"/>
     <mergeCell ref="G6:N6"/>
@@ -4209,6 +4251,21 @@
     <mergeCell ref="G18:N18"/>
     <mergeCell ref="H32:I32"/>
     <mergeCell ref="G31:N31"/>
+    <mergeCell ref="G4:M4"/>
+    <mergeCell ref="G9:N9"/>
+    <mergeCell ref="G10:N10"/>
+    <mergeCell ref="G33:N33"/>
+    <mergeCell ref="G17:N17"/>
+    <mergeCell ref="G11:N11"/>
+    <mergeCell ref="G12:N12"/>
+    <mergeCell ref="G19:N19"/>
+    <mergeCell ref="G20:N20"/>
+    <mergeCell ref="G21:N21"/>
+    <mergeCell ref="G22:N22"/>
+    <mergeCell ref="G13:N13"/>
+    <mergeCell ref="G14:N14"/>
+    <mergeCell ref="G15:N15"/>
+    <mergeCell ref="G16:N16"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4226,421 +4283,421 @@
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>31</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C6" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C7" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" t="s">
-        <v>44</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="F11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="H11" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="I11" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="J11" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="K11" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="L11" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="L11" s="7" t="s">
+      <c r="M11" s="7" t="s">
         <v>83</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="12" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C12" s="20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="93" t="s">
-        <v>196</v>
-      </c>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="94"/>
-      <c r="K12" s="94"/>
-      <c r="L12" s="94"/>
-      <c r="M12" s="95"/>
+        <v>44</v>
+      </c>
+      <c r="F12" s="95" t="s">
+        <v>195</v>
+      </c>
+      <c r="G12" s="96"/>
+      <c r="H12" s="96"/>
+      <c r="I12" s="96"/>
+      <c r="J12" s="96"/>
+      <c r="K12" s="96"/>
+      <c r="L12" s="96"/>
+      <c r="M12" s="97"/>
     </row>
     <row r="13" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="20" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F13" s="36"/>
       <c r="G13" s="37"/>
       <c r="H13" s="37"/>
       <c r="I13" s="38"/>
-      <c r="J13" s="93" t="s">
-        <v>197</v>
-      </c>
-      <c r="K13" s="94"/>
-      <c r="L13" s="94"/>
-      <c r="M13" s="95"/>
+      <c r="J13" s="95" t="s">
+        <v>196</v>
+      </c>
+      <c r="K13" s="96"/>
+      <c r="L13" s="96"/>
+      <c r="M13" s="97"/>
     </row>
     <row r="14" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="93" t="s">
-        <v>196</v>
-      </c>
-      <c r="G14" s="94"/>
-      <c r="H14" s="94"/>
-      <c r="I14" s="94"/>
-      <c r="J14" s="94"/>
-      <c r="K14" s="94"/>
-      <c r="L14" s="94"/>
-      <c r="M14" s="95"/>
+        <v>46</v>
+      </c>
+      <c r="F14" s="95" t="s">
+        <v>195</v>
+      </c>
+      <c r="G14" s="96"/>
+      <c r="H14" s="96"/>
+      <c r="I14" s="96"/>
+      <c r="J14" s="96"/>
+      <c r="K14" s="96"/>
+      <c r="L14" s="96"/>
+      <c r="M14" s="97"/>
     </row>
     <row r="15" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F15" s="36"/>
       <c r="G15" s="37"/>
       <c r="H15" s="37"/>
       <c r="I15" s="38"/>
-      <c r="J15" s="93" t="s">
-        <v>197</v>
-      </c>
-      <c r="K15" s="94"/>
-      <c r="L15" s="94"/>
-      <c r="M15" s="95"/>
+      <c r="J15" s="95" t="s">
+        <v>196</v>
+      </c>
+      <c r="K15" s="96"/>
+      <c r="L15" s="96"/>
+      <c r="M15" s="97"/>
     </row>
     <row r="16" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="93" t="s">
-        <v>196</v>
-      </c>
-      <c r="G16" s="94"/>
-      <c r="H16" s="94"/>
-      <c r="I16" s="94"/>
-      <c r="J16" s="94"/>
-      <c r="K16" s="94"/>
-      <c r="L16" s="94"/>
-      <c r="M16" s="95"/>
+        <v>48</v>
+      </c>
+      <c r="F16" s="95" t="s">
+        <v>195</v>
+      </c>
+      <c r="G16" s="96"/>
+      <c r="H16" s="96"/>
+      <c r="I16" s="96"/>
+      <c r="J16" s="96"/>
+      <c r="K16" s="96"/>
+      <c r="L16" s="96"/>
+      <c r="M16" s="97"/>
     </row>
     <row r="17" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F17" s="36"/>
       <c r="G17" s="37"/>
       <c r="H17" s="37"/>
       <c r="I17" s="38"/>
-      <c r="J17" s="93" t="s">
-        <v>197</v>
-      </c>
-      <c r="K17" s="94"/>
-      <c r="L17" s="94"/>
-      <c r="M17" s="95"/>
+      <c r="J17" s="95" t="s">
+        <v>196</v>
+      </c>
+      <c r="K17" s="96"/>
+      <c r="L17" s="96"/>
+      <c r="M17" s="97"/>
     </row>
     <row r="18" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="20" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F18" s="36"/>
       <c r="G18" s="37"/>
       <c r="H18" s="38"/>
-      <c r="I18" s="93" t="s">
-        <v>198</v>
-      </c>
-      <c r="J18" s="94"/>
-      <c r="K18" s="94"/>
-      <c r="L18" s="94"/>
-      <c r="M18" s="95"/>
+      <c r="I18" s="95" t="s">
+        <v>197</v>
+      </c>
+      <c r="J18" s="96"/>
+      <c r="K18" s="96"/>
+      <c r="L18" s="96"/>
+      <c r="M18" s="97"/>
     </row>
     <row r="19" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F19" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="G19" s="40" t="s">
-        <v>86</v>
-      </c>
       <c r="H19" s="39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I19" s="41" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J19" s="40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K19" s="42" t="s">
+        <v>88</v>
+      </c>
+      <c r="L19" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="M19" s="40" t="s">
         <v>89</v>
-      </c>
-      <c r="L19" s="41" t="s">
-        <v>88</v>
-      </c>
-      <c r="M19" s="40" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="20" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F20" s="36"/>
       <c r="G20" s="37"/>
       <c r="H20" s="38"/>
       <c r="I20" s="43" t="s">
-        <v>94</v>
-      </c>
-      <c r="J20" s="93" t="s">
-        <v>199</v>
-      </c>
-      <c r="K20" s="94"/>
-      <c r="L20" s="94"/>
-      <c r="M20" s="95"/>
+        <v>93</v>
+      </c>
+      <c r="J20" s="95" t="s">
+        <v>198</v>
+      </c>
+      <c r="K20" s="96"/>
+      <c r="L20" s="96"/>
+      <c r="M20" s="97"/>
     </row>
     <row r="21" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F21" s="36"/>
       <c r="G21" s="37"/>
       <c r="H21" s="38"/>
       <c r="I21" s="43" t="s">
-        <v>94</v>
-      </c>
-      <c r="J21" s="93" t="s">
-        <v>199</v>
-      </c>
-      <c r="K21" s="94"/>
-      <c r="L21" s="94"/>
-      <c r="M21" s="95"/>
+        <v>93</v>
+      </c>
+      <c r="J21" s="95" t="s">
+        <v>198</v>
+      </c>
+      <c r="K21" s="96"/>
+      <c r="L21" s="96"/>
+      <c r="M21" s="97"/>
     </row>
     <row r="22" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F22" s="36"/>
       <c r="G22" s="37"/>
       <c r="H22" s="38"/>
       <c r="I22" s="43" t="s">
-        <v>94</v>
-      </c>
-      <c r="J22" s="93" t="s">
-        <v>199</v>
-      </c>
-      <c r="K22" s="94"/>
-      <c r="L22" s="94"/>
-      <c r="M22" s="95"/>
+        <v>93</v>
+      </c>
+      <c r="J22" s="95" t="s">
+        <v>198</v>
+      </c>
+      <c r="K22" s="96"/>
+      <c r="L22" s="96"/>
+      <c r="M22" s="97"/>
     </row>
     <row r="23" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="20" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F23" s="93" t="s">
-        <v>200</v>
-      </c>
-      <c r="G23" s="94"/>
-      <c r="H23" s="94"/>
-      <c r="I23" s="94"/>
-      <c r="J23" s="94"/>
-      <c r="K23" s="94"/>
-      <c r="L23" s="94"/>
-      <c r="M23" s="95"/>
+        <v>55</v>
+      </c>
+      <c r="F23" s="95" t="s">
+        <v>199</v>
+      </c>
+      <c r="G23" s="96"/>
+      <c r="H23" s="96"/>
+      <c r="I23" s="96"/>
+      <c r="J23" s="96"/>
+      <c r="K23" s="96"/>
+      <c r="L23" s="96"/>
+      <c r="M23" s="97"/>
     </row>
     <row r="24" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="20" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F24" s="93" t="s">
-        <v>201</v>
-      </c>
-      <c r="G24" s="94"/>
-      <c r="H24" s="94"/>
-      <c r="I24" s="94"/>
-      <c r="J24" s="94"/>
-      <c r="K24" s="94"/>
-      <c r="L24" s="94"/>
-      <c r="M24" s="95"/>
+        <v>56</v>
+      </c>
+      <c r="F24" s="95" t="s">
+        <v>200</v>
+      </c>
+      <c r="G24" s="96"/>
+      <c r="H24" s="96"/>
+      <c r="I24" s="96"/>
+      <c r="J24" s="96"/>
+      <c r="K24" s="96"/>
+      <c r="L24" s="96"/>
+      <c r="M24" s="97"/>
     </row>
     <row r="25" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="20" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F25" s="36"/>
       <c r="G25" s="37"/>
       <c r="H25" s="37"/>
       <c r="I25" s="38"/>
-      <c r="J25" s="93" t="s">
-        <v>202</v>
-      </c>
-      <c r="K25" s="94"/>
-      <c r="L25" s="94"/>
-      <c r="M25" s="95"/>
+      <c r="J25" s="95" t="s">
+        <v>201</v>
+      </c>
+      <c r="K25" s="96"/>
+      <c r="L25" s="96"/>
+      <c r="M25" s="97"/>
     </row>
     <row r="26" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="10"/>
@@ -4653,13 +4710,13 @@
     </row>
     <row r="27" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F27" s="9"/>
       <c r="G27" s="10"/>
@@ -4672,327 +4729,327 @@
     </row>
     <row r="28" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C28" s="20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="F28" s="85" t="s">
-        <v>196</v>
-      </c>
-      <c r="G28" s="96"/>
-      <c r="H28" s="96"/>
-      <c r="I28" s="96"/>
-      <c r="J28" s="96"/>
-      <c r="K28" s="96"/>
-      <c r="L28" s="96"/>
-      <c r="M28" s="97"/>
+        <v>58</v>
+      </c>
+      <c r="F28" s="80" t="s">
+        <v>195</v>
+      </c>
+      <c r="G28" s="93"/>
+      <c r="H28" s="93"/>
+      <c r="I28" s="93"/>
+      <c r="J28" s="93"/>
+      <c r="K28" s="93"/>
+      <c r="L28" s="93"/>
+      <c r="M28" s="94"/>
     </row>
     <row r="29" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F29" s="27"/>
       <c r="G29" s="28"/>
       <c r="H29" s="28"/>
       <c r="I29" s="29"/>
-      <c r="J29" s="85" t="s">
-        <v>197</v>
-      </c>
-      <c r="K29" s="96"/>
-      <c r="L29" s="96"/>
-      <c r="M29" s="97"/>
+      <c r="J29" s="80" t="s">
+        <v>196</v>
+      </c>
+      <c r="K29" s="93"/>
+      <c r="L29" s="93"/>
+      <c r="M29" s="94"/>
     </row>
     <row r="30" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E30" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="F30" s="85" t="s">
-        <v>196</v>
-      </c>
-      <c r="G30" s="96"/>
-      <c r="H30" s="96"/>
-      <c r="I30" s="96"/>
-      <c r="J30" s="96"/>
-      <c r="K30" s="96"/>
-      <c r="L30" s="96"/>
-      <c r="M30" s="97"/>
+        <v>60</v>
+      </c>
+      <c r="F30" s="80" t="s">
+        <v>195</v>
+      </c>
+      <c r="G30" s="93"/>
+      <c r="H30" s="93"/>
+      <c r="I30" s="93"/>
+      <c r="J30" s="93"/>
+      <c r="K30" s="93"/>
+      <c r="L30" s="93"/>
+      <c r="M30" s="94"/>
     </row>
     <row r="31" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="20" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E31" s="25" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F31" s="27"/>
       <c r="G31" s="28"/>
       <c r="H31" s="28"/>
       <c r="I31" s="29"/>
-      <c r="J31" s="85" t="s">
-        <v>197</v>
-      </c>
-      <c r="K31" s="96"/>
-      <c r="L31" s="96"/>
-      <c r="M31" s="97"/>
+      <c r="J31" s="80" t="s">
+        <v>196</v>
+      </c>
+      <c r="K31" s="93"/>
+      <c r="L31" s="93"/>
+      <c r="M31" s="94"/>
     </row>
     <row r="32" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="20" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E32" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="F32" s="85" t="s">
-        <v>196</v>
-      </c>
-      <c r="G32" s="96"/>
-      <c r="H32" s="96"/>
-      <c r="I32" s="96"/>
-      <c r="J32" s="96"/>
-      <c r="K32" s="96"/>
-      <c r="L32" s="96"/>
-      <c r="M32" s="97"/>
+        <v>62</v>
+      </c>
+      <c r="F32" s="80" t="s">
+        <v>195</v>
+      </c>
+      <c r="G32" s="93"/>
+      <c r="H32" s="93"/>
+      <c r="I32" s="93"/>
+      <c r="J32" s="93"/>
+      <c r="K32" s="93"/>
+      <c r="L32" s="93"/>
+      <c r="M32" s="94"/>
     </row>
     <row r="33" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="20" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E33" s="25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F33" s="27"/>
       <c r="G33" s="28"/>
       <c r="H33" s="28"/>
       <c r="I33" s="29"/>
-      <c r="J33" s="85" t="s">
-        <v>197</v>
-      </c>
-      <c r="K33" s="96"/>
-      <c r="L33" s="96"/>
-      <c r="M33" s="97"/>
+      <c r="J33" s="80" t="s">
+        <v>196</v>
+      </c>
+      <c r="K33" s="93"/>
+      <c r="L33" s="93"/>
+      <c r="M33" s="94"/>
     </row>
     <row r="34" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="20" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E34" s="25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F34" s="27"/>
       <c r="G34" s="28"/>
       <c r="H34" s="29"/>
-      <c r="I34" s="85" t="s">
-        <v>198</v>
-      </c>
-      <c r="J34" s="96"/>
-      <c r="K34" s="96"/>
-      <c r="L34" s="96"/>
-      <c r="M34" s="97"/>
+      <c r="I34" s="80" t="s">
+        <v>197</v>
+      </c>
+      <c r="J34" s="93"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="93"/>
+      <c r="M34" s="94"/>
     </row>
     <row r="35" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="20" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E35" s="25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F35" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="G35" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="G35" s="31" t="s">
-        <v>86</v>
-      </c>
       <c r="H35" s="30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I35" s="32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J35" s="31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K35" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="L35" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="M35" s="31" t="s">
         <v>89</v>
-      </c>
-      <c r="L35" s="32" t="s">
-        <v>88</v>
-      </c>
-      <c r="M35" s="31" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="36" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C36" s="20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E36" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F36" s="27"/>
       <c r="G36" s="28"/>
       <c r="H36" s="29"/>
       <c r="I36" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="J36" s="85" t="s">
-        <v>199</v>
-      </c>
-      <c r="K36" s="96"/>
-      <c r="L36" s="96"/>
-      <c r="M36" s="97"/>
+        <v>93</v>
+      </c>
+      <c r="J36" s="80" t="s">
+        <v>198</v>
+      </c>
+      <c r="K36" s="93"/>
+      <c r="L36" s="93"/>
+      <c r="M36" s="94"/>
     </row>
     <row r="37" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="20" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E37" s="25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F37" s="27"/>
       <c r="G37" s="28"/>
       <c r="H37" s="29"/>
       <c r="I37" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="J37" s="85" t="s">
-        <v>199</v>
-      </c>
-      <c r="K37" s="96"/>
-      <c r="L37" s="96"/>
-      <c r="M37" s="97"/>
+        <v>93</v>
+      </c>
+      <c r="J37" s="80" t="s">
+        <v>198</v>
+      </c>
+      <c r="K37" s="93"/>
+      <c r="L37" s="93"/>
+      <c r="M37" s="94"/>
     </row>
     <row r="38" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E38" s="25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F38" s="27"/>
       <c r="G38" s="28"/>
       <c r="H38" s="29"/>
       <c r="I38" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="J38" s="85" t="s">
-        <v>199</v>
-      </c>
-      <c r="K38" s="96"/>
-      <c r="L38" s="96"/>
-      <c r="M38" s="97"/>
+        <v>93</v>
+      </c>
+      <c r="J38" s="80" t="s">
+        <v>198</v>
+      </c>
+      <c r="K38" s="93"/>
+      <c r="L38" s="93"/>
+      <c r="M38" s="94"/>
     </row>
     <row r="39" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="20" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E39" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="F39" s="85" t="s">
-        <v>200</v>
-      </c>
-      <c r="G39" s="96"/>
-      <c r="H39" s="96"/>
-      <c r="I39" s="96"/>
-      <c r="J39" s="96"/>
-      <c r="K39" s="96"/>
-      <c r="L39" s="96"/>
-      <c r="M39" s="97"/>
+        <v>69</v>
+      </c>
+      <c r="F39" s="80" t="s">
+        <v>199</v>
+      </c>
+      <c r="G39" s="93"/>
+      <c r="H39" s="93"/>
+      <c r="I39" s="93"/>
+      <c r="J39" s="93"/>
+      <c r="K39" s="93"/>
+      <c r="L39" s="93"/>
+      <c r="M39" s="94"/>
     </row>
     <row r="40" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="20" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E40" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="F40" s="85" t="s">
-        <v>201</v>
-      </c>
-      <c r="G40" s="96"/>
-      <c r="H40" s="96"/>
-      <c r="I40" s="96"/>
-      <c r="J40" s="96"/>
-      <c r="K40" s="96"/>
-      <c r="L40" s="96"/>
-      <c r="M40" s="97"/>
+        <v>70</v>
+      </c>
+      <c r="F40" s="80" t="s">
+        <v>200</v>
+      </c>
+      <c r="G40" s="93"/>
+      <c r="H40" s="93"/>
+      <c r="I40" s="93"/>
+      <c r="J40" s="93"/>
+      <c r="K40" s="93"/>
+      <c r="L40" s="93"/>
+      <c r="M40" s="94"/>
     </row>
     <row r="41" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="20" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E41" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F41" s="27"/>
       <c r="G41" s="28"/>
       <c r="H41" s="28"/>
       <c r="I41" s="29"/>
-      <c r="J41" s="85" t="s">
-        <v>202</v>
-      </c>
-      <c r="K41" s="96"/>
-      <c r="L41" s="96"/>
-      <c r="M41" s="97"/>
+      <c r="J41" s="80" t="s">
+        <v>201</v>
+      </c>
+      <c r="K41" s="93"/>
+      <c r="L41" s="93"/>
+      <c r="M41" s="94"/>
     </row>
     <row r="42" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="20" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E42" s="25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F42" s="27"/>
       <c r="G42" s="28"/>
@@ -5005,34 +5062,34 @@
     </row>
     <row r="43" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C43" s="20" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E43" s="25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="28"/>
       <c r="H43" s="28"/>
       <c r="I43" s="35"/>
-      <c r="J43" s="85" t="s">
-        <v>130</v>
-      </c>
-      <c r="K43" s="96"/>
-      <c r="L43" s="96"/>
-      <c r="M43" s="97"/>
+      <c r="J43" s="80" t="s">
+        <v>129</v>
+      </c>
+      <c r="K43" s="93"/>
+      <c r="L43" s="93"/>
+      <c r="M43" s="94"/>
     </row>
     <row r="44" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="21" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F44" s="9"/>
       <c r="G44" s="10"/>
@@ -5045,10 +5102,10 @@
     </row>
     <row r="45" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C45" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="8"/>
@@ -5062,10 +5119,10 @@
     </row>
     <row r="46" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C46" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
@@ -5079,10 +5136,10 @@
     </row>
     <row r="47" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C47" s="20" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
@@ -5096,10 +5153,10 @@
     </row>
     <row r="48" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C48" s="20" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -5113,10 +5170,10 @@
     </row>
     <row r="49" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C49" s="20" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -5130,10 +5187,10 @@
     </row>
     <row r="50" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C50" s="20" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
@@ -5147,10 +5204,10 @@
     </row>
     <row r="51" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C51" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
@@ -5164,10 +5221,10 @@
     </row>
     <row r="52" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C52" s="20" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -5181,10 +5238,10 @@
     </row>
     <row r="53" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C53" s="20" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
@@ -5198,10 +5255,10 @@
     </row>
     <row r="54" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C54" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
@@ -5215,10 +5272,10 @@
     </row>
     <row r="55" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C55" s="20" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
@@ -5232,10 +5289,10 @@
     </row>
     <row r="56" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C56" s="20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
@@ -5249,10 +5306,10 @@
     </row>
     <row r="57" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C57" s="20" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
@@ -5266,10 +5323,10 @@
     </row>
     <row r="58" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C58" s="20" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
@@ -5283,10 +5340,10 @@
     </row>
     <row r="59" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C59" s="20" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
@@ -5300,10 +5357,10 @@
     </row>
     <row r="60" spans="3:13" x14ac:dyDescent="0.15">
       <c r="C60" s="20" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
@@ -5317,15 +5374,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="F40:M40"/>
-    <mergeCell ref="J41:M41"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="I34:M34"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="F12:M12"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="F14:M14"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="F16:M16"/>
     <mergeCell ref="F32:M32"/>
     <mergeCell ref="I18:M18"/>
     <mergeCell ref="J20:M20"/>
@@ -5338,12 +5392,15 @@
     <mergeCell ref="J29:M29"/>
     <mergeCell ref="F30:M30"/>
     <mergeCell ref="J31:M31"/>
-    <mergeCell ref="J17:M17"/>
-    <mergeCell ref="F12:M12"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="F14:M14"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="F16:M16"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="J41:M41"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="I34:M34"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="F39:M39"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5352,9 +5409,104 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4BDE2C0-5DC7-478D-B843-6E7F3F1D9EC9}">
-  <dimension ref="A1"/>
+  <dimension ref="B1:M6"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
+  <cols>
+    <col min="5" max="5" width="20.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C5" s="24" t="s">
+        <v>396</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>398</v>
+      </c>
+      <c r="F5" s="84" t="s">
+        <v>400</v>
+      </c>
+      <c r="G5" s="85"/>
+      <c r="H5" s="85"/>
+      <c r="I5" s="85"/>
+      <c r="J5" s="85"/>
+      <c r="K5" s="85"/>
+      <c r="L5" s="85"/>
+      <c r="M5" s="86"/>
+    </row>
+    <row r="6" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C6" s="25" t="s">
+        <v>397</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>399</v>
+      </c>
+      <c r="F6" s="84" t="s">
+        <v>400</v>
+      </c>
+      <c r="G6" s="85"/>
+      <c r="H6" s="85"/>
+      <c r="I6" s="85"/>
+      <c r="J6" s="85"/>
+      <c r="K6" s="85"/>
+      <c r="L6" s="85"/>
+      <c r="M6" s="86"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="F5:M5"/>
+    <mergeCell ref="F6:M6"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5371,366 +5523,366 @@
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E2" t="s">
         <v>189</v>
-      </c>
-      <c r="E2" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="F5" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="J5" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="K5" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="L5" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="M5" s="7" t="s">
         <v>83</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="6" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C6" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="F6" s="90" t="s">
-        <v>102</v>
-      </c>
-      <c r="G6" s="91"/>
-      <c r="H6" s="91"/>
-      <c r="I6" s="91"/>
-      <c r="J6" s="91"/>
-      <c r="K6" s="91"/>
-      <c r="L6" s="91"/>
-      <c r="M6" s="92"/>
+        <v>101</v>
+      </c>
+      <c r="F6" s="84" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" s="85"/>
+      <c r="H6" s="85"/>
+      <c r="I6" s="85"/>
+      <c r="J6" s="85"/>
+      <c r="K6" s="85"/>
+      <c r="L6" s="85"/>
+      <c r="M6" s="86"/>
     </row>
     <row r="7" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C7" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="F7" s="90" t="s">
-        <v>192</v>
-      </c>
-      <c r="G7" s="91"/>
-      <c r="H7" s="91"/>
-      <c r="I7" s="91"/>
-      <c r="J7" s="91"/>
-      <c r="K7" s="91"/>
-      <c r="L7" s="91"/>
-      <c r="M7" s="92"/>
+        <v>102</v>
+      </c>
+      <c r="F7" s="84" t="s">
+        <v>191</v>
+      </c>
+      <c r="G7" s="85"/>
+      <c r="H7" s="85"/>
+      <c r="I7" s="85"/>
+      <c r="J7" s="85"/>
+      <c r="K7" s="85"/>
+      <c r="L7" s="85"/>
+      <c r="M7" s="86"/>
     </row>
     <row r="8" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F8" s="90" t="s">
-        <v>100</v>
-      </c>
-      <c r="G8" s="91"/>
-      <c r="H8" s="91"/>
-      <c r="I8" s="91"/>
-      <c r="J8" s="91"/>
-      <c r="K8" s="91"/>
-      <c r="L8" s="91"/>
-      <c r="M8" s="92"/>
+        <v>99</v>
+      </c>
+      <c r="F8" s="84" t="s">
+        <v>99</v>
+      </c>
+      <c r="G8" s="85"/>
+      <c r="H8" s="85"/>
+      <c r="I8" s="85"/>
+      <c r="J8" s="85"/>
+      <c r="K8" s="85"/>
+      <c r="L8" s="85"/>
+      <c r="M8" s="86"/>
     </row>
     <row r="9" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F9" s="90" t="s">
-        <v>193</v>
-      </c>
-      <c r="G9" s="91"/>
-      <c r="H9" s="91"/>
-      <c r="I9" s="91"/>
-      <c r="J9" s="91"/>
-      <c r="K9" s="91"/>
-      <c r="L9" s="91"/>
-      <c r="M9" s="92"/>
+        <v>100</v>
+      </c>
+      <c r="F9" s="84" t="s">
+        <v>192</v>
+      </c>
+      <c r="G9" s="85"/>
+      <c r="H9" s="85"/>
+      <c r="I9" s="85"/>
+      <c r="J9" s="85"/>
+      <c r="K9" s="85"/>
+      <c r="L9" s="85"/>
+      <c r="M9" s="86"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B19" t="s">
-        <v>44</v>
+        <v>394</v>
       </c>
     </row>
     <row r="20" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="F20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="H20" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="I20" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="J20" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="J20" s="7" t="s">
+      <c r="K20" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="K20" s="7" t="s">
+      <c r="L20" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="L20" s="7" t="s">
+      <c r="M20" s="7" t="s">
         <v>83</v>
-      </c>
-      <c r="M20" s="7" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="21" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="G21" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="G21" s="12" t="s">
+      <c r="H21" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="I21" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="J21" s="84" t="s">
         <v>118</v>
       </c>
-      <c r="J21" s="90" t="s">
-        <v>119</v>
-      </c>
-      <c r="K21" s="91"/>
-      <c r="L21" s="91"/>
-      <c r="M21" s="92"/>
+      <c r="K21" s="85"/>
+      <c r="L21" s="85"/>
+      <c r="M21" s="86"/>
     </row>
     <row r="22" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="20" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="G22" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="G22" s="12" t="s">
+      <c r="H22" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="H22" s="12" t="s">
+      <c r="I22" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="I22" s="12" t="s">
+      <c r="J22" s="84" t="s">
         <v>118</v>
       </c>
-      <c r="J22" s="90" t="s">
-        <v>119</v>
-      </c>
-      <c r="K22" s="91"/>
-      <c r="L22" s="91"/>
-      <c r="M22" s="92"/>
+      <c r="K22" s="85"/>
+      <c r="L22" s="85"/>
+      <c r="M22" s="86"/>
     </row>
     <row r="23" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E23" s="6"/>
-      <c r="F23" s="90" t="s">
+      <c r="F23" s="84" t="s">
+        <v>119</v>
+      </c>
+      <c r="G23" s="86"/>
+      <c r="H23" s="84" t="s">
         <v>120</v>
       </c>
-      <c r="G23" s="92"/>
-      <c r="H23" s="90" t="s">
-        <v>121</v>
-      </c>
-      <c r="I23" s="91"/>
-      <c r="J23" s="91"/>
-      <c r="K23" s="91"/>
-      <c r="L23" s="91"/>
-      <c r="M23" s="92"/>
+      <c r="I23" s="85"/>
+      <c r="J23" s="85"/>
+      <c r="K23" s="85"/>
+      <c r="L23" s="85"/>
+      <c r="M23" s="86"/>
     </row>
     <row r="24" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E24" s="6"/>
-      <c r="F24" s="90" t="s">
-        <v>120</v>
-      </c>
-      <c r="G24" s="92"/>
+      <c r="F24" s="84" t="s">
+        <v>119</v>
+      </c>
+      <c r="G24" s="86"/>
       <c r="H24" s="19"/>
       <c r="I24" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="K24" s="90" t="s">
         <v>122</v>
       </c>
-      <c r="L24" s="91"/>
-      <c r="M24" s="92"/>
+      <c r="K24" s="84" t="s">
+        <v>121</v>
+      </c>
+      <c r="L24" s="85"/>
+      <c r="M24" s="86"/>
     </row>
     <row r="25" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E25" s="6"/>
-      <c r="F25" s="90" t="s">
+      <c r="F25" s="84" t="s">
+        <v>124</v>
+      </c>
+      <c r="G25" s="85"/>
+      <c r="H25" s="85"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="G25" s="91"/>
-      <c r="H25" s="91"/>
-      <c r="I25" s="92"/>
-      <c r="J25" s="90" t="s">
-        <v>126</v>
-      </c>
-      <c r="K25" s="91"/>
-      <c r="L25" s="91"/>
-      <c r="M25" s="92"/>
+      <c r="K25" s="85"/>
+      <c r="L25" s="85"/>
+      <c r="M25" s="86"/>
     </row>
     <row r="26" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E26" s="6"/>
-      <c r="F26" s="90" t="s">
+      <c r="F26" s="84" t="s">
+        <v>124</v>
+      </c>
+      <c r="G26" s="85"/>
+      <c r="H26" s="85"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="G26" s="91"/>
-      <c r="H26" s="91"/>
-      <c r="I26" s="92"/>
-      <c r="J26" s="90" t="s">
-        <v>126</v>
-      </c>
-      <c r="K26" s="91"/>
-      <c r="L26" s="91"/>
-      <c r="M26" s="92"/>
+      <c r="K26" s="85"/>
+      <c r="L26" s="85"/>
+      <c r="M26" s="86"/>
     </row>
     <row r="27" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="20" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E27" s="6"/>
-      <c r="F27" s="90" t="s">
+      <c r="F27" s="84" t="s">
+        <v>126</v>
+      </c>
+      <c r="G27" s="85"/>
+      <c r="H27" s="85"/>
+      <c r="I27" s="86"/>
+      <c r="J27" s="84" t="s">
         <v>127</v>
       </c>
-      <c r="G27" s="91"/>
-      <c r="H27" s="91"/>
-      <c r="I27" s="92"/>
-      <c r="J27" s="90" t="s">
-        <v>128</v>
-      </c>
-      <c r="K27" s="91"/>
-      <c r="L27" s="91"/>
-      <c r="M27" s="92"/>
+      <c r="K27" s="85"/>
+      <c r="L27" s="85"/>
+      <c r="M27" s="86"/>
     </row>
     <row r="28" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C28" s="20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E28" s="6"/>
-      <c r="F28" s="90" t="s">
+      <c r="F28" s="84" t="s">
+        <v>126</v>
+      </c>
+      <c r="G28" s="85"/>
+      <c r="H28" s="85"/>
+      <c r="I28" s="86"/>
+      <c r="J28" s="84" t="s">
         <v>127</v>
       </c>
-      <c r="G28" s="91"/>
-      <c r="H28" s="91"/>
-      <c r="I28" s="92"/>
-      <c r="J28" s="90" t="s">
-        <v>128</v>
-      </c>
-      <c r="K28" s="91"/>
-      <c r="L28" s="91"/>
-      <c r="M28" s="92"/>
+      <c r="K28" s="85"/>
+      <c r="L28" s="85"/>
+      <c r="M28" s="86"/>
     </row>
     <row r="29" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E29" s="6"/>
       <c r="F29" s="9"/>
@@ -5744,227 +5896,227 @@
     </row>
     <row r="30" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="15"/>
       <c r="G30" s="16"/>
       <c r="H30" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="I30" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="I30" s="18" t="s">
+      <c r="J30" s="18" t="s">
         <v>112</v>
-      </c>
-      <c r="J30" s="18" t="s">
-        <v>113</v>
       </c>
       <c r="K30" s="15"/>
       <c r="L30" s="16"/>
       <c r="M30" s="18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F31" s="90" t="s">
-        <v>155</v>
-      </c>
-      <c r="G31" s="91"/>
-      <c r="H31" s="91"/>
-      <c r="I31" s="91"/>
-      <c r="J31" s="91"/>
-      <c r="K31" s="91"/>
-      <c r="L31" s="91"/>
-      <c r="M31" s="92"/>
+        <v>109</v>
+      </c>
+      <c r="F31" s="84" t="s">
+        <v>154</v>
+      </c>
+      <c r="G31" s="85"/>
+      <c r="H31" s="85"/>
+      <c r="I31" s="85"/>
+      <c r="J31" s="85"/>
+      <c r="K31" s="85"/>
+      <c r="L31" s="85"/>
+      <c r="M31" s="86"/>
     </row>
     <row r="32" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E32" s="6"/>
-      <c r="F32" s="90" t="s">
-        <v>155</v>
-      </c>
-      <c r="G32" s="91"/>
-      <c r="H32" s="91"/>
-      <c r="I32" s="91"/>
-      <c r="J32" s="91"/>
-      <c r="K32" s="91"/>
-      <c r="L32" s="91"/>
-      <c r="M32" s="92"/>
+      <c r="F32" s="84" t="s">
+        <v>154</v>
+      </c>
+      <c r="G32" s="85"/>
+      <c r="H32" s="85"/>
+      <c r="I32" s="85"/>
+      <c r="J32" s="85"/>
+      <c r="K32" s="85"/>
+      <c r="L32" s="85"/>
+      <c r="M32" s="86"/>
     </row>
     <row r="33" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E33" s="6"/>
-      <c r="F33" s="90" t="s">
-        <v>155</v>
-      </c>
-      <c r="G33" s="91"/>
-      <c r="H33" s="91"/>
-      <c r="I33" s="91"/>
-      <c r="J33" s="91"/>
-      <c r="K33" s="91"/>
-      <c r="L33" s="91"/>
-      <c r="M33" s="92"/>
+      <c r="F33" s="84" t="s">
+        <v>154</v>
+      </c>
+      <c r="G33" s="85"/>
+      <c r="H33" s="85"/>
+      <c r="I33" s="85"/>
+      <c r="J33" s="85"/>
+      <c r="K33" s="85"/>
+      <c r="L33" s="85"/>
+      <c r="M33" s="86"/>
     </row>
     <row r="34" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E34" s="6"/>
-      <c r="F34" s="90" t="s">
-        <v>155</v>
-      </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="91"/>
-      <c r="J34" s="91"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="91"/>
-      <c r="M34" s="92"/>
+      <c r="F34" s="84" t="s">
+        <v>154</v>
+      </c>
+      <c r="G34" s="85"/>
+      <c r="H34" s="85"/>
+      <c r="I34" s="85"/>
+      <c r="J34" s="85"/>
+      <c r="K34" s="85"/>
+      <c r="L34" s="85"/>
+      <c r="M34" s="86"/>
     </row>
     <row r="35" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="20" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E35" s="6"/>
-      <c r="F35" s="90" t="s">
-        <v>155</v>
-      </c>
-      <c r="G35" s="91"/>
-      <c r="H35" s="91"/>
-      <c r="I35" s="91"/>
-      <c r="J35" s="91"/>
-      <c r="K35" s="91"/>
-      <c r="L35" s="91"/>
-      <c r="M35" s="92"/>
+      <c r="F35" s="84" t="s">
+        <v>154</v>
+      </c>
+      <c r="G35" s="85"/>
+      <c r="H35" s="85"/>
+      <c r="I35" s="85"/>
+      <c r="J35" s="85"/>
+      <c r="K35" s="85"/>
+      <c r="L35" s="85"/>
+      <c r="M35" s="86"/>
     </row>
     <row r="36" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C36" s="20" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E36" s="6"/>
-      <c r="F36" s="90" t="s">
-        <v>155</v>
-      </c>
-      <c r="G36" s="91"/>
-      <c r="H36" s="91"/>
-      <c r="I36" s="91"/>
-      <c r="J36" s="91"/>
-      <c r="K36" s="91"/>
-      <c r="L36" s="91"/>
-      <c r="M36" s="92"/>
+      <c r="F36" s="84" t="s">
+        <v>154</v>
+      </c>
+      <c r="G36" s="85"/>
+      <c r="H36" s="85"/>
+      <c r="I36" s="85"/>
+      <c r="J36" s="85"/>
+      <c r="K36" s="85"/>
+      <c r="L36" s="85"/>
+      <c r="M36" s="86"/>
     </row>
     <row r="37" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="20" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E37" s="1"/>
-      <c r="F37" s="90" t="s">
-        <v>155</v>
-      </c>
-      <c r="G37" s="91"/>
-      <c r="H37" s="91"/>
-      <c r="I37" s="91"/>
-      <c r="J37" s="91"/>
-      <c r="K37" s="91"/>
-      <c r="L37" s="91"/>
-      <c r="M37" s="92"/>
+      <c r="F37" s="84" t="s">
+        <v>154</v>
+      </c>
+      <c r="G37" s="85"/>
+      <c r="H37" s="85"/>
+      <c r="I37" s="85"/>
+      <c r="J37" s="85"/>
+      <c r="K37" s="85"/>
+      <c r="L37" s="85"/>
+      <c r="M37" s="86"/>
     </row>
     <row r="38" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="20" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E38" s="1"/>
-      <c r="F38" s="90" t="s">
-        <v>155</v>
-      </c>
-      <c r="G38" s="91"/>
-      <c r="H38" s="91"/>
-      <c r="I38" s="91"/>
-      <c r="J38" s="91"/>
-      <c r="K38" s="91"/>
-      <c r="L38" s="91"/>
-      <c r="M38" s="92"/>
+      <c r="F38" s="84" t="s">
+        <v>154</v>
+      </c>
+      <c r="G38" s="85"/>
+      <c r="H38" s="85"/>
+      <c r="I38" s="85"/>
+      <c r="J38" s="85"/>
+      <c r="K38" s="85"/>
+      <c r="L38" s="85"/>
+      <c r="M38" s="86"/>
     </row>
     <row r="39" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="20" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E39" s="1"/>
-      <c r="F39" s="90" t="s">
-        <v>155</v>
-      </c>
-      <c r="G39" s="91"/>
-      <c r="H39" s="91"/>
-      <c r="I39" s="91"/>
-      <c r="J39" s="91"/>
-      <c r="K39" s="91"/>
-      <c r="L39" s="91"/>
-      <c r="M39" s="92"/>
+      <c r="F39" s="84" t="s">
+        <v>154</v>
+      </c>
+      <c r="G39" s="85"/>
+      <c r="H39" s="85"/>
+      <c r="I39" s="85"/>
+      <c r="J39" s="85"/>
+      <c r="K39" s="85"/>
+      <c r="L39" s="85"/>
+      <c r="M39" s="86"/>
     </row>
     <row r="40" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E40" s="1"/>
-      <c r="F40" s="90" t="s">
-        <v>155</v>
-      </c>
-      <c r="G40" s="91"/>
-      <c r="H40" s="91"/>
-      <c r="I40" s="91"/>
-      <c r="J40" s="91"/>
-      <c r="K40" s="91"/>
-      <c r="L40" s="91"/>
-      <c r="M40" s="92"/>
+      <c r="F40" s="84" t="s">
+        <v>154</v>
+      </c>
+      <c r="G40" s="85"/>
+      <c r="H40" s="85"/>
+      <c r="I40" s="85"/>
+      <c r="J40" s="85"/>
+      <c r="K40" s="85"/>
+      <c r="L40" s="85"/>
+      <c r="M40" s="86"/>
     </row>
     <row r="41" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="9"/>
@@ -5978,235 +6130,235 @@
     </row>
     <row r="42" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="20" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="9"/>
       <c r="G42" s="11"/>
       <c r="H42" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="I42" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="I42" s="12" t="s">
+      <c r="J42" s="84" t="s">
         <v>153</v>
       </c>
-      <c r="J42" s="90" t="s">
+      <c r="K42" s="85"/>
+      <c r="L42" s="86"/>
+      <c r="M42" s="14" t="s">
         <v>154</v>
-      </c>
-      <c r="K42" s="91"/>
-      <c r="L42" s="92"/>
-      <c r="M42" s="14" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="43" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C43" s="20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="9"/>
       <c r="G43" s="11"/>
       <c r="H43" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="I43" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="I43" s="12" t="s">
+      <c r="J43" s="84" t="s">
         <v>153</v>
       </c>
-      <c r="J43" s="90" t="s">
+      <c r="K43" s="85"/>
+      <c r="L43" s="86"/>
+      <c r="M43" s="14" t="s">
         <v>154</v>
-      </c>
-      <c r="K43" s="91"/>
-      <c r="L43" s="92"/>
-      <c r="M43" s="14" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="44" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="9"/>
       <c r="G44" s="11"/>
       <c r="H44" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="I44" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="I44" s="12" t="s">
+      <c r="J44" s="84" t="s">
         <v>153</v>
       </c>
-      <c r="J44" s="90" t="s">
+      <c r="K44" s="85"/>
+      <c r="L44" s="86"/>
+      <c r="M44" s="14" t="s">
         <v>154</v>
-      </c>
-      <c r="K44" s="91"/>
-      <c r="L44" s="92"/>
-      <c r="M44" s="14" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="45" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C45" s="20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="9"/>
       <c r="G45" s="11"/>
       <c r="H45" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="I45" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="I45" s="12" t="s">
+      <c r="J45" s="84" t="s">
         <v>153</v>
       </c>
-      <c r="J45" s="90" t="s">
+      <c r="K45" s="85"/>
+      <c r="L45" s="86"/>
+      <c r="M45" s="14" t="s">
         <v>154</v>
-      </c>
-      <c r="K45" s="91"/>
-      <c r="L45" s="92"/>
-      <c r="M45" s="14" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="46" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="9"/>
       <c r="G46" s="11"/>
       <c r="H46" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="I46" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="I46" s="12" t="s">
+      <c r="J46" s="84" t="s">
         <v>153</v>
       </c>
-      <c r="J46" s="90" t="s">
+      <c r="K46" s="85"/>
+      <c r="L46" s="86"/>
+      <c r="M46" s="14" t="s">
         <v>154</v>
-      </c>
-      <c r="K46" s="91"/>
-      <c r="L46" s="92"/>
-      <c r="M46" s="14" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="47" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="9"/>
       <c r="G47" s="11"/>
       <c r="H47" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="I47" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="I47" s="12" t="s">
+      <c r="J47" s="84" t="s">
         <v>153</v>
       </c>
-      <c r="J47" s="90" t="s">
+      <c r="K47" s="85"/>
+      <c r="L47" s="86"/>
+      <c r="M47" s="14" t="s">
         <v>154</v>
-      </c>
-      <c r="K47" s="91"/>
-      <c r="L47" s="92"/>
-      <c r="M47" s="14" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="48" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="9"/>
       <c r="G48" s="11"/>
       <c r="H48" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="I48" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="I48" s="12" t="s">
+      <c r="J48" s="84" t="s">
         <v>153</v>
       </c>
-      <c r="J48" s="90" t="s">
+      <c r="K48" s="85"/>
+      <c r="L48" s="86"/>
+      <c r="M48" s="14" t="s">
         <v>154</v>
-      </c>
-      <c r="K48" s="91"/>
-      <c r="L48" s="92"/>
-      <c r="M48" s="14" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="49" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="9"/>
       <c r="G49" s="11"/>
       <c r="H49" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="I49" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="I49" s="12" t="s">
+      <c r="J49" s="84" t="s">
         <v>153</v>
       </c>
-      <c r="J49" s="90" t="s">
+      <c r="K49" s="85"/>
+      <c r="L49" s="86"/>
+      <c r="M49" s="14" t="s">
         <v>154</v>
-      </c>
-      <c r="K49" s="91"/>
-      <c r="L49" s="92"/>
-      <c r="M49" s="14" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="50" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C50" s="20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="9"/>
       <c r="G50" s="11"/>
       <c r="H50" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="I50" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="I50" s="12" t="s">
+      <c r="J50" s="84" t="s">
         <v>153</v>
       </c>
-      <c r="J50" s="90" t="s">
+      <c r="K50" s="85"/>
+      <c r="L50" s="86"/>
+      <c r="M50" s="14" t="s">
         <v>154</v>
-      </c>
-      <c r="K50" s="91"/>
-      <c r="L50" s="92"/>
-      <c r="M50" s="14" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="51" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C51" s="20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="9"/>
@@ -6220,199 +6372,199 @@
     </row>
     <row r="52" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E52" s="1"/>
-      <c r="F52" s="90" t="s">
+      <c r="F52" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="G52" s="85"/>
+      <c r="H52" s="85"/>
+      <c r="I52" s="86"/>
+      <c r="J52" s="84" t="s">
         <v>176</v>
       </c>
-      <c r="G52" s="91"/>
-      <c r="H52" s="91"/>
-      <c r="I52" s="92"/>
-      <c r="J52" s="90" t="s">
-        <v>177</v>
-      </c>
-      <c r="K52" s="91"/>
-      <c r="L52" s="91"/>
-      <c r="M52" s="92"/>
+      <c r="K52" s="85"/>
+      <c r="L52" s="85"/>
+      <c r="M52" s="86"/>
     </row>
     <row r="53" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="21" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E53" s="13"/>
-      <c r="F53" s="90" t="s">
+      <c r="F53" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="G53" s="85"/>
+      <c r="H53" s="85"/>
+      <c r="I53" s="86"/>
+      <c r="J53" s="84" t="s">
         <v>176</v>
       </c>
-      <c r="G53" s="91"/>
-      <c r="H53" s="91"/>
-      <c r="I53" s="92"/>
-      <c r="J53" s="90" t="s">
-        <v>177</v>
-      </c>
-      <c r="K53" s="91"/>
-      <c r="L53" s="91"/>
-      <c r="M53" s="92"/>
+      <c r="K53" s="85"/>
+      <c r="L53" s="85"/>
+      <c r="M53" s="86"/>
     </row>
     <row r="54" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="20" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E54" s="1"/>
-      <c r="F54" s="90" t="s">
+      <c r="F54" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="G54" s="85"/>
+      <c r="H54" s="85"/>
+      <c r="I54" s="86"/>
+      <c r="J54" s="84" t="s">
         <v>176</v>
       </c>
-      <c r="G54" s="91"/>
-      <c r="H54" s="91"/>
-      <c r="I54" s="92"/>
-      <c r="J54" s="90" t="s">
-        <v>177</v>
-      </c>
-      <c r="K54" s="91"/>
-      <c r="L54" s="91"/>
-      <c r="M54" s="92"/>
+      <c r="K54" s="85"/>
+      <c r="L54" s="85"/>
+      <c r="M54" s="86"/>
     </row>
     <row r="55" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C55" s="20" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E55" s="1"/>
-      <c r="F55" s="90" t="s">
+      <c r="F55" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="G55" s="85"/>
+      <c r="H55" s="85"/>
+      <c r="I55" s="86"/>
+      <c r="J55" s="84" t="s">
         <v>176</v>
       </c>
-      <c r="G55" s="91"/>
-      <c r="H55" s="91"/>
-      <c r="I55" s="92"/>
-      <c r="J55" s="90" t="s">
-        <v>177</v>
-      </c>
-      <c r="K55" s="91"/>
-      <c r="L55" s="91"/>
-      <c r="M55" s="92"/>
+      <c r="K55" s="85"/>
+      <c r="L55" s="85"/>
+      <c r="M55" s="86"/>
     </row>
     <row r="56" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E56" s="1"/>
-      <c r="F56" s="90" t="s">
+      <c r="F56" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="G56" s="85"/>
+      <c r="H56" s="85"/>
+      <c r="I56" s="86"/>
+      <c r="J56" s="84" t="s">
         <v>176</v>
       </c>
-      <c r="G56" s="91"/>
-      <c r="H56" s="91"/>
-      <c r="I56" s="92"/>
-      <c r="J56" s="90" t="s">
-        <v>177</v>
-      </c>
-      <c r="K56" s="91"/>
-      <c r="L56" s="91"/>
-      <c r="M56" s="92"/>
+      <c r="K56" s="85"/>
+      <c r="L56" s="85"/>
+      <c r="M56" s="86"/>
     </row>
     <row r="57" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C57" s="20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E57" s="1"/>
-      <c r="F57" s="90" t="s">
+      <c r="F57" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="G57" s="85"/>
+      <c r="H57" s="85"/>
+      <c r="I57" s="86"/>
+      <c r="J57" s="84" t="s">
         <v>176</v>
       </c>
-      <c r="G57" s="91"/>
-      <c r="H57" s="91"/>
-      <c r="I57" s="92"/>
-      <c r="J57" s="90" t="s">
-        <v>177</v>
-      </c>
-      <c r="K57" s="91"/>
-      <c r="L57" s="91"/>
-      <c r="M57" s="92"/>
+      <c r="K57" s="85"/>
+      <c r="L57" s="85"/>
+      <c r="M57" s="86"/>
     </row>
     <row r="58" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C58" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E58" s="1"/>
-      <c r="F58" s="90" t="s">
+      <c r="F58" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="G58" s="85"/>
+      <c r="H58" s="85"/>
+      <c r="I58" s="86"/>
+      <c r="J58" s="84" t="s">
         <v>176</v>
       </c>
-      <c r="G58" s="91"/>
-      <c r="H58" s="91"/>
-      <c r="I58" s="92"/>
-      <c r="J58" s="90" t="s">
-        <v>177</v>
-      </c>
-      <c r="K58" s="91"/>
-      <c r="L58" s="91"/>
-      <c r="M58" s="92"/>
+      <c r="K58" s="85"/>
+      <c r="L58" s="85"/>
+      <c r="M58" s="86"/>
     </row>
     <row r="59" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C59" s="20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E59" s="1"/>
-      <c r="F59" s="90" t="s">
+      <c r="F59" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="G59" s="85"/>
+      <c r="H59" s="85"/>
+      <c r="I59" s="86"/>
+      <c r="J59" s="84" t="s">
         <v>176</v>
       </c>
-      <c r="G59" s="91"/>
-      <c r="H59" s="91"/>
-      <c r="I59" s="92"/>
-      <c r="J59" s="90" t="s">
-        <v>177</v>
-      </c>
-      <c r="K59" s="91"/>
-      <c r="L59" s="91"/>
-      <c r="M59" s="92"/>
+      <c r="K59" s="85"/>
+      <c r="L59" s="85"/>
+      <c r="M59" s="86"/>
     </row>
     <row r="60" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C60" s="20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E60" s="1"/>
-      <c r="F60" s="90" t="s">
+      <c r="F60" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="G60" s="85"/>
+      <c r="H60" s="85"/>
+      <c r="I60" s="86"/>
+      <c r="J60" s="84" t="s">
         <v>176</v>
       </c>
-      <c r="G60" s="91"/>
-      <c r="H60" s="91"/>
-      <c r="I60" s="92"/>
-      <c r="J60" s="90" t="s">
-        <v>177</v>
-      </c>
-      <c r="K60" s="91"/>
-      <c r="L60" s="91"/>
-      <c r="M60" s="92"/>
+      <c r="K60" s="85"/>
+      <c r="L60" s="85"/>
+      <c r="M60" s="86"/>
     </row>
     <row r="61" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C61" s="20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="9"/>
@@ -6426,13 +6578,13 @@
     </row>
     <row r="62" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C62" s="20" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E62" s="22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F62" s="9"/>
       <c r="G62" s="10"/>
@@ -6440,20 +6592,20 @@
       <c r="I62" s="10"/>
       <c r="J62" s="10"/>
       <c r="K62" s="11"/>
-      <c r="L62" s="85" t="s">
-        <v>188</v>
-      </c>
-      <c r="M62" s="87"/>
+      <c r="L62" s="80" t="s">
+        <v>187</v>
+      </c>
+      <c r="M62" s="82"/>
     </row>
     <row r="63" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C63" s="20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E63" s="23" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F63" s="9"/>
       <c r="G63" s="10"/>
@@ -6461,20 +6613,20 @@
       <c r="I63" s="10"/>
       <c r="J63" s="10"/>
       <c r="K63" s="11"/>
-      <c r="L63" s="89" t="s">
-        <v>188</v>
-      </c>
-      <c r="M63" s="87"/>
+      <c r="L63" s="83" t="s">
+        <v>187</v>
+      </c>
+      <c r="M63" s="82"/>
     </row>
     <row r="64" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C64" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E64" s="23" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F64" s="9"/>
       <c r="G64" s="10"/>
@@ -6482,20 +6634,20 @@
       <c r="I64" s="10"/>
       <c r="J64" s="10"/>
       <c r="K64" s="11"/>
-      <c r="L64" s="89" t="s">
-        <v>188</v>
-      </c>
-      <c r="M64" s="87"/>
+      <c r="L64" s="83" t="s">
+        <v>187</v>
+      </c>
+      <c r="M64" s="82"/>
     </row>
     <row r="65" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C65" s="20" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E65" s="23" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F65" s="9"/>
       <c r="G65" s="10"/>
@@ -6503,20 +6655,20 @@
       <c r="I65" s="10"/>
       <c r="J65" s="10"/>
       <c r="K65" s="11"/>
-      <c r="L65" s="89" t="s">
-        <v>188</v>
-      </c>
-      <c r="M65" s="87"/>
+      <c r="L65" s="83" t="s">
+        <v>187</v>
+      </c>
+      <c r="M65" s="82"/>
     </row>
     <row r="66" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C66" s="20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E66" s="23" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F66" s="9"/>
       <c r="G66" s="10"/>
@@ -6524,20 +6676,20 @@
       <c r="I66" s="10"/>
       <c r="J66" s="10"/>
       <c r="K66" s="11"/>
-      <c r="L66" s="89" t="s">
-        <v>188</v>
-      </c>
-      <c r="M66" s="87"/>
+      <c r="L66" s="83" t="s">
+        <v>187</v>
+      </c>
+      <c r="M66" s="82"/>
     </row>
     <row r="67" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C67" s="20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E67" s="23" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F67" s="9"/>
       <c r="G67" s="10"/>
@@ -6545,20 +6697,20 @@
       <c r="I67" s="10"/>
       <c r="J67" s="10"/>
       <c r="K67" s="11"/>
-      <c r="L67" s="89" t="s">
-        <v>188</v>
-      </c>
-      <c r="M67" s="87"/>
+      <c r="L67" s="83" t="s">
+        <v>187</v>
+      </c>
+      <c r="M67" s="82"/>
     </row>
     <row r="68" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C68" s="20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E68" s="23" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F68" s="9"/>
       <c r="G68" s="10"/>
@@ -6566,20 +6718,20 @@
       <c r="I68" s="10"/>
       <c r="J68" s="10"/>
       <c r="K68" s="11"/>
-      <c r="L68" s="89" t="s">
-        <v>188</v>
-      </c>
-      <c r="M68" s="87"/>
+      <c r="L68" s="83" t="s">
+        <v>187</v>
+      </c>
+      <c r="M68" s="82"/>
     </row>
     <row r="69" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C69" s="20" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E69" s="23" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F69" s="9"/>
       <c r="G69" s="10"/>
@@ -6587,20 +6739,20 @@
       <c r="I69" s="10"/>
       <c r="J69" s="10"/>
       <c r="K69" s="11"/>
-      <c r="L69" s="89" t="s">
-        <v>188</v>
-      </c>
-      <c r="M69" s="87"/>
+      <c r="L69" s="83" t="s">
+        <v>187</v>
+      </c>
+      <c r="M69" s="82"/>
     </row>
     <row r="70" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C70" s="20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E70" s="23" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F70" s="9"/>
       <c r="G70" s="10"/>
@@ -6608,17 +6760,17 @@
       <c r="I70" s="10"/>
       <c r="J70" s="10"/>
       <c r="K70" s="11"/>
-      <c r="L70" s="89" t="s">
-        <v>188</v>
-      </c>
-      <c r="M70" s="87"/>
+      <c r="L70" s="83" t="s">
+        <v>187</v>
+      </c>
+      <c r="M70" s="82"/>
     </row>
     <row r="71" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C71" s="20" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="9"/>
@@ -6632,6 +6784,54 @@
     </row>
   </sheetData>
   <mergeCells count="64">
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F34:M34"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="F28:I28"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="F31:M31"/>
+    <mergeCell ref="F32:M32"/>
+    <mergeCell ref="F33:M33"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="F35:M35"/>
+    <mergeCell ref="F36:M36"/>
+    <mergeCell ref="F37:M37"/>
+    <mergeCell ref="F38:M38"/>
+    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="J56:M56"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="J52:M52"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="J53:M53"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="L69:M69"/>
+    <mergeCell ref="L70:M70"/>
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="J60:M60"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="L64:M64"/>
+    <mergeCell ref="L65:M65"/>
     <mergeCell ref="F6:M6"/>
     <mergeCell ref="F7:M7"/>
     <mergeCell ref="F8:M8"/>
@@ -6648,54 +6848,6 @@
     <mergeCell ref="F55:I55"/>
     <mergeCell ref="J55:M55"/>
     <mergeCell ref="F56:I56"/>
-    <mergeCell ref="L67:M67"/>
-    <mergeCell ref="L68:M68"/>
-    <mergeCell ref="L69:M69"/>
-    <mergeCell ref="L70:M70"/>
-    <mergeCell ref="F60:I60"/>
-    <mergeCell ref="J60:M60"/>
-    <mergeCell ref="L62:M62"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="L64:M64"/>
-    <mergeCell ref="L65:M65"/>
-    <mergeCell ref="J56:M56"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="J52:M52"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="J53:M53"/>
-    <mergeCell ref="J47:L47"/>
-    <mergeCell ref="F35:M35"/>
-    <mergeCell ref="F36:M36"/>
-    <mergeCell ref="F37:M37"/>
-    <mergeCell ref="F38:M38"/>
-    <mergeCell ref="F39:M39"/>
-    <mergeCell ref="F40:M40"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="J44:L44"/>
-    <mergeCell ref="J45:L45"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="F34:M34"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="F28:I28"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="F31:M31"/>
-    <mergeCell ref="F32:M32"/>
-    <mergeCell ref="F33:M33"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="F24:G24"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6717,1068 +6869,1063 @@
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C6" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C7" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C8" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C9" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>34</v>
-      </c>
       <c r="F12" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="H12" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="I12" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="J12" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="K12" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="K12" s="7" t="s">
+      <c r="L12" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="M12" s="7" t="s">
         <v>83</v>
-      </c>
-      <c r="M12" s="7" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="13" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="62" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D13" s="63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E13" s="65" t="s">
-        <v>239</v>
-      </c>
-      <c r="F13" s="98"/>
-      <c r="G13" s="99"/>
-      <c r="H13" s="99"/>
-      <c r="I13" s="99"/>
-      <c r="J13" s="99"/>
-      <c r="K13" s="99"/>
-      <c r="L13" s="99"/>
-      <c r="M13" s="100"/>
+        <v>238</v>
+      </c>
+      <c r="F13" s="104"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="105"/>
+      <c r="I13" s="105"/>
+      <c r="J13" s="105"/>
+      <c r="K13" s="105"/>
+      <c r="L13" s="105"/>
+      <c r="M13" s="106"/>
     </row>
     <row r="14" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="20" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E14" s="45" t="s">
-        <v>129</v>
-      </c>
-      <c r="F14" s="73" t="s">
-        <v>129</v>
-      </c>
-      <c r="G14" s="74"/>
-      <c r="H14" s="74"/>
-      <c r="I14" s="74"/>
-      <c r="J14" s="74"/>
-      <c r="K14" s="74"/>
-      <c r="L14" s="74"/>
-      <c r="M14" s="75"/>
+        <v>128</v>
+      </c>
+      <c r="F14" s="76" t="s">
+        <v>128</v>
+      </c>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="77"/>
+      <c r="K14" s="77"/>
+      <c r="L14" s="77"/>
+      <c r="M14" s="78"/>
     </row>
     <row r="15" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E15" s="45" t="s">
-        <v>240</v>
-      </c>
-      <c r="F15" s="73" t="s">
-        <v>240</v>
-      </c>
-      <c r="G15" s="74"/>
-      <c r="H15" s="74"/>
-      <c r="I15" s="74"/>
-      <c r="J15" s="74"/>
-      <c r="K15" s="74"/>
-      <c r="L15" s="74"/>
-      <c r="M15" s="75"/>
+        <v>239</v>
+      </c>
+      <c r="F15" s="76" t="s">
+        <v>239</v>
+      </c>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="77"/>
+      <c r="K15" s="77"/>
+      <c r="L15" s="77"/>
+      <c r="M15" s="78"/>
     </row>
     <row r="16" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>241</v>
-      </c>
-      <c r="F16" s="73" t="s">
-        <v>241</v>
-      </c>
-      <c r="G16" s="74"/>
-      <c r="H16" s="74"/>
-      <c r="I16" s="74"/>
-      <c r="J16" s="74"/>
-      <c r="K16" s="74"/>
-      <c r="L16" s="74"/>
-      <c r="M16" s="75"/>
+        <v>240</v>
+      </c>
+      <c r="F16" s="76" t="s">
+        <v>240</v>
+      </c>
+      <c r="G16" s="77"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="77"/>
+      <c r="K16" s="77"/>
+      <c r="L16" s="77"/>
+      <c r="M16" s="78"/>
     </row>
     <row r="17" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E17" s="45" t="s">
+        <v>376</v>
+      </c>
+      <c r="F17" s="47" t="s">
+        <v>241</v>
+      </c>
+      <c r="G17" s="47" t="s">
+        <v>242</v>
+      </c>
+      <c r="H17" s="47" t="s">
+        <v>243</v>
+      </c>
+      <c r="I17" s="57" t="s">
         <v>377</v>
       </c>
-      <c r="F17" s="47" t="s">
-        <v>242</v>
-      </c>
-      <c r="G17" s="47" t="s">
-        <v>243</v>
-      </c>
-      <c r="H17" s="47" t="s">
-        <v>244</v>
-      </c>
-      <c r="I17" s="57" t="s">
+      <c r="J17" s="57" t="s">
         <v>378</v>
-      </c>
-      <c r="J17" s="57" t="s">
-        <v>379</v>
       </c>
       <c r="K17" s="46"/>
       <c r="L17" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="M17" s="47" t="s">
         <v>245</v>
-      </c>
-      <c r="M17" s="47" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="18" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="62" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D18" s="63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E18" s="65"/>
-      <c r="F18" s="101" t="s">
-        <v>247</v>
-      </c>
-      <c r="G18" s="102"/>
-      <c r="H18" s="102"/>
-      <c r="I18" s="102"/>
-      <c r="J18" s="102"/>
-      <c r="K18" s="102"/>
-      <c r="L18" s="102"/>
-      <c r="M18" s="103"/>
+      <c r="F18" s="107" t="s">
+        <v>246</v>
+      </c>
+      <c r="G18" s="108"/>
+      <c r="H18" s="108"/>
+      <c r="I18" s="108"/>
+      <c r="J18" s="108"/>
+      <c r="K18" s="108"/>
+      <c r="L18" s="108"/>
+      <c r="M18" s="109"/>
       <c r="N18" s="59" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="19" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="62" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D19" s="63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E19" s="65"/>
-      <c r="F19" s="101" t="s">
-        <v>248</v>
-      </c>
-      <c r="G19" s="102"/>
-      <c r="H19" s="102"/>
-      <c r="I19" s="102"/>
-      <c r="J19" s="102"/>
-      <c r="K19" s="102"/>
-      <c r="L19" s="102"/>
-      <c r="M19" s="103"/>
+      <c r="F19" s="107" t="s">
+        <v>247</v>
+      </c>
+      <c r="G19" s="108"/>
+      <c r="H19" s="108"/>
+      <c r="I19" s="108"/>
+      <c r="J19" s="108"/>
+      <c r="K19" s="108"/>
+      <c r="L19" s="108"/>
+      <c r="M19" s="109"/>
       <c r="N19" s="59" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="20" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E20" s="45"/>
       <c r="F20" s="57" t="s">
+        <v>248</v>
+      </c>
+      <c r="G20" s="57" t="s">
         <v>249</v>
       </c>
-      <c r="G20" s="57" t="s">
+      <c r="H20" s="57" t="s">
         <v>250</v>
       </c>
-      <c r="H20" s="57" t="s">
+      <c r="I20" s="57" t="s">
         <v>251</v>
       </c>
-      <c r="I20" s="57" t="s">
+      <c r="J20" s="58" t="s">
         <v>252</v>
       </c>
-      <c r="J20" s="58" t="s">
+      <c r="K20" s="104"/>
+      <c r="L20" s="106"/>
+      <c r="M20" s="57" t="s">
         <v>253</v>
       </c>
-      <c r="K20" s="98"/>
-      <c r="L20" s="100"/>
-      <c r="M20" s="57" t="s">
-        <v>254</v>
-      </c>
       <c r="N20" s="60" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="21" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E21" s="45"/>
       <c r="F21" s="47" t="s">
+        <v>254</v>
+      </c>
+      <c r="G21" s="47" t="s">
         <v>255</v>
       </c>
-      <c r="G21" s="47" t="s">
+      <c r="H21" s="104"/>
+      <c r="I21" s="106"/>
+      <c r="J21" s="58" t="s">
         <v>256</v>
       </c>
-      <c r="H21" s="98"/>
-      <c r="I21" s="100"/>
-      <c r="J21" s="58" t="s">
+      <c r="K21" s="58" t="s">
         <v>257</v>
       </c>
-      <c r="K21" s="58" t="s">
+      <c r="L21" s="58" t="s">
         <v>258</v>
       </c>
-      <c r="L21" s="58" t="s">
+      <c r="M21" s="58" t="s">
         <v>259</v>
-      </c>
-      <c r="M21" s="58" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="22" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E22" s="45"/>
-      <c r="F22" s="104" t="s">
-        <v>261</v>
-      </c>
-      <c r="G22" s="105"/>
-      <c r="H22" s="105"/>
-      <c r="I22" s="105"/>
-      <c r="J22" s="105"/>
-      <c r="K22" s="105"/>
-      <c r="L22" s="105"/>
-      <c r="M22" s="106"/>
+      <c r="F22" s="110" t="s">
+        <v>260</v>
+      </c>
+      <c r="G22" s="111"/>
+      <c r="H22" s="111"/>
+      <c r="I22" s="111"/>
+      <c r="J22" s="111"/>
+      <c r="K22" s="111"/>
+      <c r="L22" s="111"/>
+      <c r="M22" s="112"/>
       <c r="N22" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="23" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E23" s="44"/>
-      <c r="F23" s="104" t="s">
-        <v>262</v>
-      </c>
-      <c r="G23" s="105"/>
-      <c r="H23" s="105"/>
-      <c r="I23" s="105"/>
-      <c r="J23" s="105"/>
-      <c r="K23" s="105"/>
-      <c r="L23" s="105"/>
-      <c r="M23" s="106"/>
+      <c r="F23" s="110" t="s">
+        <v>261</v>
+      </c>
+      <c r="G23" s="111"/>
+      <c r="H23" s="111"/>
+      <c r="I23" s="111"/>
+      <c r="J23" s="111"/>
+      <c r="K23" s="111"/>
+      <c r="L23" s="111"/>
+      <c r="M23" s="112"/>
       <c r="N23" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="24" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="20" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E24" s="44"/>
-      <c r="F24" s="104" t="s">
-        <v>263</v>
-      </c>
-      <c r="G24" s="105"/>
-      <c r="H24" s="105"/>
-      <c r="I24" s="105"/>
-      <c r="J24" s="105"/>
-      <c r="K24" s="105"/>
-      <c r="L24" s="105"/>
-      <c r="M24" s="106"/>
+      <c r="F24" s="110" t="s">
+        <v>262</v>
+      </c>
+      <c r="G24" s="111"/>
+      <c r="H24" s="111"/>
+      <c r="I24" s="111"/>
+      <c r="J24" s="111"/>
+      <c r="K24" s="111"/>
+      <c r="L24" s="111"/>
+      <c r="M24" s="112"/>
       <c r="N24" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="25" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="20" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E25" s="44"/>
-      <c r="F25" s="104" t="s">
-        <v>264</v>
-      </c>
-      <c r="G25" s="105"/>
-      <c r="H25" s="105"/>
-      <c r="I25" s="105"/>
-      <c r="J25" s="105"/>
-      <c r="K25" s="105"/>
-      <c r="L25" s="105"/>
-      <c r="M25" s="106"/>
+      <c r="F25" s="110" t="s">
+        <v>263</v>
+      </c>
+      <c r="G25" s="111"/>
+      <c r="H25" s="111"/>
+      <c r="I25" s="111"/>
+      <c r="J25" s="111"/>
+      <c r="K25" s="111"/>
+      <c r="L25" s="111"/>
+      <c r="M25" s="112"/>
       <c r="N25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="26" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="62" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D26" s="63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E26" s="64"/>
-      <c r="F26" s="101" t="s">
-        <v>265</v>
-      </c>
-      <c r="G26" s="102"/>
-      <c r="H26" s="102"/>
-      <c r="I26" s="102"/>
-      <c r="J26" s="102"/>
-      <c r="K26" s="102"/>
-      <c r="L26" s="102"/>
-      <c r="M26" s="103"/>
+      <c r="F26" s="107" t="s">
+        <v>264</v>
+      </c>
+      <c r="G26" s="108"/>
+      <c r="H26" s="108"/>
+      <c r="I26" s="108"/>
+      <c r="J26" s="108"/>
+      <c r="K26" s="108"/>
+      <c r="L26" s="108"/>
+      <c r="M26" s="109"/>
       <c r="N26" s="61" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="27" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="62" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D27" s="63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E27" s="64"/>
-      <c r="F27" s="98"/>
-      <c r="G27" s="99"/>
-      <c r="H27" s="99"/>
-      <c r="I27" s="99"/>
-      <c r="J27" s="100"/>
-      <c r="K27" s="101" t="s">
-        <v>266</v>
-      </c>
-      <c r="L27" s="102"/>
-      <c r="M27" s="103"/>
+      <c r="F27" s="104"/>
+      <c r="G27" s="105"/>
+      <c r="H27" s="105"/>
+      <c r="I27" s="105"/>
+      <c r="J27" s="106"/>
+      <c r="K27" s="107" t="s">
+        <v>265</v>
+      </c>
+      <c r="L27" s="108"/>
+      <c r="M27" s="109"/>
       <c r="N27" s="59" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="28" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C28" s="20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D28" s="67" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E28" s="44"/>
-      <c r="F28" s="104" t="s">
-        <v>267</v>
-      </c>
-      <c r="G28" s="105"/>
-      <c r="H28" s="105"/>
-      <c r="I28" s="105"/>
-      <c r="J28" s="105"/>
-      <c r="K28" s="107"/>
-      <c r="L28" s="107"/>
-      <c r="M28" s="108"/>
+      <c r="F28" s="110" t="s">
+        <v>266</v>
+      </c>
+      <c r="G28" s="111"/>
+      <c r="H28" s="111"/>
+      <c r="I28" s="111"/>
+      <c r="J28" s="111"/>
+      <c r="K28" s="113"/>
+      <c r="L28" s="113"/>
+      <c r="M28" s="114"/>
       <c r="N28" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="29" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E29" s="44"/>
-      <c r="F29" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="G29" s="105"/>
-      <c r="H29" s="105"/>
-      <c r="I29" s="105"/>
-      <c r="J29" s="105"/>
-      <c r="K29" s="105"/>
-      <c r="L29" s="105"/>
-      <c r="M29" s="106"/>
+      <c r="F29" s="110" t="s">
+        <v>267</v>
+      </c>
+      <c r="G29" s="111"/>
+      <c r="H29" s="111"/>
+      <c r="I29" s="111"/>
+      <c r="J29" s="111"/>
+      <c r="K29" s="111"/>
+      <c r="L29" s="111"/>
+      <c r="M29" s="112"/>
       <c r="N29" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="30" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E30" s="44"/>
-      <c r="F30" s="104" t="s">
-        <v>269</v>
-      </c>
-      <c r="G30" s="105"/>
-      <c r="H30" s="105"/>
-      <c r="I30" s="105"/>
-      <c r="J30" s="105"/>
-      <c r="K30" s="105"/>
-      <c r="L30" s="105"/>
-      <c r="M30" s="106"/>
+      <c r="F30" s="110" t="s">
+        <v>268</v>
+      </c>
+      <c r="G30" s="111"/>
+      <c r="H30" s="111"/>
+      <c r="I30" s="111"/>
+      <c r="J30" s="111"/>
+      <c r="K30" s="111"/>
+      <c r="L30" s="111"/>
+      <c r="M30" s="112"/>
       <c r="N30" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="31" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E31" s="44"/>
-      <c r="F31" s="104" t="s">
-        <v>270</v>
-      </c>
-      <c r="G31" s="105"/>
-      <c r="H31" s="105"/>
-      <c r="I31" s="105"/>
-      <c r="J31" s="105"/>
-      <c r="K31" s="105"/>
-      <c r="L31" s="105"/>
-      <c r="M31" s="106"/>
+      <c r="F31" s="110" t="s">
+        <v>269</v>
+      </c>
+      <c r="G31" s="111"/>
+      <c r="H31" s="111"/>
+      <c r="I31" s="111"/>
+      <c r="J31" s="111"/>
+      <c r="K31" s="111"/>
+      <c r="L31" s="111"/>
+      <c r="M31" s="112"/>
       <c r="N31" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="32" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="62" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D32" s="63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E32" s="64"/>
-      <c r="F32" s="98"/>
-      <c r="G32" s="99"/>
-      <c r="H32" s="99"/>
-      <c r="I32" s="99"/>
-      <c r="J32" s="99"/>
-      <c r="K32" s="99"/>
-      <c r="L32" s="99"/>
-      <c r="M32" s="100"/>
+      <c r="F32" s="104"/>
+      <c r="G32" s="105"/>
+      <c r="H32" s="105"/>
+      <c r="I32" s="105"/>
+      <c r="J32" s="105"/>
+      <c r="K32" s="105"/>
+      <c r="L32" s="105"/>
+      <c r="M32" s="106"/>
     </row>
     <row r="33" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="62" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D33" s="63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E33" s="64"/>
-      <c r="F33" s="98"/>
-      <c r="G33" s="99"/>
-      <c r="H33" s="99"/>
-      <c r="I33" s="99"/>
-      <c r="J33" s="99"/>
-      <c r="K33" s="99"/>
-      <c r="L33" s="99"/>
-      <c r="M33" s="100"/>
+      <c r="F33" s="104"/>
+      <c r="G33" s="105"/>
+      <c r="H33" s="105"/>
+      <c r="I33" s="105"/>
+      <c r="J33" s="105"/>
+      <c r="K33" s="105"/>
+      <c r="L33" s="105"/>
+      <c r="M33" s="106"/>
     </row>
     <row r="34" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="62" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D34" s="63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E34" s="64"/>
-      <c r="F34" s="101" t="s">
-        <v>271</v>
-      </c>
-      <c r="G34" s="102"/>
-      <c r="H34" s="102"/>
-      <c r="I34" s="102"/>
-      <c r="J34" s="102"/>
-      <c r="K34" s="102"/>
-      <c r="L34" s="102"/>
-      <c r="M34" s="103"/>
+      <c r="F34" s="107" t="s">
+        <v>270</v>
+      </c>
+      <c r="G34" s="108"/>
+      <c r="H34" s="108"/>
+      <c r="I34" s="108"/>
+      <c r="J34" s="108"/>
+      <c r="K34" s="108"/>
+      <c r="L34" s="108"/>
+      <c r="M34" s="109"/>
       <c r="N34" s="59" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="35" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="62" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D35" s="63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E35" s="65"/>
-      <c r="F35" s="101" t="s">
-        <v>272</v>
-      </c>
-      <c r="G35" s="103"/>
-      <c r="H35" s="98"/>
-      <c r="I35" s="99"/>
-      <c r="J35" s="99"/>
-      <c r="K35" s="99"/>
-      <c r="L35" s="99"/>
-      <c r="M35" s="100"/>
+      <c r="F35" s="107" t="s">
+        <v>271</v>
+      </c>
+      <c r="G35" s="109"/>
+      <c r="H35" s="104"/>
+      <c r="I35" s="105"/>
+      <c r="J35" s="105"/>
+      <c r="K35" s="105"/>
+      <c r="L35" s="105"/>
+      <c r="M35" s="106"/>
       <c r="N35" s="59" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="36" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C36" s="62" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D36" s="63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E36" s="65"/>
-      <c r="F36" s="98"/>
-      <c r="G36" s="99"/>
-      <c r="H36" s="99"/>
-      <c r="I36" s="99"/>
-      <c r="J36" s="100"/>
-      <c r="K36" s="101" t="s">
-        <v>273</v>
-      </c>
-      <c r="L36" s="102"/>
-      <c r="M36" s="103"/>
+      <c r="F36" s="104"/>
+      <c r="G36" s="105"/>
+      <c r="H36" s="105"/>
+      <c r="I36" s="105"/>
+      <c r="J36" s="106"/>
+      <c r="K36" s="107" t="s">
+        <v>272</v>
+      </c>
+      <c r="L36" s="108"/>
+      <c r="M36" s="109"/>
       <c r="N36" s="59" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="37" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="62" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D37" s="63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E37" s="64"/>
-      <c r="F37" s="98"/>
-      <c r="G37" s="99"/>
-      <c r="H37" s="99"/>
-      <c r="I37" s="100"/>
-      <c r="J37" s="101" t="s">
-        <v>274</v>
-      </c>
-      <c r="K37" s="102"/>
-      <c r="L37" s="102"/>
-      <c r="M37" s="103"/>
+      <c r="F37" s="104"/>
+      <c r="G37" s="105"/>
+      <c r="H37" s="105"/>
+      <c r="I37" s="106"/>
+      <c r="J37" s="107" t="s">
+        <v>273</v>
+      </c>
+      <c r="K37" s="108"/>
+      <c r="L37" s="108"/>
+      <c r="M37" s="109"/>
       <c r="N37" s="59" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="38" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="62" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D38" s="63" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E38" s="64"/>
-      <c r="F38" s="98"/>
-      <c r="G38" s="99"/>
-      <c r="H38" s="99"/>
-      <c r="I38" s="100"/>
-      <c r="J38" s="101" t="s">
-        <v>275</v>
-      </c>
-      <c r="K38" s="102"/>
-      <c r="L38" s="102"/>
-      <c r="M38" s="103"/>
+      <c r="F38" s="104"/>
+      <c r="G38" s="105"/>
+      <c r="H38" s="105"/>
+      <c r="I38" s="106"/>
+      <c r="J38" s="107" t="s">
+        <v>274</v>
+      </c>
+      <c r="K38" s="108"/>
+      <c r="L38" s="108"/>
+      <c r="M38" s="109"/>
       <c r="N38" s="59" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="39" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="62" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D39" s="63" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E39" s="64"/>
-      <c r="F39" s="101" t="s">
-        <v>276</v>
-      </c>
-      <c r="G39" s="102"/>
-      <c r="H39" s="102"/>
-      <c r="I39" s="102"/>
-      <c r="J39" s="102"/>
-      <c r="K39" s="102"/>
-      <c r="L39" s="102"/>
-      <c r="M39" s="103"/>
+      <c r="F39" s="107" t="s">
+        <v>275</v>
+      </c>
+      <c r="G39" s="108"/>
+      <c r="H39" s="108"/>
+      <c r="I39" s="108"/>
+      <c r="J39" s="108"/>
+      <c r="K39" s="108"/>
+      <c r="L39" s="108"/>
+      <c r="M39" s="109"/>
       <c r="N39" s="59" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="40" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="62" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D40" s="63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E40" s="64"/>
-      <c r="F40" s="98"/>
-      <c r="G40" s="99"/>
-      <c r="H40" s="99"/>
-      <c r="I40" s="99"/>
-      <c r="J40" s="99"/>
-      <c r="K40" s="99"/>
-      <c r="L40" s="99"/>
-      <c r="M40" s="100"/>
+      <c r="F40" s="104"/>
+      <c r="G40" s="105"/>
+      <c r="H40" s="105"/>
+      <c r="I40" s="105"/>
+      <c r="J40" s="105"/>
+      <c r="K40" s="105"/>
+      <c r="L40" s="105"/>
+      <c r="M40" s="106"/>
     </row>
     <row r="41" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="62" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D41" s="63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E41" s="64"/>
-      <c r="F41" s="98"/>
-      <c r="G41" s="99"/>
-      <c r="H41" s="99"/>
-      <c r="I41" s="99"/>
-      <c r="J41" s="99"/>
-      <c r="K41" s="99"/>
-      <c r="L41" s="99"/>
-      <c r="M41" s="100"/>
+      <c r="F41" s="104"/>
+      <c r="G41" s="105"/>
+      <c r="H41" s="105"/>
+      <c r="I41" s="105"/>
+      <c r="J41" s="105"/>
+      <c r="K41" s="105"/>
+      <c r="L41" s="105"/>
+      <c r="M41" s="106"/>
     </row>
     <row r="42" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="62" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D42" s="63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E42" s="64"/>
-      <c r="F42" s="98"/>
-      <c r="G42" s="99"/>
-      <c r="H42" s="99"/>
-      <c r="I42" s="99"/>
-      <c r="J42" s="99"/>
-      <c r="K42" s="99"/>
-      <c r="L42" s="99"/>
-      <c r="M42" s="100"/>
+      <c r="F42" s="104"/>
+      <c r="G42" s="105"/>
+      <c r="H42" s="105"/>
+      <c r="I42" s="105"/>
+      <c r="J42" s="105"/>
+      <c r="K42" s="105"/>
+      <c r="L42" s="105"/>
+      <c r="M42" s="106"/>
     </row>
     <row r="43" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C43" s="62" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D43" s="63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E43" s="64"/>
-      <c r="F43" s="98"/>
-      <c r="G43" s="99"/>
-      <c r="H43" s="99"/>
-      <c r="I43" s="99"/>
-      <c r="J43" s="99"/>
-      <c r="K43" s="99"/>
-      <c r="L43" s="99"/>
-      <c r="M43" s="100"/>
+      <c r="F43" s="104"/>
+      <c r="G43" s="105"/>
+      <c r="H43" s="105"/>
+      <c r="I43" s="105"/>
+      <c r="J43" s="105"/>
+      <c r="K43" s="105"/>
+      <c r="L43" s="105"/>
+      <c r="M43" s="106"/>
     </row>
     <row r="44" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="62" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D44" s="63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E44" s="64"/>
-      <c r="F44" s="98"/>
-      <c r="G44" s="99"/>
-      <c r="H44" s="99"/>
-      <c r="I44" s="99"/>
-      <c r="J44" s="99"/>
-      <c r="K44" s="99"/>
-      <c r="L44" s="99"/>
-      <c r="M44" s="100"/>
+      <c r="F44" s="104"/>
+      <c r="G44" s="105"/>
+      <c r="H44" s="105"/>
+      <c r="I44" s="105"/>
+      <c r="J44" s="105"/>
+      <c r="K44" s="105"/>
+      <c r="L44" s="105"/>
+      <c r="M44" s="106"/>
     </row>
     <row r="45" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C45" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E45" s="45"/>
       <c r="F45" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="G45" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="G45" s="47" t="s">
-        <v>116</v>
-      </c>
       <c r="H45" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I45" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="J45" s="76" t="s">
         <v>118</v>
       </c>
-      <c r="J45" s="73" t="s">
-        <v>119</v>
-      </c>
-      <c r="K45" s="74"/>
-      <c r="L45" s="74"/>
-      <c r="M45" s="75"/>
+      <c r="K45" s="77"/>
+      <c r="L45" s="77"/>
+      <c r="M45" s="78"/>
     </row>
     <row r="46" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="20" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E46" s="45"/>
-      <c r="F46" s="73" t="s">
-        <v>286</v>
-      </c>
-      <c r="G46" s="75"/>
-      <c r="H46" s="73" t="s">
-        <v>121</v>
-      </c>
-      <c r="I46" s="74"/>
-      <c r="J46" s="74"/>
-      <c r="K46" s="74"/>
-      <c r="L46" s="74"/>
-      <c r="M46" s="75"/>
+      <c r="F46" s="76" t="s">
+        <v>285</v>
+      </c>
+      <c r="G46" s="78"/>
+      <c r="H46" s="76" t="s">
+        <v>120</v>
+      </c>
+      <c r="I46" s="77"/>
+      <c r="J46" s="77"/>
+      <c r="K46" s="77"/>
+      <c r="L46" s="77"/>
+      <c r="M46" s="78"/>
     </row>
     <row r="47" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E47" s="45"/>
-      <c r="F47" s="109" t="s">
+      <c r="F47" s="98" t="s">
+        <v>124</v>
+      </c>
+      <c r="G47" s="99"/>
+      <c r="H47" s="99"/>
+      <c r="I47" s="100"/>
+      <c r="J47" s="76" t="s">
         <v>125</v>
       </c>
-      <c r="G47" s="110"/>
-      <c r="H47" s="110"/>
-      <c r="I47" s="111"/>
-      <c r="J47" s="73" t="s">
-        <v>126</v>
-      </c>
-      <c r="K47" s="74"/>
-      <c r="L47" s="74"/>
-      <c r="M47" s="75"/>
+      <c r="K47" s="77"/>
+      <c r="L47" s="77"/>
+      <c r="M47" s="78"/>
     </row>
     <row r="48" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E48" s="6"/>
-      <c r="F48" s="73" t="s">
+      <c r="F48" s="76" t="s">
+        <v>126</v>
+      </c>
+      <c r="G48" s="77"/>
+      <c r="H48" s="77"/>
+      <c r="I48" s="78"/>
+      <c r="J48" s="101" t="s">
         <v>127</v>
       </c>
-      <c r="G48" s="74"/>
-      <c r="H48" s="74"/>
-      <c r="I48" s="75"/>
-      <c r="J48" s="112" t="s">
-        <v>128</v>
-      </c>
-      <c r="K48" s="113"/>
-      <c r="L48" s="113"/>
-      <c r="M48" s="114"/>
+      <c r="K48" s="102"/>
+      <c r="L48" s="102"/>
+      <c r="M48" s="103"/>
     </row>
     <row r="49" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E49" s="6"/>
-      <c r="F49" s="90" t="s">
-        <v>155</v>
-      </c>
-      <c r="G49" s="91"/>
-      <c r="H49" s="91"/>
-      <c r="I49" s="91"/>
-      <c r="J49" s="91"/>
-      <c r="K49" s="91"/>
-      <c r="L49" s="91"/>
-      <c r="M49" s="92"/>
+      <c r="F49" s="84" t="s">
+        <v>154</v>
+      </c>
+      <c r="G49" s="85"/>
+      <c r="H49" s="85"/>
+      <c r="I49" s="85"/>
+      <c r="J49" s="85"/>
+      <c r="K49" s="85"/>
+      <c r="L49" s="85"/>
+      <c r="M49" s="86"/>
     </row>
     <row r="50" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C50" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E50" s="6"/>
-      <c r="F50" s="82"/>
-      <c r="G50" s="84"/>
+      <c r="F50" s="73"/>
+      <c r="G50" s="75"/>
       <c r="H50" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="I50" s="90" t="s">
+        <v>286</v>
+      </c>
+      <c r="I50" s="84" t="s">
+        <v>153</v>
+      </c>
+      <c r="J50" s="85"/>
+      <c r="K50" s="86"/>
+      <c r="L50" s="84" t="s">
         <v>154</v>
       </c>
-      <c r="J50" s="91"/>
-      <c r="K50" s="92"/>
-      <c r="L50" s="90" t="s">
-        <v>155</v>
-      </c>
-      <c r="M50" s="92"/>
+      <c r="M50" s="86"/>
     </row>
     <row r="51" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C51" s="20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E51" s="6"/>
       <c r="F51" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="G51" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="G51" s="12" t="s">
+      <c r="H51" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="I51" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="K51" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="H51" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="I51" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="J51" s="12" t="s">
+      <c r="L51" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="M51" s="12" t="s">
         <v>113</v>
-      </c>
-      <c r="K51" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="L51" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="M51" s="12" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="52" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="20" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E52" s="6"/>
-      <c r="F52" s="82"/>
-      <c r="G52" s="83"/>
-      <c r="H52" s="83"/>
-      <c r="I52" s="84"/>
-      <c r="J52" s="90" t="s">
-        <v>122</v>
-      </c>
-      <c r="K52" s="91"/>
-      <c r="L52" s="92"/>
+      <c r="F52" s="73"/>
+      <c r="G52" s="74"/>
+      <c r="H52" s="74"/>
+      <c r="I52" s="75"/>
+      <c r="J52" s="84" t="s">
+        <v>121</v>
+      </c>
+      <c r="K52" s="85"/>
+      <c r="L52" s="86"/>
       <c r="M52" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="20" t="s">
+        <v>295</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E53" s="22" t="s">
         <v>296</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E53" s="22" t="s">
-        <v>297</v>
-      </c>
-      <c r="F53" s="98"/>
-      <c r="G53" s="99"/>
-      <c r="H53" s="99"/>
-      <c r="I53" s="99"/>
-      <c r="J53" s="99"/>
-      <c r="K53" s="100"/>
-      <c r="L53" s="89" t="s">
-        <v>295</v>
-      </c>
-      <c r="M53" s="87"/>
+      <c r="F53" s="104"/>
+      <c r="G53" s="105"/>
+      <c r="H53" s="105"/>
+      <c r="I53" s="105"/>
+      <c r="J53" s="105"/>
+      <c r="K53" s="106"/>
+      <c r="L53" s="83" t="s">
+        <v>294</v>
+      </c>
+      <c r="M53" s="82"/>
     </row>
     <row r="54" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="62" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D54" s="63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E54" s="66"/>
-      <c r="F54" s="98"/>
-      <c r="G54" s="99"/>
-      <c r="H54" s="99"/>
-      <c r="I54" s="99"/>
-      <c r="J54" s="99"/>
-      <c r="K54" s="99"/>
-      <c r="L54" s="99"/>
-      <c r="M54" s="100"/>
+      <c r="F54" s="104"/>
+      <c r="G54" s="105"/>
+      <c r="H54" s="105"/>
+      <c r="I54" s="105"/>
+      <c r="J54" s="105"/>
+      <c r="K54" s="105"/>
+      <c r="L54" s="105"/>
+      <c r="M54" s="106"/>
     </row>
     <row r="55" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="56" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="55" t="s">
+        <v>360</v>
+      </c>
+      <c r="D56" t="s">
+        <v>39</v>
+      </c>
+      <c r="F56" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="D56" t="s">
-        <v>40</v>
-      </c>
-      <c r="F56" s="12" t="s">
+      <c r="G56" s="12" t="s">
         <v>362</v>
       </c>
-      <c r="G56" s="12" t="s">
+      <c r="H56" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="H56" s="12" t="s">
+      <c r="I56" s="12" t="s">
         <v>364</v>
       </c>
-      <c r="I56" s="12" t="s">
+      <c r="J56" s="56" t="s">
+        <v>366</v>
+      </c>
+      <c r="K56" s="73"/>
+      <c r="L56" s="75"/>
+      <c r="M56" s="56" t="s">
         <v>365</v>
-      </c>
-      <c r="J56" s="56" t="s">
-        <v>367</v>
-      </c>
-      <c r="K56" s="82"/>
-      <c r="L56" s="84"/>
-      <c r="M56" s="56" t="s">
-        <v>366</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="F47:I47"/>
-    <mergeCell ref="J47:M47"/>
-    <mergeCell ref="F48:I48"/>
-    <mergeCell ref="J48:M48"/>
-    <mergeCell ref="F49:M49"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="I50:K50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="F42:M42"/>
-    <mergeCell ref="F43:M43"/>
-    <mergeCell ref="F44:M44"/>
-    <mergeCell ref="J45:M45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="F26:M26"/>
-    <mergeCell ref="F24:M24"/>
-    <mergeCell ref="F25:M25"/>
-    <mergeCell ref="F22:M22"/>
-    <mergeCell ref="K27:M27"/>
-    <mergeCell ref="F27:J27"/>
+    <mergeCell ref="K56:L56"/>
+    <mergeCell ref="F13:M13"/>
+    <mergeCell ref="F15:M15"/>
+    <mergeCell ref="F54:M54"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="F53:K53"/>
+    <mergeCell ref="J52:L52"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="F41:M41"/>
+    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="F31:M31"/>
+    <mergeCell ref="F33:M33"/>
+    <mergeCell ref="F14:M14"/>
+    <mergeCell ref="F16:M16"/>
+    <mergeCell ref="F18:M18"/>
     <mergeCell ref="F19:M19"/>
     <mergeCell ref="F38:I38"/>
     <mergeCell ref="F28:M28"/>
@@ -7795,22 +7942,27 @@
     <mergeCell ref="K20:L20"/>
     <mergeCell ref="F36:J36"/>
     <mergeCell ref="F23:M23"/>
-    <mergeCell ref="K56:L56"/>
-    <mergeCell ref="F13:M13"/>
-    <mergeCell ref="F15:M15"/>
-    <mergeCell ref="F54:M54"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="F53:K53"/>
-    <mergeCell ref="J52:L52"/>
-    <mergeCell ref="F40:M40"/>
-    <mergeCell ref="F41:M41"/>
-    <mergeCell ref="F39:M39"/>
-    <mergeCell ref="F29:M29"/>
-    <mergeCell ref="F31:M31"/>
-    <mergeCell ref="F33:M33"/>
-    <mergeCell ref="F14:M14"/>
-    <mergeCell ref="F16:M16"/>
-    <mergeCell ref="F18:M18"/>
+    <mergeCell ref="F26:M26"/>
+    <mergeCell ref="F24:M24"/>
+    <mergeCell ref="F25:M25"/>
+    <mergeCell ref="F22:M22"/>
+    <mergeCell ref="K27:M27"/>
+    <mergeCell ref="F27:J27"/>
+    <mergeCell ref="F42:M42"/>
+    <mergeCell ref="F43:M43"/>
+    <mergeCell ref="F44:M44"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="F47:I47"/>
+    <mergeCell ref="J47:M47"/>
+    <mergeCell ref="F48:I48"/>
+    <mergeCell ref="J48:M48"/>
+    <mergeCell ref="F49:M49"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="F50:G50"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7820,9 +7972,15 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D191A0C-02CD-4BD6-9BF3-D97117CF844C}">
-  <dimension ref="A1"/>
+  <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
